--- a/Assets/Data/Amstrad CPC 664/MC0005A/Data CPC 664 MC0005A.xlsx
+++ b/Assets/Data/Amstrad CPC 664/MC0005A/Data CPC 664 MC0005A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dennis\AppData\Local\Classic-Repair-Toolbox\Data\Amstrad CPC 664\MC0005A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF674B62-E010-443A-9B44-BEF4413D00A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DD0179F-2CC6-40E3-8125-14CF9257F2BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1153" uniqueCount="476">
   <si>
     <t>Name</t>
   </si>
@@ -1009,6 +1009,546 @@
     <t>T.LVL</t>
   </si>
   <si>
+    <t>UUID v4</t>
+  </si>
+  <si>
+    <t>0629d066-ef9e-4e2d-a34f-d737794dde79</t>
+  </si>
+  <si>
+    <t>5dfd86e1-140b-488d-9370-d56d5df12541</t>
+  </si>
+  <si>
+    <t>b24ffa4d-99a3-44b9-84c5-a79c5fd6f738</t>
+  </si>
+  <si>
+    <t>56953cb8-e709-4d95-8b24-11b077320132</t>
+  </si>
+  <si>
+    <t>d58cf776-b12a-4330-97ed-02a2159299c7</t>
+  </si>
+  <si>
+    <t>9e943af1-6aaf-4eac-be59-3aa34a5f45e7</t>
+  </si>
+  <si>
+    <t>6f148154-9e48-4c76-981a-d5ecb8e84f13</t>
+  </si>
+  <si>
+    <t>8de4002f-a425-4c21-9eb7-7bf727e3f49d</t>
+  </si>
+  <si>
+    <t>9f60623e-3e0d-4b85-8e4a-72ff3fe20583</t>
+  </si>
+  <si>
+    <t>a9cf2299-d736-41e6-b9f5-8ba18a5bb91d</t>
+  </si>
+  <si>
+    <t>6180984e-f95b-4bfb-8482-429b32eeea08</t>
+  </si>
+  <si>
+    <t>a69ff9a4-38cf-4a0b-a236-1175646a78f2</t>
+  </si>
+  <si>
+    <t>50317c5f-b0b6-4dab-afa3-b033a65743de</t>
+  </si>
+  <si>
+    <t>7eb1a540-de5b-4cba-86da-f6a967af3810</t>
+  </si>
+  <si>
+    <t>7f67826c-5d82-42c7-887b-81345b9aac94</t>
+  </si>
+  <si>
+    <t>fd652a05-a2ff-4504-9638-24abbc8dd504</t>
+  </si>
+  <si>
+    <t>ce688230-402c-4e6a-bdc4-cf4dd3bb011d</t>
+  </si>
+  <si>
+    <t>8823e180-923d-4940-ad9b-0cc772136182</t>
+  </si>
+  <si>
+    <t>a1c8c7c4-ac95-4f56-8222-eaeb35f9fbc0</t>
+  </si>
+  <si>
+    <t>ad5182cb-1387-4254-a049-3b5b7fa1ddbc</t>
+  </si>
+  <si>
+    <t>51e3c0b4-af35-407b-a9cc-087358ee72df</t>
+  </si>
+  <si>
+    <t>350b4c5c-0289-470b-8b24-5965e05efc9a</t>
+  </si>
+  <si>
+    <t>fba64855-5650-4987-91a2-3fff43e7b7a3</t>
+  </si>
+  <si>
+    <t>44407649-1ab0-46c8-9723-ef27ec478671</t>
+  </si>
+  <si>
+    <t>26ee9c55-9072-41ff-9efd-2d4b8ac35187</t>
+  </si>
+  <si>
+    <t>fb5c633c-371f-44e7-b775-926400b9349e</t>
+  </si>
+  <si>
+    <t>2e224223-c1f2-4ca2-af12-e7119b501660</t>
+  </si>
+  <si>
+    <t>3a11e188-f4e7-4805-ba6e-9f63ec25be88</t>
+  </si>
+  <si>
+    <t>7f9a6b0f-55b0-45df-b7e3-9ccd213aa67c</t>
+  </si>
+  <si>
+    <t>e8bb352f-5584-461a-9ae4-fd1685f8e263</t>
+  </si>
+  <si>
+    <t>98b3986e-08c4-4edd-82fb-36e3c207bc24</t>
+  </si>
+  <si>
+    <t>6d524432-29bb-4410-9af6-b79bce788872</t>
+  </si>
+  <si>
+    <t>3c322e11-4e41-4465-bd56-24e9e6bb33b5</t>
+  </si>
+  <si>
+    <t>e775f8f5-a333-4ab1-a1d6-528322c7487c</t>
+  </si>
+  <si>
+    <t>cf40714e-9f29-43e5-a58a-0020efb4db78</t>
+  </si>
+  <si>
+    <t>545875f1-7a1c-4484-8a40-b99b9ecbd76d</t>
+  </si>
+  <si>
+    <t>455ece71-1b7b-44cd-a357-f5a41cda1330</t>
+  </si>
+  <si>
+    <t>9aa3a6a2-dc70-4937-9949-5da64b1ee155</t>
+  </si>
+  <si>
+    <t>461ec208-5603-48ba-b6f3-9c8a1311b5b3</t>
+  </si>
+  <si>
+    <t>0d01fa4d-ed84-44f1-953a-570ac7625a61</t>
+  </si>
+  <si>
+    <t>89263cda-27e1-43f1-b8ae-9eb88ece98e4</t>
+  </si>
+  <si>
+    <t>8e60410d-1afc-4244-bfe8-292e3547cb02</t>
+  </si>
+  <si>
+    <t>3ad92068-e510-4d86-bdd8-efcac822c348</t>
+  </si>
+  <si>
+    <t>b4a6a750-0dcb-4f29-8dd7-a87ce10ffe60</t>
+  </si>
+  <si>
+    <t>6056f3c0-2c68-404a-a637-63c940fadd59</t>
+  </si>
+  <si>
+    <t>df51a707-c158-40c5-96c2-5d04e4832923</t>
+  </si>
+  <si>
+    <t>d8bd58c7-7fd2-4518-9a4f-cc7c0f14edbf</t>
+  </si>
+  <si>
+    <t>d1628f2e-da71-4f18-bdab-a16cb5985a9d</t>
+  </si>
+  <si>
+    <t>504e0b44-2231-4792-9b72-6b6d3718ca39</t>
+  </si>
+  <si>
+    <t>46805d00-9834-4149-acd5-1d416b86e828</t>
+  </si>
+  <si>
+    <t>350ec075-858d-4145-a4a2-7f606afdcf70</t>
+  </si>
+  <si>
+    <t>3c2f8903-0970-41ec-9376-b3e43b629f91</t>
+  </si>
+  <si>
+    <t>6104f50b-5385-4585-8fcf-e8c0e6315ef1</t>
+  </si>
+  <si>
+    <t>3773315f-4455-4362-a69e-9aafa7cafb01</t>
+  </si>
+  <si>
+    <t>5d655589-6ebb-4f90-8a19-0033faeb10ec</t>
+  </si>
+  <si>
+    <t>be19b43c-8a32-4ea1-9780-4ee2e5a6a160</t>
+  </si>
+  <si>
+    <t>8dfe26aa-c0bb-4743-84d0-674a45dc4720</t>
+  </si>
+  <si>
+    <t>1ef091e1-f94f-4b27-9cde-d680b97a7df5</t>
+  </si>
+  <si>
+    <t>cb267ebc-fa82-4a1a-b089-6427cca6dc4d</t>
+  </si>
+  <si>
+    <t>9c2dd6e2-2662-4023-bf18-f5672ce5531d</t>
+  </si>
+  <si>
+    <t>25862f0a-68ae-45af-9e56-c884c5a82dab</t>
+  </si>
+  <si>
+    <t>05fff277-cce6-45d8-9a0d-319f0e3812db</t>
+  </si>
+  <si>
+    <t>f8a328e5-5592-4d51-97a8-347556d5ed0b</t>
+  </si>
+  <si>
+    <t>b30a3c27-d863-4cff-874f-7a08e6c7a666</t>
+  </si>
+  <si>
+    <t>e9090218-b623-4c5a-af3f-09d9f4b1f4cc</t>
+  </si>
+  <si>
+    <t>613b804a-711a-4368-8af9-3db7783d43ac</t>
+  </si>
+  <si>
+    <t>df5ab529-34c9-44ac-bed6-e3e3c88beea1</t>
+  </si>
+  <si>
+    <t>43258656-cb90-4872-bf2f-a4763bd0e65f</t>
+  </si>
+  <si>
+    <t>2d3b2615-ce9b-473f-a83c-ba4359856c44</t>
+  </si>
+  <si>
+    <t>a6eb53bb-e418-4652-b65d-92e99dd84da0</t>
+  </si>
+  <si>
+    <t>fe0cab98-828f-4bad-8b7b-07fcf9a552fb</t>
+  </si>
+  <si>
+    <t>8edcd0c1-632a-4036-a8dc-8766e4859ec2</t>
+  </si>
+  <si>
+    <t>d47f3a5d-d547-4fb2-a26c-98801d813284</t>
+  </si>
+  <si>
+    <t>81ccc3e6-df26-46b4-8347-d552fcef278b</t>
+  </si>
+  <si>
+    <t>6a736993-be1a-4cfc-a5ef-4ccde3076a96</t>
+  </si>
+  <si>
+    <t>31aeae8f-7bf5-4609-bf82-363ae550953d</t>
+  </si>
+  <si>
+    <t>25d8ff86-2668-4dd7-af56-d87999c33be5</t>
+  </si>
+  <si>
+    <t>dbf903b6-b5a2-441b-92ab-4166b3687b55</t>
+  </si>
+  <si>
+    <t>08957130-492c-411f-b3b3-474da3d8cfb5</t>
+  </si>
+  <si>
+    <t>aee098db-3395-4106-962c-faa8c7c19144</t>
+  </si>
+  <si>
+    <t>7d9580a0-8639-49a1-b4e5-f6129b24376f</t>
+  </si>
+  <si>
+    <t>5b2dd609-648f-45cb-be31-1bfaba7b94ee</t>
+  </si>
+  <si>
+    <t>ca4d8d64-26fe-4d85-a0bc-fd00deafa58d</t>
+  </si>
+  <si>
+    <t>006b6ed8-965a-4170-a8f9-806c67dc03e1</t>
+  </si>
+  <si>
+    <t>5acbbce1-4735-4f69-8351-4fc0d291c5c0</t>
+  </si>
+  <si>
+    <t>f3108d2b-9521-4c67-bb4d-a658d92ccbdd</t>
+  </si>
+  <si>
+    <t>c2952aa9-2ac6-4c42-8341-e584af99dac3</t>
+  </si>
+  <si>
+    <t>b9716a47-17c5-40c9-8000-177e071a9131</t>
+  </si>
+  <si>
+    <t>e9439812-2a22-4a6a-906b-4842606ef094</t>
+  </si>
+  <si>
+    <t>a1a7b3ef-18c5-4585-951c-26a254cfe0a2</t>
+  </si>
+  <si>
+    <t>b3d1efe1-90ba-451c-aaf2-6ffc25d65da2</t>
+  </si>
+  <si>
+    <t>e9069eec-4466-4fa2-bafb-cfbf4ff2ec33</t>
+  </si>
+  <si>
+    <t>81cbc670-51f8-4229-9805-295aa03e3b15</t>
+  </si>
+  <si>
+    <t>e9dc019b-2f37-44da-986c-49e6d0f82114</t>
+  </si>
+  <si>
+    <t>3bc7a32d-6b64-4596-b347-13e65950d070</t>
+  </si>
+  <si>
+    <t>331eab9c-edc3-454c-af89-fc1ea5dc9c1f</t>
+  </si>
+  <si>
+    <t>24d51cc4-e41e-4e94-8387-f239a32a961f</t>
+  </si>
+  <si>
+    <t>9dc2e3bd-421d-4da1-928c-55f0ec062d3f</t>
+  </si>
+  <si>
+    <t>a7d0d086-a2ac-46bb-89ad-02c4fb17f0f6</t>
+  </si>
+  <si>
+    <t>20ccb5e0-801a-4a7e-90fb-0119931a059a</t>
+  </si>
+  <si>
+    <t>ac6263f6-de58-4c9b-9008-7cf2a6e11321</t>
+  </si>
+  <si>
+    <t>c436cc22-8187-41a0-86d6-d79088544312</t>
+  </si>
+  <si>
+    <t>5c30079c-6341-4f85-8d9a-e26c0a33c666</t>
+  </si>
+  <si>
+    <t>93826731-fb1e-4526-ac89-ff550374549a</t>
+  </si>
+  <si>
+    <t>924531e6-4a0e-4dd2-8fac-06bad3943fd8</t>
+  </si>
+  <si>
+    <t>ed0026fd-c667-4664-b6e7-023fdb9b4853</t>
+  </si>
+  <si>
+    <t>97602b03-5954-4ac5-a70d-e4a3841c3f02</t>
+  </si>
+  <si>
+    <t>aebda2ea-3f65-4336-be70-f5028b22c72c</t>
+  </si>
+  <si>
+    <t>21a23cf8-b1bc-46d0-94c3-020bbbf66158</t>
+  </si>
+  <si>
+    <t>9b14660a-11fa-4fb9-8ad8-31c067f531ba</t>
+  </si>
+  <si>
+    <t>4c741131-a83e-4143-8ff4-3006716412f4</t>
+  </si>
+  <si>
+    <t>9a44787b-4eda-4af3-883a-e496370724b3</t>
+  </si>
+  <si>
+    <t>57c65383-6726-41d5-b22a-48731702515e</t>
+  </si>
+  <si>
+    <t>45fc934e-1511-4bb9-836e-3f9d9f43256a</t>
+  </si>
+  <si>
+    <t>31527a4f-4247-4314-b113-97d9184a4a6a</t>
+  </si>
+  <si>
+    <t>e44ab449-7f2c-44e1-822c-c303405c28f6</t>
+  </si>
+  <si>
+    <t>3ddf6875-6b2e-408c-8857-64481cf4dd3e</t>
+  </si>
+  <si>
+    <t>8824ac3a-38ba-4742-acc8-13c4b62766df</t>
+  </si>
+  <si>
+    <t>a3b54cae-2e76-4126-a49f-e457f7424f29</t>
+  </si>
+  <si>
+    <t>b447af71-fa78-4c6b-a394-8a81d784ffed</t>
+  </si>
+  <si>
+    <t>68f96e6a-4947-4a28-a1e0-c8424ef2e878</t>
+  </si>
+  <si>
+    <t>d51ea6eb-3d7c-453b-be80-35fbd12ef22f</t>
+  </si>
+  <si>
+    <t>1b549913-9efb-4d2d-b83b-65c0a1661b8f</t>
+  </si>
+  <si>
+    <t>ffd7fb29-4a62-43ce-a4c0-7db0a180d56a</t>
+  </si>
+  <si>
+    <t>29546490-137f-458f-ba4d-e03dd0d94d0e</t>
+  </si>
+  <si>
+    <t>77979a9d-000e-46e4-ad3f-b93911c9f6f8</t>
+  </si>
+  <si>
+    <t>784fa026-f389-49eb-aa18-910140d06fab</t>
+  </si>
+  <si>
+    <t>7280ca01-6794-42e4-9b2c-f5b24a19cedf</t>
+  </si>
+  <si>
+    <t>21ee7c85-abcb-4d75-b955-ce27d16d3173</t>
+  </si>
+  <si>
+    <t>7413ddc7-d011-4955-bb29-bf67edbb3d1f</t>
+  </si>
+  <si>
+    <t>269f84da-e28a-4878-b792-6b5d699c2072</t>
+  </si>
+  <si>
+    <t>3aafbe97-88cb-4fad-ae5d-96cba7525cbb</t>
+  </si>
+  <si>
+    <t>3104f1a4-3566-4aea-95b5-5146f48319f3</t>
+  </si>
+  <si>
+    <t>ac529a58-9908-4547-bb64-6cf62f76e8df</t>
+  </si>
+  <si>
+    <t>ddced538-d5f1-45a1-aaf9-25c7cfd5aa8d</t>
+  </si>
+  <si>
+    <t>4866f582-7a57-4793-b48a-e96ea6e3b8b0</t>
+  </si>
+  <si>
+    <t>d13457e7-60e5-40d0-9bdc-74e9d57027f9</t>
+  </si>
+  <si>
+    <t>3c2eed2f-e9a9-4e4f-beef-393b81920c61</t>
+  </si>
+  <si>
+    <t>27bd099e-a732-4123-a2b8-78f8892d5e00</t>
+  </si>
+  <si>
+    <t>b7c535fe-3473-4fe1-a5da-e3a9bbdd2752</t>
+  </si>
+  <si>
+    <t>87ed449a-5ceb-430e-b192-6e3fed7cd985</t>
+  </si>
+  <si>
+    <t>998b096e-83dd-405d-806a-4d7afed776b7</t>
+  </si>
+  <si>
+    <t>ee1de676-9317-403d-9ba3-31f513d184f5</t>
+  </si>
+  <si>
+    <t>60383529-e3ec-4bd9-b155-5e53aec93726</t>
+  </si>
+  <si>
+    <t>0cb836df-fc5b-4e70-8247-56c1aebdc76c</t>
+  </si>
+  <si>
+    <t>0666cef2-9e59-45fd-8653-01d8d721b057</t>
+  </si>
+  <si>
+    <t>6323a183-8f66-4275-8da6-b97440c08a56</t>
+  </si>
+  <si>
+    <t>b0ac07b1-0278-4f05-babc-6fa041ee86c9</t>
+  </si>
+  <si>
+    <t>cd3c8b7c-5d69-43fc-9351-1542f2cd2f73</t>
+  </si>
+  <si>
+    <t>8089be51-adf7-473e-bd55-c7e2052f1d01</t>
+  </si>
+  <si>
+    <t>ac31109d-e8cb-4a52-8abc-6a9080df8689</t>
+  </si>
+  <si>
+    <t>5b4c3170-1fcb-4f85-820a-5473308b6707</t>
+  </si>
+  <si>
+    <t>aaa21cfd-7b2e-49f2-b119-83f1c9e77601</t>
+  </si>
+  <si>
+    <t>9c969ac7-ccf8-479b-a4f2-5360e8c72620</t>
+  </si>
+  <si>
+    <t>2cd6a92a-ab3d-4815-b54d-f1e5883ebea0</t>
+  </si>
+  <si>
+    <t>3702cb2a-5b9f-4ef8-a957-94f0e4daa6c9</t>
+  </si>
+  <si>
+    <t>5c16c168-8dbb-4efb-b5cf-93bbf5187be5</t>
+  </si>
+  <si>
+    <t>1c6dbad2-3cda-416c-9f9b-4a5e6bdb8501</t>
+  </si>
+  <si>
+    <t>8f1843c8-802a-4f71-97d7-bfc0e8a3a90f</t>
+  </si>
+  <si>
+    <t>36aa8c38-a7bb-4d42-aa7f-65e51d0dcad5</t>
+  </si>
+  <si>
+    <t>06480f54-f904-4585-8aeb-2959aa23c9aa</t>
+  </si>
+  <si>
+    <t>9f948ef3-dbfc-4954-bd21-bc3ea0125d5b</t>
+  </si>
+  <si>
+    <t>4295ed0d-6062-488a-86c2-296cdb61860d</t>
+  </si>
+  <si>
+    <t>d2b86b94-a622-4001-ae28-fa61eb641ecb</t>
+  </si>
+  <si>
+    <t>4a5ee5d9-101e-4b50-a176-80e87027c5e0</t>
+  </si>
+  <si>
+    <t>f0e6a227-32e6-416e-a45e-f9e7a45ac45e</t>
+  </si>
+  <si>
+    <t>b7d86e81-f073-4e9b-b22a-1c8d707c825c</t>
+  </si>
+  <si>
+    <t>6b71e36b-a14e-4395-bb0f-9ccf6c9f5f3a</t>
+  </si>
+  <si>
+    <t>501ecf2e-e5be-48f5-b238-63a29294bbe5</t>
+  </si>
+  <si>
+    <t>CAD/image alignment points</t>
+  </si>
+  <si>
+    <t>CAD name</t>
+  </si>
+  <si>
+    <t>CAD 1 Top X</t>
+  </si>
+  <si>
+    <t>CAD 1 Top Y</t>
+  </si>
+  <si>
+    <t>Image 1 Top X</t>
+  </si>
+  <si>
+    <t>Image 1 Top Y</t>
+  </si>
+  <si>
+    <t>CAD 2 Bottom X</t>
+  </si>
+  <si>
+    <t>CAD 2 Bottom Y</t>
+  </si>
+  <si>
+    <t>Image 2 Bottom X</t>
+  </si>
+  <si>
+    <t>Image 2 Bottom Y</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve"># Revision date: </t>
     </r>
@@ -1021,7 +1561,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>2026-March-30</t>
+      <t>2026-April-10</t>
     </r>
   </si>
 </sst>
@@ -1111,7 +1651,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1142,6 +1682,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1157,7 +1715,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1312,11 +1870,40 @@
     <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1635,40 +2222,78 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBB56770-8233-4B8D-A81F-EDDC9713B054}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:P59"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="38.6640625" style="27" customWidth="1"/>
-    <col min="2" max="2" width="89" style="33" customWidth="1"/>
+    <col min="2" max="2" width="64.5546875" style="33" customWidth="1"/>
     <col min="3" max="4" width="14" style="33" customWidth="1"/>
     <col min="5" max="5" width="16.44140625" style="33" customWidth="1"/>
     <col min="6" max="6" width="16.33203125" style="33" customWidth="1"/>
-    <col min="7" max="16384" width="8.88671875" style="33"/>
+    <col min="7" max="7" width="20.5546875" customWidth="1"/>
+    <col min="8" max="8" width="7.21875" style="60" customWidth="1"/>
+    <col min="9" max="9" width="7.5546875" style="60" customWidth="1"/>
+    <col min="10" max="10" width="12.44140625" style="60" customWidth="1"/>
+    <col min="11" max="11" width="12.109375" style="60" customWidth="1"/>
+    <col min="12" max="12" width="10.21875" style="60" customWidth="1"/>
+    <col min="13" max="13" width="9.5546875" style="60" customWidth="1"/>
+    <col min="14" max="14" width="12.44140625" style="60" customWidth="1"/>
+    <col min="15" max="15" width="12.88671875" style="60" customWidth="1"/>
+    <col min="16" max="16" width="36.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="8.88671875" style="33"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="9" customFormat="1" ht="21">
+    <row r="1" spans="1:16" s="9" customFormat="1" ht="21">
       <c r="A1" s="8" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" s="8" customFormat="1" ht="21">
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
+      <c r="P1" s="6"/>
+    </row>
+    <row r="2" spans="1:16" s="8" customFormat="1" ht="21">
       <c r="A2" s="8" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" s="8" customFormat="1" ht="21">
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
+      <c r="M2" s="22"/>
+      <c r="N2" s="22"/>
+      <c r="O2" s="22"/>
+      <c r="P2" s="7"/>
+    </row>
+    <row r="3" spans="1:16" s="8" customFormat="1" ht="21">
       <c r="A3" s="8" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>475</v>
+      </c>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+      <c r="J3" s="22"/>
+      <c r="K3" s="22"/>
+      <c r="L3" s="22"/>
+      <c r="M3" s="22"/>
+      <c r="N3" s="22"/>
+      <c r="O3" s="22"/>
+      <c r="P3"/>
+    </row>
+    <row r="4" spans="1:16">
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
       <c r="F4" s="32"/>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="G4" s="59"/>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5" s="17" t="s">
         <v>249</v>
       </c>
@@ -1677,8 +2302,9 @@
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
       <c r="F5" s="32"/>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="G5" s="59"/>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6" s="21" t="s">
         <v>33</v>
       </c>
@@ -1687,27 +2313,41 @@
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
       <c r="F6" s="32"/>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="G6" s="59"/>
+    </row>
+    <row r="7" spans="1:16">
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
       <c r="F7" s="32"/>
-    </row>
-    <row r="8" spans="1:6" s="9" customFormat="1">
+      <c r="G7" s="59"/>
+    </row>
+    <row r="8" spans="1:16" s="9" customFormat="1">
       <c r="A8" s="14" t="s">
         <v>36</v>
       </c>
       <c r="B8" s="14"/>
-      <c r="C8" s="54" t="s">
+      <c r="C8" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="54"/>
-      <c r="E8" s="54"/>
-      <c r="F8" s="54"/>
-    </row>
-    <row r="9" spans="1:6" s="4" customFormat="1" ht="28.8">
+      <c r="D8" s="58"/>
+      <c r="E8" s="58"/>
+      <c r="F8" s="58"/>
+      <c r="G8" s="61"/>
+      <c r="H8" s="62" t="s">
+        <v>465</v>
+      </c>
+      <c r="I8" s="62"/>
+      <c r="J8" s="62"/>
+      <c r="K8" s="62"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="62"/>
+      <c r="N8" s="62"/>
+      <c r="O8" s="62"/>
+      <c r="P8" s="5"/>
+    </row>
+    <row r="9" spans="1:16" s="4" customFormat="1" ht="28.8">
       <c r="A9" s="13" t="s">
         <v>22</v>
       </c>
@@ -1726,8 +2366,38 @@
       <c r="F9" s="13" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="G9" s="63" t="s">
+        <v>466</v>
+      </c>
+      <c r="H9" s="64" t="s">
+        <v>467</v>
+      </c>
+      <c r="I9" s="64" t="s">
+        <v>468</v>
+      </c>
+      <c r="J9" s="64" t="s">
+        <v>469</v>
+      </c>
+      <c r="K9" s="64" t="s">
+        <v>470</v>
+      </c>
+      <c r="L9" s="64" t="s">
+        <v>471</v>
+      </c>
+      <c r="M9" s="64" t="s">
+        <v>472</v>
+      </c>
+      <c r="N9" s="64" t="s">
+        <v>473</v>
+      </c>
+      <c r="O9" s="64" t="s">
+        <v>474</v>
+      </c>
+      <c r="P9" s="55" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
       <c r="A10" s="33" t="s">
         <v>142</v>
       </c>
@@ -1746,8 +2416,12 @@
       <c r="F10" s="32">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="G10" s="59"/>
+      <c r="P10" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
       <c r="A11" s="33" t="s">
         <v>141</v>
       </c>
@@ -1766,8 +2440,12 @@
       <c r="F11" s="32">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="12" spans="1:6">
+      <c r="G11" s="59"/>
+      <c r="P11" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
       <c r="A12" s="33" t="s">
         <v>71</v>
       </c>
@@ -1786,8 +2464,20 @@
       <c r="F12" s="32">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="13" spans="1:6">
+      <c r="G12" s="59"/>
+      <c r="H12" s="65"/>
+      <c r="I12" s="65"/>
+      <c r="J12" s="65"/>
+      <c r="K12" s="65"/>
+      <c r="L12" s="65"/>
+      <c r="M12" s="65"/>
+      <c r="N12" s="65"/>
+      <c r="O12" s="65"/>
+      <c r="P12" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
       <c r="A13" s="33" t="s">
         <v>72</v>
       </c>
@@ -1806,70 +2496,128 @@
       <c r="F13" s="32">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="14" spans="1:6">
+      <c r="G13" s="59"/>
+      <c r="H13" s="65"/>
+      <c r="I13" s="65"/>
+      <c r="J13" s="65"/>
+      <c r="K13" s="65"/>
+      <c r="L13" s="65"/>
+      <c r="M13" s="65"/>
+      <c r="N13" s="65"/>
+      <c r="O13" s="65"/>
+      <c r="P13" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
       <c r="A14" s="33"/>
-    </row>
-    <row r="15" spans="1:6">
+      <c r="G14" s="59"/>
+      <c r="H14" s="65"/>
+      <c r="I14" s="65"/>
+      <c r="J14" s="65"/>
+      <c r="K14" s="65"/>
+      <c r="L14" s="65"/>
+      <c r="M14" s="65"/>
+      <c r="N14" s="65"/>
+      <c r="O14" s="65"/>
+    </row>
+    <row r="15" spans="1:16">
       <c r="A15" s="34"/>
-    </row>
-    <row r="16" spans="1:6">
+      <c r="G15" s="59"/>
+      <c r="H15" s="65"/>
+      <c r="I15" s="65"/>
+      <c r="J15" s="65"/>
+      <c r="K15" s="65"/>
+      <c r="L15" s="66"/>
+      <c r="M15" s="66"/>
+      <c r="N15" s="65"/>
+      <c r="O15" s="65"/>
+    </row>
+    <row r="16" spans="1:16">
       <c r="A16" s="9"/>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:16">
       <c r="A17" s="9"/>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:16">
       <c r="A18" s="9"/>
-    </row>
-    <row r="19" spans="1:1">
+      <c r="P18" s="1"/>
+    </row>
+    <row r="19" spans="1:16">
       <c r="A19" s="33"/>
-    </row>
-    <row r="20" spans="1:1">
+      <c r="P19" s="1"/>
+    </row>
+    <row r="20" spans="1:16">
       <c r="A20" s="33"/>
-    </row>
-    <row r="21" spans="1:1">
+      <c r="P20" s="1"/>
+    </row>
+    <row r="21" spans="1:16">
       <c r="A21" s="34"/>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:16">
       <c r="A22" s="9"/>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:16">
       <c r="A23" s="9"/>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:16">
       <c r="A24" s="9"/>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:16">
       <c r="A25" s="33"/>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:16">
       <c r="A26" s="19"/>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:16">
       <c r="A27" s="9"/>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:16">
       <c r="A28" s="33"/>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:16">
       <c r="A29" s="9"/>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:16">
       <c r="A30" s="19"/>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:16">
       <c r="A31" s="9"/>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:16">
       <c r="A32" s="9"/>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:16">
       <c r="A33" s="9"/>
     </row>
+    <row r="34" spans="1:16">
+      <c r="P34" s="57"/>
+    </row>
+    <row r="36" spans="1:16">
+      <c r="P36" s="57"/>
+    </row>
+    <row r="49" spans="16:16">
+      <c r="P49" s="4"/>
+    </row>
+    <row r="55" spans="16:16">
+      <c r="P55" s="1"/>
+    </row>
+    <row r="56" spans="16:16">
+      <c r="P56" s="1"/>
+    </row>
+    <row r="57" spans="16:16">
+      <c r="P57" s="1"/>
+    </row>
+    <row r="58" spans="16:16">
+      <c r="P58" s="1"/>
+    </row>
+    <row r="59" spans="16:16">
+      <c r="P59" s="1"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="C8:F8"/>
+    <mergeCell ref="H8:O8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1879,7 +2627,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1251FF9-425C-410E-B269-C7726F9C2504}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:G200"/>
+  <dimension ref="A1:H200"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="15" style="1" customWidth="1"/>
@@ -1888,37 +2636,38 @@
     <col min="4" max="4" width="21.109375" style="1" customWidth="1"/>
     <col min="5" max="6" width="10" style="1" customWidth="1"/>
     <col min="7" max="7" width="42.33203125" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="1"/>
+    <col min="8" max="8" width="38.33203125" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="21">
+    <row r="1" spans="1:8" ht="21">
       <c r="A1" s="8" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="31" customFormat="1" ht="21">
+    <row r="2" spans="1:8" s="31" customFormat="1" ht="21">
       <c r="A2" s="31" t="s">
         <v>54</v>
       </c>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:8">
       <c r="A3" s="11"/>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:8">
       <c r="A4" s="17" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:8">
       <c r="A5" s="21" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:8">
       <c r="A6" s="11"/>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:8">
       <c r="A7" s="10" t="s">
         <v>12</v>
       </c>
@@ -1928,8 +2677,9 @@
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
       <c r="G7" s="10"/>
-    </row>
-    <row r="8" spans="1:7" s="6" customFormat="1" ht="28.8">
+      <c r="H7" s="10"/>
+    </row>
+    <row r="8" spans="1:8" s="6" customFormat="1" ht="28.8">
       <c r="A8" s="13" t="s">
         <v>3</v>
       </c>
@@ -1951,8 +2701,11 @@
       <c r="G8" s="13" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="9" spans="1:7">
+      <c r="H8" s="55" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="9" t="s">
         <v>137</v>
       </c>
@@ -1971,8 +2724,11 @@
       <c r="G9" s="1" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="10" spans="1:7">
+      <c r="H9" s="1" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="49" t="s">
         <v>78</v>
       </c>
@@ -1991,8 +2747,11 @@
       <c r="G10" s="1" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="11" spans="1:7">
+      <c r="H10" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="9" t="s">
         <v>108</v>
       </c>
@@ -2011,8 +2770,11 @@
       <c r="G11" s="1" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="12" spans="1:7">
+      <c r="H11" s="1" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="9" t="s">
         <v>112</v>
       </c>
@@ -2031,8 +2793,11 @@
       <c r="G12" s="1" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="13" spans="1:7">
+      <c r="H12" s="1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="9" t="s">
         <v>113</v>
       </c>
@@ -2051,8 +2816,11 @@
       <c r="G13" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="14" spans="1:7">
+      <c r="H13" s="1" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="9" t="s">
         <v>149</v>
       </c>
@@ -2071,8 +2839,11 @@
       <c r="G14" s="1" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="15" spans="1:7">
+      <c r="H14" s="56" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="49" t="s">
         <v>73</v>
       </c>
@@ -2091,8 +2862,11 @@
       <c r="G15" s="1" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="16" spans="1:7">
+      <c r="H15" s="1" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" s="49" t="s">
         <v>82</v>
       </c>
@@ -2111,8 +2885,11 @@
       <c r="G16" s="1" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="17" spans="1:7">
+      <c r="H16" s="1" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" s="9" t="s">
         <v>114</v>
       </c>
@@ -2131,8 +2908,11 @@
       <c r="G17" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="18" spans="1:7">
+      <c r="H17" s="1" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" s="9" t="s">
         <v>132</v>
       </c>
@@ -2151,8 +2931,11 @@
       <c r="G18" s="1" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="19" spans="1:7">
+      <c r="H18" s="1" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
         <v>52</v>
       </c>
@@ -2171,8 +2954,11 @@
       <c r="G19" s="1" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="20" spans="1:7">
+      <c r="H19" s="1" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
         <v>91</v>
       </c>
@@ -2188,8 +2974,11 @@
       <c r="E20" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="21" spans="1:7">
+      <c r="H20" s="1" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" s="9" t="s">
         <v>115</v>
       </c>
@@ -2208,8 +2997,11 @@
       <c r="G21" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="22" spans="1:7">
+      <c r="H21" s="1" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
         <v>106</v>
       </c>
@@ -2225,8 +3017,11 @@
       <c r="E22" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="23" spans="1:7">
+      <c r="H22" s="1" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
         <v>104</v>
       </c>
@@ -2242,8 +3037,11 @@
       <c r="E23" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="24" spans="1:7">
+      <c r="H23" s="1" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
         <v>87</v>
       </c>
@@ -2262,8 +3060,11 @@
       <c r="G24" s="1" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="25" spans="1:7">
+      <c r="H24" s="1" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
         <v>94</v>
       </c>
@@ -2282,8 +3083,11 @@
       <c r="G25" s="1" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="26" spans="1:7">
+      <c r="H25" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
         <v>96</v>
       </c>
@@ -2302,8 +3106,11 @@
       <c r="G26" s="1" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="27" spans="1:7">
+      <c r="H26" s="1" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
         <v>97</v>
       </c>
@@ -2322,8 +3129,11 @@
       <c r="G27" s="1" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="28" spans="1:7">
+      <c r="H27" s="1" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
         <v>98</v>
       </c>
@@ -2342,8 +3152,11 @@
       <c r="G28" s="1" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="29" spans="1:7">
+      <c r="H28" s="1" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
       <c r="A29" s="1" t="s">
         <v>99</v>
       </c>
@@ -2362,8 +3175,11 @@
       <c r="G29" s="1" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="30" spans="1:7">
+      <c r="H29" s="1" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
         <v>100</v>
       </c>
@@ -2382,8 +3198,11 @@
       <c r="G30" s="1" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="31" spans="1:7">
+      <c r="H30" s="1" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
         <v>101</v>
       </c>
@@ -2402,8 +3221,11 @@
       <c r="G31" s="1" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="32" spans="1:7">
+      <c r="H31" s="1" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
         <v>102</v>
       </c>
@@ -2422,8 +3244,11 @@
       <c r="G32" s="1" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="33" spans="1:5">
+      <c r="H32" s="1" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
       <c r="A33" s="9" t="s">
         <v>143</v>
       </c>
@@ -2439,8 +3264,11 @@
       <c r="E33" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="34" spans="1:5">
+      <c r="H33" s="1" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
       <c r="A34" s="9" t="s">
         <v>162</v>
       </c>
@@ -2456,47 +3284,50 @@
       <c r="E34" s="1" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="35" spans="1:5">
+      <c r="H34" s="1" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
       <c r="A35" s="9"/>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:8">
       <c r="A36" s="35"/>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:8">
       <c r="A37" s="35"/>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:8">
       <c r="A38" s="35"/>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:8">
       <c r="A39" s="35"/>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:8">
       <c r="A40" s="35"/>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:8">
       <c r="A41" s="35"/>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:8">
       <c r="A42" s="35"/>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:8">
       <c r="A43" s="11"/>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:8">
       <c r="A44" s="11"/>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:8">
       <c r="A45" s="11"/>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:8">
       <c r="A46" s="35"/>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:8">
       <c r="A47" s="35"/>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:8">
       <c r="A48" s="35"/>
     </row>
     <row r="49" spans="1:1">
@@ -3303,7 +4134,8 @@
     <col min="8" max="8" width="7.33203125" style="1" customWidth="1"/>
     <col min="9" max="9" width="95.88671875" style="1" customWidth="1"/>
     <col min="10" max="10" width="73.6640625" style="44" customWidth="1"/>
-    <col min="11" max="16384" width="8.88671875" style="1"/>
+    <col min="11" max="11" width="39" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="21">
@@ -3368,6 +4200,7 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10"/>
       <c r="J7" s="46"/>
+      <c r="K7" s="46"/>
     </row>
     <row r="8" spans="1:12" s="6" customFormat="1" ht="28.8">
       <c r="A8" s="13" t="s">
@@ -3400,6 +4233,9 @@
       <c r="J8" s="47" t="s">
         <v>48</v>
       </c>
+      <c r="K8" s="55" t="s">
+        <v>295</v>
+      </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="1" t="s">
@@ -3414,6 +4250,9 @@
       <c r="J9" s="44" t="s">
         <v>253</v>
       </c>
+      <c r="K9" s="56" t="s">
+        <v>322</v>
+      </c>
       <c r="L9" s="9"/>
     </row>
     <row r="10" spans="1:12" ht="28.8">
@@ -3428,6 +4267,9 @@
       </c>
       <c r="J10" s="44" t="s">
         <v>239</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="115.2">
@@ -3445,6 +4287,9 @@
       <c r="J11" s="44" t="s">
         <v>258</v>
       </c>
+      <c r="K11" s="1" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="12" spans="1:12" ht="28.8">
       <c r="A12" s="50" t="s">
@@ -3463,6 +4308,9 @@
       </c>
       <c r="J12" s="53" t="s">
         <v>257</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="13" spans="1:12" s="41" customFormat="1">
@@ -3482,6 +4330,9 @@
         <v>109</v>
       </c>
       <c r="J13" s="44"/>
+      <c r="K13" s="41" t="s">
+        <v>326</v>
+      </c>
     </row>
     <row r="14" spans="1:12" ht="57.6">
       <c r="A14" s="1" t="s">
@@ -3496,6 +4347,9 @@
       <c r="J14" s="44" t="s">
         <v>254</v>
       </c>
+      <c r="K14" s="1" t="s">
+        <v>327</v>
+      </c>
     </row>
     <row r="15" spans="1:12" ht="28.8">
       <c r="A15" s="1" t="s">
@@ -3510,6 +4364,9 @@
       <c r="J15" s="44" t="s">
         <v>194</v>
       </c>
+      <c r="K15" s="1" t="s">
+        <v>328</v>
+      </c>
     </row>
     <row r="16" spans="1:12" ht="57.6">
       <c r="A16" s="1" t="s">
@@ -3524,8 +4381,11 @@
       <c r="J16" s="44" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" ht="28.8">
+      <c r="K16" s="1" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="28.8">
       <c r="A17" s="1" t="s">
         <v>113</v>
       </c>
@@ -3538,8 +4398,11 @@
       <c r="J17" s="44" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="18" spans="1:10">
+      <c r="K17" s="1" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" s="1" t="s">
         <v>149</v>
       </c>
@@ -3549,8 +4412,11 @@
       <c r="I18" s="1" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" ht="57.6">
+      <c r="K18" s="1" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="57.6">
       <c r="A19" s="9" t="s">
         <v>73</v>
       </c>
@@ -3565,8 +4431,11 @@
       <c r="J19" s="44" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" ht="28.8">
+      <c r="K19" s="1" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="28.8">
       <c r="A20" s="9" t="s">
         <v>73</v>
       </c>
@@ -3586,8 +4455,11 @@
       <c r="J20" s="44" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="21" spans="1:10">
+      <c r="K20" s="1" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21" s="9" t="s">
         <v>82</v>
       </c>
@@ -3599,8 +4471,11 @@
       <c r="I21" s="1" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" ht="57.6">
+      <c r="K21" s="1" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="57.6">
       <c r="A22" s="1" t="s">
         <v>114</v>
       </c>
@@ -3613,8 +4488,11 @@
       <c r="J22" s="44" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" ht="28.8">
+      <c r="K22" s="1" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="28.8">
       <c r="A23" s="1" t="s">
         <v>114</v>
       </c>
@@ -3627,8 +4505,11 @@
       <c r="J23" s="44" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="24" spans="1:10">
+      <c r="K23" s="1" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
       <c r="A24" s="1" t="s">
         <v>132</v>
       </c>
@@ -3638,8 +4519,11 @@
       <c r="I24" s="1" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="25" spans="1:10">
+      <c r="K24" s="56" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
       <c r="A25" s="35" t="s">
         <v>52</v>
       </c>
@@ -3652,8 +4536,11 @@
         <v>126</v>
       </c>
       <c r="J25" s="1"/>
-    </row>
-    <row r="26" spans="1:10">
+      <c r="K25" s="1" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26" s="9" t="s">
         <v>91</v>
       </c>
@@ -3665,8 +4552,11 @@
       <c r="I26" s="1" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" ht="67.5" customHeight="1">
+      <c r="K26" s="1" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="67.5" customHeight="1">
       <c r="A27" s="1" t="s">
         <v>115</v>
       </c>
@@ -3679,8 +4569,11 @@
       <c r="J27" s="44" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" ht="28.8">
+      <c r="K27" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="28.8">
       <c r="A28" s="1" t="s">
         <v>115</v>
       </c>
@@ -3693,8 +4586,11 @@
       <c r="J28" s="44" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="29" spans="1:10">
+      <c r="K28" s="1" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
       <c r="A29" s="1" t="s">
         <v>106</v>
       </c>
@@ -3704,8 +4600,11 @@
       <c r="I29" s="1" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="30" spans="1:10">
+      <c r="K29" s="1" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
       <c r="A30" s="1" t="s">
         <v>104</v>
       </c>
@@ -3715,8 +4614,11 @@
       <c r="I30" s="1" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" ht="144">
+      <c r="K30" s="1" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="144">
       <c r="A31" s="9" t="s">
         <v>87</v>
       </c>
@@ -3731,8 +4633,11 @@
       <c r="J31" s="44" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" ht="28.8">
+      <c r="K31" s="1" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="28.8">
       <c r="A32" s="9" t="s">
         <v>87</v>
       </c>
@@ -3752,8 +4657,11 @@
       <c r="J32" s="44" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="33" spans="1:10">
+      <c r="K32" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
       <c r="A33" s="9" t="s">
         <v>87</v>
       </c>
@@ -3773,8 +4681,11 @@
       <c r="J33" s="44" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" ht="28.8">
+      <c r="K33" s="1" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="28.8">
       <c r="A34" s="9" t="s">
         <v>87</v>
       </c>
@@ -3794,8 +4705,11 @@
       <c r="J34" s="44" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="35" spans="1:10">
+      <c r="K34" s="1" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
       <c r="A35" s="9" t="s">
         <v>87</v>
       </c>
@@ -3815,8 +4729,11 @@
       <c r="J35" s="44" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="36" spans="1:10">
+      <c r="K35" s="1" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
       <c r="A36" s="9" t="s">
         <v>87</v>
       </c>
@@ -3836,8 +4753,11 @@
       <c r="J36" s="44" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" ht="57.6">
+      <c r="K36" s="1" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="57.6">
       <c r="A37" s="50" t="s">
         <v>94</v>
       </c>
@@ -3853,8 +4773,11 @@
       <c r="J37" s="53" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="38" spans="1:10">
+      <c r="K37" s="1" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
       <c r="A38" s="50" t="s">
         <v>94</v>
       </c>
@@ -3874,8 +4797,11 @@
       <c r="J38" s="53" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="39" spans="1:10">
+      <c r="K38" s="1" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
       <c r="A39" s="50" t="s">
         <v>94</v>
       </c>
@@ -3895,8 +4821,11 @@
       <c r="J39" s="53" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="40" spans="1:10">
+      <c r="K39" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
       <c r="A40" s="50" t="s">
         <v>94</v>
       </c>
@@ -3916,8 +4845,11 @@
       <c r="J40" s="53" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="41" spans="1:10" ht="72">
+      <c r="K40" s="1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="72">
       <c r="A41" s="50" t="s">
         <v>94</v>
       </c>
@@ -3935,8 +4867,11 @@
       <c r="J41" s="53" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="42" spans="1:10" ht="57.6">
+      <c r="K41" s="1" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="57.6">
       <c r="A42" s="50" t="s">
         <v>96</v>
       </c>
@@ -3952,8 +4887,11 @@
       <c r="J42" s="53" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="43" spans="1:10">
+      <c r="K42" s="1" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
       <c r="A43" s="50" t="s">
         <v>96</v>
       </c>
@@ -3973,8 +4911,11 @@
       <c r="J43" s="53" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="44" spans="1:10">
+      <c r="K43" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
       <c r="A44" s="50" t="s">
         <v>96</v>
       </c>
@@ -3994,8 +4935,11 @@
       <c r="J44" s="53" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="45" spans="1:10">
+      <c r="K44" s="1" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
       <c r="A45" s="50" t="s">
         <v>96</v>
       </c>
@@ -4015,8 +4959,11 @@
       <c r="J45" s="53" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="46" spans="1:10" ht="72">
+      <c r="K45" s="1" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="72">
       <c r="A46" s="50" t="s">
         <v>96</v>
       </c>
@@ -4034,8 +4981,11 @@
       <c r="J46" s="53" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="47" spans="1:10" ht="57.6">
+      <c r="K46" s="1" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="57.6">
       <c r="A47" s="50" t="s">
         <v>97</v>
       </c>
@@ -4051,8 +5001,11 @@
       <c r="J47" s="53" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="48" spans="1:10">
+      <c r="K47" s="1" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
       <c r="A48" s="50" t="s">
         <v>97</v>
       </c>
@@ -4072,8 +5025,11 @@
       <c r="J48" s="53" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="49" spans="1:10">
+      <c r="K48" s="1" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
       <c r="A49" s="50" t="s">
         <v>97</v>
       </c>
@@ -4093,8 +5049,11 @@
       <c r="J49" s="53" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="50" spans="1:10">
+      <c r="K49" s="1" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11">
       <c r="A50" s="50" t="s">
         <v>97</v>
       </c>
@@ -4114,8 +5073,11 @@
       <c r="J50" s="53" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="51" spans="1:10" ht="72">
+      <c r="K50" s="1" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="72">
       <c r="A51" s="50" t="s">
         <v>97</v>
       </c>
@@ -4133,8 +5095,11 @@
       <c r="J51" s="53" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="52" spans="1:10" ht="57.6">
+      <c r="K51" s="1" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" ht="57.6">
       <c r="A52" s="50" t="s">
         <v>98</v>
       </c>
@@ -4150,8 +5115,11 @@
       <c r="J52" s="53" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="53" spans="1:10">
+      <c r="K52" s="1" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11">
       <c r="A53" s="50" t="s">
         <v>98</v>
       </c>
@@ -4171,8 +5139,11 @@
       <c r="J53" s="53" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="54" spans="1:10">
+      <c r="K53" s="1" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11">
       <c r="A54" s="50" t="s">
         <v>98</v>
       </c>
@@ -4192,8 +5163,11 @@
       <c r="J54" s="53" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="55" spans="1:10">
+      <c r="K54" s="1" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11">
       <c r="A55" s="50" t="s">
         <v>98</v>
       </c>
@@ -4213,8 +5187,11 @@
       <c r="J55" s="53" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="56" spans="1:10" ht="72">
+      <c r="K55" s="1" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="72">
       <c r="A56" s="50" t="s">
         <v>98</v>
       </c>
@@ -4232,8 +5209,11 @@
       <c r="J56" s="53" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="57" spans="1:10" ht="57.6">
+      <c r="K56" s="1" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="57.6">
       <c r="A57" s="50" t="s">
         <v>99</v>
       </c>
@@ -4249,8 +5229,11 @@
       <c r="J57" s="53" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="58" spans="1:10">
+      <c r="K57" s="1" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11">
       <c r="A58" s="50" t="s">
         <v>99</v>
       </c>
@@ -4270,8 +5253,11 @@
       <c r="J58" s="53" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="59" spans="1:10">
+      <c r="K58" s="1" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11">
       <c r="A59" s="50" t="s">
         <v>99</v>
       </c>
@@ -4291,8 +5277,11 @@
       <c r="J59" s="53" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="60" spans="1:10">
+      <c r="K59" s="1" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11">
       <c r="A60" s="50" t="s">
         <v>99</v>
       </c>
@@ -4312,8 +5301,11 @@
       <c r="J60" s="53" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="61" spans="1:10" ht="72">
+      <c r="K60" s="1" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" ht="72">
       <c r="A61" s="50" t="s">
         <v>99</v>
       </c>
@@ -4331,8 +5323,11 @@
       <c r="J61" s="53" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="62" spans="1:10" ht="57.6">
+      <c r="K61" s="1" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" ht="57.6">
       <c r="A62" s="50" t="s">
         <v>100</v>
       </c>
@@ -4348,8 +5343,11 @@
       <c r="J62" s="53" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="63" spans="1:10">
+      <c r="K62" s="1" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11">
       <c r="A63" s="50" t="s">
         <v>100</v>
       </c>
@@ -4369,8 +5367,11 @@
       <c r="J63" s="53" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="64" spans="1:10">
+      <c r="K63" s="1" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11">
       <c r="A64" s="50" t="s">
         <v>100</v>
       </c>
@@ -4390,8 +5391,11 @@
       <c r="J64" s="53" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="65" spans="1:10">
+      <c r="K64" s="1" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11">
       <c r="A65" s="50" t="s">
         <v>100</v>
       </c>
@@ -4411,8 +5415,11 @@
       <c r="J65" s="53" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="66" spans="1:10" ht="72">
+      <c r="K65" s="1" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" ht="72">
       <c r="A66" s="50" t="s">
         <v>100</v>
       </c>
@@ -4430,8 +5437,11 @@
       <c r="J66" s="53" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="67" spans="1:10" ht="57.6">
+      <c r="K66" s="1" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" ht="57.6">
       <c r="A67" s="50" t="s">
         <v>101</v>
       </c>
@@ -4447,8 +5457,11 @@
       <c r="J67" s="53" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="68" spans="1:10">
+      <c r="K67" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11">
       <c r="A68" s="50" t="s">
         <v>101</v>
       </c>
@@ -4468,8 +5481,11 @@
       <c r="J68" s="53" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="69" spans="1:10">
+      <c r="K68" s="1" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11">
       <c r="A69" s="50" t="s">
         <v>101</v>
       </c>
@@ -4489,8 +5505,11 @@
       <c r="J69" s="53" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="70" spans="1:10">
+      <c r="K69" s="1" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11">
       <c r="A70" s="50" t="s">
         <v>101</v>
       </c>
@@ -4510,8 +5529,11 @@
       <c r="J70" s="53" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="71" spans="1:10" ht="72">
+      <c r="K70" s="1" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" ht="72">
       <c r="A71" s="50" t="s">
         <v>101</v>
       </c>
@@ -4529,8 +5551,11 @@
       <c r="J71" s="53" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="72" spans="1:10" ht="57.6">
+      <c r="K71" s="1" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" ht="57.6">
       <c r="A72" s="50" t="s">
         <v>102</v>
       </c>
@@ -4546,8 +5571,11 @@
       <c r="J72" s="53" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="73" spans="1:10">
+      <c r="K72" s="1" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11">
       <c r="A73" s="50" t="s">
         <v>102</v>
       </c>
@@ -4567,8 +5595,11 @@
       <c r="J73" s="53" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="74" spans="1:10">
+      <c r="K73" s="1" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11">
       <c r="A74" s="50" t="s">
         <v>102</v>
       </c>
@@ -4588,8 +5619,11 @@
       <c r="J74" s="53" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="75" spans="1:10">
+      <c r="K74" s="1" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11">
       <c r="A75" s="50" t="s">
         <v>102</v>
       </c>
@@ -4609,8 +5643,11 @@
       <c r="J75" s="53" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="76" spans="1:10" ht="72">
+      <c r="K75" s="1" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" ht="72">
       <c r="A76" s="50" t="s">
         <v>102</v>
       </c>
@@ -4628,8 +5665,11 @@
       <c r="J76" s="53" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="77" spans="1:10" ht="57.6">
+      <c r="K76" s="1" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" ht="57.6">
       <c r="A77" s="1" t="s">
         <v>143</v>
       </c>
@@ -4642,8 +5682,11 @@
       <c r="J77" s="44" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="78" spans="1:10">
+      <c r="K77" s="1" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11">
       <c r="A78" s="51" t="s">
         <v>130</v>
       </c>
@@ -4657,8 +5700,11 @@
         <v>131</v>
       </c>
       <c r="J78" s="40"/>
-    </row>
-    <row r="79" spans="1:10">
+      <c r="K78" s="1" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11">
       <c r="A79" s="1" t="s">
         <v>162</v>
       </c>
@@ -4668,8 +5714,11 @@
       <c r="I79" s="1" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="80" spans="1:10">
+      <c r="K79" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11">
       <c r="A80" s="1" t="s">
         <v>162</v>
       </c>
@@ -4687,6 +5736,9 @@
       </c>
       <c r="J80" s="44" t="s">
         <v>170</v>
+      </c>
+      <c r="K80" s="1" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="173" spans="5:5">
@@ -6180,7 +7232,7 @@
       <c r="E997" s="40"/>
     </row>
     <row r="1011" spans="5:8">
-      <c r="H1011" s="55"/>
+      <c r="H1011" s="54"/>
     </row>
     <row r="1014" spans="5:8">
       <c r="E1014" s="40"/>
@@ -10102,56 +11154,60 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F00A795-F924-4957-BF24-7CBCF1582012}">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.33203125" customWidth="1"/>
     <col min="2" max="2" width="36.6640625" customWidth="1"/>
-    <col min="3" max="3" width="82.44140625" customWidth="1"/>
+    <col min="3" max="3" width="65.88671875" customWidth="1"/>
+    <col min="4" max="4" width="39" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="6" customFormat="1" ht="21">
+    <row r="1" spans="1:4" s="6" customFormat="1" ht="21">
       <c r="A1" s="8" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" s="7" customFormat="1" ht="21">
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" spans="1:4" s="7" customFormat="1" ht="21">
       <c r="A2" s="31" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="4"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:4">
       <c r="A4" s="17" t="s">
         <v>249</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:4">
       <c r="A5" s="21" t="s">
         <v>29</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:4">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:4">
       <c r="A7" s="5" t="s">
         <v>13</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
-    </row>
-    <row r="8" spans="1:3">
+      <c r="D7" s="46"/>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" s="3" t="s">
         <v>3</v>
       </c>
@@ -10161,8 +11217,11 @@
       <c r="C8" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
+      <c r="D8" s="55" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>52</v>
       </c>
@@ -10172,8 +11231,11 @@
       <c r="C9" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
+      <c r="D9" s="56" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>52</v>
       </c>
@@ -10183,8 +11245,11 @@
       <c r="C10" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="11" spans="1:3">
+      <c r="D10" s="1" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" s="50" t="s">
         <v>73</v>
       </c>
@@ -10194,8 +11259,11 @@
       <c r="C11" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
+      <c r="D11" s="1" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" s="50" t="s">
         <v>78</v>
       </c>
@@ -10205,8 +11273,11 @@
       <c r="C12" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="13" spans="1:3">
+      <c r="D12" s="1" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
         <v>82</v>
       </c>
@@ -10216,8 +11287,11 @@
       <c r="C13" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="14" spans="1:3">
+      <c r="D13" s="41" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
         <v>82</v>
       </c>
@@ -10227,8 +11301,11 @@
       <c r="C14" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="15" spans="1:3">
+      <c r="D14" s="1" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
         <v>91</v>
       </c>
@@ -10238,8 +11315,11 @@
       <c r="C15" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="16" spans="1:3">
+      <c r="D15" s="1" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
         <v>94</v>
       </c>
@@ -10249,8 +11329,11 @@
       <c r="C16" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
+      <c r="D16" s="1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17" t="s">
         <v>96</v>
       </c>
@@ -10260,8 +11343,11 @@
       <c r="C17" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
+      <c r="D17" s="1" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18" t="s">
         <v>97</v>
       </c>
@@ -10271,8 +11357,11 @@
       <c r="C18" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
+      <c r="D18" s="1" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
       <c r="A19" t="s">
         <v>98</v>
       </c>
@@ -10282,8 +11371,11 @@
       <c r="C19" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
+      <c r="D19" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
       <c r="A20" t="s">
         <v>99</v>
       </c>
@@ -10293,8 +11385,11 @@
       <c r="C20" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="21" spans="1:3">
+      <c r="D20" s="1" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
       <c r="A21" t="s">
         <v>100</v>
       </c>
@@ -10304,8 +11399,11 @@
       <c r="C21" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="22" spans="1:3">
+      <c r="D21" s="1" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
       <c r="A22" t="s">
         <v>101</v>
       </c>
@@ -10315,8 +11413,11 @@
       <c r="C22" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="23" spans="1:3">
+      <c r="D22" s="1" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
       <c r="A23" t="s">
         <v>102</v>
       </c>
@@ -10326,8 +11427,11 @@
       <c r="C23" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="24" spans="1:3">
+      <c r="D23" s="1" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
       <c r="A24" s="9" t="s">
         <v>104</v>
       </c>
@@ -10337,8 +11441,11 @@
       <c r="C24" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="25" spans="1:3">
+      <c r="D24" s="56" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
       <c r="A25" s="9" t="s">
         <v>106</v>
       </c>
@@ -10348,8 +11455,11 @@
       <c r="C25" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="26" spans="1:3">
+      <c r="D25" s="1" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
       <c r="A26" s="9" t="s">
         <v>108</v>
       </c>
@@ -10359,8 +11469,11 @@
       <c r="C26" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="27" spans="1:3">
+      <c r="D26" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
       <c r="A27" s="9" t="s">
         <v>112</v>
       </c>
@@ -10370,8 +11483,11 @@
       <c r="C27" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="28" spans="1:3">
+      <c r="D27" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
       <c r="A28" s="9" t="s">
         <v>113</v>
       </c>
@@ -10381,8 +11497,11 @@
       <c r="C28" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="29" spans="1:3">
+      <c r="D28" s="1" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
       <c r="A29" s="9" t="s">
         <v>114</v>
       </c>
@@ -10392,8 +11511,11 @@
       <c r="C29" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="30" spans="1:3">
+      <c r="D29" s="1" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
       <c r="A30" s="9" t="s">
         <v>115</v>
       </c>
@@ -10403,8 +11525,11 @@
       <c r="C30" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="31" spans="1:3">
+      <c r="D30" s="1" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
       <c r="A31" s="9" t="s">
         <v>132</v>
       </c>
@@ -10414,8 +11539,11 @@
       <c r="C31" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="32" spans="1:3">
+      <c r="D31" s="1" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
       <c r="A32" s="9" t="s">
         <v>137</v>
       </c>
@@ -10425,8 +11553,11 @@
       <c r="C32" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="33" spans="1:3">
+      <c r="D32" s="1" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
       <c r="A33" s="9" t="s">
         <v>143</v>
       </c>
@@ -10436,8 +11567,11 @@
       <c r="C33" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="34" spans="1:3">
+      <c r="D33" s="1" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
       <c r="A34" s="9" t="s">
         <v>149</v>
       </c>
@@ -10447,8 +11581,11 @@
       <c r="C34" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="35" spans="1:3">
+      <c r="D34" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
       <c r="A35" s="9" t="s">
         <v>162</v>
       </c>
@@ -10457,6 +11594,9 @@
       </c>
       <c r="C35" t="s">
         <v>166</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>420</v>
       </c>
     </row>
   </sheetData>
@@ -10468,48 +11608,52 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9014B11-7294-4050-ABF4-8B4EFBD7F103}">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.33203125" customWidth="1"/>
     <col min="2" max="2" width="50.33203125" customWidth="1"/>
-    <col min="3" max="3" width="102.109375" customWidth="1"/>
+    <col min="3" max="3" width="89.33203125" customWidth="1"/>
+    <col min="4" max="4" width="39" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="6" customFormat="1" ht="21">
+    <row r="1" spans="1:4" s="6" customFormat="1" ht="21">
       <c r="A1" s="8" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" s="7" customFormat="1" ht="21">
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" spans="1:4" s="7" customFormat="1" ht="21">
       <c r="A2" s="31" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="9"/>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:4">
       <c r="A4" s="17" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:4">
       <c r="A5" s="21" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:4">
       <c r="A6" s="9"/>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:4">
       <c r="A7" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
-    </row>
-    <row r="8" spans="1:3">
+      <c r="D7" s="46"/>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" s="3" t="s">
         <v>3</v>
       </c>
@@ -10519,8 +11663,11 @@
       <c r="C8" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
+      <c r="D8" s="55" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>52</v>
       </c>
@@ -10530,8 +11677,11 @@
       <c r="C9" s="39" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
+      <c r="D9" s="56" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>73</v>
       </c>
@@ -10541,8 +11691,11 @@
       <c r="C10" s="39" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="11" spans="1:3">
+      <c r="D10" s="1" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>78</v>
       </c>
@@ -10552,8 +11705,11 @@
       <c r="C11" s="39" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
+      <c r="D11" s="1" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
         <v>78</v>
       </c>
@@ -10563,8 +11719,11 @@
       <c r="C12" s="39" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="13" spans="1:3">
+      <c r="D12" s="1" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
         <v>78</v>
       </c>
@@ -10574,8 +11733,11 @@
       <c r="C13" s="39" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="14" spans="1:3">
+      <c r="D13" s="41" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
         <v>82</v>
       </c>
@@ -10585,8 +11747,11 @@
       <c r="C14" s="39" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="15" spans="1:3">
+      <c r="D14" s="1" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
         <v>82</v>
       </c>
@@ -10596,8 +11761,11 @@
       <c r="C15" s="39" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="16" spans="1:3">
+      <c r="D15" s="1" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
         <v>82</v>
       </c>
@@ -10607,8 +11775,11 @@
       <c r="C16" s="39" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
+      <c r="D16" s="1" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17" s="50" t="s">
         <v>87</v>
       </c>
@@ -10618,8 +11789,11 @@
       <c r="C17" s="39" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
+      <c r="D17" s="1" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18" s="50" t="s">
         <v>87</v>
       </c>
@@ -10629,8 +11803,11 @@
       <c r="C18" s="39" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
+      <c r="D18" s="1" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
       <c r="A19" s="50" t="s">
         <v>87</v>
       </c>
@@ -10640,8 +11817,11 @@
       <c r="C19" s="39" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
+      <c r="D19" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
       <c r="A20" s="50" t="s">
         <v>87</v>
       </c>
@@ -10651,8 +11831,11 @@
       <c r="C20" s="39" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="21" spans="1:3">
+      <c r="D20" s="1" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
       <c r="A21" s="50" t="s">
         <v>87</v>
       </c>
@@ -10662,8 +11845,11 @@
       <c r="C21" s="39" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D21" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15.75" customHeight="1">
       <c r="A22" s="9" t="s">
         <v>108</v>
       </c>
@@ -10673,8 +11859,11 @@
       <c r="C22" s="39" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="23" spans="1:3">
+      <c r="D22" s="1" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
       <c r="A23" t="s">
         <v>112</v>
       </c>
@@ -10684,8 +11873,11 @@
       <c r="C23" s="39" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="24" spans="1:3">
+      <c r="D23" s="1" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
       <c r="A24" t="s">
         <v>106</v>
       </c>
@@ -10695,8 +11887,11 @@
       <c r="C24" s="39" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="25" spans="1:3">
+      <c r="D24" s="56" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
       <c r="A25" t="s">
         <v>104</v>
       </c>
@@ -10706,8 +11901,11 @@
       <c r="C25" s="39" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="26" spans="1:3">
+      <c r="D25" s="1" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
       <c r="A26" s="50" t="s">
         <v>94</v>
       </c>
@@ -10717,8 +11915,11 @@
       <c r="C26" s="39" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="27" spans="1:3">
+      <c r="D26" s="1" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
       <c r="A27" s="50" t="s">
         <v>96</v>
       </c>
@@ -10728,8 +11929,11 @@
       <c r="C27" s="39" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="28" spans="1:3">
+      <c r="D27" s="1" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
       <c r="A28" s="50" t="s">
         <v>97</v>
       </c>
@@ -10739,8 +11943,11 @@
       <c r="C28" s="39" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="29" spans="1:3">
+      <c r="D28" s="1" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
       <c r="A29" s="50" t="s">
         <v>98</v>
       </c>
@@ -10750,8 +11957,11 @@
       <c r="C29" s="39" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="30" spans="1:3">
+      <c r="D29" s="1" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
       <c r="A30" s="50" t="s">
         <v>99</v>
       </c>
@@ -10761,8 +11971,11 @@
       <c r="C30" s="39" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="31" spans="1:3">
+      <c r="D30" s="1" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
       <c r="A31" s="50" t="s">
         <v>100</v>
       </c>
@@ -10772,8 +11985,11 @@
       <c r="C31" s="39" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="32" spans="1:3">
+      <c r="D31" s="1" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
       <c r="A32" s="50" t="s">
         <v>101</v>
       </c>
@@ -10783,8 +11999,11 @@
       <c r="C32" s="39" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="33" spans="1:3">
+      <c r="D32" s="1" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
       <c r="A33" s="50" t="s">
         <v>102</v>
       </c>
@@ -10794,8 +12013,11 @@
       <c r="C33" s="39" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="34" spans="1:3">
+      <c r="D33" s="1" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
       <c r="A34" s="50" t="s">
         <v>94</v>
       </c>
@@ -10805,8 +12027,11 @@
       <c r="C34" s="39" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="35" spans="1:3">
+      <c r="D34" s="1" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
       <c r="A35" s="50" t="s">
         <v>96</v>
       </c>
@@ -10816,8 +12041,11 @@
       <c r="C35" s="39" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="36" spans="1:3">
+      <c r="D35" s="1" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
       <c r="A36" s="50" t="s">
         <v>97</v>
       </c>
@@ -10827,8 +12055,11 @@
       <c r="C36" s="39" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="37" spans="1:3">
+      <c r="D36" s="1" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
       <c r="A37" s="50" t="s">
         <v>98</v>
       </c>
@@ -10838,8 +12069,11 @@
       <c r="C37" s="39" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="38" spans="1:3">
+      <c r="D37" s="1" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
       <c r="A38" s="50" t="s">
         <v>99</v>
       </c>
@@ -10849,8 +12083,11 @@
       <c r="C38" s="39" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="39" spans="1:3">
+      <c r="D38" s="1" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
       <c r="A39" s="50" t="s">
         <v>100</v>
       </c>
@@ -10860,8 +12097,11 @@
       <c r="C39" s="39" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="40" spans="1:3">
+      <c r="D39" s="1" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
       <c r="A40" s="50" t="s">
         <v>101</v>
       </c>
@@ -10871,8 +12111,11 @@
       <c r="C40" s="39" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="41" spans="1:3">
+      <c r="D40" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
       <c r="A41" s="50" t="s">
         <v>102</v>
       </c>
@@ -10882,8 +12125,11 @@
       <c r="C41" s="39" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="42" spans="1:3">
+      <c r="D41" s="1" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
       <c r="A42" s="50"/>
     </row>
   </sheetData>
@@ -10924,54 +12170,58 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B01DEE13-8567-47C0-98EF-B4590CF5D2FE}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="24.44140625" customWidth="1"/>
     <col min="2" max="2" width="43.44140625" customWidth="1"/>
-    <col min="3" max="3" width="107.33203125" customWidth="1"/>
+    <col min="3" max="3" width="78.33203125" customWidth="1"/>
+    <col min="4" max="4" width="39" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="6" customFormat="1" ht="21">
+    <row r="1" spans="1:4" s="6" customFormat="1" ht="21">
       <c r="A1" s="8" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" s="7" customFormat="1" ht="21">
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" spans="1:4" s="7" customFormat="1" ht="21">
       <c r="A2" s="31" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" spans="1:4">
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:4">
       <c r="A4" s="17" t="s">
         <v>249</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:4">
       <c r="A5" s="21" t="s">
         <v>45</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:4">
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:4">
       <c r="A7" s="5" t="s">
         <v>17</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
-    </row>
-    <row r="8" spans="1:3">
+      <c r="D7" s="46"/>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" s="3" t="s">
         <v>18</v>
       </c>
@@ -10981,8 +12231,11 @@
       <c r="C8" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
+      <c r="D8" s="55" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>40</v>
       </c>
@@ -10992,29 +12245,38 @@
       <c r="C9" s="4" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="14" spans="1:3">
+      <c r="D9" s="56" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="D13" s="41"/>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" s="17"/>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:4">
       <c r="A15" s="20"/>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:4">
       <c r="A19" s="18"/>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:4">
       <c r="A23" s="18"/>
     </row>
-    <row r="26" spans="1:1">
+    <row r="24" spans="1:4">
+      <c r="D24" s="56"/>
+    </row>
+    <row r="26" spans="1:4">
       <c r="A26" s="19"/>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:4">
       <c r="A27" s="9"/>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:4">
       <c r="A28" s="9"/>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:4">
       <c r="A29" s="9"/>
     </row>
   </sheetData>
@@ -11026,46 +12288,50 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{787D0651-AC56-4C79-A3A0-381B16C48D1E}">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="25.6640625" customWidth="1"/>
     <col min="2" max="2" width="44.44140625" customWidth="1"/>
-    <col min="3" max="3" width="86.5546875" customWidth="1"/>
+    <col min="3" max="3" width="73.44140625" customWidth="1"/>
+    <col min="4" max="4" width="39" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="6" customFormat="1" ht="21">
+    <row r="1" spans="1:4" s="6" customFormat="1" ht="21">
       <c r="A1" s="8" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" s="7" customFormat="1" ht="21">
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" spans="1:4" s="7" customFormat="1" ht="21">
       <c r="A2" s="31" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
+      <c r="D2" s="2"/>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="17" t="s">
         <v>249</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:4">
       <c r="A5" s="21" t="s">
         <v>27</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:4">
       <c r="A7" s="5" t="s">
         <v>16</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
-    </row>
-    <row r="8" spans="1:3">
+      <c r="D7" s="46"/>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" s="3" t="s">
         <v>18</v>
       </c>
@@ -11075,8 +12341,11 @@
       <c r="C8" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
+      <c r="D8" s="55" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>69</v>
       </c>
@@ -11086,8 +12355,11 @@
       <c r="C9" s="39" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
+      <c r="D9" s="56" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>69</v>
       </c>
@@ -11097,8 +12369,11 @@
       <c r="C10" s="39" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="11" spans="1:3">
+      <c r="D10" s="1" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" s="17" t="s">
         <v>215</v>
       </c>
@@ -11108,21 +12383,28 @@
       <c r="C11" s="39" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
+      <c r="D11" s="1" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" s="20"/>
     </row>
-    <row r="16" spans="1:3">
+    <row r="13" spans="1:4">
+      <c r="D13" s="41"/>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" s="18"/>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:4">
       <c r="A20" s="18"/>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:4">
       <c r="A23" s="19"/>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:4">
       <c r="A24" s="9"/>
+      <c r="D24" s="56"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -11137,28 +12419,31 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBCEBA5B-6A50-48EF-B74E-B76FA9984AEF}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="33.33203125" customWidth="1"/>
     <col min="2" max="2" width="16.88671875" customWidth="1"/>
     <col min="3" max="3" width="38.88671875" customWidth="1"/>
     <col min="4" max="4" width="47.6640625" customWidth="1"/>
+    <col min="5" max="5" width="39" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="6" customFormat="1" ht="21">
+    <row r="1" spans="1:5" s="6" customFormat="1" ht="21">
       <c r="A1" s="8" t="s">
         <v>53</v>
       </c>
       <c r="B1" s="8"/>
-    </row>
-    <row r="2" spans="1:4" s="7" customFormat="1" ht="21">
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:5" s="7" customFormat="1" ht="21">
       <c r="A2" s="31" t="s">
         <v>54</v>
       </c>
       <c r="B2" s="8"/>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="E2" s="2"/>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="17" t="s">
         <v>249</v>
       </c>
@@ -11166,7 +12451,7 @@
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:5">
       <c r="A5" s="21" t="s">
         <v>46</v>
       </c>
@@ -11174,15 +12459,16 @@
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:5">
       <c r="A7" s="5" t="s">
         <v>41</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="E7" s="46"/>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="3" t="s">
         <v>18</v>
       </c>
@@ -11195,8 +12481,11 @@
       <c r="D8" s="3" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="E8" s="55" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>259</v>
       </c>
@@ -11206,8 +12495,11 @@
       <c r="D9" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="10" spans="1:4">
+      <c r="E9" s="56" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
         <v>260</v>
       </c>
@@ -11217,8 +12509,11 @@
       <c r="D10" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="11" spans="1:4">
+      <c r="E10" s="1" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
         <v>263</v>
       </c>
@@ -11228,6 +12523,15 @@
       <c r="D11" s="39" t="s">
         <v>264</v>
       </c>
+      <c r="E11" s="1" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="E13" s="41"/>
+    </row>
+    <row r="24" spans="5:5">
+      <c r="E24" s="56"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/Assets/Data/Amstrad CPC 664/MC0005A/Data CPC 664 MC0005A.xlsx
+++ b/Assets/Data/Amstrad CPC 664/MC0005A/Data CPC 664 MC0005A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dennis\AppData\Local\Classic-Repair-Toolbox\Data\Amstrad CPC 664\MC0005A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DD0179F-2CC6-40E3-8125-14CF9257F2BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E02E74F-E094-415A-B995-AEDF31CF939A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1153" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1157" uniqueCount="478">
   <si>
     <t>Name</t>
   </si>
@@ -901,9 +901,6 @@
 Functional equivalents are available from VRetro or ETO's adapter PCB allows the use of an AY-3-8910.</t>
   </si>
   <si>
-    <t>Excel data</t>
-  </si>
-  <si>
     <t>Oscilloscope baseline measurement</t>
   </si>
   <si>
@@ -1547,6 +1544,15 @@
   </si>
   <si>
     <t>Image 2 Bottom Y</t>
+  </si>
+  <si>
+    <t>Board labelling</t>
+  </si>
+  <si>
+    <t>dd68be37-fdb6-4277-a24e-6b2e97f0ef9e</t>
+  </si>
+  <si>
+    <t>Board data</t>
   </si>
   <si>
     <r>
@@ -1561,7 +1567,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>2026-April-10</t>
+      <t>2026-April-16</t>
     </r>
   </si>
 </sst>
@@ -1878,9 +1884,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1888,9 +1891,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1904,6 +1904,12 @@
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2231,14 +2237,14 @@
     <col min="5" max="5" width="16.44140625" style="33" customWidth="1"/>
     <col min="6" max="6" width="16.33203125" style="33" customWidth="1"/>
     <col min="7" max="7" width="20.5546875" customWidth="1"/>
-    <col min="8" max="8" width="7.21875" style="60" customWidth="1"/>
-    <col min="9" max="9" width="7.5546875" style="60" customWidth="1"/>
-    <col min="10" max="10" width="12.44140625" style="60" customWidth="1"/>
-    <col min="11" max="11" width="12.109375" style="60" customWidth="1"/>
-    <col min="12" max="12" width="10.21875" style="60" customWidth="1"/>
-    <col min="13" max="13" width="9.5546875" style="60" customWidth="1"/>
-    <col min="14" max="14" width="12.44140625" style="60" customWidth="1"/>
-    <col min="15" max="15" width="12.88671875" style="60" customWidth="1"/>
+    <col min="8" max="8" width="7.21875" style="59" customWidth="1"/>
+    <col min="9" max="9" width="7.5546875" style="59" customWidth="1"/>
+    <col min="10" max="10" width="12.44140625" style="59" customWidth="1"/>
+    <col min="11" max="11" width="12.109375" style="59" customWidth="1"/>
+    <col min="12" max="12" width="10.21875" style="59" customWidth="1"/>
+    <col min="13" max="13" width="9.5546875" style="59" customWidth="1"/>
+    <col min="14" max="14" width="12.44140625" style="59" customWidth="1"/>
+    <col min="15" max="15" width="12.88671875" style="59" customWidth="1"/>
     <col min="16" max="16" width="36.33203125" bestFit="1" customWidth="1"/>
     <col min="17" max="16384" width="8.88671875" style="33"/>
   </cols>
@@ -2273,7 +2279,7 @@
     </row>
     <row r="3" spans="1:16" s="8" customFormat="1" ht="21">
       <c r="A3" s="8" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="H3" s="22"/>
       <c r="I3" s="22"/>
@@ -2291,7 +2297,7 @@
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
       <c r="F4" s="32"/>
-      <c r="G4" s="59"/>
+      <c r="G4" s="58"/>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="17" t="s">
@@ -2302,7 +2308,7 @@
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
       <c r="F5" s="32"/>
-      <c r="G5" s="59"/>
+      <c r="G5" s="58"/>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="21" t="s">
@@ -2313,7 +2319,7 @@
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
       <c r="F6" s="32"/>
-      <c r="G6" s="59"/>
+      <c r="G6" s="58"/>
     </row>
     <row r="7" spans="1:16">
       <c r="B7" s="9"/>
@@ -2321,30 +2327,30 @@
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
       <c r="F7" s="32"/>
-      <c r="G7" s="59"/>
+      <c r="G7" s="58"/>
     </row>
     <row r="8" spans="1:16" s="9" customFormat="1">
       <c r="A8" s="14" t="s">
         <v>36</v>
       </c>
       <c r="B8" s="14"/>
-      <c r="C8" s="58" t="s">
+      <c r="C8" s="65" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="58"/>
-      <c r="E8" s="58"/>
-      <c r="F8" s="58"/>
-      <c r="G8" s="61"/>
-      <c r="H8" s="62" t="s">
-        <v>465</v>
-      </c>
-      <c r="I8" s="62"/>
-      <c r="J8" s="62"/>
-      <c r="K8" s="62"/>
-      <c r="L8" s="62"/>
-      <c r="M8" s="62"/>
-      <c r="N8" s="62"/>
-      <c r="O8" s="62"/>
+      <c r="D8" s="65"/>
+      <c r="E8" s="65"/>
+      <c r="F8" s="65"/>
+      <c r="G8" s="60"/>
+      <c r="H8" s="66" t="s">
+        <v>464</v>
+      </c>
+      <c r="I8" s="66"/>
+      <c r="J8" s="66"/>
+      <c r="K8" s="66"/>
+      <c r="L8" s="66"/>
+      <c r="M8" s="66"/>
+      <c r="N8" s="66"/>
+      <c r="O8" s="66"/>
       <c r="P8" s="5"/>
     </row>
     <row r="9" spans="1:16" s="4" customFormat="1" ht="28.8">
@@ -2366,35 +2372,35 @@
       <c r="F9" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="G9" s="63" t="s">
+      <c r="G9" s="61" t="s">
+        <v>465</v>
+      </c>
+      <c r="H9" s="62" t="s">
         <v>466</v>
       </c>
-      <c r="H9" s="64" t="s">
+      <c r="I9" s="62" t="s">
         <v>467</v>
       </c>
-      <c r="I9" s="64" t="s">
+      <c r="J9" s="62" t="s">
         <v>468</v>
       </c>
-      <c r="J9" s="64" t="s">
+      <c r="K9" s="62" t="s">
         <v>469</v>
       </c>
-      <c r="K9" s="64" t="s">
+      <c r="L9" s="62" t="s">
         <v>470</v>
       </c>
-      <c r="L9" s="64" t="s">
+      <c r="M9" s="62" t="s">
         <v>471</v>
       </c>
-      <c r="M9" s="64" t="s">
+      <c r="N9" s="62" t="s">
         <v>472</v>
       </c>
-      <c r="N9" s="64" t="s">
+      <c r="O9" s="62" t="s">
         <v>473</v>
       </c>
-      <c r="O9" s="64" t="s">
-        <v>474</v>
-      </c>
       <c r="P9" s="55" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2402,7 +2408,7 @@
         <v>142</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>9</v>
@@ -2416,9 +2422,9 @@
       <c r="F10" s="32">
         <v>0.5</v>
       </c>
-      <c r="G10" s="59"/>
+      <c r="G10" s="58"/>
       <c r="P10" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2426,7 +2432,7 @@
         <v>141</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C11" s="33" t="s">
         <v>9</v>
@@ -2440,9 +2446,9 @@
       <c r="F11" s="32">
         <v>0.5</v>
       </c>
-      <c r="G11" s="59"/>
+      <c r="G11" s="58"/>
       <c r="P11" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2464,17 +2470,17 @@
       <c r="F12" s="32">
         <v>0.5</v>
       </c>
-      <c r="G12" s="59"/>
-      <c r="H12" s="65"/>
-      <c r="I12" s="65"/>
-      <c r="J12" s="65"/>
-      <c r="K12" s="65"/>
-      <c r="L12" s="65"/>
-      <c r="M12" s="65"/>
-      <c r="N12" s="65"/>
-      <c r="O12" s="65"/>
+      <c r="G12" s="58"/>
+      <c r="H12" s="63"/>
+      <c r="I12" s="63"/>
+      <c r="J12" s="63"/>
+      <c r="K12" s="63"/>
+      <c r="L12" s="63"/>
+      <c r="M12" s="63"/>
+      <c r="N12" s="63"/>
+      <c r="O12" s="63"/>
       <c r="P12" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2482,7 +2488,7 @@
         <v>72</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>9</v>
@@ -2496,42 +2502,42 @@
       <c r="F13" s="32">
         <v>0.5</v>
       </c>
-      <c r="G13" s="59"/>
-      <c r="H13" s="65"/>
-      <c r="I13" s="65"/>
-      <c r="J13" s="65"/>
-      <c r="K13" s="65"/>
-      <c r="L13" s="65"/>
-      <c r="M13" s="65"/>
-      <c r="N13" s="65"/>
-      <c r="O13" s="65"/>
+      <c r="G13" s="58"/>
+      <c r="H13" s="63"/>
+      <c r="I13" s="63"/>
+      <c r="J13" s="63"/>
+      <c r="K13" s="63"/>
+      <c r="L13" s="63"/>
+      <c r="M13" s="63"/>
+      <c r="N13" s="63"/>
+      <c r="O13" s="63"/>
       <c r="P13" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="33"/>
-      <c r="G14" s="59"/>
-      <c r="H14" s="65"/>
-      <c r="I14" s="65"/>
-      <c r="J14" s="65"/>
-      <c r="K14" s="65"/>
-      <c r="L14" s="65"/>
-      <c r="M14" s="65"/>
-      <c r="N14" s="65"/>
-      <c r="O14" s="65"/>
+      <c r="G14" s="58"/>
+      <c r="H14" s="63"/>
+      <c r="I14" s="63"/>
+      <c r="J14" s="63"/>
+      <c r="K14" s="63"/>
+      <c r="L14" s="63"/>
+      <c r="M14" s="63"/>
+      <c r="N14" s="63"/>
+      <c r="O14" s="63"/>
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="34"/>
-      <c r="G15" s="59"/>
-      <c r="H15" s="65"/>
-      <c r="I15" s="65"/>
-      <c r="J15" s="65"/>
-      <c r="K15" s="65"/>
-      <c r="L15" s="66"/>
-      <c r="M15" s="66"/>
-      <c r="N15" s="65"/>
-      <c r="O15" s="65"/>
+      <c r="G15" s="58"/>
+      <c r="H15" s="63"/>
+      <c r="I15" s="63"/>
+      <c r="J15" s="63"/>
+      <c r="K15" s="63"/>
+      <c r="L15" s="64"/>
+      <c r="M15" s="64"/>
+      <c r="N15" s="63"/>
+      <c r="O15" s="63"/>
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="9"/>
@@ -2702,7 +2708,7 @@
         <v>21</v>
       </c>
       <c r="H8" s="55" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -2710,7 +2716,7 @@
         <v>137</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>138</v>
@@ -2722,10 +2728,10 @@
         <v>24</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -2748,7 +2754,7 @@
         <v>81</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -2756,7 +2762,7 @@
         <v>108</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C11" s="1">
         <v>40022</v>
@@ -2768,10 +2774,10 @@
         <v>24</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -2794,7 +2800,7 @@
         <v>118</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -2817,7 +2823,7 @@
         <v>118</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -2840,7 +2846,7 @@
         <v>151</v>
       </c>
       <c r="H14" s="56" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -2863,7 +2869,7 @@
         <v>76</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -2886,7 +2892,7 @@
         <v>85</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -2909,7 +2915,7 @@
         <v>118</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -2917,7 +2923,7 @@
         <v>132</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>134</v>
@@ -2932,7 +2938,7 @@
         <v>133</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -2955,7 +2961,7 @@
         <v>65</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -2963,7 +2969,7 @@
         <v>91</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>92</v>
@@ -2975,7 +2981,7 @@
         <v>24</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -2998,7 +3004,7 @@
         <v>118</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -3018,7 +3024,7 @@
         <v>24</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -3026,7 +3032,7 @@
         <v>104</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>105</v>
@@ -3038,7 +3044,7 @@
         <v>24</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -3061,7 +3067,7 @@
         <v>89</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -3069,7 +3075,7 @@
         <v>94</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C25" s="1">
         <v>4164</v>
@@ -3084,7 +3090,7 @@
         <v>195</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -3092,7 +3098,7 @@
         <v>96</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C26" s="1">
         <v>4164</v>
@@ -3107,7 +3113,7 @@
         <v>196</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -3115,7 +3121,7 @@
         <v>97</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C27" s="1">
         <v>4164</v>
@@ -3130,7 +3136,7 @@
         <v>197</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -3138,7 +3144,7 @@
         <v>98</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C28" s="1">
         <v>4164</v>
@@ -3153,7 +3159,7 @@
         <v>198</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -3161,7 +3167,7 @@
         <v>99</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C29" s="1">
         <v>4164</v>
@@ -3176,7 +3182,7 @@
         <v>199</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -3184,7 +3190,7 @@
         <v>100</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C30" s="1">
         <v>4164</v>
@@ -3199,7 +3205,7 @@
         <v>200</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -3207,7 +3213,7 @@
         <v>101</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C31" s="1">
         <v>4164</v>
@@ -3222,7 +3228,7 @@
         <v>201</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -3230,7 +3236,7 @@
         <v>102</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C32" s="1">
         <v>4164</v>
@@ -3245,7 +3251,7 @@
         <v>202</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -3253,7 +3259,7 @@
         <v>143</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>144</v>
@@ -3265,7 +3271,7 @@
         <v>24</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -3285,7 +3291,7 @@
         <v>163</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -4219,13 +4225,13 @@
         <v>47</v>
       </c>
       <c r="F8" s="13" t="s">
+        <v>291</v>
+      </c>
+      <c r="G8" s="13" t="s">
         <v>292</v>
       </c>
-      <c r="G8" s="13" t="s">
+      <c r="H8" s="13" t="s">
         <v>293</v>
-      </c>
-      <c r="H8" s="13" t="s">
-        <v>294</v>
       </c>
       <c r="I8" s="13" t="s">
         <v>1</v>
@@ -4234,7 +4240,7 @@
         <v>48</v>
       </c>
       <c r="K8" s="55" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -4251,7 +4257,7 @@
         <v>253</v>
       </c>
       <c r="K9" s="56" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="L9" s="9"/>
     </row>
@@ -4269,7 +4275,7 @@
         <v>239</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="115.2">
@@ -4288,7 +4294,7 @@
         <v>258</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="28.8">
@@ -4310,7 +4316,7 @@
         <v>257</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="13" spans="1:12" s="41" customFormat="1">
@@ -4331,7 +4337,7 @@
       </c>
       <c r="J13" s="44"/>
       <c r="K13" s="41" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="57.6">
@@ -4348,7 +4354,7 @@
         <v>254</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="28.8">
@@ -4365,7 +4371,7 @@
         <v>194</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="57.6">
@@ -4382,7 +4388,7 @@
         <v>254</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="28.8">
@@ -4399,7 +4405,7 @@
         <v>194</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -4413,7 +4419,7 @@
         <v>152</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="57.6">
@@ -4432,7 +4438,7 @@
         <v>235</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="28.8">
@@ -4456,7 +4462,7 @@
         <v>255</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -4472,7 +4478,7 @@
         <v>127</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="57.6">
@@ -4489,7 +4495,7 @@
         <v>254</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="28.8">
@@ -4506,7 +4512,7 @@
         <v>194</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -4520,7 +4526,7 @@
         <v>135</v>
       </c>
       <c r="K24" s="56" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -4537,7 +4543,7 @@
       </c>
       <c r="J25" s="1"/>
       <c r="K25" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -4553,7 +4559,7 @@
         <v>185</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="67.5" customHeight="1">
@@ -4570,7 +4576,7 @@
         <v>254</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="28.8">
@@ -4587,7 +4593,7 @@
         <v>194</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -4601,7 +4607,7 @@
         <v>182</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -4615,7 +4621,7 @@
         <v>184</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="144">
@@ -4634,7 +4640,7 @@
         <v>161</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="28.8">
@@ -4658,7 +4664,7 @@
         <v>177</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -4682,7 +4688,7 @@
         <v>172</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="28.8">
@@ -4706,7 +4712,7 @@
         <v>180</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -4730,7 +4736,7 @@
         <v>173</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -4754,7 +4760,7 @@
         <v>171</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="57.6">
@@ -4774,7 +4780,7 @@
         <v>256</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -4798,7 +4804,7 @@
         <v>214</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -4822,7 +4828,7 @@
         <v>210</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -4846,7 +4852,7 @@
         <v>207</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="72">
@@ -4868,7 +4874,7 @@
         <v>231</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="57.6">
@@ -4888,7 +4894,7 @@
         <v>256</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -4912,7 +4918,7 @@
         <v>214</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -4936,7 +4942,7 @@
         <v>210</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -4960,7 +4966,7 @@
         <v>207</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="72">
@@ -4982,7 +4988,7 @@
         <v>231</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="57.6">
@@ -5002,7 +5008,7 @@
         <v>256</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -5026,7 +5032,7 @@
         <v>214</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -5050,7 +5056,7 @@
         <v>210</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -5074,7 +5080,7 @@
         <v>207</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="51" spans="1:11" ht="72">
@@ -5096,7 +5102,7 @@
         <v>231</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="57.6">
@@ -5116,7 +5122,7 @@
         <v>256</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -5140,7 +5146,7 @@
         <v>214</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -5164,7 +5170,7 @@
         <v>210</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -5188,7 +5194,7 @@
         <v>207</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="72">
@@ -5210,7 +5216,7 @@
         <v>231</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="57" spans="1:11" ht="57.6">
@@ -5230,7 +5236,7 @@
         <v>256</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -5254,7 +5260,7 @@
         <v>214</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -5278,7 +5284,7 @@
         <v>210</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="60" spans="1:11">
@@ -5302,7 +5308,7 @@
         <v>207</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="61" spans="1:11" ht="72">
@@ -5324,7 +5330,7 @@
         <v>231</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="62" spans="1:11" ht="57.6">
@@ -5344,7 +5350,7 @@
         <v>256</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="63" spans="1:11">
@@ -5368,7 +5374,7 @@
         <v>214</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -5392,7 +5398,7 @@
         <v>210</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -5416,7 +5422,7 @@
         <v>207</v>
       </c>
       <c r="K65" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="66" spans="1:11" ht="72">
@@ -5438,7 +5444,7 @@
         <v>231</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="67" spans="1:11" ht="57.6">
@@ -5458,7 +5464,7 @@
         <v>256</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -5482,7 +5488,7 @@
         <v>214</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="69" spans="1:11">
@@ -5506,7 +5512,7 @@
         <v>210</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -5530,7 +5536,7 @@
         <v>207</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="71" spans="1:11" ht="72">
@@ -5552,7 +5558,7 @@
         <v>231</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="72" spans="1:11" ht="57.6">
@@ -5572,7 +5578,7 @@
         <v>256</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="73" spans="1:11">
@@ -5596,7 +5602,7 @@
         <v>214</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -5620,7 +5626,7 @@
         <v>210</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="75" spans="1:11">
@@ -5644,7 +5650,7 @@
         <v>207</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="76" spans="1:11" ht="72">
@@ -5666,7 +5672,7 @@
         <v>231</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="77" spans="1:11" ht="57.6">
@@ -5683,7 +5689,7 @@
         <v>146</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="78" spans="1:11">
@@ -5701,7 +5707,7 @@
       </c>
       <c r="J78" s="40"/>
       <c r="K78" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="79" spans="1:11">
@@ -5715,7 +5721,7 @@
         <v>165</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="80" spans="1:11">
@@ -5738,7 +5744,7 @@
         <v>170</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="173" spans="5:5">
@@ -9854,7 +9860,7 @@
         <v>71</v>
       </c>
       <c r="B70" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C70" s="12">
         <v>1288</v>
@@ -9874,7 +9880,7 @@
         <v>71</v>
       </c>
       <c r="B71" s="12" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C71" s="12">
         <v>1473</v>
@@ -9894,7 +9900,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="12" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C72" s="12">
         <v>1215</v>
@@ -9914,7 +9920,7 @@
         <v>71</v>
       </c>
       <c r="B73" s="12" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C73" s="12">
         <v>697</v>
@@ -9934,7 +9940,7 @@
         <v>71</v>
       </c>
       <c r="B74" s="12" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C74" s="12">
         <v>1048</v>
@@ -9954,7 +9960,7 @@
         <v>71</v>
       </c>
       <c r="B75" s="12" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C75" s="12">
         <v>1313</v>
@@ -9974,7 +9980,7 @@
         <v>71</v>
       </c>
       <c r="B76" s="12" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C76" s="12">
         <v>890</v>
@@ -9994,7 +10000,7 @@
         <v>71</v>
       </c>
       <c r="B77" s="12" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C77" s="12">
         <v>1393</v>
@@ -10014,7 +10020,7 @@
         <v>71</v>
       </c>
       <c r="B78" s="12" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C78" s="12">
         <v>970</v>
@@ -10034,7 +10040,7 @@
         <v>71</v>
       </c>
       <c r="B79" s="12" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C79" s="12">
         <v>969</v>
@@ -10054,7 +10060,7 @@
         <v>71</v>
       </c>
       <c r="B80" s="12" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C80" s="12">
         <v>889</v>
@@ -10074,7 +10080,7 @@
         <v>71</v>
       </c>
       <c r="B81" s="12" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C81" s="12">
         <v>1051</v>
@@ -10094,7 +10100,7 @@
         <v>71</v>
       </c>
       <c r="B82" s="12" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C82" s="12">
         <v>1217</v>
@@ -11218,7 +11224,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="55" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -11232,7 +11238,7 @@
         <v>60</v>
       </c>
       <c r="D9" s="56" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -11246,7 +11252,7 @@
         <v>62</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -11260,7 +11266,7 @@
         <v>154</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -11274,7 +11280,7 @@
         <v>155</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -11288,7 +11294,7 @@
         <v>156</v>
       </c>
       <c r="D13" s="41" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -11302,7 +11308,7 @@
         <v>157</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -11316,7 +11322,7 @@
         <v>93</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -11330,7 +11336,7 @@
         <v>103</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -11344,7 +11350,7 @@
         <v>103</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -11358,7 +11364,7 @@
         <v>103</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -11372,7 +11378,7 @@
         <v>103</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -11386,7 +11392,7 @@
         <v>103</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -11400,7 +11406,7 @@
         <v>103</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -11414,7 +11420,7 @@
         <v>103</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -11428,7 +11434,7 @@
         <v>103</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -11439,10 +11445,10 @@
         <v>59</v>
       </c>
       <c r="C24" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D24" s="56" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -11453,10 +11459,10 @@
         <v>59</v>
       </c>
       <c r="C25" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -11470,7 +11476,7 @@
         <v>111</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -11484,7 +11490,7 @@
         <v>129</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -11498,7 +11504,7 @@
         <v>129</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -11512,7 +11518,7 @@
         <v>129</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -11526,7 +11532,7 @@
         <v>129</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -11540,7 +11546,7 @@
         <v>136</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -11554,7 +11560,7 @@
         <v>140</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -11568,7 +11574,7 @@
         <v>145</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -11582,7 +11588,7 @@
         <v>153</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -11596,7 +11602,7 @@
         <v>166</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
   </sheetData>
@@ -11664,7 +11670,7 @@
         <v>15</v>
       </c>
       <c r="D8" s="55" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -11678,7 +11684,7 @@
         <v>67</v>
       </c>
       <c r="D9" s="56" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -11692,7 +11698,7 @@
         <v>77</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -11706,7 +11712,7 @@
         <v>224</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -11720,7 +11726,7 @@
         <v>225</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -11734,7 +11740,7 @@
         <v>228</v>
       </c>
       <c r="D13" s="41" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -11748,7 +11754,7 @@
         <v>86</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -11762,7 +11768,7 @@
         <v>119</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -11776,7 +11782,7 @@
         <v>122</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -11790,7 +11796,7 @@
         <v>90</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -11804,7 +11810,7 @@
         <v>119</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -11818,7 +11824,7 @@
         <v>190</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -11832,7 +11838,7 @@
         <v>186</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -11846,7 +11852,7 @@
         <v>188</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15.75" customHeight="1">
@@ -11860,7 +11866,7 @@
         <v>110</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -11874,7 +11880,7 @@
         <v>119</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -11888,7 +11894,7 @@
         <v>119</v>
       </c>
       <c r="D24" s="56" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -11902,7 +11908,7 @@
         <v>119</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -11916,7 +11922,7 @@
         <v>190</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -11930,7 +11936,7 @@
         <v>190</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -11944,7 +11950,7 @@
         <v>190</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -11958,7 +11964,7 @@
         <v>190</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -11972,7 +11978,7 @@
         <v>190</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -11986,7 +11992,7 @@
         <v>190</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -12000,7 +12006,7 @@
         <v>190</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -12014,7 +12020,7 @@
         <v>190</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -12028,7 +12034,7 @@
         <v>230</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -12042,7 +12048,7 @@
         <v>230</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -12056,7 +12062,7 @@
         <v>230</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -12070,7 +12076,7 @@
         <v>230</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -12084,7 +12090,7 @@
         <v>230</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -12098,7 +12104,7 @@
         <v>230</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -12112,7 +12118,7 @@
         <v>230</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -12126,7 +12132,7 @@
         <v>230</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -12232,7 +12238,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="55" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -12246,7 +12252,7 @@
         <v>56</v>
       </c>
       <c r="D9" s="56" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -12342,7 +12348,7 @@
         <v>15</v>
       </c>
       <c r="D8" s="55" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -12356,7 +12362,7 @@
         <v>58</v>
       </c>
       <c r="D9" s="56" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -12370,7 +12376,7 @@
         <v>68</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -12384,7 +12390,7 @@
         <v>217</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -12419,7 +12425,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBCEBA5B-6A50-48EF-B74E-B76FA9984AEF}">
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="33.33203125" customWidth="1"/>
@@ -12482,60 +12488,74 @@
         <v>44</v>
       </c>
       <c r="E8" s="55" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C9" t="s">
-        <v>262</v>
-      </c>
-      <c r="D9" t="s">
-        <v>261</v>
-      </c>
-      <c r="E9" s="56" t="s">
-        <v>462</v>
+        <v>66</v>
+      </c>
+      <c r="D9" s="39" t="s">
+        <v>263</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
+        <v>474</v>
+      </c>
+      <c r="C10" t="s">
+        <v>261</v>
+      </c>
+      <c r="D10" t="s">
         <v>260</v>
       </c>
-      <c r="C10" t="s">
-        <v>262</v>
-      </c>
-      <c r="D10" t="s">
-        <v>261</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>463</v>
+      <c r="E10" s="56" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>263</v>
+        <v>476</v>
       </c>
       <c r="C11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D11" s="39" t="s">
-        <v>264</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="E13" s="41"/>
-    </row>
-    <row r="24" spans="5:5">
-      <c r="E24" s="56"/>
+        <v>261</v>
+      </c>
+      <c r="D11" t="s">
+        <v>260</v>
+      </c>
+      <c r="E11" s="56" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C12" t="s">
+        <v>261</v>
+      </c>
+      <c r="D12" t="s">
+        <v>260</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="E14" s="41"/>
+    </row>
+    <row r="25" spans="5:5">
+      <c r="E25" s="56"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D11" r:id="rId1" xr:uid="{9604E299-48FC-4B70-80FB-D23726D038D8}"/>
+    <hyperlink ref="D9" r:id="rId1" xr:uid="{9604E299-48FC-4B70-80FB-D23726D038D8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId2"/>

--- a/Assets/Data/Amstrad CPC 664/MC0005A/Data CPC 664 MC0005A.xlsx
+++ b/Assets/Data/Amstrad CPC 664/MC0005A/Data CPC 664 MC0005A.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbewe\RetroComputing\CRT\Data\Amstrad CPC 664\MC0005A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A79CD13D-1BDF-4969-AA7A-04ABD3A02579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BABDE638-6469-442A-8A88-B07AD2AA496E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13950" yWindow="0" windowWidth="14880" windowHeight="15585" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Board schematics" sheetId="5" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1259" uniqueCount="526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1259" uniqueCount="546">
   <si>
     <t>Name</t>
   </si>
@@ -831,9 +831,6 @@
     <t>XTAL 16 MHz</t>
   </si>
   <si>
-    <t>Pulsing Active Low</t>
-  </si>
-  <si>
     <t>Pulsing</t>
   </si>
   <si>
@@ -1734,6 +1731,69 @@
       </rPr>
       <t>2026-April-19</t>
     </r>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC117_3_W.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC117_4_RAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC117_15_CAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC118_3_W.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC118_4_RAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC118_15_CAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC119_3_W.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC119_4_RAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC119_15_CAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC121_3_W.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC121_4_RAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC121_15_CAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC122_3_W.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC122_4_RAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC122_15_CAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC123_3_W.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC123_4_RAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC123_15_CAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC124_3_W.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC124_4_RAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC124_15_CAS.jpg</t>
   </si>
 </sst>
 </file>
@@ -2406,7 +2466,7 @@
     </row>
     <row r="3" spans="1:16" s="8" customFormat="1" ht="21">
       <c r="A3" s="8" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -2456,7 +2516,7 @@
       <c r="F8" s="54"/>
       <c r="G8" s="55"/>
       <c r="H8" s="56" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="I8" s="56"/>
       <c r="J8" s="56"/>
@@ -2487,34 +2547,34 @@
         <v>38</v>
       </c>
       <c r="G9" s="57" t="s">
+        <v>330</v>
+      </c>
+      <c r="H9" s="58" t="s">
         <v>331</v>
       </c>
-      <c r="H9" s="58" t="s">
+      <c r="I9" s="58" t="s">
         <v>332</v>
       </c>
-      <c r="I9" s="58" t="s">
+      <c r="J9" s="58" t="s">
         <v>333</v>
       </c>
-      <c r="J9" s="58" t="s">
+      <c r="K9" s="58" t="s">
         <v>334</v>
       </c>
-      <c r="K9" s="58" t="s">
+      <c r="L9" s="58" t="s">
         <v>335</v>
       </c>
-      <c r="L9" s="58" t="s">
+      <c r="M9" s="58" t="s">
         <v>336</v>
       </c>
-      <c r="M9" s="58" t="s">
+      <c r="N9" s="58" t="s">
         <v>337</v>
       </c>
-      <c r="N9" s="58" t="s">
+      <c r="O9" s="58" t="s">
         <v>338</v>
       </c>
-      <c r="O9" s="58" t="s">
+      <c r="P9" s="59" t="s">
         <v>339</v>
-      </c>
-      <c r="P9" s="59" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2522,7 +2582,7 @@
         <v>138</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>9</v>
@@ -2546,7 +2606,7 @@
       <c r="N10" s="61"/>
       <c r="O10" s="61"/>
       <c r="P10" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2554,7 +2614,7 @@
         <v>137</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C11" s="33" t="s">
         <v>9</v>
@@ -2578,7 +2638,7 @@
       <c r="N11" s="61"/>
       <c r="O11" s="61"/>
       <c r="P11" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2610,7 +2670,7 @@
       <c r="N12" s="62"/>
       <c r="O12" s="62"/>
       <c r="P12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2618,7 +2678,7 @@
         <v>72</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>9</v>
@@ -2642,7 +2702,7 @@
       <c r="N13" s="62"/>
       <c r="O13" s="62"/>
       <c r="P13" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2793,7 +2853,7 @@
         <v>21</v>
       </c>
       <c r="H8" s="59" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -2801,7 +2861,7 @@
         <v>133</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>134</v>
@@ -2813,10 +2873,10 @@
         <v>24</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -2839,7 +2899,7 @@
         <v>81</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -2847,7 +2907,7 @@
         <v>108</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C11" s="1">
         <v>40022</v>
@@ -2859,10 +2919,10 @@
         <v>24</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -2885,7 +2945,7 @@
         <v>118</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -2908,7 +2968,7 @@
         <v>118</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -2931,7 +2991,7 @@
         <v>145</v>
       </c>
       <c r="H14" s="63" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -2954,7 +3014,7 @@
         <v>76</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -2977,7 +3037,7 @@
         <v>85</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -3000,7 +3060,7 @@
         <v>118</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -3008,7 +3068,7 @@
         <v>128</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>130</v>
@@ -3023,7 +3083,7 @@
         <v>129</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -3046,7 +3106,7 @@
         <v>65</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -3054,7 +3114,7 @@
         <v>91</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>92</v>
@@ -3066,7 +3126,7 @@
         <v>24</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -3089,7 +3149,7 @@
         <v>118</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -3109,7 +3169,7 @@
         <v>24</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -3117,7 +3177,7 @@
         <v>104</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>105</v>
@@ -3129,7 +3189,7 @@
         <v>24</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -3152,7 +3212,7 @@
         <v>89</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -3160,7 +3220,7 @@
         <v>94</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C25" s="1">
         <v>4164</v>
@@ -3175,7 +3235,7 @@
         <v>181</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -3183,7 +3243,7 @@
         <v>96</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C26" s="1">
         <v>4164</v>
@@ -3198,7 +3258,7 @@
         <v>182</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -3206,7 +3266,7 @@
         <v>97</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C27" s="1">
         <v>4164</v>
@@ -3221,7 +3281,7 @@
         <v>183</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -3229,7 +3289,7 @@
         <v>98</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C28" s="1">
         <v>4164</v>
@@ -3244,7 +3304,7 @@
         <v>184</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -3252,7 +3312,7 @@
         <v>99</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C29" s="1">
         <v>4164</v>
@@ -3267,7 +3327,7 @@
         <v>185</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -3275,7 +3335,7 @@
         <v>100</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C30" s="1">
         <v>4164</v>
@@ -3290,7 +3350,7 @@
         <v>186</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -3298,7 +3358,7 @@
         <v>101</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C31" s="1">
         <v>4164</v>
@@ -3313,7 +3373,7 @@
         <v>187</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -3321,7 +3381,7 @@
         <v>102</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C32" s="1">
         <v>4164</v>
@@ -3336,7 +3396,7 @@
         <v>188</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -3344,7 +3404,7 @@
         <v>139</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>140</v>
@@ -3356,7 +3416,7 @@
         <v>24</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -3376,7 +3436,7 @@
         <v>156</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -4309,13 +4369,13 @@
         <v>47</v>
       </c>
       <c r="F8" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="G8" s="13" t="s">
         <v>264</v>
       </c>
-      <c r="G8" s="13" t="s">
+      <c r="H8" s="13" t="s">
         <v>265</v>
-      </c>
-      <c r="H8" s="13" t="s">
-        <v>266</v>
       </c>
       <c r="I8" s="13" t="s">
         <v>1</v>
@@ -4324,7 +4384,7 @@
         <v>48</v>
       </c>
       <c r="K8" s="59" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="90">
@@ -4338,10 +4398,10 @@
         <v>135</v>
       </c>
       <c r="J9" s="44" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K9" s="63" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="L9" s="9"/>
     </row>
@@ -4359,7 +4419,7 @@
         <v>225</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="135">
@@ -4375,10 +4435,10 @@
         <v>208</v>
       </c>
       <c r="J11" s="44" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="30">
@@ -4397,10 +4457,10 @@
         <v>219</v>
       </c>
       <c r="J12" s="52" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="13" spans="1:12" s="41" customFormat="1">
@@ -4421,7 +4481,7 @@
       </c>
       <c r="J13" s="44"/>
       <c r="K13" s="41" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="30">
@@ -4435,10 +4495,10 @@
         <v>126</v>
       </c>
       <c r="J14" s="44" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="30">
@@ -4455,7 +4515,7 @@
         <v>180</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="30">
@@ -4469,10 +4529,10 @@
         <v>126</v>
       </c>
       <c r="J16" s="44" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="30">
@@ -4489,7 +4549,7 @@
         <v>180</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -4503,7 +4563,7 @@
         <v>146</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="75">
@@ -4522,7 +4582,7 @@
         <v>221</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="30">
@@ -4537,16 +4597,16 @@
         <v>222</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>223</v>
       </c>
       <c r="J20" s="44" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -4559,10 +4619,10 @@
         <v>26</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="45">
@@ -4574,28 +4634,28 @@
         <v>4</v>
       </c>
       <c r="D22" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I22" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>311</v>
-      </c>
       <c r="J22" s="44" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="45">
@@ -4607,28 +4667,28 @@
         <v>18</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E23" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="F23" s="1" t="s">
-        <v>273</v>
-      </c>
       <c r="G23" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H23" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="H23" s="1" t="s">
-        <v>269</v>
-      </c>
       <c r="I23" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="J23" s="44" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="45">
@@ -4640,28 +4700,28 @@
         <v>38</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G24" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H24" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="H24" s="1" t="s">
-        <v>269</v>
-      </c>
       <c r="I24" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="J24" s="44" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="45">
@@ -4673,28 +4733,28 @@
         <v>39</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E25" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="F25" s="1" t="s">
-        <v>273</v>
-      </c>
       <c r="G25" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H25" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="H25" s="1" t="s">
-        <v>269</v>
-      </c>
       <c r="I25" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="J25" s="44" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="45">
@@ -4706,28 +4766,28 @@
         <v>40</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G26" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H26" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="H26" s="1" t="s">
-        <v>269</v>
-      </c>
       <c r="I26" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="J26" s="44" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="60">
@@ -4741,10 +4801,10 @@
         <v>126</v>
       </c>
       <c r="J27" s="44" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="30">
@@ -4761,7 +4821,7 @@
         <v>180</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -4775,7 +4835,7 @@
         <v>131</v>
       </c>
       <c r="K29" s="63" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -4792,7 +4852,7 @@
       </c>
       <c r="J30" s="1"/>
       <c r="K30" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -4808,7 +4868,7 @@
         <v>171</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="67.5" customHeight="1">
@@ -4822,10 +4882,10 @@
         <v>126</v>
       </c>
       <c r="J32" s="44" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="30">
@@ -4842,7 +4902,7 @@
         <v>180</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -4856,7 +4916,7 @@
         <v>168</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -4870,7 +4930,7 @@
         <v>170</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="150">
@@ -4889,7 +4949,7 @@
         <v>154</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="60">
@@ -4907,22 +4967,22 @@
         <v>165</v>
       </c>
       <c r="F37" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G37" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="G37" s="1" t="s">
+      <c r="H37" s="1" t="s">
         <v>268</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>269</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>166</v>
       </c>
       <c r="J37" s="44" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="45">
@@ -4934,28 +4994,28 @@
         <v>5</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E38" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="F38" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="F38" s="1" t="s">
-        <v>273</v>
-      </c>
       <c r="G38" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H38" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="H38" s="1" t="s">
-        <v>269</v>
-      </c>
       <c r="I38" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J38" s="44" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="90">
@@ -4967,28 +5027,28 @@
         <v>8</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F39" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I39" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="G39" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="I39" s="1" t="s">
+      <c r="J39" s="44" t="s">
         <v>274</v>
       </c>
-      <c r="J39" s="44" t="s">
-        <v>275</v>
-      </c>
       <c r="K39" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="90">
@@ -5000,28 +5060,28 @@
         <v>10</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G40" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H40" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="H40" s="1" t="s">
-        <v>269</v>
-      </c>
       <c r="I40" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J40" s="44" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="90">
@@ -5033,28 +5093,28 @@
         <v>12</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G41" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H41" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="H41" s="1" t="s">
-        <v>269</v>
-      </c>
       <c r="I41" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J41" s="44" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="60">
@@ -5066,28 +5126,28 @@
         <v>14</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>165</v>
       </c>
       <c r="F42" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G42" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="G42" s="1" t="s">
+      <c r="H42" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="H42" s="1" t="s">
-        <v>269</v>
-      </c>
       <c r="I42" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="J42" s="44" t="s">
         <v>286</v>
       </c>
-      <c r="J42" s="44" t="s">
-        <v>287</v>
-      </c>
       <c r="K42" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="45">
@@ -5099,28 +5159,28 @@
         <v>16</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>237</v>
       </c>
       <c r="F43" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G43" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="G43" s="1" t="s">
+      <c r="H43" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="H43" s="1" t="s">
-        <v>269</v>
-      </c>
       <c r="I43" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J43" s="44" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="45">
@@ -5132,28 +5192,28 @@
         <v>19</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>161</v>
       </c>
       <c r="F44" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G44" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="G44" s="1" t="s">
+      <c r="H44" s="1" t="s">
         <v>268</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>269</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>152</v>
       </c>
       <c r="J44" s="44" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="45">
@@ -5165,28 +5225,28 @@
         <v>23</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>237</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G45" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H45" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="H45" s="1" t="s">
-        <v>269</v>
-      </c>
       <c r="I45" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="J45" s="44" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="45">
@@ -5204,22 +5264,22 @@
         <v>124</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G46" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H46" s="1" t="s">
         <v>268</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>269</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>153</v>
       </c>
       <c r="J46" s="44" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="45">
@@ -5231,28 +5291,28 @@
         <v>31</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>237</v>
       </c>
       <c r="F47" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G47" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="G47" s="1" t="s">
+      <c r="H47" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="H47" s="1" t="s">
-        <v>269</v>
-      </c>
       <c r="I47" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="J47" s="44" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="K47" s="63" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="45">
@@ -5264,28 +5324,28 @@
         <v>33</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>237</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G48" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H48" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="H48" s="1" t="s">
-        <v>269</v>
-      </c>
       <c r="I48" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="J48" s="44" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="45">
@@ -5297,28 +5357,28 @@
         <v>34</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>237</v>
       </c>
       <c r="F49" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I49" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="G49" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="I49" s="1" t="s">
-        <v>303</v>
-      </c>
       <c r="J49" s="44" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="60">
@@ -5335,10 +5395,10 @@
         <v>169</v>
       </c>
       <c r="J50" s="52" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -5356,13 +5416,13 @@
         <v>237</v>
       </c>
       <c r="I51" s="41" t="s">
-        <v>199</v>
+        <v>525</v>
       </c>
       <c r="J51" s="52" t="s">
         <v>200</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -5380,13 +5440,13 @@
         <v>237</v>
       </c>
       <c r="I52" s="41" t="s">
-        <v>197</v>
+        <v>526</v>
       </c>
       <c r="J52" s="52" t="s">
         <v>196</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -5404,13 +5464,13 @@
         <v>237</v>
       </c>
       <c r="I53" s="41" t="s">
-        <v>194</v>
+        <v>527</v>
       </c>
       <c r="J53" s="52" t="s">
         <v>193</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="54" spans="1:11" ht="75">
@@ -5432,7 +5492,7 @@
         <v>217</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="55" spans="1:11" ht="60">
@@ -5449,10 +5509,10 @@
         <v>169</v>
       </c>
       <c r="J55" s="52" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -5470,13 +5530,13 @@
         <v>237</v>
       </c>
       <c r="I56" s="41" t="s">
-        <v>199</v>
+        <v>528</v>
       </c>
       <c r="J56" s="52" t="s">
         <v>200</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -5494,13 +5554,13 @@
         <v>237</v>
       </c>
       <c r="I57" s="41" t="s">
-        <v>197</v>
+        <v>529</v>
       </c>
       <c r="J57" s="52" t="s">
         <v>196</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -5518,13 +5578,13 @@
         <v>237</v>
       </c>
       <c r="I58" s="41" t="s">
-        <v>194</v>
+        <v>530</v>
       </c>
       <c r="J58" s="52" t="s">
         <v>193</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="75">
@@ -5546,7 +5606,7 @@
         <v>217</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="60" spans="1:11" ht="60">
@@ -5563,10 +5623,10 @@
         <v>169</v>
       </c>
       <c r="J60" s="52" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -5584,13 +5644,13 @@
         <v>237</v>
       </c>
       <c r="I61" s="41" t="s">
-        <v>199</v>
+        <v>531</v>
       </c>
       <c r="J61" s="52" t="s">
         <v>200</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -5608,13 +5668,13 @@
         <v>237</v>
       </c>
       <c r="I62" s="41" t="s">
-        <v>197</v>
+        <v>532</v>
       </c>
       <c r="J62" s="52" t="s">
         <v>196</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="63" spans="1:11">
@@ -5632,13 +5692,13 @@
         <v>237</v>
       </c>
       <c r="I63" s="41" t="s">
-        <v>194</v>
+        <v>533</v>
       </c>
       <c r="J63" s="52" t="s">
         <v>193</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="64" spans="1:11" ht="75">
@@ -5660,7 +5720,7 @@
         <v>217</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="65" spans="1:11" ht="60">
@@ -5677,10 +5737,10 @@
         <v>169</v>
       </c>
       <c r="J65" s="52" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="K65" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="66" spans="1:11">
@@ -5704,7 +5764,7 @@
         <v>200</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="67" spans="1:11">
@@ -5728,7 +5788,7 @@
         <v>196</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -5752,7 +5812,7 @@
         <v>193</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="69" spans="1:11" ht="75">
@@ -5774,7 +5834,7 @@
         <v>217</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="70" spans="1:11" ht="60">
@@ -5791,10 +5851,10 @@
         <v>169</v>
       </c>
       <c r="J70" s="52" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -5812,13 +5872,13 @@
         <v>237</v>
       </c>
       <c r="I71" s="41" t="s">
-        <v>199</v>
+        <v>534</v>
       </c>
       <c r="J71" s="52" t="s">
         <v>200</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -5836,13 +5896,13 @@
         <v>237</v>
       </c>
       <c r="I72" s="41" t="s">
-        <v>197</v>
+        <v>535</v>
       </c>
       <c r="J72" s="52" t="s">
         <v>196</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="73" spans="1:11">
@@ -5860,13 +5920,13 @@
         <v>237</v>
       </c>
       <c r="I73" s="41" t="s">
-        <v>194</v>
+        <v>536</v>
       </c>
       <c r="J73" s="52" t="s">
         <v>193</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="74" spans="1:11" ht="75">
@@ -5888,7 +5948,7 @@
         <v>217</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="75" spans="1:11" ht="60">
@@ -5905,10 +5965,10 @@
         <v>169</v>
       </c>
       <c r="J75" s="52" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -5926,13 +5986,13 @@
         <v>237</v>
       </c>
       <c r="I76" s="41" t="s">
-        <v>199</v>
+        <v>537</v>
       </c>
       <c r="J76" s="52" t="s">
         <v>200</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="77" spans="1:11">
@@ -5950,13 +6010,13 @@
         <v>237</v>
       </c>
       <c r="I77" s="41" t="s">
-        <v>197</v>
+        <v>538</v>
       </c>
       <c r="J77" s="52" t="s">
         <v>196</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="78" spans="1:11">
@@ -5974,13 +6034,13 @@
         <v>237</v>
       </c>
       <c r="I78" s="41" t="s">
-        <v>194</v>
+        <v>539</v>
       </c>
       <c r="J78" s="52" t="s">
         <v>193</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="79" spans="1:11" ht="75">
@@ -6002,7 +6062,7 @@
         <v>217</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="80" spans="1:11" ht="60">
@@ -6019,10 +6079,10 @@
         <v>169</v>
       </c>
       <c r="J80" s="52" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="81" spans="1:11">
@@ -6040,13 +6100,13 @@
         <v>237</v>
       </c>
       <c r="I81" s="41" t="s">
-        <v>199</v>
+        <v>540</v>
       </c>
       <c r="J81" s="52" t="s">
         <v>200</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -6064,13 +6124,13 @@
         <v>237</v>
       </c>
       <c r="I82" s="41" t="s">
-        <v>197</v>
+        <v>541</v>
       </c>
       <c r="J82" s="52" t="s">
         <v>196</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="83" spans="1:11">
@@ -6088,13 +6148,13 @@
         <v>237</v>
       </c>
       <c r="I83" s="41" t="s">
-        <v>194</v>
+        <v>542</v>
       </c>
       <c r="J83" s="52" t="s">
         <v>193</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="84" spans="1:11" ht="75">
@@ -6116,7 +6176,7 @@
         <v>217</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="85" spans="1:11" ht="60">
@@ -6133,10 +6193,10 @@
         <v>169</v>
       </c>
       <c r="J85" s="52" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="K85" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="86" spans="1:11">
@@ -6154,13 +6214,13 @@
         <v>237</v>
       </c>
       <c r="I86" s="41" t="s">
-        <v>199</v>
+        <v>543</v>
       </c>
       <c r="J86" s="52" t="s">
         <v>200</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="87" spans="1:11">
@@ -6178,13 +6238,13 @@
         <v>237</v>
       </c>
       <c r="I87" s="41" t="s">
-        <v>197</v>
+        <v>544</v>
       </c>
       <c r="J87" s="52" t="s">
         <v>196</v>
       </c>
       <c r="K87" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="88" spans="1:11">
@@ -6202,13 +6262,13 @@
         <v>237</v>
       </c>
       <c r="I88" s="41" t="s">
-        <v>194</v>
+        <v>545</v>
       </c>
       <c r="J88" s="52" t="s">
         <v>193</v>
       </c>
       <c r="K88" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="89" spans="1:11" ht="75">
@@ -6230,7 +6290,7 @@
         <v>217</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="90" spans="1:11" ht="60">
@@ -6247,7 +6307,7 @@
         <v>142</v>
       </c>
       <c r="K90" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="91" spans="1:11">
@@ -6261,7 +6321,7 @@
         <v>158</v>
       </c>
       <c r="K91" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="92" spans="1:11">
@@ -6284,7 +6344,7 @@
         <v>163</v>
       </c>
       <c r="K92" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="185" spans="5:5">
@@ -11486,7 +11546,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="59" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -11500,7 +11560,7 @@
         <v>60</v>
       </c>
       <c r="D9" s="63" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -11514,7 +11574,7 @@
         <v>62</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -11528,7 +11588,7 @@
         <v>148</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -11542,7 +11602,7 @@
         <v>149</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -11556,7 +11616,7 @@
         <v>150</v>
       </c>
       <c r="D13" s="41" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -11570,7 +11630,7 @@
         <v>151</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -11584,7 +11644,7 @@
         <v>93</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -11598,7 +11658,7 @@
         <v>103</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -11612,7 +11672,7 @@
         <v>103</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -11626,7 +11686,7 @@
         <v>103</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -11640,7 +11700,7 @@
         <v>103</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -11654,7 +11714,7 @@
         <v>103</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -11668,7 +11728,7 @@
         <v>103</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -11682,7 +11742,7 @@
         <v>103</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -11696,7 +11756,7 @@
         <v>103</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -11707,10 +11767,10 @@
         <v>59</v>
       </c>
       <c r="C24" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D24" s="63" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -11721,10 +11781,10 @@
         <v>59</v>
       </c>
       <c r="C25" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -11738,7 +11798,7 @@
         <v>111</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -11752,7 +11812,7 @@
         <v>127</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -11766,7 +11826,7 @@
         <v>127</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -11780,7 +11840,7 @@
         <v>127</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -11794,7 +11854,7 @@
         <v>127</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -11808,7 +11868,7 @@
         <v>132</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -11822,7 +11882,7 @@
         <v>136</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -11836,7 +11896,7 @@
         <v>141</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -11850,7 +11910,7 @@
         <v>147</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -11864,7 +11924,7 @@
         <v>159</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
   </sheetData>
@@ -11932,7 +11992,7 @@
         <v>15</v>
       </c>
       <c r="D8" s="59" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -11946,7 +12006,7 @@
         <v>67</v>
       </c>
       <c r="D9" s="63" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -11960,7 +12020,7 @@
         <v>77</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -11974,7 +12034,7 @@
         <v>210</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -11988,7 +12048,7 @@
         <v>211</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -12002,7 +12062,7 @@
         <v>214</v>
       </c>
       <c r="D13" s="41" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -12016,7 +12076,7 @@
         <v>86</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -12030,7 +12090,7 @@
         <v>119</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -12044,7 +12104,7 @@
         <v>122</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -12058,7 +12118,7 @@
         <v>90</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -12072,7 +12132,7 @@
         <v>119</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -12086,7 +12146,7 @@
         <v>176</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -12100,7 +12160,7 @@
         <v>172</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -12114,7 +12174,7 @@
         <v>174</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15.75" customHeight="1">
@@ -12128,7 +12188,7 @@
         <v>110</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -12142,7 +12202,7 @@
         <v>119</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -12156,7 +12216,7 @@
         <v>119</v>
       </c>
       <c r="D24" s="63" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -12170,7 +12230,7 @@
         <v>119</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -12184,7 +12244,7 @@
         <v>176</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -12198,7 +12258,7 @@
         <v>176</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -12212,7 +12272,7 @@
         <v>176</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -12226,7 +12286,7 @@
         <v>176</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -12240,7 +12300,7 @@
         <v>176</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -12254,7 +12314,7 @@
         <v>176</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -12268,7 +12328,7 @@
         <v>176</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -12282,7 +12342,7 @@
         <v>176</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -12296,7 +12356,7 @@
         <v>216</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -12310,7 +12370,7 @@
         <v>216</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -12324,7 +12384,7 @@
         <v>216</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -12338,7 +12398,7 @@
         <v>216</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -12352,7 +12412,7 @@
         <v>216</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -12366,7 +12426,7 @@
         <v>216</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -12380,7 +12440,7 @@
         <v>216</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -12394,7 +12454,7 @@
         <v>216</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -12500,7 +12560,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="59" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -12514,7 +12574,7 @@
         <v>56</v>
       </c>
       <c r="D9" s="63" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -12610,7 +12670,7 @@
         <v>15</v>
       </c>
       <c r="D8" s="59" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -12624,7 +12684,7 @@
         <v>58</v>
       </c>
       <c r="D9" s="63" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -12638,7 +12698,7 @@
         <v>68</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -12652,7 +12712,7 @@
         <v>203</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -12750,63 +12810,63 @@
         <v>44</v>
       </c>
       <c r="E8" s="59" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C9" t="s">
         <v>66</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C10" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D10" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E10" s="63" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C11" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E11" s="63" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
+        <v>244</v>
+      </c>
+      <c r="C12" t="s">
+        <v>246</v>
+      </c>
+      <c r="D12" t="s">
         <v>245</v>
       </c>
-      <c r="C12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D12" t="s">
-        <v>246</v>
-      </c>
       <c r="E12" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="14" spans="1:5">

--- a/Assets/Data/Amstrad CPC 664/MC0005A/Data CPC 664 MC0005A.xlsx
+++ b/Assets/Data/Amstrad CPC 664/MC0005A/Data CPC 664 MC0005A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbewe\RetroComputing\CRT\Data\Amstrad CPC 664\MC0005A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BABDE638-6469-442A-8A88-B07AD2AA496E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF744327-BAE4-4372-B70D-16BF9B361F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1259" uniqueCount="546">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1337" uniqueCount="546">
   <si>
     <t>Name</t>
   </si>
@@ -4599,6 +4599,15 @@
       <c r="E20" s="1" t="s">
         <v>237</v>
       </c>
+      <c r="F20" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>268</v>
+      </c>
       <c r="I20" s="1" t="s">
         <v>223</v>
       </c>
@@ -5415,6 +5424,15 @@
       <c r="E51" s="41" t="s">
         <v>237</v>
       </c>
+      <c r="F51" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>268</v>
+      </c>
       <c r="I51" s="41" t="s">
         <v>525</v>
       </c>
@@ -5439,6 +5457,15 @@
       <c r="E52" s="41" t="s">
         <v>237</v>
       </c>
+      <c r="F52" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>268</v>
+      </c>
       <c r="I52" s="41" t="s">
         <v>526</v>
       </c>
@@ -5462,6 +5489,15 @@
       </c>
       <c r="E53" s="41" t="s">
         <v>237</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>268</v>
       </c>
       <c r="I53" s="41" t="s">
         <v>527</v>
@@ -5529,6 +5565,15 @@
       <c r="E56" s="41" t="s">
         <v>237</v>
       </c>
+      <c r="F56" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>268</v>
+      </c>
       <c r="I56" s="41" t="s">
         <v>528</v>
       </c>
@@ -5553,6 +5598,15 @@
       <c r="E57" s="41" t="s">
         <v>237</v>
       </c>
+      <c r="F57" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>268</v>
+      </c>
       <c r="I57" s="41" t="s">
         <v>529</v>
       </c>
@@ -5576,6 +5630,15 @@
       </c>
       <c r="E58" s="41" t="s">
         <v>237</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>268</v>
       </c>
       <c r="I58" s="41" t="s">
         <v>530</v>
@@ -5643,6 +5706,15 @@
       <c r="E61" s="41" t="s">
         <v>237</v>
       </c>
+      <c r="F61" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>268</v>
+      </c>
       <c r="I61" s="41" t="s">
         <v>531</v>
       </c>
@@ -5667,6 +5739,15 @@
       <c r="E62" s="41" t="s">
         <v>237</v>
       </c>
+      <c r="F62" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>268</v>
+      </c>
       <c r="I62" s="41" t="s">
         <v>532</v>
       </c>
@@ -5690,6 +5771,15 @@
       </c>
       <c r="E63" s="41" t="s">
         <v>237</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>268</v>
       </c>
       <c r="I63" s="41" t="s">
         <v>533</v>
@@ -5757,6 +5847,15 @@
       <c r="E66" s="41" t="s">
         <v>237</v>
       </c>
+      <c r="F66" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>268</v>
+      </c>
       <c r="I66" s="41" t="s">
         <v>199</v>
       </c>
@@ -5781,6 +5880,15 @@
       <c r="E67" s="41" t="s">
         <v>237</v>
       </c>
+      <c r="F67" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>268</v>
+      </c>
       <c r="I67" s="41" t="s">
         <v>197</v>
       </c>
@@ -5804,6 +5912,15 @@
       </c>
       <c r="E68" s="41" t="s">
         <v>237</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>268</v>
       </c>
       <c r="I68" s="41" t="s">
         <v>194</v>
@@ -5871,6 +5988,15 @@
       <c r="E71" s="41" t="s">
         <v>237</v>
       </c>
+      <c r="F71" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>268</v>
+      </c>
       <c r="I71" s="41" t="s">
         <v>534</v>
       </c>
@@ -5895,6 +6021,15 @@
       <c r="E72" s="41" t="s">
         <v>237</v>
       </c>
+      <c r="F72" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>268</v>
+      </c>
       <c r="I72" s="41" t="s">
         <v>535</v>
       </c>
@@ -5918,6 +6053,15 @@
       </c>
       <c r="E73" s="41" t="s">
         <v>237</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>268</v>
       </c>
       <c r="I73" s="41" t="s">
         <v>536</v>
@@ -5985,6 +6129,15 @@
       <c r="E76" s="41" t="s">
         <v>237</v>
       </c>
+      <c r="F76" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>268</v>
+      </c>
       <c r="I76" s="41" t="s">
         <v>537</v>
       </c>
@@ -6009,6 +6162,15 @@
       <c r="E77" s="41" t="s">
         <v>237</v>
       </c>
+      <c r="F77" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>268</v>
+      </c>
       <c r="I77" s="41" t="s">
         <v>538</v>
       </c>
@@ -6032,6 +6194,15 @@
       </c>
       <c r="E78" s="41" t="s">
         <v>237</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>268</v>
       </c>
       <c r="I78" s="41" t="s">
         <v>539</v>
@@ -6099,6 +6270,15 @@
       <c r="E81" s="41" t="s">
         <v>237</v>
       </c>
+      <c r="F81" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>268</v>
+      </c>
       <c r="I81" s="41" t="s">
         <v>540</v>
       </c>
@@ -6123,6 +6303,15 @@
       <c r="E82" s="41" t="s">
         <v>237</v>
       </c>
+      <c r="F82" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>268</v>
+      </c>
       <c r="I82" s="41" t="s">
         <v>541</v>
       </c>
@@ -6146,6 +6335,15 @@
       </c>
       <c r="E83" s="41" t="s">
         <v>237</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>268</v>
       </c>
       <c r="I83" s="41" t="s">
         <v>542</v>
@@ -6213,6 +6411,15 @@
       <c r="E86" s="41" t="s">
         <v>237</v>
       </c>
+      <c r="F86" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>268</v>
+      </c>
       <c r="I86" s="41" t="s">
         <v>543</v>
       </c>
@@ -6237,6 +6444,15 @@
       <c r="E87" s="41" t="s">
         <v>237</v>
       </c>
+      <c r="F87" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>268</v>
+      </c>
       <c r="I87" s="41" t="s">
         <v>544</v>
       </c>
@@ -6260,6 +6476,15 @@
       </c>
       <c r="E88" s="41" t="s">
         <v>237</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>268</v>
       </c>
       <c r="I88" s="41" t="s">
         <v>545</v>
@@ -6336,6 +6561,15 @@
       </c>
       <c r="E92" s="1" t="s">
         <v>124</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>268</v>
       </c>
       <c r="I92" s="1" t="s">
         <v>162</v>

--- a/Assets/Data/Amstrad CPC 664/MC0005A/Data CPC 664 MC0005A.xlsx
+++ b/Assets/Data/Amstrad CPC 664/MC0005A/Data CPC 664 MC0005A.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbewe\RetroComputing\CRT\Data\Amstrad CPC 664\MC0005A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF744327-BAE4-4372-B70D-16BF9B361F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD929A52-D2DB-41D8-9BAD-3762C6701C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Board schematics" sheetId="5" r:id="rId1"/>
@@ -24,7 +24,7 @@
     <sheet name="Credits" sheetId="13" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Component images'!$A$8:$J$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Component images'!$A$8:$J$132</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1337" uniqueCount="546">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1679" uniqueCount="676">
   <si>
     <t>Name</t>
   </si>
@@ -1717,6 +1717,465 @@
     <t>8c91c782-9999-4105-8683-a9cf405f0a5c</t>
   </si>
   <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC117_3_W.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC117_4_RAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC117_15_CAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC118_3_W.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC118_4_RAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC118_15_CAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC119_3_W.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC119_4_RAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC119_15_CAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC121_3_W.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC121_4_RAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC121_15_CAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC122_3_W.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC122_4_RAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC122_15_CAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC123_3_W.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC123_4_RAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC123_15_CAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC124_3_W.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC124_4_RAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC124_15_CAS.jpg</t>
+  </si>
+  <si>
+    <t>/MREQ</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_19_MREQ.jpg</t>
+  </si>
+  <si>
+    <t>/IORQ</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_20_IORQ.jpg</t>
+  </si>
+  <si>
+    <t>/HALT</t>
+  </si>
+  <si>
+    <t>HIGH</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_18_HALT.jpg</t>
+  </si>
+  <si>
+    <t>/M1</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_27_M1.jpg</t>
+  </si>
+  <si>
+    <t>/RFSH</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_28_RFSH.jpg</t>
+  </si>
+  <si>
+    <t>2a2c585e-d929-4df9-aa4e-462a7547d4b8</t>
+  </si>
+  <si>
+    <t>9eb2bce7-f31f-4eb6-8f8c-aa7c7c11519a</t>
+  </si>
+  <si>
+    <t>2d5c6816-9dd1-4003-834e-5824a2301dfd</t>
+  </si>
+  <si>
+    <t>93529858-2cc6-48e2-b97a-baa54fee5207</t>
+  </si>
+  <si>
+    <t>d2591511-dea5-41f8-ba19-c98b42ee74b3</t>
+  </si>
+  <si>
+    <t>A10</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_40_A10.jpg</t>
+  </si>
+  <si>
+    <t>D0</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>D2</t>
+  </si>
+  <si>
+    <t>D3</t>
+  </si>
+  <si>
+    <t>D4</t>
+  </si>
+  <si>
+    <t>D5</t>
+  </si>
+  <si>
+    <t>D6</t>
+  </si>
+  <si>
+    <t>D7</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_14_D0.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_15_D1.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_12_D2.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_8_D3.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_7_D4.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_9_D5.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_10_D6.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_13_D7.jpg</t>
+  </si>
+  <si>
+    <t>18f244f9-4c21-4803-b428-33ac3d34f27d</t>
+  </si>
+  <si>
+    <t>a6568f2a-42bd-403c-a793-4e599d33903e</t>
+  </si>
+  <si>
+    <t>df903ca6-bbe3-47c3-b332-da61711ae2af</t>
+  </si>
+  <si>
+    <t>e1174e58-e170-429f-8802-bb3fe24babe9</t>
+  </si>
+  <si>
+    <t>0c294d2f-2899-4493-a2e8-379adc9f8d06</t>
+  </si>
+  <si>
+    <t>c515c26c-a996-4360-9899-b9432f62e391</t>
+  </si>
+  <si>
+    <t>a5ff565c-c815-4a73-9c83-6053960388a0</t>
+  </si>
+  <si>
+    <t>1920945e-833c-4b95-a33c-fb7a3a9d24d6</t>
+  </si>
+  <si>
+    <t>CLK</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_6_CLK.jpg</t>
+  </si>
+  <si>
+    <t>Input from Gate Array /NPHI (Pin 19) via IC125 Not Gate.
+Trace taken at Ready Prompt.</t>
+  </si>
+  <si>
+    <t>Trace taken at Ready Prompt.</t>
+  </si>
+  <si>
+    <t>Output to Expansion Port (Pin 30)
+Trace taken at Ready Prompt.</t>
+  </si>
+  <si>
+    <t>Output to Gate Array /NM1 (Pin 20)
+Trace taken at Ready Prompt.</t>
+  </si>
+  <si>
+    <t>Output to Gate Array /NIORQ (Pin 18). Combined with /RD and /WR to provide /IORD and /IOWR using OR Gates from IC112.
+Trace taken at Ready Prompt.</t>
+  </si>
+  <si>
+    <t>Output to Gate Array /NMREQ (Pin 17)
+Trace taken at Ready Prompt.</t>
+  </si>
+  <si>
+    <t>Output to Expansion Port (Pin 34)
+Trace taken at Ready Prompt.</t>
+  </si>
+  <si>
+    <t>adf3733e-4d49-45c9-9dcb-eb773e6067cb</t>
+  </si>
+  <si>
+    <t>A0</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>A3</t>
+  </si>
+  <si>
+    <t>A4</t>
+  </si>
+  <si>
+    <t>A5</t>
+  </si>
+  <si>
+    <t>A6</t>
+  </si>
+  <si>
+    <t>A7</t>
+  </si>
+  <si>
+    <t>A8</t>
+  </si>
+  <si>
+    <t>A9</t>
+  </si>
+  <si>
+    <t>A11</t>
+  </si>
+  <si>
+    <t>A12</t>
+  </si>
+  <si>
+    <t>A13</t>
+  </si>
+  <si>
+    <t>A14</t>
+  </si>
+  <si>
+    <t>A15</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_30_A0.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_31_A1.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_32_A2.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_33_A3.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_34_A4.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_35_A5.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_36_A6.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_37_A7.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_38_A8.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_39_A9.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_1_A11.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_2_A12.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_3_A13.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_4_A14.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_5_A15.jpg</t>
+  </si>
+  <si>
+    <t>385bd464-2634-4e9c-8fab-f89483763090</t>
+  </si>
+  <si>
+    <t>ad73f2cb-4d3d-4647-9593-8e0e3ed98909</t>
+  </si>
+  <si>
+    <t>4b6a2495-6846-481b-abdc-567ce8666641</t>
+  </si>
+  <si>
+    <t>8d3775ef-12bc-465d-8a15-8f37a1021e76</t>
+  </si>
+  <si>
+    <t>b67483b9-c093-4d14-8364-ffa44790cc64</t>
+  </si>
+  <si>
+    <t>929ff7d7-1ebd-4797-abcb-9e1752cb287b</t>
+  </si>
+  <si>
+    <t>28ea6bd3-875f-49c5-b749-603768f0d278</t>
+  </si>
+  <si>
+    <t>5dad29c4-8308-42d2-95a2-d60fe836333a</t>
+  </si>
+  <si>
+    <t>607e360a-95ae-48db-8b76-d86b8f1a752f</t>
+  </si>
+  <si>
+    <t>e1d0d16d-ab75-4578-b187-e95a4051f3f9</t>
+  </si>
+  <si>
+    <t>edd13b67-892d-42db-a9fc-f6561d68c8b3</t>
+  </si>
+  <si>
+    <t>59c0a93d-70e9-46c3-b78e-bde7786618fe</t>
+  </si>
+  <si>
+    <t>d88ad8fd-2f2e-438c-8df8-92b8a6768dfb</t>
+  </si>
+  <si>
+    <t>20efc209-36eb-4b84-9985-f640d1c142c2</t>
+  </si>
+  <si>
+    <t>25a9bfa2-3085-4bbc-8bae-bb4cbcc21bdd</t>
+  </si>
+  <si>
+    <t>a84622f4-5a51-4872-91e8-bfca3b4897aa</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_17_NMI.jpg</t>
+  </si>
+  <si>
+    <t>Input from Expansion Port (Pin 36).</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_16_INT.jpg</t>
+  </si>
+  <si>
+    <t>Input from Gate Array /NINTERRUPT (Pin 32).</t>
+  </si>
+  <si>
+    <t>/WAIT</t>
+  </si>
+  <si>
+    <t>/NMI</t>
+  </si>
+  <si>
+    <t>/INT</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_24_WAIT.jpg</t>
+  </si>
+  <si>
+    <t>Input from Gate Array /READY (Pin 22).</t>
+  </si>
+  <si>
+    <t>/RESET</t>
+  </si>
+  <si>
+    <t>/BUSRQ</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_25_BUSRQ.jpg</t>
+  </si>
+  <si>
+    <t>Input from Expansion Port (Pin 37).</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_26_RESET.jpg</t>
+  </si>
+  <si>
+    <t>Input from IC110.</t>
+  </si>
+  <si>
+    <t>/RD</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_21_RD.jpg</t>
+  </si>
+  <si>
+    <t>Ouput to Gate Array /NRD (Pin 21).</t>
+  </si>
+  <si>
+    <t>Output to Expansion Port (Pin 32).</t>
+  </si>
+  <si>
+    <t>/WR</t>
+  </si>
+  <si>
+    <t>/BUSAK</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_22_WR.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_23_BUSAK.jpg</t>
+  </si>
+  <si>
+    <t>Output to Expansion Port (Pin 38).</t>
+  </si>
+  <si>
+    <t>cb52ccd4-bf58-4871-94ba-c475f90bce46</t>
+  </si>
+  <si>
+    <t>9e65f56c-621c-4d46-b9aa-c0a77d011450</t>
+  </si>
+  <si>
+    <t>f7e8d3bd-5a4f-4d5b-afd8-76aea6713453</t>
+  </si>
+  <si>
+    <t>18d3a311-3dab-473b-9271-9f8ff5f0dc54</t>
+  </si>
+  <si>
+    <t>c9bb61ad-fd00-4e69-806f-366891d98065</t>
+  </si>
+  <si>
+    <t>f033819e-4529-4c9f-aa0e-c44a1f7bc8ee</t>
+  </si>
+  <si>
+    <t>06e5c836-f65f-4cf0-a5de-2833904ea444</t>
+  </si>
+  <si>
+    <t>6603d7c7-806b-4518-84d5-6aff7b4afc6c</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve"># Revision date: </t>
     </r>
@@ -1729,78 +2188,15 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>2026-April-19</t>
+      <t>2026-April-21</t>
     </r>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC117_3_W.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC117_4_RAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC117_15_CAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC118_3_W.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC118_4_RAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC118_15_CAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC119_3_W.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC119_4_RAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC119_15_CAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC121_3_W.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC121_4_RAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC121_15_CAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC122_3_W.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC122_4_RAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC122_15_CAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC123_3_W.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC123_4_RAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC123_15_CAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC124_3_W.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC124_4_RAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC124_15_CAS.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1876,6 +2272,17 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -1941,7 +2348,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2096,13 +2503,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -2123,6 +2524,15 @@
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2466,7 +2876,7 @@
     </row>
     <row r="3" spans="1:16" s="8" customFormat="1" ht="21">
       <c r="A3" s="8" t="s">
-        <v>524</v>
+        <v>675</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -2508,23 +2918,23 @@
         <v>36</v>
       </c>
       <c r="B8" s="14"/>
-      <c r="C8" s="54" t="s">
+      <c r="C8" s="63" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="54"/>
-      <c r="E8" s="54"/>
-      <c r="F8" s="54"/>
-      <c r="G8" s="55"/>
-      <c r="H8" s="56" t="s">
+      <c r="D8" s="63"/>
+      <c r="E8" s="63"/>
+      <c r="F8" s="63"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="64" t="s">
         <v>329</v>
       </c>
-      <c r="I8" s="56"/>
-      <c r="J8" s="56"/>
-      <c r="K8" s="56"/>
-      <c r="L8" s="56"/>
-      <c r="M8" s="56"/>
-      <c r="N8" s="56"/>
-      <c r="O8" s="56"/>
+      <c r="I8" s="64"/>
+      <c r="J8" s="64"/>
+      <c r="K8" s="64"/>
+      <c r="L8" s="64"/>
+      <c r="M8" s="64"/>
+      <c r="N8" s="64"/>
+      <c r="O8" s="64"/>
       <c r="P8" s="5"/>
     </row>
     <row r="9" spans="1:16" s="4" customFormat="1" ht="45">
@@ -2546,34 +2956,34 @@
       <c r="F9" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="G9" s="57" t="s">
+      <c r="G9" s="55" t="s">
         <v>330</v>
       </c>
-      <c r="H9" s="58" t="s">
+      <c r="H9" s="56" t="s">
         <v>331</v>
       </c>
-      <c r="I9" s="58" t="s">
+      <c r="I9" s="56" t="s">
         <v>332</v>
       </c>
-      <c r="J9" s="58" t="s">
+      <c r="J9" s="56" t="s">
         <v>333</v>
       </c>
-      <c r="K9" s="58" t="s">
+      <c r="K9" s="56" t="s">
         <v>334</v>
       </c>
-      <c r="L9" s="58" t="s">
+      <c r="L9" s="56" t="s">
         <v>335</v>
       </c>
-      <c r="M9" s="58" t="s">
+      <c r="M9" s="56" t="s">
         <v>336</v>
       </c>
-      <c r="N9" s="58" t="s">
+      <c r="N9" s="56" t="s">
         <v>337</v>
       </c>
-      <c r="O9" s="58" t="s">
+      <c r="O9" s="56" t="s">
         <v>338</v>
       </c>
-      <c r="P9" s="59" t="s">
+      <c r="P9" s="57" t="s">
         <v>339</v>
       </c>
     </row>
@@ -2596,15 +3006,15 @@
       <c r="F10" s="32">
         <v>0.5</v>
       </c>
-      <c r="G10" s="60"/>
-      <c r="H10" s="61"/>
-      <c r="I10" s="61"/>
-      <c r="J10" s="61"/>
-      <c r="K10" s="61"/>
-      <c r="L10" s="61"/>
-      <c r="M10" s="61"/>
-      <c r="N10" s="61"/>
-      <c r="O10" s="61"/>
+      <c r="G10" s="58"/>
+      <c r="H10" s="59"/>
+      <c r="I10" s="59"/>
+      <c r="J10" s="59"/>
+      <c r="K10" s="59"/>
+      <c r="L10" s="59"/>
+      <c r="M10" s="59"/>
+      <c r="N10" s="59"/>
+      <c r="O10" s="59"/>
       <c r="P10" t="s">
         <v>340</v>
       </c>
@@ -2628,15 +3038,15 @@
       <c r="F11" s="32">
         <v>0.5</v>
       </c>
-      <c r="G11" s="60"/>
-      <c r="H11" s="61"/>
-      <c r="I11" s="61"/>
-      <c r="J11" s="61"/>
-      <c r="K11" s="61"/>
-      <c r="L11" s="61"/>
-      <c r="M11" s="61"/>
-      <c r="N11" s="61"/>
-      <c r="O11" s="61"/>
+      <c r="G11" s="58"/>
+      <c r="H11" s="59"/>
+      <c r="I11" s="59"/>
+      <c r="J11" s="59"/>
+      <c r="K11" s="59"/>
+      <c r="L11" s="59"/>
+      <c r="M11" s="59"/>
+      <c r="N11" s="59"/>
+      <c r="O11" s="59"/>
       <c r="P11" t="s">
         <v>341</v>
       </c>
@@ -2660,15 +3070,15 @@
       <c r="F12" s="32">
         <v>0.5</v>
       </c>
-      <c r="G12" s="60"/>
-      <c r="H12" s="62"/>
-      <c r="I12" s="62"/>
-      <c r="J12" s="62"/>
-      <c r="K12" s="62"/>
-      <c r="L12" s="62"/>
-      <c r="M12" s="62"/>
-      <c r="N12" s="62"/>
-      <c r="O12" s="62"/>
+      <c r="G12" s="58"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="60"/>
+      <c r="J12" s="60"/>
+      <c r="K12" s="60"/>
+      <c r="L12" s="60"/>
+      <c r="M12" s="60"/>
+      <c r="N12" s="60"/>
+      <c r="O12" s="60"/>
       <c r="P12" t="s">
         <v>342</v>
       </c>
@@ -2692,15 +3102,15 @@
       <c r="F13" s="32">
         <v>0.5</v>
       </c>
-      <c r="G13" s="60"/>
-      <c r="H13" s="62"/>
-      <c r="I13" s="62"/>
-      <c r="J13" s="62"/>
-      <c r="K13" s="62"/>
-      <c r="L13" s="62"/>
-      <c r="M13" s="62"/>
-      <c r="N13" s="62"/>
-      <c r="O13" s="62"/>
+      <c r="G13" s="58"/>
+      <c r="H13" s="60"/>
+      <c r="I13" s="60"/>
+      <c r="J13" s="60"/>
+      <c r="K13" s="60"/>
+      <c r="L13" s="60"/>
+      <c r="M13" s="60"/>
+      <c r="N13" s="60"/>
+      <c r="O13" s="60"/>
       <c r="P13" t="s">
         <v>343</v>
       </c>
@@ -2852,7 +3262,7 @@
       <c r="G8" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="H8" s="59" t="s">
+      <c r="H8" s="57" t="s">
         <v>339</v>
       </c>
     </row>
@@ -2990,7 +3400,7 @@
       <c r="G14" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="H14" s="63" t="s">
+      <c r="H14" s="61" t="s">
         <v>349</v>
       </c>
     </row>
@@ -4272,7 +4682,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35D2A4B1-8E0B-46C6-8B83-02048610537D}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:L2845"/>
+  <dimension ref="A1:L2883"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15" style="1" customWidth="1"/>
@@ -4383,11 +4793,11 @@
       <c r="J8" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="K8" s="59" t="s">
+      <c r="K8" s="57" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="90">
+    <row r="9" spans="1:12">
       <c r="A9" s="1" t="s">
         <v>133</v>
       </c>
@@ -4400,12 +4810,12 @@
       <c r="J9" s="44" t="s">
         <v>238</v>
       </c>
-      <c r="K9" s="63" t="s">
+      <c r="K9" s="61" t="s">
         <v>440</v>
       </c>
       <c r="L9" s="9"/>
     </row>
-    <row r="10" spans="1:12" ht="90">
+    <row r="10" spans="1:12" ht="30">
       <c r="A10" s="1" t="s">
         <v>133</v>
       </c>
@@ -4843,12 +5253,12 @@
       <c r="I29" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="K29" s="63" t="s">
+      <c r="K29" s="61" t="s">
         <v>460</v>
       </c>
     </row>
     <row r="30" spans="1:11">
-      <c r="A30" s="35" t="s">
+      <c r="A30" s="62" t="s">
         <v>52</v>
       </c>
       <c r="B30" s="12"/>
@@ -4865,118 +5275,219 @@
       </c>
     </row>
     <row r="31" spans="1:11">
-      <c r="A31" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="B31" s="9"/>
-      <c r="C31" s="27"/>
-      <c r="D31" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="K31" s="1" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" ht="67.5" customHeight="1">
-      <c r="A32" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="J32" s="44" t="s">
-        <v>239</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" ht="30">
-      <c r="A33" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="J33" s="44" t="s">
-        <v>180</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>464</v>
+      <c r="A31" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31" s="12"/>
+      <c r="C31" s="23">
+        <v>1</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>607</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I31" s="9" t="s">
+        <v>622</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="K31" s="61" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="B32" s="12"/>
+      <c r="C32" s="23">
+        <v>2</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>608</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>623</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="K32" s="61" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="B33" s="12"/>
+      <c r="C33" s="23">
+        <v>3</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>609</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>624</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="K33" s="61" t="s">
+        <v>640</v>
       </c>
     </row>
     <row r="34" spans="1:11">
-      <c r="A34" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="K34" s="1" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11">
-      <c r="A35" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I35" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="K35" s="1" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" ht="150">
-      <c r="A36" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="B36" s="9"/>
-      <c r="C36" s="27"/>
-      <c r="D36" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="J36" s="44" t="s">
-        <v>154</v>
-      </c>
-      <c r="K36" s="1" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" ht="60">
-      <c r="A37" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="B37" s="9"/>
-      <c r="C37" s="27">
+      <c r="A34" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="B34" s="12"/>
+      <c r="C34" s="23">
         <v>4</v>
       </c>
-      <c r="D37" s="1" t="s">
-        <v>164</v>
+      <c r="D34" s="9" t="s">
+        <v>610</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I34" s="9" t="s">
+        <v>625</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="K34" s="61" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="53.25" customHeight="1">
+      <c r="A35" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="B35" s="12"/>
+      <c r="C35" s="23">
+        <v>5</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>611</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I35" s="9" t="s">
+        <v>626</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="K35" s="61" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="45">
+      <c r="A36" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="B36" s="12"/>
+      <c r="C36" s="23">
+        <v>6</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>587</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>588</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="K36" s="61" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="B37" s="12"/>
+      <c r="C37" s="23">
+        <v>7</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>567</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>165</v>
+        <v>237</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>266</v>
+        <v>307</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>267</v>
@@ -4984,32 +5495,32 @@
       <c r="H37" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="I37" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="J37" s="44" t="s">
-        <v>269</v>
+      <c r="I37" s="9" t="s">
+        <v>575</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>590</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" ht="45">
-      <c r="A38" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="B38" s="9"/>
-      <c r="C38" s="27">
-        <v>5</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>283</v>
+        <v>583</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="B38" s="12"/>
+      <c r="C38" s="23">
+        <v>8</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>566</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>271</v>
+        <v>237</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>272</v>
+        <v>307</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>267</v>
@@ -5017,32 +5528,32 @@
       <c r="H38" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="I38" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="J38" s="44" t="s">
-        <v>279</v>
+      <c r="I38" s="9" t="s">
+        <v>574</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>590</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" ht="90">
-      <c r="A39" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="B39" s="9"/>
-      <c r="C39" s="27">
-        <v>8</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>270</v>
+        <v>582</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="B39" s="12"/>
+      <c r="C39" s="23">
+        <v>9</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>568</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>237</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>272</v>
+        <v>307</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>267</v>
@@ -5050,32 +5561,32 @@
       <c r="H39" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="I39" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="J39" s="44" t="s">
-        <v>274</v>
+      <c r="I39" s="9" t="s">
+        <v>576</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>590</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" ht="90">
-      <c r="A40" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="B40" s="9"/>
-      <c r="C40" s="27">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="B40" s="12"/>
+      <c r="C40" s="23">
         <v>10</v>
       </c>
-      <c r="D40" s="1" t="s">
-        <v>275</v>
+      <c r="D40" s="9" t="s">
+        <v>569</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>237</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>272</v>
+        <v>307</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>267</v>
@@ -5083,32 +5594,32 @@
       <c r="H40" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="I40" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="J40" s="44" t="s">
-        <v>280</v>
+      <c r="I40" s="9" t="s">
+        <v>577</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>590</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" ht="90">
-      <c r="A41" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="B41" s="9"/>
-      <c r="C41" s="27">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="B41" s="12"/>
+      <c r="C41" s="23">
         <v>12</v>
       </c>
-      <c r="D41" s="1" t="s">
-        <v>278</v>
+      <c r="D41" s="9" t="s">
+        <v>565</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>237</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>272</v>
+        <v>307</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>267</v>
@@ -5116,32 +5627,32 @@
       <c r="H41" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="I41" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="J41" s="44" t="s">
-        <v>281</v>
+      <c r="I41" s="9" t="s">
+        <v>573</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>590</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" ht="60">
-      <c r="A42" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="B42" s="9"/>
-      <c r="C42" s="27">
-        <v>14</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>284</v>
+        <v>581</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="B42" s="12"/>
+      <c r="C42" s="23">
+        <v>13</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>570</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>165</v>
+        <v>237</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>266</v>
+        <v>307</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>267</v>
@@ -5149,32 +5660,32 @@
       <c r="H42" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="I42" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="J42" s="44" t="s">
-        <v>286</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" ht="45">
-      <c r="A43" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="B43" s="9"/>
-      <c r="C43" s="27">
-        <v>16</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>287</v>
+      <c r="I42" s="9" t="s">
+        <v>578</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="K42" s="61" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="B43" s="12"/>
+      <c r="C43" s="23">
+        <v>14</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>563</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>237</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>266</v>
+        <v>307</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>267</v>
@@ -5182,32 +5693,32 @@
       <c r="H43" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="I43" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="J43" s="44" t="s">
-        <v>299</v>
+      <c r="I43" s="9" t="s">
+        <v>571</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>590</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" ht="45">
-      <c r="A44" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="B44" s="9"/>
-      <c r="C44" s="27">
-        <v>19</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>290</v>
+        <v>579</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="B44" s="12"/>
+      <c r="C44" s="23">
+        <v>15</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>564</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>161</v>
+        <v>237</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>266</v>
+        <v>307</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>267</v>
@@ -5215,32 +5726,32 @@
       <c r="H44" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="I44" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="J44" s="44" t="s">
-        <v>289</v>
+      <c r="I44" s="9" t="s">
+        <v>572</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>590</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" ht="45">
-      <c r="A45" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="B45" s="9"/>
-      <c r="C45" s="27">
-        <v>23</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>292</v>
+        <v>580</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45" s="12"/>
+      <c r="C45" s="23">
+        <v>16</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>649</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>237</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>272</v>
+        <v>307</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>267</v>
@@ -5248,32 +5759,32 @@
       <c r="H45" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="I45" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="J45" s="44" t="s">
-        <v>293</v>
-      </c>
-      <c r="K45" s="1" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" ht="45">
-      <c r="A46" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="B46" s="9"/>
-      <c r="C46" s="27">
-        <v>24</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>123</v>
+      <c r="I45" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="K45" s="61" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="B46" s="12"/>
+      <c r="C46" s="23">
+        <v>17</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>648</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>124</v>
+        <v>550</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>291</v>
+        <v>307</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>267</v>
@@ -5281,32 +5792,32 @@
       <c r="H46" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="I46" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="J46" s="44" t="s">
-        <v>298</v>
-      </c>
-      <c r="K46" s="1" t="s">
-        <v>475</v>
+      <c r="I46" s="9" t="s">
+        <v>643</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="K46" s="61" t="s">
+        <v>674</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="45">
-      <c r="A47" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="B47" s="9"/>
-      <c r="C47" s="27">
-        <v>31</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>294</v>
+      <c r="A47" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="B47" s="12"/>
+      <c r="C47" s="23">
+        <v>18</v>
+      </c>
+      <c r="D47" s="33" t="s">
+        <v>549</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>237</v>
+        <v>550</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>266</v>
+        <v>320</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>267</v>
@@ -5314,32 +5825,32 @@
       <c r="H47" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="I47" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="J47" s="44" t="s">
-        <v>305</v>
-      </c>
-      <c r="K47" s="63" t="s">
-        <v>477</v>
+      <c r="I47" s="9" t="s">
+        <v>551</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>556</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="45">
-      <c r="A48" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="B48" s="9"/>
-      <c r="C48" s="27">
-        <v>33</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>296</v>
+      <c r="A48" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="B48" s="12"/>
+      <c r="C48" s="23">
+        <v>19</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>545</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>237</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>307</v>
+        <v>266</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>267</v>
@@ -5347,32 +5858,32 @@
       <c r="H48" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="I48" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="J48" s="44" t="s">
-        <v>297</v>
+      <c r="I48" s="9" t="s">
+        <v>546</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>594</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" ht="45">
-      <c r="A49" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="B49" s="9"/>
-      <c r="C49" s="27">
-        <v>34</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>300</v>
+        <v>557</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="60">
+      <c r="A49" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="B49" s="12"/>
+      <c r="C49" s="23">
+        <v>20</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>547</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>237</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>301</v>
+        <v>320</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>267</v>
@@ -5380,48 +5891,61 @@
       <c r="H49" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="I49" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="J49" s="44" t="s">
-        <v>304</v>
+      <c r="I49" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>593</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" ht="60">
-      <c r="A50" s="50" t="s">
-        <v>94</v>
-      </c>
-      <c r="B50" s="50"/>
-      <c r="C50" s="51"/>
-      <c r="D50" s="41" t="s">
-        <v>26</v>
-      </c>
-      <c r="E50" s="41"/>
-      <c r="I50" s="41" t="s">
-        <v>169</v>
-      </c>
-      <c r="J50" s="52" t="s">
-        <v>241</v>
-      </c>
-      <c r="K50" s="1" t="s">
-        <v>480</v>
+        <v>558</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="B50" s="12"/>
+      <c r="C50" s="23">
+        <v>21</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>658</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I50" s="9" t="s">
+        <v>659</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="K50" s="61" t="s">
+        <v>667</v>
       </c>
     </row>
     <row r="51" spans="1:11">
-      <c r="A51" s="50" t="s">
-        <v>94</v>
-      </c>
-      <c r="B51" s="50"/>
-      <c r="C51" s="51">
-        <v>3</v>
-      </c>
-      <c r="D51" s="41" t="s">
-        <v>198</v>
-      </c>
-      <c r="E51" s="41" t="s">
+      <c r="A51" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="B51" s="12"/>
+      <c r="C51" s="23">
+        <v>22</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>662</v>
+      </c>
+      <c r="E51" s="1" t="s">
         <v>237</v>
       </c>
       <c r="F51" s="1" t="s">
@@ -5433,32 +5957,32 @@
       <c r="H51" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="I51" s="41" t="s">
-        <v>525</v>
-      </c>
-      <c r="J51" s="52" t="s">
-        <v>200</v>
-      </c>
-      <c r="K51" s="1" t="s">
-        <v>481</v>
+      <c r="I51" s="9" t="s">
+        <v>664</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="K51" s="61" t="s">
+        <v>668</v>
       </c>
     </row>
     <row r="52" spans="1:11">
-      <c r="A52" s="50" t="s">
-        <v>94</v>
-      </c>
-      <c r="B52" s="50"/>
-      <c r="C52" s="51">
-        <v>4</v>
-      </c>
-      <c r="D52" s="41" t="s">
-        <v>195</v>
-      </c>
-      <c r="E52" s="41" t="s">
-        <v>237</v>
+      <c r="A52" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="B52" s="12"/>
+      <c r="C52" s="23">
+        <v>23</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>663</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>550</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>266</v>
+        <v>307</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>267</v>
@@ -5466,28 +5990,28 @@
       <c r="H52" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="I52" s="41" t="s">
-        <v>526</v>
-      </c>
-      <c r="J52" s="52" t="s">
-        <v>196</v>
-      </c>
-      <c r="K52" s="1" t="s">
-        <v>482</v>
+      <c r="I52" s="9" t="s">
+        <v>665</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="K52" s="61" t="s">
+        <v>669</v>
       </c>
     </row>
     <row r="53" spans="1:11">
-      <c r="A53" s="50" t="s">
-        <v>94</v>
-      </c>
-      <c r="B53" s="50"/>
-      <c r="C53" s="51">
-        <v>15</v>
-      </c>
-      <c r="D53" s="41" t="s">
-        <v>192</v>
-      </c>
-      <c r="E53" s="41" t="s">
+      <c r="A53" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="B53" s="12"/>
+      <c r="C53" s="23">
+        <v>24</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>647</v>
+      </c>
+      <c r="E53" s="1" t="s">
         <v>237</v>
       </c>
       <c r="F53" s="1" t="s">
@@ -5499,70 +6023,94 @@
       <c r="H53" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="I53" s="41" t="s">
-        <v>527</v>
-      </c>
-      <c r="J53" s="52" t="s">
-        <v>193</v>
-      </c>
-      <c r="K53" s="1" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" ht="75">
-      <c r="A54" s="50" t="s">
-        <v>94</v>
-      </c>
-      <c r="B54" s="50"/>
-      <c r="C54" s="51"/>
-      <c r="D54" s="41" t="s">
-        <v>189</v>
-      </c>
-      <c r="E54" s="41" t="s">
-        <v>190</v>
-      </c>
-      <c r="I54" s="41" t="s">
-        <v>218</v>
-      </c>
-      <c r="J54" s="52" t="s">
-        <v>217</v>
-      </c>
-      <c r="K54" s="1" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" ht="60">
-      <c r="A55" s="50" t="s">
-        <v>96</v>
-      </c>
-      <c r="B55" s="50"/>
-      <c r="C55" s="51"/>
-      <c r="D55" s="41" t="s">
+      <c r="I53" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="K53" s="61" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11">
+      <c r="A54" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="B54" s="12"/>
+      <c r="C54" s="23">
+        <v>25</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I54" s="9" t="s">
+        <v>654</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="K54" s="61" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11">
+      <c r="A55" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="B55" s="12"/>
+      <c r="C55" s="23">
         <v>26</v>
       </c>
-      <c r="E55" s="41"/>
-      <c r="I55" s="41" t="s">
-        <v>169</v>
-      </c>
-      <c r="J55" s="52" t="s">
-        <v>241</v>
-      </c>
-      <c r="K55" s="1" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11">
-      <c r="A56" s="50" t="s">
-        <v>96</v>
-      </c>
-      <c r="B56" s="50"/>
-      <c r="C56" s="51">
-        <v>3</v>
-      </c>
-      <c r="D56" s="41" t="s">
-        <v>198</v>
-      </c>
-      <c r="E56" s="41" t="s">
+      <c r="D55" s="9" t="s">
+        <v>652</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I55" s="9" t="s">
+        <v>656</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="K55" s="61" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="45">
+      <c r="A56" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="B56" s="12"/>
+      <c r="C56" s="23">
+        <v>27</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>552</v>
+      </c>
+      <c r="E56" s="1" t="s">
         <v>237</v>
       </c>
       <c r="F56" s="1" t="s">
@@ -5574,32 +6122,32 @@
       <c r="H56" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="I56" s="41" t="s">
-        <v>528</v>
-      </c>
-      <c r="J56" s="52" t="s">
-        <v>200</v>
+      <c r="I56" s="9" t="s">
+        <v>553</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>592</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11">
-      <c r="A57" s="50" t="s">
-        <v>96</v>
-      </c>
-      <c r="B57" s="50"/>
-      <c r="C57" s="51">
-        <v>4</v>
-      </c>
-      <c r="D57" s="41" t="s">
-        <v>195</v>
-      </c>
-      <c r="E57" s="41" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="45">
+      <c r="A57" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="B57" s="12"/>
+      <c r="C57" s="23">
+        <v>28</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>554</v>
+      </c>
+      <c r="E57" s="1" t="s">
         <v>237</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>266</v>
+        <v>307</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>267</v>
@@ -5607,32 +6155,32 @@
       <c r="H57" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="I57" s="41" t="s">
-        <v>529</v>
-      </c>
-      <c r="J57" s="52" t="s">
-        <v>196</v>
+      <c r="I57" s="9" t="s">
+        <v>555</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>591</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>487</v>
+        <v>560</v>
       </c>
     </row>
     <row r="58" spans="1:11">
-      <c r="A58" s="50" t="s">
-        <v>96</v>
-      </c>
-      <c r="B58" s="50"/>
-      <c r="C58" s="51">
-        <v>15</v>
-      </c>
-      <c r="D58" s="41" t="s">
-        <v>192</v>
-      </c>
-      <c r="E58" s="41" t="s">
+      <c r="A58" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="B58" s="12"/>
+      <c r="C58" s="23">
+        <v>30</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>597</v>
+      </c>
+      <c r="E58" s="1" t="s">
         <v>237</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>266</v>
+        <v>307</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>267</v>
@@ -5640,70 +6188,94 @@
       <c r="H58" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="I58" s="41" t="s">
-        <v>530</v>
-      </c>
-      <c r="J58" s="52" t="s">
-        <v>193</v>
-      </c>
-      <c r="K58" s="1" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" ht="75">
-      <c r="A59" s="50" t="s">
-        <v>96</v>
-      </c>
-      <c r="B59" s="50"/>
-      <c r="C59" s="51"/>
-      <c r="D59" s="41" t="s">
-        <v>189</v>
-      </c>
-      <c r="E59" s="41" t="s">
-        <v>190</v>
-      </c>
-      <c r="I59" s="41" t="s">
-        <v>218</v>
-      </c>
-      <c r="J59" s="52" t="s">
-        <v>217</v>
-      </c>
-      <c r="K59" s="1" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" ht="60">
-      <c r="A60" s="50" t="s">
-        <v>97</v>
-      </c>
-      <c r="B60" s="50"/>
-      <c r="C60" s="51"/>
-      <c r="D60" s="41" t="s">
-        <v>26</v>
-      </c>
-      <c r="E60" s="41"/>
-      <c r="I60" s="41" t="s">
-        <v>169</v>
-      </c>
-      <c r="J60" s="52" t="s">
-        <v>241</v>
-      </c>
-      <c r="K60" s="1" t="s">
-        <v>490</v>
+      <c r="I58" s="9" t="s">
+        <v>612</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="K58" s="61" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11">
+      <c r="A59" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="B59" s="12"/>
+      <c r="C59" s="23">
+        <v>31</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>598</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I59" s="9" t="s">
+        <v>613</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="K59" s="61" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11">
+      <c r="A60" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="B60" s="12"/>
+      <c r="C60" s="23">
+        <v>32</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>599</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I60" s="9" t="s">
+        <v>614</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="K60" s="61" t="s">
+        <v>629</v>
       </c>
     </row>
     <row r="61" spans="1:11">
-      <c r="A61" s="50" t="s">
-        <v>97</v>
-      </c>
-      <c r="B61" s="50"/>
-      <c r="C61" s="51">
-        <v>3</v>
-      </c>
-      <c r="D61" s="41" t="s">
-        <v>198</v>
-      </c>
-      <c r="E61" s="41" t="s">
+      <c r="A61" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="B61" s="12"/>
+      <c r="C61" s="23">
+        <v>33</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>600</v>
+      </c>
+      <c r="E61" s="1" t="s">
         <v>237</v>
       </c>
       <c r="F61" s="1" t="s">
@@ -5715,32 +6287,32 @@
       <c r="H61" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="I61" s="41" t="s">
-        <v>531</v>
-      </c>
-      <c r="J61" s="52" t="s">
-        <v>200</v>
-      </c>
-      <c r="K61" s="1" t="s">
-        <v>491</v>
+      <c r="I61" s="9" t="s">
+        <v>615</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="K61" s="61" t="s">
+        <v>630</v>
       </c>
     </row>
     <row r="62" spans="1:11">
-      <c r="A62" s="50" t="s">
-        <v>97</v>
-      </c>
-      <c r="B62" s="50"/>
-      <c r="C62" s="51">
-        <v>4</v>
-      </c>
-      <c r="D62" s="41" t="s">
-        <v>195</v>
-      </c>
-      <c r="E62" s="41" t="s">
+      <c r="A62" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="B62" s="12"/>
+      <c r="C62" s="23">
+        <v>34</v>
+      </c>
+      <c r="D62" s="9" t="s">
+        <v>601</v>
+      </c>
+      <c r="E62" s="1" t="s">
         <v>237</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>266</v>
+        <v>307</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>267</v>
@@ -5748,32 +6320,32 @@
       <c r="H62" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="I62" s="41" t="s">
-        <v>532</v>
-      </c>
-      <c r="J62" s="52" t="s">
-        <v>196</v>
-      </c>
-      <c r="K62" s="1" t="s">
-        <v>492</v>
+      <c r="I62" s="9" t="s">
+        <v>616</v>
+      </c>
+      <c r="J62" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="K62" s="61" t="s">
+        <v>631</v>
       </c>
     </row>
     <row r="63" spans="1:11">
-      <c r="A63" s="50" t="s">
-        <v>97</v>
-      </c>
-      <c r="B63" s="50"/>
-      <c r="C63" s="51">
-        <v>15</v>
-      </c>
-      <c r="D63" s="41" t="s">
-        <v>192</v>
-      </c>
-      <c r="E63" s="41" t="s">
+      <c r="A63" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="B63" s="12"/>
+      <c r="C63" s="23">
+        <v>35</v>
+      </c>
+      <c r="D63" s="9" t="s">
+        <v>602</v>
+      </c>
+      <c r="E63" s="1" t="s">
         <v>237</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>266</v>
+        <v>307</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>267</v>
@@ -5781,70 +6353,94 @@
       <c r="H63" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="I63" s="41" t="s">
-        <v>533</v>
-      </c>
-      <c r="J63" s="52" t="s">
-        <v>193</v>
-      </c>
-      <c r="K63" s="1" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" ht="75">
-      <c r="A64" s="50" t="s">
-        <v>97</v>
-      </c>
-      <c r="B64" s="50"/>
-      <c r="C64" s="51"/>
-      <c r="D64" s="41" t="s">
-        <v>189</v>
-      </c>
-      <c r="E64" s="41" t="s">
-        <v>190</v>
-      </c>
-      <c r="I64" s="41" t="s">
-        <v>218</v>
-      </c>
-      <c r="J64" s="52" t="s">
-        <v>217</v>
-      </c>
-      <c r="K64" s="1" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" ht="60">
-      <c r="A65" s="50" t="s">
-        <v>98</v>
-      </c>
-      <c r="B65" s="50"/>
-      <c r="C65" s="51"/>
-      <c r="D65" s="41" t="s">
-        <v>26</v>
-      </c>
-      <c r="E65" s="41"/>
-      <c r="I65" s="41" t="s">
-        <v>169</v>
-      </c>
-      <c r="J65" s="52" t="s">
-        <v>241</v>
-      </c>
-      <c r="K65" s="1" t="s">
-        <v>495</v>
+      <c r="I63" s="9" t="s">
+        <v>617</v>
+      </c>
+      <c r="J63" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="K63" s="61" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11">
+      <c r="A64" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="B64" s="12"/>
+      <c r="C64" s="23">
+        <v>36</v>
+      </c>
+      <c r="D64" s="9" t="s">
+        <v>603</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I64" s="9" t="s">
+        <v>618</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="K64" s="61" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11">
+      <c r="A65" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="B65" s="12"/>
+      <c r="C65" s="23">
+        <v>37</v>
+      </c>
+      <c r="D65" s="9" t="s">
+        <v>604</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I65" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="K65" s="61" t="s">
+        <v>634</v>
       </c>
     </row>
     <row r="66" spans="1:11">
-      <c r="A66" s="50" t="s">
-        <v>98</v>
-      </c>
-      <c r="B66" s="50"/>
-      <c r="C66" s="51">
-        <v>3</v>
-      </c>
-      <c r="D66" s="41" t="s">
-        <v>198</v>
-      </c>
-      <c r="E66" s="41" t="s">
+      <c r="A66" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="B66" s="12"/>
+      <c r="C66" s="23">
+        <v>38</v>
+      </c>
+      <c r="D66" s="9" t="s">
+        <v>605</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>237</v>
       </c>
       <c r="F66" s="1" t="s">
@@ -5856,32 +6452,32 @@
       <c r="H66" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="I66" s="41" t="s">
-        <v>199</v>
-      </c>
-      <c r="J66" s="52" t="s">
-        <v>200</v>
-      </c>
-      <c r="K66" s="1" t="s">
-        <v>496</v>
+      <c r="I66" s="9" t="s">
+        <v>620</v>
+      </c>
+      <c r="J66" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="K66" s="61" t="s">
+        <v>635</v>
       </c>
     </row>
     <row r="67" spans="1:11">
-      <c r="A67" s="50" t="s">
-        <v>98</v>
-      </c>
-      <c r="B67" s="50"/>
-      <c r="C67" s="51">
-        <v>4</v>
-      </c>
-      <c r="D67" s="41" t="s">
-        <v>195</v>
-      </c>
-      <c r="E67" s="41" t="s">
+      <c r="A67" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="B67" s="12"/>
+      <c r="C67" s="23">
+        <v>39</v>
+      </c>
+      <c r="D67" s="9" t="s">
+        <v>606</v>
+      </c>
+      <c r="E67" s="1" t="s">
         <v>237</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>266</v>
+        <v>307</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>267</v>
@@ -5889,32 +6485,32 @@
       <c r="H67" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="I67" s="41" t="s">
-        <v>197</v>
-      </c>
-      <c r="J67" s="52" t="s">
-        <v>196</v>
-      </c>
-      <c r="K67" s="1" t="s">
-        <v>497</v>
+      <c r="I67" s="9" t="s">
+        <v>621</v>
+      </c>
+      <c r="J67" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="K67" s="61" t="s">
+        <v>636</v>
       </c>
     </row>
     <row r="68" spans="1:11">
-      <c r="A68" s="50" t="s">
-        <v>98</v>
-      </c>
-      <c r="B68" s="50"/>
-      <c r="C68" s="51">
-        <v>15</v>
-      </c>
-      <c r="D68" s="41" t="s">
-        <v>192</v>
-      </c>
-      <c r="E68" s="41" t="s">
+      <c r="A68" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="B68" s="12"/>
+      <c r="C68" s="23">
+        <v>40</v>
+      </c>
+      <c r="D68" s="9" t="s">
+        <v>561</v>
+      </c>
+      <c r="E68" s="1" t="s">
         <v>237</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>266</v>
+        <v>307</v>
       </c>
       <c r="G68" s="1" t="s">
         <v>267</v>
@@ -5922,215 +6518,162 @@
       <c r="H68" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="I68" s="41" t="s">
-        <v>194</v>
-      </c>
-      <c r="J68" s="52" t="s">
-        <v>193</v>
+      <c r="I68" s="9" t="s">
+        <v>562</v>
+      </c>
+      <c r="J68" s="1" t="s">
+        <v>590</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" ht="75">
-      <c r="A69" s="50" t="s">
-        <v>98</v>
-      </c>
-      <c r="B69" s="50"/>
-      <c r="C69" s="51"/>
-      <c r="D69" s="41" t="s">
-        <v>189</v>
-      </c>
-      <c r="E69" s="41" t="s">
-        <v>190</v>
-      </c>
-      <c r="I69" s="41" t="s">
-        <v>218</v>
-      </c>
-      <c r="J69" s="52" t="s">
-        <v>217</v>
+        <v>637</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11">
+      <c r="A69" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="B69" s="9"/>
+      <c r="C69" s="27"/>
+      <c r="D69" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>171</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" ht="60">
-      <c r="A70" s="50" t="s">
-        <v>99</v>
-      </c>
-      <c r="B70" s="50"/>
-      <c r="C70" s="51"/>
-      <c r="D70" s="41" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" ht="67.5" customHeight="1">
+      <c r="A70" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D70" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E70" s="41"/>
-      <c r="I70" s="41" t="s">
-        <v>169</v>
-      </c>
-      <c r="J70" s="52" t="s">
-        <v>241</v>
+      <c r="I70" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="J70" s="44" t="s">
+        <v>239</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11">
-      <c r="A71" s="50" t="s">
-        <v>99</v>
-      </c>
-      <c r="B71" s="50"/>
-      <c r="C71" s="51">
-        <v>3</v>
-      </c>
-      <c r="D71" s="41" t="s">
-        <v>198</v>
-      </c>
-      <c r="E71" s="41" t="s">
-        <v>237</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="G71" s="1" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" ht="30">
+      <c r="A71" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="J71" s="44" t="s">
+        <v>180</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11">
+      <c r="A72" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="K72" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11">
+      <c r="A73" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="K73" s="1" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" ht="150">
+      <c r="A74" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="B74" s="9"/>
+      <c r="C74" s="27"/>
+      <c r="D74" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="J74" s="44" t="s">
+        <v>154</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" ht="60">
+      <c r="A75" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="B75" s="9"/>
+      <c r="C75" s="27">
+        <v>4</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G75" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="H71" s="1" t="s">
+      <c r="H75" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="I71" s="41" t="s">
-        <v>534</v>
-      </c>
-      <c r="J71" s="52" t="s">
-        <v>200</v>
-      </c>
-      <c r="K71" s="1" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11">
-      <c r="A72" s="50" t="s">
-        <v>99</v>
-      </c>
-      <c r="B72" s="50"/>
-      <c r="C72" s="51">
-        <v>4</v>
-      </c>
-      <c r="D72" s="41" t="s">
-        <v>195</v>
-      </c>
-      <c r="E72" s="41" t="s">
-        <v>237</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="G72" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="H72" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="I72" s="41" t="s">
-        <v>535</v>
-      </c>
-      <c r="J72" s="52" t="s">
-        <v>196</v>
-      </c>
-      <c r="K72" s="1" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11">
-      <c r="A73" s="50" t="s">
-        <v>99</v>
-      </c>
-      <c r="B73" s="50"/>
-      <c r="C73" s="51">
-        <v>15</v>
-      </c>
-      <c r="D73" s="41" t="s">
-        <v>192</v>
-      </c>
-      <c r="E73" s="41" t="s">
-        <v>237</v>
-      </c>
-      <c r="F73" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="G73" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="H73" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="I73" s="41" t="s">
-        <v>536</v>
-      </c>
-      <c r="J73" s="52" t="s">
-        <v>193</v>
-      </c>
-      <c r="K73" s="1" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" ht="75">
-      <c r="A74" s="50" t="s">
-        <v>99</v>
-      </c>
-      <c r="B74" s="50"/>
-      <c r="C74" s="51"/>
-      <c r="D74" s="41" t="s">
-        <v>189</v>
-      </c>
-      <c r="E74" s="41" t="s">
-        <v>190</v>
-      </c>
-      <c r="I74" s="41" t="s">
-        <v>218</v>
-      </c>
-      <c r="J74" s="52" t="s">
-        <v>217</v>
-      </c>
-      <c r="K74" s="1" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" ht="60">
-      <c r="A75" s="50" t="s">
-        <v>100</v>
-      </c>
-      <c r="B75" s="50"/>
-      <c r="C75" s="51"/>
-      <c r="D75" s="41" t="s">
-        <v>26</v>
-      </c>
-      <c r="E75" s="41"/>
-      <c r="I75" s="41" t="s">
-        <v>169</v>
-      </c>
-      <c r="J75" s="52" t="s">
-        <v>241</v>
+      <c r="I75" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="J75" s="44" t="s">
+        <v>269</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11">
-      <c r="A76" s="50" t="s">
-        <v>100</v>
-      </c>
-      <c r="B76" s="50"/>
-      <c r="C76" s="51">
-        <v>3</v>
-      </c>
-      <c r="D76" s="41" t="s">
-        <v>198</v>
-      </c>
-      <c r="E76" s="41" t="s">
-        <v>237</v>
+        <v>468</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" ht="45">
+      <c r="A76" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="B76" s="9"/>
+      <c r="C76" s="27">
+        <v>5</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>271</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>307</v>
+        <v>272</v>
       </c>
       <c r="G76" s="1" t="s">
         <v>267</v>
@@ -6138,32 +6681,32 @@
       <c r="H76" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="I76" s="41" t="s">
-        <v>537</v>
-      </c>
-      <c r="J76" s="52" t="s">
-        <v>200</v>
+      <c r="I76" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="J76" s="44" t="s">
+        <v>279</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11">
-      <c r="A77" s="50" t="s">
-        <v>100</v>
-      </c>
-      <c r="B77" s="50"/>
-      <c r="C77" s="51">
-        <v>4</v>
-      </c>
-      <c r="D77" s="41" t="s">
-        <v>195</v>
-      </c>
-      <c r="E77" s="41" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" ht="90">
+      <c r="A77" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="B77" s="9"/>
+      <c r="C77" s="27">
+        <v>8</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="E77" s="1" t="s">
         <v>237</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="G77" s="1" t="s">
         <v>267</v>
@@ -6171,32 +6714,32 @@
       <c r="H77" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="I77" s="41" t="s">
-        <v>538</v>
-      </c>
-      <c r="J77" s="52" t="s">
-        <v>196</v>
+      <c r="I77" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="J77" s="44" t="s">
+        <v>274</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11">
-      <c r="A78" s="50" t="s">
-        <v>100</v>
-      </c>
-      <c r="B78" s="50"/>
-      <c r="C78" s="51">
-        <v>15</v>
-      </c>
-      <c r="D78" s="41" t="s">
-        <v>192</v>
-      </c>
-      <c r="E78" s="41" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" ht="90">
+      <c r="A78" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="B78" s="9"/>
+      <c r="C78" s="27">
+        <v>10</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="E78" s="1" t="s">
         <v>237</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="G78" s="1" t="s">
         <v>267</v>
@@ -6204,74 +6747,98 @@
       <c r="H78" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="I78" s="41" t="s">
-        <v>539</v>
-      </c>
-      <c r="J78" s="52" t="s">
-        <v>193</v>
+      <c r="I78" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="J78" s="44" t="s">
+        <v>280</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" ht="75">
-      <c r="A79" s="50" t="s">
-        <v>100</v>
-      </c>
-      <c r="B79" s="50"/>
-      <c r="C79" s="51"/>
-      <c r="D79" s="41" t="s">
-        <v>189</v>
-      </c>
-      <c r="E79" s="41" t="s">
-        <v>190</v>
-      </c>
-      <c r="I79" s="41" t="s">
-        <v>218</v>
-      </c>
-      <c r="J79" s="52" t="s">
-        <v>217</v>
+        <v>472</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" ht="90">
+      <c r="A79" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="B79" s="9"/>
+      <c r="C79" s="27">
+        <v>12</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="J79" s="44" t="s">
+        <v>281</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>509</v>
+        <v>473</v>
       </c>
     </row>
     <row r="80" spans="1:11" ht="60">
-      <c r="A80" s="50" t="s">
-        <v>101</v>
-      </c>
-      <c r="B80" s="50"/>
-      <c r="C80" s="51"/>
-      <c r="D80" s="41" t="s">
-        <v>26</v>
-      </c>
-      <c r="E80" s="41"/>
-      <c r="I80" s="41" t="s">
-        <v>169</v>
-      </c>
-      <c r="J80" s="52" t="s">
-        <v>241</v>
+      <c r="A80" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="B80" s="9"/>
+      <c r="C80" s="27">
+        <v>14</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="J80" s="44" t="s">
+        <v>286</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11">
-      <c r="A81" s="50" t="s">
-        <v>101</v>
-      </c>
-      <c r="B81" s="50"/>
-      <c r="C81" s="51">
-        <v>3</v>
-      </c>
-      <c r="D81" s="41" t="s">
-        <v>198</v>
-      </c>
-      <c r="E81" s="41" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" ht="45">
+      <c r="A81" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="B81" s="9"/>
+      <c r="C81" s="27">
+        <v>16</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E81" s="1" t="s">
         <v>237</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>307</v>
+        <v>266</v>
       </c>
       <c r="G81" s="1" t="s">
         <v>267</v>
@@ -6279,29 +6846,29 @@
       <c r="H81" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="I81" s="41" t="s">
-        <v>540</v>
-      </c>
-      <c r="J81" s="52" t="s">
-        <v>200</v>
+      <c r="I81" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="J81" s="44" t="s">
+        <v>299</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11">
-      <c r="A82" s="50" t="s">
-        <v>101</v>
-      </c>
-      <c r="B82" s="50"/>
-      <c r="C82" s="51">
-        <v>4</v>
-      </c>
-      <c r="D82" s="41" t="s">
-        <v>195</v>
-      </c>
-      <c r="E82" s="41" t="s">
-        <v>237</v>
+        <v>523</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" ht="45">
+      <c r="A82" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="B82" s="9"/>
+      <c r="C82" s="27">
+        <v>19</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>161</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>266</v>
@@ -6312,32 +6879,32 @@
       <c r="H82" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="I82" s="41" t="s">
-        <v>541</v>
-      </c>
-      <c r="J82" s="52" t="s">
-        <v>196</v>
+      <c r="I82" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="J82" s="44" t="s">
+        <v>289</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11">
-      <c r="A83" s="50" t="s">
-        <v>101</v>
-      </c>
-      <c r="B83" s="50"/>
-      <c r="C83" s="51">
-        <v>15</v>
-      </c>
-      <c r="D83" s="41" t="s">
-        <v>192</v>
-      </c>
-      <c r="E83" s="41" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" ht="45">
+      <c r="A83" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="B83" s="9"/>
+      <c r="C83" s="27">
+        <v>23</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="E83" s="1" t="s">
         <v>237</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="G83" s="1" t="s">
         <v>267</v>
@@ -6345,70 +6912,94 @@
       <c r="H83" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="I83" s="41" t="s">
-        <v>542</v>
-      </c>
-      <c r="J83" s="52" t="s">
-        <v>193</v>
+      <c r="I83" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="J83" s="44" t="s">
+        <v>293</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11" ht="75">
-      <c r="A84" s="50" t="s">
-        <v>101</v>
-      </c>
-      <c r="B84" s="50"/>
-      <c r="C84" s="51"/>
-      <c r="D84" s="41" t="s">
-        <v>189</v>
-      </c>
-      <c r="E84" s="41" t="s">
-        <v>190</v>
-      </c>
-      <c r="I84" s="41" t="s">
-        <v>218</v>
-      </c>
-      <c r="J84" s="52" t="s">
-        <v>217</v>
+        <v>476</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" ht="45">
+      <c r="A84" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="B84" s="9"/>
+      <c r="C84" s="27">
+        <v>24</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="J84" s="44" t="s">
+        <v>298</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11" ht="60">
-      <c r="A85" s="50" t="s">
-        <v>102</v>
-      </c>
-      <c r="B85" s="50"/>
-      <c r="C85" s="51"/>
-      <c r="D85" s="41" t="s">
-        <v>26</v>
-      </c>
-      <c r="E85" s="41"/>
-      <c r="I85" s="41" t="s">
-        <v>169</v>
-      </c>
-      <c r="J85" s="52" t="s">
-        <v>241</v>
-      </c>
-      <c r="K85" s="1" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11">
-      <c r="A86" s="50" t="s">
-        <v>102</v>
-      </c>
-      <c r="B86" s="50"/>
-      <c r="C86" s="51">
-        <v>3</v>
-      </c>
-      <c r="D86" s="41" t="s">
-        <v>198</v>
-      </c>
-      <c r="E86" s="41" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" ht="45">
+      <c r="A85" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="B85" s="9"/>
+      <c r="C85" s="27">
+        <v>31</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="J85" s="44" t="s">
+        <v>305</v>
+      </c>
+      <c r="K85" s="61" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" ht="45">
+      <c r="A86" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="B86" s="9"/>
+      <c r="C86" s="27">
+        <v>33</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="E86" s="1" t="s">
         <v>237</v>
       </c>
       <c r="F86" s="1" t="s">
@@ -6420,32 +7011,32 @@
       <c r="H86" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="I86" s="41" t="s">
-        <v>543</v>
-      </c>
-      <c r="J86" s="52" t="s">
-        <v>200</v>
+      <c r="I86" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="J86" s="44" t="s">
+        <v>297</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11">
-      <c r="A87" s="50" t="s">
-        <v>102</v>
-      </c>
-      <c r="B87" s="50"/>
-      <c r="C87" s="51">
-        <v>4</v>
-      </c>
-      <c r="D87" s="41" t="s">
-        <v>195</v>
-      </c>
-      <c r="E87" s="41" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" ht="45">
+      <c r="A87" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="B87" s="9"/>
+      <c r="C87" s="27">
+        <v>34</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="E87" s="1" t="s">
         <v>237</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>266</v>
+        <v>301</v>
       </c>
       <c r="G87" s="1" t="s">
         <v>267</v>
@@ -6453,319 +7044,1240 @@
       <c r="H87" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="I87" s="41" t="s">
+      <c r="I87" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="J87" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="K87" s="1" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" ht="60">
+      <c r="A88" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="B88" s="50"/>
+      <c r="C88" s="51"/>
+      <c r="D88" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="E88" s="41"/>
+      <c r="I88" s="41" t="s">
+        <v>169</v>
+      </c>
+      <c r="J88" s="52" t="s">
+        <v>241</v>
+      </c>
+      <c r="K88" s="1" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11">
+      <c r="A89" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="B89" s="50"/>
+      <c r="C89" s="51">
+        <v>3</v>
+      </c>
+      <c r="D89" s="41" t="s">
+        <v>198</v>
+      </c>
+      <c r="E89" s="41" t="s">
+        <v>237</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I89" s="41" t="s">
+        <v>524</v>
+      </c>
+      <c r="J89" s="52" t="s">
+        <v>200</v>
+      </c>
+      <c r="K89" s="1" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11">
+      <c r="A90" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="B90" s="50"/>
+      <c r="C90" s="51">
+        <v>4</v>
+      </c>
+      <c r="D90" s="41" t="s">
+        <v>195</v>
+      </c>
+      <c r="E90" s="41" t="s">
+        <v>237</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I90" s="41" t="s">
+        <v>525</v>
+      </c>
+      <c r="J90" s="52" t="s">
+        <v>196</v>
+      </c>
+      <c r="K90" s="1" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11">
+      <c r="A91" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="B91" s="50"/>
+      <c r="C91" s="51">
+        <v>15</v>
+      </c>
+      <c r="D91" s="41" t="s">
+        <v>192</v>
+      </c>
+      <c r="E91" s="41" t="s">
+        <v>237</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I91" s="41" t="s">
+        <v>526</v>
+      </c>
+      <c r="J91" s="52" t="s">
+        <v>193</v>
+      </c>
+      <c r="K91" s="1" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" ht="75">
+      <c r="A92" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="B92" s="50"/>
+      <c r="C92" s="51"/>
+      <c r="D92" s="41" t="s">
+        <v>189</v>
+      </c>
+      <c r="E92" s="41" t="s">
+        <v>190</v>
+      </c>
+      <c r="I92" s="41" t="s">
+        <v>218</v>
+      </c>
+      <c r="J92" s="52" t="s">
+        <v>217</v>
+      </c>
+      <c r="K92" s="1" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" ht="60">
+      <c r="A93" s="50" t="s">
+        <v>96</v>
+      </c>
+      <c r="B93" s="50"/>
+      <c r="C93" s="51"/>
+      <c r="D93" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="E93" s="41"/>
+      <c r="I93" s="41" t="s">
+        <v>169</v>
+      </c>
+      <c r="J93" s="52" t="s">
+        <v>241</v>
+      </c>
+      <c r="K93" s="1" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11">
+      <c r="A94" s="50" t="s">
+        <v>96</v>
+      </c>
+      <c r="B94" s="50"/>
+      <c r="C94" s="51">
+        <v>3</v>
+      </c>
+      <c r="D94" s="41" t="s">
+        <v>198</v>
+      </c>
+      <c r="E94" s="41" t="s">
+        <v>237</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I94" s="41" t="s">
+        <v>527</v>
+      </c>
+      <c r="J94" s="52" t="s">
+        <v>200</v>
+      </c>
+      <c r="K94" s="1" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11">
+      <c r="A95" s="50" t="s">
+        <v>96</v>
+      </c>
+      <c r="B95" s="50"/>
+      <c r="C95" s="51">
+        <v>4</v>
+      </c>
+      <c r="D95" s="41" t="s">
+        <v>195</v>
+      </c>
+      <c r="E95" s="41" t="s">
+        <v>237</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I95" s="41" t="s">
+        <v>528</v>
+      </c>
+      <c r="J95" s="52" t="s">
+        <v>196</v>
+      </c>
+      <c r="K95" s="1" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11">
+      <c r="A96" s="50" t="s">
+        <v>96</v>
+      </c>
+      <c r="B96" s="50"/>
+      <c r="C96" s="51">
+        <v>15</v>
+      </c>
+      <c r="D96" s="41" t="s">
+        <v>192</v>
+      </c>
+      <c r="E96" s="41" t="s">
+        <v>237</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H96" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I96" s="41" t="s">
+        <v>529</v>
+      </c>
+      <c r="J96" s="52" t="s">
+        <v>193</v>
+      </c>
+      <c r="K96" s="1" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" ht="75">
+      <c r="A97" s="50" t="s">
+        <v>96</v>
+      </c>
+      <c r="B97" s="50"/>
+      <c r="C97" s="51"/>
+      <c r="D97" s="41" t="s">
+        <v>189</v>
+      </c>
+      <c r="E97" s="41" t="s">
+        <v>190</v>
+      </c>
+      <c r="I97" s="41" t="s">
+        <v>218</v>
+      </c>
+      <c r="J97" s="52" t="s">
+        <v>217</v>
+      </c>
+      <c r="K97" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" ht="60">
+      <c r="A98" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B98" s="50"/>
+      <c r="C98" s="51"/>
+      <c r="D98" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="E98" s="41"/>
+      <c r="I98" s="41" t="s">
+        <v>169</v>
+      </c>
+      <c r="J98" s="52" t="s">
+        <v>241</v>
+      </c>
+      <c r="K98" s="1" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11">
+      <c r="A99" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B99" s="50"/>
+      <c r="C99" s="51">
+        <v>3</v>
+      </c>
+      <c r="D99" s="41" t="s">
+        <v>198</v>
+      </c>
+      <c r="E99" s="41" t="s">
+        <v>237</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H99" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I99" s="41" t="s">
+        <v>530</v>
+      </c>
+      <c r="J99" s="52" t="s">
+        <v>200</v>
+      </c>
+      <c r="K99" s="1" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11">
+      <c r="A100" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B100" s="50"/>
+      <c r="C100" s="51">
+        <v>4</v>
+      </c>
+      <c r="D100" s="41" t="s">
+        <v>195</v>
+      </c>
+      <c r="E100" s="41" t="s">
+        <v>237</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H100" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I100" s="41" t="s">
+        <v>531</v>
+      </c>
+      <c r="J100" s="52" t="s">
+        <v>196</v>
+      </c>
+      <c r="K100" s="1" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11">
+      <c r="A101" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B101" s="50"/>
+      <c r="C101" s="51">
+        <v>15</v>
+      </c>
+      <c r="D101" s="41" t="s">
+        <v>192</v>
+      </c>
+      <c r="E101" s="41" t="s">
+        <v>237</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H101" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I101" s="41" t="s">
+        <v>532</v>
+      </c>
+      <c r="J101" s="52" t="s">
+        <v>193</v>
+      </c>
+      <c r="K101" s="1" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" ht="75">
+      <c r="A102" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B102" s="50"/>
+      <c r="C102" s="51"/>
+      <c r="D102" s="41" t="s">
+        <v>189</v>
+      </c>
+      <c r="E102" s="41" t="s">
+        <v>190</v>
+      </c>
+      <c r="I102" s="41" t="s">
+        <v>218</v>
+      </c>
+      <c r="J102" s="52" t="s">
+        <v>217</v>
+      </c>
+      <c r="K102" s="1" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" ht="60">
+      <c r="A103" s="50" t="s">
+        <v>98</v>
+      </c>
+      <c r="B103" s="50"/>
+      <c r="C103" s="51"/>
+      <c r="D103" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="E103" s="41"/>
+      <c r="I103" s="41" t="s">
+        <v>169</v>
+      </c>
+      <c r="J103" s="52" t="s">
+        <v>241</v>
+      </c>
+      <c r="K103" s="1" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11">
+      <c r="A104" s="50" t="s">
+        <v>98</v>
+      </c>
+      <c r="B104" s="50"/>
+      <c r="C104" s="51">
+        <v>3</v>
+      </c>
+      <c r="D104" s="41" t="s">
+        <v>198</v>
+      </c>
+      <c r="E104" s="41" t="s">
+        <v>237</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H104" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I104" s="41" t="s">
+        <v>199</v>
+      </c>
+      <c r="J104" s="52" t="s">
+        <v>200</v>
+      </c>
+      <c r="K104" s="1" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11">
+      <c r="A105" s="50" t="s">
+        <v>98</v>
+      </c>
+      <c r="B105" s="50"/>
+      <c r="C105" s="51">
+        <v>4</v>
+      </c>
+      <c r="D105" s="41" t="s">
+        <v>195</v>
+      </c>
+      <c r="E105" s="41" t="s">
+        <v>237</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H105" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I105" s="41" t="s">
+        <v>197</v>
+      </c>
+      <c r="J105" s="52" t="s">
+        <v>196</v>
+      </c>
+      <c r="K105" s="1" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11">
+      <c r="A106" s="50" t="s">
+        <v>98</v>
+      </c>
+      <c r="B106" s="50"/>
+      <c r="C106" s="51">
+        <v>15</v>
+      </c>
+      <c r="D106" s="41" t="s">
+        <v>192</v>
+      </c>
+      <c r="E106" s="41" t="s">
+        <v>237</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H106" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I106" s="41" t="s">
+        <v>194</v>
+      </c>
+      <c r="J106" s="52" t="s">
+        <v>193</v>
+      </c>
+      <c r="K106" s="1" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" ht="75">
+      <c r="A107" s="50" t="s">
+        <v>98</v>
+      </c>
+      <c r="B107" s="50"/>
+      <c r="C107" s="51"/>
+      <c r="D107" s="41" t="s">
+        <v>189</v>
+      </c>
+      <c r="E107" s="41" t="s">
+        <v>190</v>
+      </c>
+      <c r="I107" s="41" t="s">
+        <v>218</v>
+      </c>
+      <c r="J107" s="52" t="s">
+        <v>217</v>
+      </c>
+      <c r="K107" s="1" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" ht="60">
+      <c r="A108" s="50" t="s">
+        <v>99</v>
+      </c>
+      <c r="B108" s="50"/>
+      <c r="C108" s="51"/>
+      <c r="D108" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="E108" s="41"/>
+      <c r="I108" s="41" t="s">
+        <v>169</v>
+      </c>
+      <c r="J108" s="52" t="s">
+        <v>241</v>
+      </c>
+      <c r="K108" s="1" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11">
+      <c r="A109" s="50" t="s">
+        <v>99</v>
+      </c>
+      <c r="B109" s="50"/>
+      <c r="C109" s="51">
+        <v>3</v>
+      </c>
+      <c r="D109" s="41" t="s">
+        <v>198</v>
+      </c>
+      <c r="E109" s="41" t="s">
+        <v>237</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H109" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I109" s="41" t="s">
+        <v>533</v>
+      </c>
+      <c r="J109" s="52" t="s">
+        <v>200</v>
+      </c>
+      <c r="K109" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11">
+      <c r="A110" s="50" t="s">
+        <v>99</v>
+      </c>
+      <c r="B110" s="50"/>
+      <c r="C110" s="51">
+        <v>4</v>
+      </c>
+      <c r="D110" s="41" t="s">
+        <v>195</v>
+      </c>
+      <c r="E110" s="41" t="s">
+        <v>237</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G110" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H110" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I110" s="41" t="s">
+        <v>534</v>
+      </c>
+      <c r="J110" s="52" t="s">
+        <v>196</v>
+      </c>
+      <c r="K110" s="1" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11">
+      <c r="A111" s="50" t="s">
+        <v>99</v>
+      </c>
+      <c r="B111" s="50"/>
+      <c r="C111" s="51">
+        <v>15</v>
+      </c>
+      <c r="D111" s="41" t="s">
+        <v>192</v>
+      </c>
+      <c r="E111" s="41" t="s">
+        <v>237</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H111" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I111" s="41" t="s">
+        <v>535</v>
+      </c>
+      <c r="J111" s="52" t="s">
+        <v>193</v>
+      </c>
+      <c r="K111" s="1" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" ht="75">
+      <c r="A112" s="50" t="s">
+        <v>99</v>
+      </c>
+      <c r="B112" s="50"/>
+      <c r="C112" s="51"/>
+      <c r="D112" s="41" t="s">
+        <v>189</v>
+      </c>
+      <c r="E112" s="41" t="s">
+        <v>190</v>
+      </c>
+      <c r="I112" s="41" t="s">
+        <v>218</v>
+      </c>
+      <c r="J112" s="52" t="s">
+        <v>217</v>
+      </c>
+      <c r="K112" s="1" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" ht="60">
+      <c r="A113" s="50" t="s">
+        <v>100</v>
+      </c>
+      <c r="B113" s="50"/>
+      <c r="C113" s="51"/>
+      <c r="D113" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="E113" s="41"/>
+      <c r="I113" s="41" t="s">
+        <v>169</v>
+      </c>
+      <c r="J113" s="52" t="s">
+        <v>241</v>
+      </c>
+      <c r="K113" s="1" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11">
+      <c r="A114" s="50" t="s">
+        <v>100</v>
+      </c>
+      <c r="B114" s="50"/>
+      <c r="C114" s="51">
+        <v>3</v>
+      </c>
+      <c r="D114" s="41" t="s">
+        <v>198</v>
+      </c>
+      <c r="E114" s="41" t="s">
+        <v>237</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="G114" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H114" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I114" s="41" t="s">
+        <v>536</v>
+      </c>
+      <c r="J114" s="52" t="s">
+        <v>200</v>
+      </c>
+      <c r="K114" s="1" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11">
+      <c r="A115" s="50" t="s">
+        <v>100</v>
+      </c>
+      <c r="B115" s="50"/>
+      <c r="C115" s="51">
+        <v>4</v>
+      </c>
+      <c r="D115" s="41" t="s">
+        <v>195</v>
+      </c>
+      <c r="E115" s="41" t="s">
+        <v>237</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G115" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H115" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I115" s="41" t="s">
+        <v>537</v>
+      </c>
+      <c r="J115" s="52" t="s">
+        <v>196</v>
+      </c>
+      <c r="K115" s="1" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11">
+      <c r="A116" s="50" t="s">
+        <v>100</v>
+      </c>
+      <c r="B116" s="50"/>
+      <c r="C116" s="51">
+        <v>15</v>
+      </c>
+      <c r="D116" s="41" t="s">
+        <v>192</v>
+      </c>
+      <c r="E116" s="41" t="s">
+        <v>237</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G116" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H116" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I116" s="41" t="s">
+        <v>538</v>
+      </c>
+      <c r="J116" s="52" t="s">
+        <v>193</v>
+      </c>
+      <c r="K116" s="1" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" ht="75">
+      <c r="A117" s="50" t="s">
+        <v>100</v>
+      </c>
+      <c r="B117" s="50"/>
+      <c r="C117" s="51"/>
+      <c r="D117" s="41" t="s">
+        <v>189</v>
+      </c>
+      <c r="E117" s="41" t="s">
+        <v>190</v>
+      </c>
+      <c r="I117" s="41" t="s">
+        <v>218</v>
+      </c>
+      <c r="J117" s="52" t="s">
+        <v>217</v>
+      </c>
+      <c r="K117" s="1" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" ht="60">
+      <c r="A118" s="50" t="s">
+        <v>101</v>
+      </c>
+      <c r="B118" s="50"/>
+      <c r="C118" s="51"/>
+      <c r="D118" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="E118" s="41"/>
+      <c r="I118" s="41" t="s">
+        <v>169</v>
+      </c>
+      <c r="J118" s="52" t="s">
+        <v>241</v>
+      </c>
+      <c r="K118" s="1" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11">
+      <c r="A119" s="50" t="s">
+        <v>101</v>
+      </c>
+      <c r="B119" s="50"/>
+      <c r="C119" s="51">
+        <v>3</v>
+      </c>
+      <c r="D119" s="41" t="s">
+        <v>198</v>
+      </c>
+      <c r="E119" s="41" t="s">
+        <v>237</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="G119" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H119" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I119" s="41" t="s">
+        <v>539</v>
+      </c>
+      <c r="J119" s="52" t="s">
+        <v>200</v>
+      </c>
+      <c r="K119" s="1" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11">
+      <c r="A120" s="50" t="s">
+        <v>101</v>
+      </c>
+      <c r="B120" s="50"/>
+      <c r="C120" s="51">
+        <v>4</v>
+      </c>
+      <c r="D120" s="41" t="s">
+        <v>195</v>
+      </c>
+      <c r="E120" s="41" t="s">
+        <v>237</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G120" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H120" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I120" s="41" t="s">
+        <v>540</v>
+      </c>
+      <c r="J120" s="52" t="s">
+        <v>196</v>
+      </c>
+      <c r="K120" s="1" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11">
+      <c r="A121" s="50" t="s">
+        <v>101</v>
+      </c>
+      <c r="B121" s="50"/>
+      <c r="C121" s="51">
+        <v>15</v>
+      </c>
+      <c r="D121" s="41" t="s">
+        <v>192</v>
+      </c>
+      <c r="E121" s="41" t="s">
+        <v>237</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G121" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H121" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I121" s="41" t="s">
+        <v>541</v>
+      </c>
+      <c r="J121" s="52" t="s">
+        <v>193</v>
+      </c>
+      <c r="K121" s="1" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" ht="75">
+      <c r="A122" s="50" t="s">
+        <v>101</v>
+      </c>
+      <c r="B122" s="50"/>
+      <c r="C122" s="51"/>
+      <c r="D122" s="41" t="s">
+        <v>189</v>
+      </c>
+      <c r="E122" s="41" t="s">
+        <v>190</v>
+      </c>
+      <c r="I122" s="41" t="s">
+        <v>218</v>
+      </c>
+      <c r="J122" s="52" t="s">
+        <v>217</v>
+      </c>
+      <c r="K122" s="1" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" ht="60">
+      <c r="A123" s="50" t="s">
+        <v>102</v>
+      </c>
+      <c r="B123" s="50"/>
+      <c r="C123" s="51"/>
+      <c r="D123" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="E123" s="41"/>
+      <c r="I123" s="41" t="s">
+        <v>169</v>
+      </c>
+      <c r="J123" s="52" t="s">
+        <v>241</v>
+      </c>
+      <c r="K123" s="1" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11">
+      <c r="A124" s="50" t="s">
+        <v>102</v>
+      </c>
+      <c r="B124" s="50"/>
+      <c r="C124" s="51">
+        <v>3</v>
+      </c>
+      <c r="D124" s="41" t="s">
+        <v>198</v>
+      </c>
+      <c r="E124" s="41" t="s">
+        <v>237</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="G124" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H124" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I124" s="41" t="s">
+        <v>542</v>
+      </c>
+      <c r="J124" s="52" t="s">
+        <v>200</v>
+      </c>
+      <c r="K124" s="1" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11">
+      <c r="A125" s="50" t="s">
+        <v>102</v>
+      </c>
+      <c r="B125" s="50"/>
+      <c r="C125" s="51">
+        <v>4</v>
+      </c>
+      <c r="D125" s="41" t="s">
+        <v>195</v>
+      </c>
+      <c r="E125" s="41" t="s">
+        <v>237</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G125" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H125" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I125" s="41" t="s">
+        <v>543</v>
+      </c>
+      <c r="J125" s="52" t="s">
+        <v>196</v>
+      </c>
+      <c r="K125" s="1" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11">
+      <c r="A126" s="50" t="s">
+        <v>102</v>
+      </c>
+      <c r="B126" s="50"/>
+      <c r="C126" s="51">
+        <v>15</v>
+      </c>
+      <c r="D126" s="41" t="s">
+        <v>192</v>
+      </c>
+      <c r="E126" s="41" t="s">
+        <v>237</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G126" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H126" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I126" s="41" t="s">
         <v>544</v>
       </c>
-      <c r="J87" s="52" t="s">
-        <v>196</v>
-      </c>
-      <c r="K87" s="1" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11">
-      <c r="A88" s="50" t="s">
+      <c r="J126" s="52" t="s">
+        <v>193</v>
+      </c>
+      <c r="K126" s="1" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" ht="75">
+      <c r="A127" s="50" t="s">
         <v>102</v>
       </c>
-      <c r="B88" s="50"/>
-      <c r="C88" s="51">
-        <v>15</v>
-      </c>
-      <c r="D88" s="41" t="s">
-        <v>192</v>
-      </c>
-      <c r="E88" s="41" t="s">
-        <v>237</v>
-      </c>
-      <c r="F88" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="G88" s="1" t="s">
+      <c r="B127" s="50"/>
+      <c r="C127" s="51"/>
+      <c r="D127" s="41" t="s">
+        <v>189</v>
+      </c>
+      <c r="E127" s="41" t="s">
+        <v>190</v>
+      </c>
+      <c r="I127" s="41" t="s">
+        <v>218</v>
+      </c>
+      <c r="J127" s="52" t="s">
+        <v>217</v>
+      </c>
+      <c r="K127" s="1" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" ht="60">
+      <c r="A128" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I128" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="J128" s="44" t="s">
+        <v>142</v>
+      </c>
+      <c r="K128" s="1" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11">
+      <c r="A129" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I129" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="K129" s="1" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11">
+      <c r="A130" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C130" s="28">
+        <v>1</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="G130" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="H88" s="1" t="s">
+      <c r="H130" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="I88" s="41" t="s">
-        <v>545</v>
-      </c>
-      <c r="J88" s="52" t="s">
-        <v>193</v>
-      </c>
-      <c r="K88" s="1" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11" ht="75">
-      <c r="A89" s="50" t="s">
-        <v>102</v>
-      </c>
-      <c r="B89" s="50"/>
-      <c r="C89" s="51"/>
-      <c r="D89" s="41" t="s">
-        <v>189</v>
-      </c>
-      <c r="E89" s="41" t="s">
-        <v>190</v>
-      </c>
-      <c r="I89" s="41" t="s">
-        <v>218</v>
-      </c>
-      <c r="J89" s="52" t="s">
-        <v>217</v>
-      </c>
-      <c r="K89" s="1" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11" ht="60">
-      <c r="A90" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I90" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="J90" s="44" t="s">
-        <v>142</v>
-      </c>
-      <c r="K90" s="1" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11">
-      <c r="A91" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I91" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="K91" s="1" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11">
-      <c r="A92" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="C92" s="28">
-        <v>1</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="F92" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="G92" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="H92" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="I92" s="1" t="s">
+      <c r="I130" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="J92" s="44" t="s">
+      <c r="J130" s="44" t="s">
         <v>163</v>
       </c>
-      <c r="K92" s="1" t="s">
+      <c r="K130" s="1" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="185" spans="5:5">
-      <c r="E185" s="40"/>
-    </row>
-    <row r="186" spans="5:5">
-      <c r="E186" s="40"/>
-    </row>
-    <row r="187" spans="5:5">
-      <c r="E187" s="40"/>
-    </row>
-    <row r="188" spans="5:5">
-      <c r="E188" s="40"/>
-    </row>
-    <row r="189" spans="5:5">
-      <c r="E189" s="40"/>
-    </row>
-    <row r="190" spans="5:5">
-      <c r="E190" s="40"/>
-    </row>
-    <row r="191" spans="5:5">
-      <c r="E191" s="40"/>
-    </row>
-    <row r="201" spans="5:10">
-      <c r="E201" s="40"/>
-    </row>
-    <row r="203" spans="5:10">
-      <c r="E203" s="40"/>
-      <c r="J203" s="48"/>
-    </row>
-    <row r="204" spans="5:10">
-      <c r="J204" s="48"/>
-    </row>
-    <row r="205" spans="5:10">
-      <c r="E205" s="41"/>
-      <c r="J205" s="48"/>
-    </row>
-    <row r="206" spans="5:10">
-      <c r="E206" s="40"/>
-      <c r="J206" s="48"/>
-    </row>
-    <row r="207" spans="5:10">
-      <c r="E207" s="40"/>
-      <c r="J207" s="48"/>
-    </row>
-    <row r="208" spans="5:10">
-      <c r="E208" s="40"/>
-      <c r="J208" s="48"/>
-    </row>
-    <row r="209" spans="5:10">
-      <c r="E209" s="40"/>
-      <c r="J209" s="48"/>
-    </row>
-    <row r="210" spans="5:10">
-      <c r="E210" s="40"/>
-      <c r="J210" s="48"/>
-    </row>
-    <row r="211" spans="5:10">
-      <c r="E211" s="42"/>
-      <c r="J211" s="48"/>
-    </row>
-    <row r="212" spans="5:10">
-      <c r="E212" s="40"/>
-      <c r="J212" s="48"/>
-    </row>
-    <row r="213" spans="5:10">
-      <c r="E213" s="40"/>
-      <c r="J213" s="48"/>
-    </row>
-    <row r="214" spans="5:10">
-      <c r="E214" s="40"/>
-      <c r="J214" s="48"/>
-    </row>
-    <row r="215" spans="5:10">
-      <c r="E215" s="40"/>
-      <c r="J215" s="48"/>
-    </row>
-    <row r="216" spans="5:10">
-      <c r="E216" s="40"/>
-      <c r="J216" s="48"/>
-    </row>
-    <row r="217" spans="5:10">
-      <c r="E217" s="40"/>
-      <c r="J217" s="48"/>
-    </row>
-    <row r="218" spans="5:10">
-      <c r="E218" s="40"/>
-      <c r="J218" s="48"/>
-    </row>
-    <row r="219" spans="5:10">
-      <c r="E219" s="40"/>
-      <c r="J219" s="48"/>
-    </row>
-    <row r="220" spans="5:10">
-      <c r="E220" s="40"/>
-      <c r="J220" s="48"/>
-    </row>
-    <row r="221" spans="5:10">
-      <c r="E221" s="40"/>
-      <c r="J221" s="48"/>
-    </row>
-    <row r="222" spans="5:10">
-      <c r="E222" s="40"/>
-      <c r="J222" s="48"/>
-    </row>
-    <row r="223" spans="5:10">
+    <row r="223" spans="5:5">
       <c r="E223" s="40"/>
-      <c r="J223" s="48"/>
-    </row>
-    <row r="224" spans="5:10">
+    </row>
+    <row r="224" spans="5:5">
       <c r="E224" s="40"/>
-      <c r="J224" s="48"/>
-    </row>
-    <row r="225" spans="5:10">
+    </row>
+    <row r="225" spans="5:5">
       <c r="E225" s="40"/>
-      <c r="J225" s="48"/>
-    </row>
-    <row r="226" spans="5:10">
+    </row>
+    <row r="226" spans="5:5">
       <c r="E226" s="40"/>
-      <c r="J226" s="48"/>
-    </row>
-    <row r="227" spans="5:10">
+    </row>
+    <row r="227" spans="5:5">
       <c r="E227" s="40"/>
-      <c r="J227" s="48"/>
-    </row>
-    <row r="228" spans="5:10">
+    </row>
+    <row r="228" spans="5:5">
       <c r="E228" s="40"/>
-      <c r="J228" s="48"/>
-    </row>
-    <row r="229" spans="5:10">
+    </row>
+    <row r="229" spans="5:5">
       <c r="E229" s="40"/>
-      <c r="J229" s="48"/>
-    </row>
-    <row r="230" spans="5:10">
-      <c r="E230" s="40"/>
-      <c r="J230" s="48"/>
-    </row>
-    <row r="231" spans="5:10">
-      <c r="E231" s="40"/>
-      <c r="J231" s="48"/>
-    </row>
-    <row r="232" spans="5:10">
-      <c r="E232" s="40"/>
-      <c r="J232" s="48"/>
-    </row>
-    <row r="233" spans="5:10">
-      <c r="E233" s="40"/>
-      <c r="J233" s="48"/>
-    </row>
-    <row r="234" spans="5:10">
-      <c r="E234" s="40"/>
-      <c r="J234" s="48"/>
-    </row>
-    <row r="235" spans="5:10">
-      <c r="E235" s="40"/>
-      <c r="J235" s="48"/>
-    </row>
-    <row r="236" spans="5:10">
-      <c r="E236" s="40"/>
-      <c r="J236" s="48"/>
-    </row>
-    <row r="237" spans="5:10">
-      <c r="E237" s="40"/>
-      <c r="J237" s="48"/>
-    </row>
-    <row r="238" spans="5:10">
-      <c r="E238" s="40"/>
-      <c r="J238" s="48"/>
-    </row>
-    <row r="239" spans="5:10">
+    </row>
+    <row r="239" spans="5:5">
       <c r="E239" s="40"/>
-      <c r="J239" s="48"/>
-    </row>
-    <row r="240" spans="5:10">
-      <c r="E240" s="40"/>
-      <c r="J240" s="48"/>
     </row>
     <row r="241" spans="5:10">
       <c r="E241" s="40"/>
       <c r="J241" s="48"/>
     </row>
     <row r="242" spans="5:10">
-      <c r="E242" s="40"/>
       <c r="J242" s="48"/>
     </row>
     <row r="243" spans="5:10">
-      <c r="E243" s="40"/>
+      <c r="E243" s="41"/>
       <c r="J243" s="48"/>
     </row>
     <row r="244" spans="5:10">
@@ -6789,243 +8301,284 @@
       <c r="J248" s="48"/>
     </row>
     <row r="249" spans="5:10">
-      <c r="E249" s="40"/>
+      <c r="E249" s="42"/>
       <c r="J249" s="48"/>
     </row>
     <row r="250" spans="5:10">
       <c r="E250" s="40"/>
       <c r="J250" s="48"/>
     </row>
+    <row r="251" spans="5:10">
+      <c r="E251" s="40"/>
+      <c r="J251" s="48"/>
+    </row>
+    <row r="252" spans="5:10">
+      <c r="E252" s="40"/>
+      <c r="J252" s="48"/>
+    </row>
+    <row r="253" spans="5:10">
+      <c r="E253" s="40"/>
+      <c r="J253" s="48"/>
+    </row>
+    <row r="254" spans="5:10">
+      <c r="E254" s="40"/>
+      <c r="J254" s="48"/>
+    </row>
+    <row r="255" spans="5:10">
+      <c r="E255" s="40"/>
+      <c r="J255" s="48"/>
+    </row>
+    <row r="256" spans="5:10">
+      <c r="E256" s="40"/>
+      <c r="J256" s="48"/>
+    </row>
+    <row r="257" spans="5:10">
+      <c r="E257" s="40"/>
+      <c r="J257" s="48"/>
+    </row>
     <row r="258" spans="5:10">
       <c r="E258" s="40"/>
+      <c r="J258" s="48"/>
+    </row>
+    <row r="259" spans="5:10">
+      <c r="E259" s="40"/>
+      <c r="J259" s="48"/>
+    </row>
+    <row r="260" spans="5:10">
+      <c r="E260" s="40"/>
+      <c r="J260" s="48"/>
+    </row>
+    <row r="261" spans="5:10">
+      <c r="E261" s="40"/>
+      <c r="J261" s="48"/>
+    </row>
+    <row r="262" spans="5:10">
+      <c r="E262" s="40"/>
+      <c r="J262" s="48"/>
+    </row>
+    <row r="263" spans="5:10">
+      <c r="E263" s="40"/>
+      <c r="J263" s="48"/>
+    </row>
+    <row r="264" spans="5:10">
+      <c r="E264" s="40"/>
+      <c r="J264" s="48"/>
+    </row>
+    <row r="265" spans="5:10">
+      <c r="E265" s="40"/>
+      <c r="J265" s="48"/>
+    </row>
+    <row r="266" spans="5:10">
+      <c r="E266" s="40"/>
+      <c r="J266" s="48"/>
     </row>
     <row r="267" spans="5:10">
+      <c r="E267" s="40"/>
       <c r="J267" s="48"/>
     </row>
     <row r="268" spans="5:10">
+      <c r="E268" s="40"/>
       <c r="J268" s="48"/>
     </row>
     <row r="269" spans="5:10">
+      <c r="E269" s="40"/>
       <c r="J269" s="48"/>
     </row>
     <row r="270" spans="5:10">
+      <c r="E270" s="40"/>
       <c r="J270" s="48"/>
     </row>
     <row r="271" spans="5:10">
+      <c r="E271" s="40"/>
       <c r="J271" s="48"/>
     </row>
     <row r="272" spans="5:10">
+      <c r="E272" s="40"/>
       <c r="J272" s="48"/>
     </row>
-    <row r="273" spans="10:10">
+    <row r="273" spans="5:10">
+      <c r="E273" s="40"/>
       <c r="J273" s="48"/>
     </row>
-    <row r="274" spans="10:10">
+    <row r="274" spans="5:10">
+      <c r="E274" s="40"/>
       <c r="J274" s="48"/>
     </row>
-    <row r="275" spans="10:10">
+    <row r="275" spans="5:10">
+      <c r="E275" s="40"/>
       <c r="J275" s="48"/>
     </row>
-    <row r="276" spans="10:10">
+    <row r="276" spans="5:10">
+      <c r="E276" s="40"/>
       <c r="J276" s="48"/>
     </row>
-    <row r="277" spans="10:10">
+    <row r="277" spans="5:10">
+      <c r="E277" s="40"/>
       <c r="J277" s="48"/>
     </row>
-    <row r="278" spans="10:10">
+    <row r="278" spans="5:10">
+      <c r="E278" s="40"/>
       <c r="J278" s="48"/>
     </row>
-    <row r="279" spans="10:10">
+    <row r="279" spans="5:10">
+      <c r="E279" s="40"/>
       <c r="J279" s="48"/>
     </row>
-    <row r="280" spans="10:10">
+    <row r="280" spans="5:10">
+      <c r="E280" s="40"/>
       <c r="J280" s="48"/>
     </row>
-    <row r="310" spans="5:5">
-      <c r="E310" s="40"/>
-    </row>
-    <row r="329" spans="5:5">
-      <c r="E329" s="40"/>
-    </row>
-    <row r="330" spans="5:5">
-      <c r="E330" s="40"/>
-    </row>
-    <row r="333" spans="5:5">
-      <c r="E333" s="40"/>
-    </row>
-    <row r="334" spans="5:5">
-      <c r="E334" s="40"/>
-    </row>
-    <row r="335" spans="5:5">
-      <c r="E335" s="40"/>
-    </row>
-    <row r="336" spans="5:5">
-      <c r="E336" s="40"/>
-    </row>
-    <row r="337" spans="5:5">
-      <c r="E337" s="40"/>
-    </row>
-    <row r="338" spans="5:5">
-      <c r="E338" s="40"/>
-    </row>
-    <row r="344" spans="5:5">
-      <c r="E344" s="40"/>
-    </row>
-    <row r="345" spans="5:5">
-      <c r="E345" s="40"/>
-    </row>
-    <row r="346" spans="5:5">
-      <c r="E346" s="40"/>
-    </row>
-    <row r="347" spans="5:5">
-      <c r="E347" s="40"/>
+    <row r="281" spans="5:10">
+      <c r="E281" s="40"/>
+      <c r="J281" s="48"/>
+    </row>
+    <row r="282" spans="5:10">
+      <c r="E282" s="40"/>
+      <c r="J282" s="48"/>
+    </row>
+    <row r="283" spans="5:10">
+      <c r="E283" s="40"/>
+      <c r="J283" s="48"/>
+    </row>
+    <row r="284" spans="5:10">
+      <c r="E284" s="40"/>
+      <c r="J284" s="48"/>
+    </row>
+    <row r="285" spans="5:10">
+      <c r="E285" s="40"/>
+      <c r="J285" s="48"/>
+    </row>
+    <row r="286" spans="5:10">
+      <c r="E286" s="40"/>
+      <c r="J286" s="48"/>
+    </row>
+    <row r="287" spans="5:10">
+      <c r="E287" s="40"/>
+      <c r="J287" s="48"/>
+    </row>
+    <row r="288" spans="5:10">
+      <c r="E288" s="40"/>
+      <c r="J288" s="48"/>
+    </row>
+    <row r="296" spans="5:5">
+      <c r="E296" s="40"/>
+    </row>
+    <row r="305" spans="10:10">
+      <c r="J305" s="48"/>
+    </row>
+    <row r="306" spans="10:10">
+      <c r="J306" s="48"/>
+    </row>
+    <row r="307" spans="10:10">
+      <c r="J307" s="48"/>
+    </row>
+    <row r="308" spans="10:10">
+      <c r="J308" s="48"/>
+    </row>
+    <row r="309" spans="10:10">
+      <c r="J309" s="48"/>
+    </row>
+    <row r="310" spans="10:10">
+      <c r="J310" s="48"/>
+    </row>
+    <row r="311" spans="10:10">
+      <c r="J311" s="48"/>
+    </row>
+    <row r="312" spans="10:10">
+      <c r="J312" s="48"/>
+    </row>
+    <row r="313" spans="10:10">
+      <c r="J313" s="48"/>
+    </row>
+    <row r="314" spans="10:10">
+      <c r="J314" s="48"/>
+    </row>
+    <row r="315" spans="10:10">
+      <c r="J315" s="48"/>
+    </row>
+    <row r="316" spans="10:10">
+      <c r="J316" s="48"/>
+    </row>
+    <row r="317" spans="10:10">
+      <c r="J317" s="48"/>
+    </row>
+    <row r="318" spans="10:10">
+      <c r="J318" s="48"/>
     </row>
     <row r="348" spans="5:5">
       <c r="E348" s="40"/>
     </row>
-    <row r="349" spans="5:5">
-      <c r="E349" s="40"/>
-    </row>
-    <row r="350" spans="5:5">
-      <c r="E350" s="40"/>
-    </row>
-    <row r="352" spans="5:5">
-      <c r="E352" s="40"/>
-    </row>
-    <row r="353" spans="5:5">
-      <c r="E353" s="40"/>
-    </row>
-    <row r="354" spans="5:5">
-      <c r="E354" s="40"/>
-    </row>
-    <row r="355" spans="5:5">
-      <c r="E355" s="40"/>
-    </row>
-    <row r="359" spans="5:5">
-      <c r="E359" s="40"/>
-    </row>
-    <row r="366" spans="5:5">
-      <c r="E366" s="40"/>
-    </row>
-    <row r="370" spans="5:5">
-      <c r="E370" s="40"/>
-    </row>
-    <row r="381" spans="5:5">
-      <c r="E381" s="40"/>
-    </row>
-    <row r="391" spans="5:10">
+    <row r="367" spans="5:5">
+      <c r="E367" s="40"/>
+    </row>
+    <row r="368" spans="5:5">
+      <c r="E368" s="40"/>
+    </row>
+    <row r="371" spans="5:5">
+      <c r="E371" s="40"/>
+    </row>
+    <row r="372" spans="5:5">
+      <c r="E372" s="40"/>
+    </row>
+    <row r="373" spans="5:5">
+      <c r="E373" s="40"/>
+    </row>
+    <row r="374" spans="5:5">
+      <c r="E374" s="40"/>
+    </row>
+    <row r="375" spans="5:5">
+      <c r="E375" s="40"/>
+    </row>
+    <row r="376" spans="5:5">
+      <c r="E376" s="40"/>
+    </row>
+    <row r="382" spans="5:5">
+      <c r="E382" s="40"/>
+    </row>
+    <row r="383" spans="5:5">
+      <c r="E383" s="40"/>
+    </row>
+    <row r="384" spans="5:5">
+      <c r="E384" s="40"/>
+    </row>
+    <row r="385" spans="5:5">
+      <c r="E385" s="40"/>
+    </row>
+    <row r="386" spans="5:5">
+      <c r="E386" s="40"/>
+    </row>
+    <row r="387" spans="5:5">
+      <c r="E387" s="40"/>
+    </row>
+    <row r="388" spans="5:5">
+      <c r="E388" s="40"/>
+    </row>
+    <row r="390" spans="5:5">
+      <c r="E390" s="40"/>
+    </row>
+    <row r="391" spans="5:5">
       <c r="E391" s="40"/>
     </row>
-    <row r="393" spans="5:10">
-      <c r="J393" s="48"/>
-    </row>
-    <row r="394" spans="5:10">
-      <c r="J394" s="48"/>
-    </row>
-    <row r="395" spans="5:10">
-      <c r="J395" s="48"/>
-    </row>
-    <row r="396" spans="5:10">
-      <c r="J396" s="48"/>
-    </row>
-    <row r="397" spans="5:10">
-      <c r="J397" s="48"/>
-    </row>
-    <row r="398" spans="5:10">
-      <c r="J398" s="48"/>
-    </row>
-    <row r="399" spans="5:10">
-      <c r="J399" s="48"/>
-    </row>
-    <row r="400" spans="5:10">
-      <c r="J400" s="48"/>
-    </row>
-    <row r="401" spans="5:10">
-      <c r="J401" s="48"/>
-    </row>
-    <row r="402" spans="5:10">
-      <c r="J402" s="48"/>
-    </row>
-    <row r="403" spans="5:10">
-      <c r="J403" s="48"/>
-    </row>
-    <row r="404" spans="5:10">
-      <c r="J404" s="48"/>
-    </row>
-    <row r="405" spans="5:10">
-      <c r="J405" s="48"/>
-    </row>
-    <row r="406" spans="5:10">
-      <c r="J406" s="48"/>
-    </row>
-    <row r="407" spans="5:10">
-      <c r="J407" s="48"/>
-    </row>
-    <row r="408" spans="5:10">
-      <c r="J408" s="48"/>
-    </row>
-    <row r="409" spans="5:10">
-      <c r="J409" s="48"/>
-    </row>
-    <row r="410" spans="5:10">
-      <c r="J410" s="48"/>
-    </row>
-    <row r="411" spans="5:10">
-      <c r="J411" s="48"/>
-    </row>
-    <row r="412" spans="5:10">
-      <c r="E412" s="40"/>
-      <c r="J412" s="48"/>
-    </row>
-    <row r="414" spans="5:10">
-      <c r="J414" s="48"/>
-    </row>
-    <row r="415" spans="5:10">
-      <c r="J415" s="48"/>
-    </row>
-    <row r="416" spans="5:10">
-      <c r="J416" s="48"/>
-    </row>
-    <row r="417" spans="5:10">
-      <c r="J417" s="48"/>
-    </row>
-    <row r="418" spans="5:10">
-      <c r="J418" s="48"/>
+    <row r="392" spans="5:5">
+      <c r="E392" s="40"/>
+    </row>
+    <row r="393" spans="5:5">
+      <c r="E393" s="40"/>
+    </row>
+    <row r="397" spans="5:5">
+      <c r="E397" s="40"/>
+    </row>
+    <row r="404" spans="5:5">
+      <c r="E404" s="40"/>
+    </row>
+    <row r="408" spans="5:5">
+      <c r="E408" s="40"/>
     </row>
     <row r="419" spans="5:10">
-      <c r="J419" s="48"/>
-    </row>
-    <row r="420" spans="5:10">
-      <c r="J420" s="48"/>
-    </row>
-    <row r="421" spans="5:10">
-      <c r="E421" s="40"/>
-      <c r="J421" s="48"/>
-    </row>
-    <row r="422" spans="5:10">
-      <c r="J422" s="48"/>
-    </row>
-    <row r="423" spans="5:10">
-      <c r="J423" s="48"/>
-    </row>
-    <row r="424" spans="5:10">
-      <c r="J424" s="48"/>
-    </row>
-    <row r="425" spans="5:10">
-      <c r="J425" s="48"/>
-    </row>
-    <row r="426" spans="5:10">
-      <c r="J426" s="48"/>
-    </row>
-    <row r="427" spans="5:10">
-      <c r="J427" s="48"/>
-    </row>
-    <row r="428" spans="5:10">
-      <c r="J428" s="48"/>
+      <c r="E419" s="40"/>
     </row>
     <row r="429" spans="5:10">
       <c r="E429" s="40"/>
-      <c r="J429" s="48"/>
     </row>
     <row r="431" spans="5:10">
       <c r="J431" s="48"/>
@@ -7033,484 +8586,443 @@
     <row r="432" spans="5:10">
       <c r="J432" s="48"/>
     </row>
-    <row r="433" spans="5:10">
+    <row r="433" spans="10:10">
       <c r="J433" s="48"/>
     </row>
-    <row r="434" spans="5:10">
+    <row r="434" spans="10:10">
       <c r="J434" s="48"/>
     </row>
-    <row r="435" spans="5:10">
+    <row r="435" spans="10:10">
       <c r="J435" s="48"/>
     </row>
-    <row r="436" spans="5:10">
+    <row r="436" spans="10:10">
       <c r="J436" s="48"/>
     </row>
-    <row r="437" spans="5:10">
+    <row r="437" spans="10:10">
       <c r="J437" s="48"/>
     </row>
-    <row r="438" spans="5:10">
-      <c r="E438" s="40"/>
+    <row r="438" spans="10:10">
       <c r="J438" s="48"/>
     </row>
-    <row r="439" spans="5:10">
+    <row r="439" spans="10:10">
       <c r="J439" s="48"/>
     </row>
-    <row r="440" spans="5:10">
+    <row r="440" spans="10:10">
       <c r="J440" s="48"/>
     </row>
-    <row r="441" spans="5:10">
+    <row r="441" spans="10:10">
       <c r="J441" s="48"/>
     </row>
-    <row r="442" spans="5:10">
+    <row r="442" spans="10:10">
       <c r="J442" s="48"/>
     </row>
-    <row r="443" spans="5:10">
+    <row r="443" spans="10:10">
       <c r="J443" s="48"/>
     </row>
-    <row r="444" spans="5:10">
+    <row r="444" spans="10:10">
       <c r="J444" s="48"/>
     </row>
-    <row r="445" spans="5:10">
+    <row r="445" spans="10:10">
       <c r="J445" s="48"/>
     </row>
-    <row r="446" spans="5:10">
-      <c r="E446" s="40"/>
+    <row r="446" spans="10:10">
       <c r="J446" s="48"/>
     </row>
-    <row r="454" spans="5:5">
-      <c r="E454" s="40"/>
-    </row>
-    <row r="461" spans="5:5">
-      <c r="E461" s="40"/>
-    </row>
-    <row r="477" spans="5:5">
-      <c r="E477" s="41"/>
-    </row>
-    <row r="478" spans="5:5">
-      <c r="E478" s="41"/>
-    </row>
-    <row r="481" spans="5:5">
-      <c r="E481" s="41"/>
-    </row>
-    <row r="482" spans="5:5">
-      <c r="E482" s="40"/>
-    </row>
-    <row r="495" spans="5:5">
-      <c r="E495" s="40"/>
-    </row>
-    <row r="507" spans="5:5">
-      <c r="E507" s="40"/>
-    </row>
-    <row r="511" spans="5:5">
-      <c r="E511" s="40"/>
-    </row>
-    <row r="512" spans="5:5">
-      <c r="E512" s="40"/>
-    </row>
-    <row r="513" spans="5:5">
-      <c r="E513" s="40"/>
-    </row>
-    <row r="514" spans="5:5">
-      <c r="E514" s="40"/>
+    <row r="447" spans="10:10">
+      <c r="J447" s="48"/>
+    </row>
+    <row r="448" spans="10:10">
+      <c r="J448" s="48"/>
+    </row>
+    <row r="449" spans="5:10">
+      <c r="J449" s="48"/>
+    </row>
+    <row r="450" spans="5:10">
+      <c r="E450" s="40"/>
+      <c r="J450" s="48"/>
+    </row>
+    <row r="452" spans="5:10">
+      <c r="J452" s="48"/>
+    </row>
+    <row r="453" spans="5:10">
+      <c r="J453" s="48"/>
+    </row>
+    <row r="454" spans="5:10">
+      <c r="J454" s="48"/>
+    </row>
+    <row r="455" spans="5:10">
+      <c r="J455" s="48"/>
+    </row>
+    <row r="456" spans="5:10">
+      <c r="J456" s="48"/>
+    </row>
+    <row r="457" spans="5:10">
+      <c r="J457" s="48"/>
+    </row>
+    <row r="458" spans="5:10">
+      <c r="J458" s="48"/>
+    </row>
+    <row r="459" spans="5:10">
+      <c r="E459" s="40"/>
+      <c r="J459" s="48"/>
+    </row>
+    <row r="460" spans="5:10">
+      <c r="J460" s="48"/>
+    </row>
+    <row r="461" spans="5:10">
+      <c r="J461" s="48"/>
+    </row>
+    <row r="462" spans="5:10">
+      <c r="J462" s="48"/>
+    </row>
+    <row r="463" spans="5:10">
+      <c r="J463" s="48"/>
+    </row>
+    <row r="464" spans="5:10">
+      <c r="J464" s="48"/>
+    </row>
+    <row r="465" spans="5:10">
+      <c r="J465" s="48"/>
+    </row>
+    <row r="466" spans="5:10">
+      <c r="J466" s="48"/>
+    </row>
+    <row r="467" spans="5:10">
+      <c r="E467" s="40"/>
+      <c r="J467" s="48"/>
+    </row>
+    <row r="469" spans="5:10">
+      <c r="J469" s="48"/>
+    </row>
+    <row r="470" spans="5:10">
+      <c r="J470" s="48"/>
+    </row>
+    <row r="471" spans="5:10">
+      <c r="J471" s="48"/>
+    </row>
+    <row r="472" spans="5:10">
+      <c r="J472" s="48"/>
+    </row>
+    <row r="473" spans="5:10">
+      <c r="J473" s="48"/>
+    </row>
+    <row r="474" spans="5:10">
+      <c r="J474" s="48"/>
+    </row>
+    <row r="475" spans="5:10">
+      <c r="J475" s="48"/>
+    </row>
+    <row r="476" spans="5:10">
+      <c r="E476" s="40"/>
+      <c r="J476" s="48"/>
+    </row>
+    <row r="477" spans="5:10">
+      <c r="J477" s="48"/>
+    </row>
+    <row r="478" spans="5:10">
+      <c r="J478" s="48"/>
+    </row>
+    <row r="479" spans="5:10">
+      <c r="J479" s="48"/>
+    </row>
+    <row r="480" spans="5:10">
+      <c r="J480" s="48"/>
+    </row>
+    <row r="481" spans="5:10">
+      <c r="J481" s="48"/>
+    </row>
+    <row r="482" spans="5:10">
+      <c r="J482" s="48"/>
+    </row>
+    <row r="483" spans="5:10">
+      <c r="J483" s="48"/>
+    </row>
+    <row r="484" spans="5:10">
+      <c r="E484" s="40"/>
+      <c r="J484" s="48"/>
+    </row>
+    <row r="492" spans="5:10">
+      <c r="E492" s="40"/>
+    </row>
+    <row r="499" spans="5:5">
+      <c r="E499" s="40"/>
     </row>
     <row r="515" spans="5:5">
-      <c r="E515" s="40"/>
+      <c r="E515" s="41"/>
     </row>
     <row r="516" spans="5:5">
-      <c r="E516" s="40"/>
-    </row>
-    <row r="517" spans="5:5">
-      <c r="E517" s="40"/>
-    </row>
-    <row r="518" spans="5:5">
-      <c r="E518" s="40"/>
+      <c r="E516" s="41"/>
     </row>
     <row r="519" spans="5:5">
-      <c r="E519" s="40"/>
+      <c r="E519" s="41"/>
     </row>
     <row r="520" spans="5:5">
       <c r="E520" s="40"/>
     </row>
-    <row r="521" spans="5:5">
-      <c r="E521" s="40"/>
-    </row>
-    <row r="522" spans="5:5">
-      <c r="E522" s="40"/>
-    </row>
-    <row r="523" spans="5:5">
-      <c r="E523" s="40"/>
-    </row>
-    <row r="524" spans="5:5">
-      <c r="E524" s="40"/>
-    </row>
-    <row r="525" spans="5:5">
-      <c r="E525" s="40"/>
-    </row>
-    <row r="526" spans="5:5">
-      <c r="E526" s="40"/>
-    </row>
-    <row r="527" spans="5:5">
-      <c r="E527" s="40"/>
-    </row>
-    <row r="528" spans="5:5">
-      <c r="E528" s="40"/>
-    </row>
-    <row r="529" spans="5:10">
-      <c r="E529" s="40"/>
-    </row>
-    <row r="530" spans="5:10">
-      <c r="E530" s="40"/>
-    </row>
-    <row r="531" spans="5:10">
-      <c r="E531" s="40"/>
-    </row>
-    <row r="532" spans="5:10">
-      <c r="E532" s="40"/>
-    </row>
-    <row r="533" spans="5:10">
+    <row r="533" spans="5:5">
       <c r="E533" s="40"/>
     </row>
-    <row r="534" spans="5:10">
-      <c r="E534" s="40"/>
-    </row>
-    <row r="536" spans="5:10">
-      <c r="J536" s="48"/>
-    </row>
-    <row r="537" spans="5:10">
-      <c r="J537" s="48"/>
-    </row>
-    <row r="538" spans="5:10">
-      <c r="J538" s="48"/>
-    </row>
-    <row r="539" spans="5:10">
-      <c r="J539" s="48"/>
-    </row>
-    <row r="540" spans="5:10">
-      <c r="J540" s="48"/>
-    </row>
-    <row r="541" spans="5:10">
-      <c r="J541" s="48"/>
-    </row>
-    <row r="542" spans="5:10">
-      <c r="J542" s="48"/>
-    </row>
-    <row r="543" spans="5:10">
-      <c r="J543" s="48"/>
-    </row>
-    <row r="544" spans="5:10">
-      <c r="J544" s="48"/>
-    </row>
-    <row r="545" spans="5:10">
-      <c r="J545" s="48"/>
-    </row>
-    <row r="546" spans="5:10">
-      <c r="J546" s="48"/>
-    </row>
-    <row r="547" spans="5:10">
-      <c r="J547" s="48"/>
-    </row>
-    <row r="548" spans="5:10">
-      <c r="J548" s="48"/>
-    </row>
-    <row r="549" spans="5:10">
+    <row r="545" spans="5:5">
+      <c r="E545" s="40"/>
+    </row>
+    <row r="549" spans="5:5">
       <c r="E549" s="40"/>
-      <c r="J549" s="48"/>
-    </row>
-    <row r="551" spans="5:10">
+    </row>
+    <row r="550" spans="5:5">
+      <c r="E550" s="40"/>
+    </row>
+    <row r="551" spans="5:5">
       <c r="E551" s="40"/>
     </row>
-    <row r="552" spans="5:10">
+    <row r="552" spans="5:5">
       <c r="E552" s="40"/>
     </row>
-    <row r="553" spans="5:10">
+    <row r="553" spans="5:5">
       <c r="E553" s="40"/>
     </row>
-    <row r="554" spans="5:10">
+    <row r="554" spans="5:5">
       <c r="E554" s="40"/>
     </row>
-    <row r="555" spans="5:10">
+    <row r="555" spans="5:5">
       <c r="E555" s="40"/>
     </row>
-    <row r="556" spans="5:10">
+    <row r="556" spans="5:5">
       <c r="E556" s="40"/>
     </row>
-    <row r="557" spans="5:10">
+    <row r="557" spans="5:5">
       <c r="E557" s="40"/>
     </row>
-    <row r="558" spans="5:10">
+    <row r="558" spans="5:5">
       <c r="E558" s="40"/>
     </row>
-    <row r="559" spans="5:10">
+    <row r="559" spans="5:5">
       <c r="E559" s="40"/>
     </row>
-    <row r="560" spans="5:10">
+    <row r="560" spans="5:5">
       <c r="E560" s="40"/>
     </row>
-    <row r="561" spans="5:5">
+    <row r="561" spans="5:10">
       <c r="E561" s="40"/>
     </row>
-    <row r="562" spans="5:5">
+    <row r="562" spans="5:10">
       <c r="E562" s="40"/>
     </row>
-    <row r="563" spans="5:5">
+    <row r="563" spans="5:10">
       <c r="E563" s="40"/>
     </row>
-    <row r="564" spans="5:5">
+    <row r="564" spans="5:10">
       <c r="E564" s="40"/>
     </row>
-    <row r="565" spans="5:5">
+    <row r="565" spans="5:10">
       <c r="E565" s="40"/>
     </row>
-    <row r="566" spans="5:5">
+    <row r="566" spans="5:10">
       <c r="E566" s="40"/>
     </row>
-    <row r="567" spans="5:5">
+    <row r="567" spans="5:10">
       <c r="E567" s="40"/>
     </row>
-    <row r="568" spans="5:5">
+    <row r="568" spans="5:10">
       <c r="E568" s="40"/>
     </row>
-    <row r="569" spans="5:5">
+    <row r="569" spans="5:10">
       <c r="E569" s="40"/>
     </row>
-    <row r="570" spans="5:5">
+    <row r="570" spans="5:10">
       <c r="E570" s="40"/>
     </row>
-    <row r="571" spans="5:5">
+    <row r="571" spans="5:10">
       <c r="E571" s="40"/>
     </row>
-    <row r="572" spans="5:5">
+    <row r="572" spans="5:10">
       <c r="E572" s="40"/>
     </row>
-    <row r="573" spans="5:5">
-      <c r="E573" s="40"/>
-    </row>
-    <row r="574" spans="5:5">
-      <c r="E574" s="40"/>
-    </row>
-    <row r="575" spans="5:5">
-      <c r="E575" s="40"/>
-    </row>
-    <row r="576" spans="5:5">
-      <c r="E576" s="40"/>
-    </row>
-    <row r="577" spans="5:5">
-      <c r="E577" s="40"/>
-    </row>
-    <row r="578" spans="5:5">
-      <c r="E578" s="40"/>
-    </row>
-    <row r="579" spans="5:5">
-      <c r="E579" s="40"/>
-    </row>
-    <row r="580" spans="5:5">
-      <c r="E580" s="40"/>
-    </row>
-    <row r="581" spans="5:5">
-      <c r="E581" s="40"/>
-    </row>
-    <row r="582" spans="5:5">
-      <c r="E582" s="40"/>
-    </row>
-    <row r="583" spans="5:5">
-      <c r="E583" s="40"/>
-    </row>
-    <row r="584" spans="5:5">
-      <c r="E584" s="40"/>
-    </row>
-    <row r="585" spans="5:5">
-      <c r="E585" s="40"/>
-    </row>
-    <row r="586" spans="5:5">
-      <c r="E586" s="40"/>
-    </row>
-    <row r="587" spans="5:5">
+    <row r="574" spans="5:10">
+      <c r="J574" s="48"/>
+    </row>
+    <row r="575" spans="5:10">
+      <c r="J575" s="48"/>
+    </row>
+    <row r="576" spans="5:10">
+      <c r="J576" s="48"/>
+    </row>
+    <row r="577" spans="5:10">
+      <c r="J577" s="48"/>
+    </row>
+    <row r="578" spans="5:10">
+      <c r="J578" s="48"/>
+    </row>
+    <row r="579" spans="5:10">
+      <c r="J579" s="48"/>
+    </row>
+    <row r="580" spans="5:10">
+      <c r="J580" s="48"/>
+    </row>
+    <row r="581" spans="5:10">
+      <c r="J581" s="48"/>
+    </row>
+    <row r="582" spans="5:10">
+      <c r="J582" s="48"/>
+    </row>
+    <row r="583" spans="5:10">
+      <c r="J583" s="48"/>
+    </row>
+    <row r="584" spans="5:10">
+      <c r="J584" s="48"/>
+    </row>
+    <row r="585" spans="5:10">
+      <c r="J585" s="48"/>
+    </row>
+    <row r="586" spans="5:10">
+      <c r="J586" s="48"/>
+    </row>
+    <row r="587" spans="5:10">
       <c r="E587" s="40"/>
-    </row>
-    <row r="588" spans="5:5">
-      <c r="E588" s="40"/>
-    </row>
-    <row r="589" spans="5:5">
+      <c r="J587" s="48"/>
+    </row>
+    <row r="589" spans="5:10">
       <c r="E589" s="40"/>
     </row>
-    <row r="590" spans="5:5">
+    <row r="590" spans="5:10">
       <c r="E590" s="40"/>
     </row>
-    <row r="591" spans="5:5">
+    <row r="591" spans="5:10">
       <c r="E591" s="40"/>
     </row>
-    <row r="592" spans="5:5">
+    <row r="592" spans="5:10">
       <c r="E592" s="40"/>
     </row>
-    <row r="593" spans="5:10">
+    <row r="593" spans="5:5">
       <c r="E593" s="40"/>
     </row>
-    <row r="594" spans="5:10">
+    <row r="594" spans="5:5">
       <c r="E594" s="40"/>
     </row>
-    <row r="595" spans="5:10">
+    <row r="595" spans="5:5">
       <c r="E595" s="40"/>
     </row>
-    <row r="596" spans="5:10">
+    <row r="596" spans="5:5">
       <c r="E596" s="40"/>
     </row>
-    <row r="597" spans="5:10">
+    <row r="597" spans="5:5">
       <c r="E597" s="40"/>
     </row>
-    <row r="598" spans="5:10">
+    <row r="598" spans="5:5">
       <c r="E598" s="40"/>
     </row>
-    <row r="600" spans="5:10">
+    <row r="599" spans="5:5">
+      <c r="E599" s="40"/>
+    </row>
+    <row r="600" spans="5:5">
       <c r="E600" s="40"/>
-      <c r="J600" s="48"/>
-    </row>
-    <row r="601" spans="5:10">
+    </row>
+    <row r="601" spans="5:5">
       <c r="E601" s="40"/>
-      <c r="J601" s="48"/>
-    </row>
-    <row r="602" spans="5:10">
+    </row>
+    <row r="602" spans="5:5">
       <c r="E602" s="40"/>
-      <c r="J602" s="48"/>
-    </row>
-    <row r="603" spans="5:10">
+    </row>
+    <row r="603" spans="5:5">
       <c r="E603" s="40"/>
-      <c r="J603" s="48"/>
-    </row>
-    <row r="604" spans="5:10">
+    </row>
+    <row r="604" spans="5:5">
       <c r="E604" s="40"/>
-      <c r="J604" s="48"/>
-    </row>
-    <row r="605" spans="5:10">
+    </row>
+    <row r="605" spans="5:5">
       <c r="E605" s="40"/>
-      <c r="J605" s="48"/>
-    </row>
-    <row r="606" spans="5:10">
+    </row>
+    <row r="606" spans="5:5">
       <c r="E606" s="40"/>
-      <c r="J606" s="48"/>
-    </row>
-    <row r="607" spans="5:10">
+    </row>
+    <row r="607" spans="5:5">
       <c r="E607" s="40"/>
-      <c r="J607" s="48"/>
-    </row>
-    <row r="608" spans="5:10">
+    </row>
+    <row r="608" spans="5:5">
       <c r="E608" s="40"/>
-      <c r="J608" s="48"/>
-    </row>
-    <row r="609" spans="5:10">
+    </row>
+    <row r="609" spans="5:5">
       <c r="E609" s="40"/>
-      <c r="J609" s="48"/>
-    </row>
-    <row r="610" spans="5:10">
+    </row>
+    <row r="610" spans="5:5">
       <c r="E610" s="40"/>
-      <c r="J610" s="48"/>
-    </row>
-    <row r="611" spans="5:10">
+    </row>
+    <row r="611" spans="5:5">
       <c r="E611" s="40"/>
-      <c r="J611" s="48"/>
-    </row>
-    <row r="612" spans="5:10">
+    </row>
+    <row r="612" spans="5:5">
       <c r="E612" s="40"/>
-      <c r="J612" s="48"/>
-    </row>
-    <row r="613" spans="5:10">
+    </row>
+    <row r="613" spans="5:5">
       <c r="E613" s="40"/>
-      <c r="J613" s="48"/>
-    </row>
-    <row r="614" spans="5:10">
+    </row>
+    <row r="614" spans="5:5">
       <c r="E614" s="40"/>
-      <c r="J614" s="48"/>
-    </row>
-    <row r="615" spans="5:10">
+    </row>
+    <row r="615" spans="5:5">
       <c r="E615" s="40"/>
-      <c r="J615" s="48"/>
-    </row>
-    <row r="616" spans="5:10">
+    </row>
+    <row r="616" spans="5:5">
       <c r="E616" s="40"/>
-      <c r="J616" s="48"/>
-    </row>
-    <row r="617" spans="5:10">
+    </row>
+    <row r="617" spans="5:5">
       <c r="E617" s="40"/>
-      <c r="J617" s="48"/>
-    </row>
-    <row r="618" spans="5:10">
+    </row>
+    <row r="618" spans="5:5">
       <c r="E618" s="40"/>
-      <c r="J618" s="48"/>
-    </row>
-    <row r="619" spans="5:10">
+    </row>
+    <row r="619" spans="5:5">
       <c r="E619" s="40"/>
-      <c r="J619" s="48"/>
-    </row>
-    <row r="620" spans="5:10">
+    </row>
+    <row r="620" spans="5:5">
       <c r="E620" s="40"/>
-      <c r="J620" s="48"/>
-    </row>
-    <row r="621" spans="5:10">
+    </row>
+    <row r="621" spans="5:5">
       <c r="E621" s="40"/>
-      <c r="J621" s="48"/>
-    </row>
-    <row r="622" spans="5:10">
+    </row>
+    <row r="622" spans="5:5">
       <c r="E622" s="40"/>
-      <c r="J622" s="48"/>
-    </row>
-    <row r="623" spans="5:10">
+    </row>
+    <row r="623" spans="5:5">
       <c r="E623" s="40"/>
-      <c r="J623" s="48"/>
-    </row>
-    <row r="624" spans="5:10">
+    </row>
+    <row r="624" spans="5:5">
       <c r="E624" s="40"/>
-      <c r="J624" s="48"/>
     </row>
     <row r="625" spans="5:10">
       <c r="E625" s="40"/>
-      <c r="J625" s="48"/>
     </row>
     <row r="626" spans="5:10">
       <c r="E626" s="40"/>
-      <c r="J626" s="48"/>
     </row>
     <row r="627" spans="5:10">
       <c r="E627" s="40"/>
-      <c r="J627" s="48"/>
     </row>
     <row r="628" spans="5:10">
       <c r="E628" s="40"/>
-      <c r="J628" s="48"/>
     </row>
     <row r="629" spans="5:10">
       <c r="E629" s="40"/>
-      <c r="J629" s="48"/>
     </row>
     <row r="630" spans="5:10">
       <c r="E630" s="40"/>
-      <c r="J630" s="48"/>
     </row>
     <row r="631" spans="5:10">
       <c r="E631" s="40"/>
-      <c r="J631" s="48"/>
     </row>
     <row r="632" spans="5:10">
       <c r="E632" s="40"/>
-      <c r="J632" s="48"/>
     </row>
     <row r="633" spans="5:10">
       <c r="E633" s="40"/>
-      <c r="J633" s="48"/>
     </row>
     <row r="634" spans="5:10">
       <c r="E634" s="40"/>
-      <c r="J634" s="48"/>
     </row>
     <row r="635" spans="5:10">
       <c r="E635" s="40"/>
-      <c r="J635" s="48"/>
     </row>
     <row r="636" spans="5:10">
       <c r="E636" s="40"/>
-      <c r="J636" s="48"/>
-    </row>
-    <row r="637" spans="5:10">
-      <c r="E637" s="40"/>
-      <c r="J637" s="48"/>
     </row>
     <row r="638" spans="5:10">
       <c r="E638" s="40"/>
@@ -7552,309 +9064,359 @@
       <c r="E647" s="40"/>
       <c r="J647" s="48"/>
     </row>
+    <row r="648" spans="5:10">
+      <c r="E648" s="40"/>
+      <c r="J648" s="48"/>
+    </row>
+    <row r="649" spans="5:10">
+      <c r="E649" s="40"/>
+      <c r="J649" s="48"/>
+    </row>
+    <row r="650" spans="5:10">
+      <c r="E650" s="40"/>
+      <c r="J650" s="48"/>
+    </row>
+    <row r="651" spans="5:10">
+      <c r="E651" s="40"/>
+      <c r="J651" s="48"/>
+    </row>
+    <row r="652" spans="5:10">
+      <c r="E652" s="40"/>
+      <c r="J652" s="48"/>
+    </row>
+    <row r="653" spans="5:10">
+      <c r="E653" s="40"/>
+      <c r="J653" s="48"/>
+    </row>
+    <row r="654" spans="5:10">
+      <c r="E654" s="40"/>
+      <c r="J654" s="48"/>
+    </row>
+    <row r="655" spans="5:10">
+      <c r="E655" s="40"/>
+      <c r="J655" s="48"/>
+    </row>
+    <row r="656" spans="5:10">
+      <c r="E656" s="40"/>
+      <c r="J656" s="48"/>
+    </row>
     <row r="657" spans="5:10">
       <c r="E657" s="40"/>
+      <c r="J657" s="48"/>
+    </row>
+    <row r="658" spans="5:10">
+      <c r="E658" s="40"/>
+      <c r="J658" s="48"/>
+    </row>
+    <row r="659" spans="5:10">
+      <c r="E659" s="40"/>
+      <c r="J659" s="48"/>
+    </row>
+    <row r="660" spans="5:10">
+      <c r="E660" s="40"/>
+      <c r="J660" s="48"/>
+    </row>
+    <row r="661" spans="5:10">
+      <c r="E661" s="40"/>
+      <c r="J661" s="48"/>
+    </row>
+    <row r="662" spans="5:10">
+      <c r="E662" s="40"/>
+      <c r="J662" s="48"/>
+    </row>
+    <row r="663" spans="5:10">
+      <c r="E663" s="40"/>
+      <c r="J663" s="48"/>
+    </row>
+    <row r="664" spans="5:10">
+      <c r="E664" s="40"/>
+      <c r="J664" s="48"/>
+    </row>
+    <row r="665" spans="5:10">
+      <c r="E665" s="40"/>
+      <c r="J665" s="48"/>
+    </row>
+    <row r="666" spans="5:10">
+      <c r="E666" s="40"/>
+      <c r="J666" s="48"/>
+    </row>
+    <row r="667" spans="5:10">
+      <c r="E667" s="40"/>
+      <c r="J667" s="48"/>
     </row>
     <row r="668" spans="5:10">
+      <c r="E668" s="40"/>
       <c r="J668" s="48"/>
     </row>
     <row r="669" spans="5:10">
+      <c r="E669" s="40"/>
       <c r="J669" s="48"/>
     </row>
     <row r="670" spans="5:10">
+      <c r="E670" s="40"/>
       <c r="J670" s="48"/>
     </row>
     <row r="671" spans="5:10">
+      <c r="E671" s="40"/>
       <c r="J671" s="48"/>
     </row>
     <row r="672" spans="5:10">
+      <c r="E672" s="40"/>
       <c r="J672" s="48"/>
     </row>
     <row r="673" spans="5:10">
+      <c r="E673" s="40"/>
       <c r="J673" s="48"/>
     </row>
     <row r="674" spans="5:10">
+      <c r="E674" s="40"/>
       <c r="J674" s="48"/>
     </row>
     <row r="675" spans="5:10">
+      <c r="E675" s="40"/>
       <c r="J675" s="48"/>
     </row>
     <row r="676" spans="5:10">
+      <c r="E676" s="40"/>
       <c r="J676" s="48"/>
     </row>
     <row r="677" spans="5:10">
+      <c r="E677" s="40"/>
       <c r="J677" s="48"/>
     </row>
     <row r="678" spans="5:10">
+      <c r="E678" s="40"/>
       <c r="J678" s="48"/>
     </row>
     <row r="679" spans="5:10">
+      <c r="E679" s="40"/>
       <c r="J679" s="48"/>
     </row>
     <row r="680" spans="5:10">
+      <c r="E680" s="40"/>
       <c r="J680" s="48"/>
     </row>
     <row r="681" spans="5:10">
+      <c r="E681" s="40"/>
       <c r="J681" s="48"/>
     </row>
     <row r="682" spans="5:10">
+      <c r="E682" s="40"/>
       <c r="J682" s="48"/>
     </row>
     <row r="683" spans="5:10">
+      <c r="E683" s="40"/>
       <c r="J683" s="48"/>
     </row>
     <row r="684" spans="5:10">
+      <c r="E684" s="40"/>
       <c r="J684" s="48"/>
     </row>
     <row r="685" spans="5:10">
+      <c r="E685" s="40"/>
       <c r="J685" s="48"/>
     </row>
-    <row r="686" spans="5:10">
-      <c r="J686" s="48"/>
-    </row>
-    <row r="687" spans="5:10">
-      <c r="E687" s="40"/>
-      <c r="J687" s="48"/>
-    </row>
-    <row r="697" spans="5:5">
-      <c r="E697" s="40"/>
-    </row>
-    <row r="708" spans="5:10">
-      <c r="E708" s="40"/>
+    <row r="695" spans="5:5">
+      <c r="E695" s="40"/>
+    </row>
+    <row r="706" spans="10:10">
+      <c r="J706" s="48"/>
+    </row>
+    <row r="707" spans="10:10">
+      <c r="J707" s="48"/>
+    </row>
+    <row r="708" spans="10:10">
       <c r="J708" s="48"/>
     </row>
-    <row r="709" spans="5:10">
-      <c r="E709" s="40"/>
+    <row r="709" spans="10:10">
       <c r="J709" s="48"/>
     </row>
-    <row r="710" spans="5:10">
-      <c r="E710" s="40"/>
+    <row r="710" spans="10:10">
       <c r="J710" s="48"/>
     </row>
-    <row r="711" spans="5:10">
-      <c r="E711" s="40"/>
+    <row r="711" spans="10:10">
       <c r="J711" s="48"/>
     </row>
-    <row r="712" spans="5:10">
-      <c r="E712" s="40"/>
+    <row r="712" spans="10:10">
       <c r="J712" s="48"/>
     </row>
-    <row r="713" spans="5:10">
-      <c r="E713" s="40"/>
+    <row r="713" spans="10:10">
       <c r="J713" s="48"/>
     </row>
-    <row r="714" spans="5:10">
-      <c r="E714" s="40"/>
+    <row r="714" spans="10:10">
       <c r="J714" s="48"/>
     </row>
-    <row r="715" spans="5:10">
-      <c r="E715" s="40"/>
+    <row r="715" spans="10:10">
       <c r="J715" s="48"/>
     </row>
-    <row r="716" spans="5:10">
-      <c r="E716" s="40"/>
+    <row r="716" spans="10:10">
       <c r="J716" s="48"/>
     </row>
-    <row r="717" spans="5:10">
-      <c r="E717" s="40"/>
+    <row r="717" spans="10:10">
       <c r="J717" s="48"/>
     </row>
-    <row r="718" spans="5:10">
-      <c r="E718" s="40"/>
+    <row r="718" spans="10:10">
       <c r="J718" s="48"/>
     </row>
-    <row r="719" spans="5:10">
-      <c r="E719" s="40"/>
+    <row r="719" spans="10:10">
       <c r="J719" s="48"/>
     </row>
-    <row r="720" spans="5:10">
-      <c r="E720" s="40"/>
+    <row r="720" spans="10:10">
       <c r="J720" s="48"/>
     </row>
     <row r="721" spans="5:10">
-      <c r="E721" s="40"/>
       <c r="J721" s="48"/>
     </row>
     <row r="722" spans="5:10">
-      <c r="E722" s="40"/>
       <c r="J722" s="48"/>
     </row>
     <row r="723" spans="5:10">
-      <c r="E723" s="40"/>
       <c r="J723" s="48"/>
+    </row>
+    <row r="724" spans="5:10">
+      <c r="J724" s="48"/>
     </row>
     <row r="725" spans="5:10">
       <c r="E725" s="40"/>
       <c r="J725" s="48"/>
     </row>
-    <row r="726" spans="5:10">
-      <c r="E726" s="40"/>
-      <c r="J726" s="48"/>
-    </row>
-    <row r="727" spans="5:10">
-      <c r="E727" s="40"/>
-      <c r="J727" s="48"/>
-    </row>
-    <row r="728" spans="5:10">
-      <c r="E728" s="40"/>
-      <c r="J728" s="48"/>
-    </row>
-    <row r="729" spans="5:10">
-      <c r="E729" s="40"/>
-      <c r="J729" s="48"/>
-    </row>
-    <row r="730" spans="5:10">
-      <c r="E730" s="40"/>
-      <c r="J730" s="48"/>
-    </row>
-    <row r="731" spans="5:10">
-      <c r="E731" s="40"/>
-      <c r="J731" s="48"/>
-    </row>
-    <row r="732" spans="5:10">
-      <c r="E732" s="40"/>
-      <c r="J732" s="48"/>
-    </row>
-    <row r="733" spans="5:10">
-      <c r="E733" s="40"/>
-      <c r="J733" s="48"/>
-    </row>
-    <row r="734" spans="5:10">
-      <c r="E734" s="40"/>
-      <c r="J734" s="48"/>
-    </row>
     <row r="735" spans="5:10">
       <c r="E735" s="40"/>
-      <c r="J735" s="48"/>
-    </row>
-    <row r="736" spans="5:10">
-      <c r="E736" s="40"/>
-      <c r="J736" s="48"/>
-    </row>
-    <row r="737" spans="5:10">
-      <c r="E737" s="40"/>
-      <c r="J737" s="48"/>
-    </row>
-    <row r="738" spans="5:10">
-      <c r="E738" s="40"/>
-      <c r="J738" s="48"/>
-    </row>
-    <row r="741" spans="5:10">
-      <c r="E741" s="40"/>
-    </row>
-    <row r="745" spans="5:10">
-      <c r="E745" s="40"/>
     </row>
     <row r="746" spans="5:10">
       <c r="E746" s="40"/>
+      <c r="J746" s="48"/>
     </row>
     <row r="747" spans="5:10">
       <c r="E747" s="40"/>
+      <c r="J747" s="48"/>
     </row>
     <row r="748" spans="5:10">
       <c r="E748" s="40"/>
+      <c r="J748" s="48"/>
+    </row>
+    <row r="749" spans="5:10">
+      <c r="E749" s="40"/>
+      <c r="J749" s="48"/>
+    </row>
+    <row r="750" spans="5:10">
+      <c r="E750" s="40"/>
+      <c r="J750" s="48"/>
     </row>
     <row r="751" spans="5:10">
       <c r="E751" s="40"/>
+      <c r="J751" s="48"/>
     </row>
     <row r="752" spans="5:10">
       <c r="E752" s="40"/>
-    </row>
-    <row r="753" spans="5:5">
+      <c r="J752" s="48"/>
+    </row>
+    <row r="753" spans="5:10">
       <c r="E753" s="40"/>
-    </row>
-    <row r="754" spans="5:5">
+      <c r="J753" s="48"/>
+    </row>
+    <row r="754" spans="5:10">
       <c r="E754" s="40"/>
-    </row>
-    <row r="757" spans="5:5">
+      <c r="J754" s="48"/>
+    </row>
+    <row r="755" spans="5:10">
+      <c r="E755" s="40"/>
+      <c r="J755" s="48"/>
+    </row>
+    <row r="756" spans="5:10">
+      <c r="E756" s="40"/>
+      <c r="J756" s="48"/>
+    </row>
+    <row r="757" spans="5:10">
       <c r="E757" s="40"/>
-    </row>
-    <row r="758" spans="5:5">
+      <c r="J757" s="48"/>
+    </row>
+    <row r="758" spans="5:10">
       <c r="E758" s="40"/>
-    </row>
-    <row r="759" spans="5:5">
+      <c r="J758" s="48"/>
+    </row>
+    <row r="759" spans="5:10">
       <c r="E759" s="40"/>
-    </row>
-    <row r="760" spans="5:5">
+      <c r="J759" s="48"/>
+    </row>
+    <row r="760" spans="5:10">
       <c r="E760" s="40"/>
-    </row>
-    <row r="761" spans="5:5">
+      <c r="J760" s="48"/>
+    </row>
+    <row r="761" spans="5:10">
       <c r="E761" s="40"/>
-    </row>
-    <row r="762" spans="5:5">
-      <c r="E762" s="40"/>
-    </row>
-    <row r="763" spans="5:5">
+      <c r="J761" s="48"/>
+    </row>
+    <row r="763" spans="5:10">
       <c r="E763" s="40"/>
-    </row>
-    <row r="764" spans="5:5">
+      <c r="J763" s="48"/>
+    </row>
+    <row r="764" spans="5:10">
       <c r="E764" s="40"/>
-    </row>
-    <row r="765" spans="5:5">
+      <c r="J764" s="48"/>
+    </row>
+    <row r="765" spans="5:10">
       <c r="E765" s="40"/>
-    </row>
-    <row r="766" spans="5:5">
+      <c r="J765" s="48"/>
+    </row>
+    <row r="766" spans="5:10">
       <c r="E766" s="40"/>
-    </row>
-    <row r="767" spans="5:5">
+      <c r="J766" s="48"/>
+    </row>
+    <row r="767" spans="5:10">
       <c r="E767" s="40"/>
-    </row>
-    <row r="768" spans="5:5">
+      <c r="J767" s="48"/>
+    </row>
+    <row r="768" spans="5:10">
       <c r="E768" s="40"/>
-    </row>
-    <row r="769" spans="5:5">
+      <c r="J768" s="48"/>
+    </row>
+    <row r="769" spans="5:10">
       <c r="E769" s="40"/>
-    </row>
-    <row r="770" spans="5:5">
+      <c r="J769" s="48"/>
+    </row>
+    <row r="770" spans="5:10">
       <c r="E770" s="40"/>
-    </row>
-    <row r="772" spans="5:5">
+      <c r="J770" s="48"/>
+    </row>
+    <row r="771" spans="5:10">
+      <c r="E771" s="40"/>
+      <c r="J771" s="48"/>
+    </row>
+    <row r="772" spans="5:10">
       <c r="E772" s="40"/>
-    </row>
-    <row r="773" spans="5:5">
+      <c r="J772" s="48"/>
+    </row>
+    <row r="773" spans="5:10">
       <c r="E773" s="40"/>
-    </row>
-    <row r="774" spans="5:5">
+      <c r="J773" s="48"/>
+    </row>
+    <row r="774" spans="5:10">
       <c r="E774" s="40"/>
-    </row>
-    <row r="775" spans="5:5">
+      <c r="J774" s="48"/>
+    </row>
+    <row r="775" spans="5:10">
       <c r="E775" s="40"/>
-    </row>
-    <row r="776" spans="5:5">
+      <c r="J775" s="48"/>
+    </row>
+    <row r="776" spans="5:10">
       <c r="E776" s="40"/>
-    </row>
-    <row r="777" spans="5:5">
-      <c r="E777" s="40"/>
-    </row>
-    <row r="778" spans="5:5">
-      <c r="E778" s="40"/>
-    </row>
-    <row r="779" spans="5:5">
+      <c r="J776" s="48"/>
+    </row>
+    <row r="779" spans="5:10">
       <c r="E779" s="40"/>
     </row>
-    <row r="780" spans="5:5">
-      <c r="E780" s="40"/>
-    </row>
-    <row r="781" spans="5:5">
-      <c r="E781" s="40"/>
-    </row>
-    <row r="782" spans="5:5">
-      <c r="E782" s="40"/>
-    </row>
-    <row r="783" spans="5:5">
+    <row r="783" spans="5:10">
       <c r="E783" s="40"/>
     </row>
-    <row r="784" spans="5:5">
+    <row r="784" spans="5:10">
       <c r="E784" s="40"/>
     </row>
     <row r="785" spans="5:5">
       <c r="E785" s="40"/>
     </row>
-    <row r="787" spans="5:5">
-      <c r="E787" s="40"/>
-    </row>
-    <row r="788" spans="5:5">
-      <c r="E788" s="40"/>
+    <row r="786" spans="5:5">
+      <c r="E786" s="40"/>
     </row>
     <row r="789" spans="5:5">
       <c r="E789" s="40"/>
@@ -7868,12 +9430,6 @@
     <row r="792" spans="5:5">
       <c r="E792" s="40"/>
     </row>
-    <row r="793" spans="5:5">
-      <c r="E793" s="40"/>
-    </row>
-    <row r="794" spans="5:5">
-      <c r="E794" s="40"/>
-    </row>
     <row r="795" spans="5:5">
       <c r="E795" s="40"/>
     </row>
@@ -7892,6 +9448,9 @@
     <row r="800" spans="5:5">
       <c r="E800" s="40"/>
     </row>
+    <row r="801" spans="5:5">
+      <c r="E801" s="40"/>
+    </row>
     <row r="802" spans="5:5">
       <c r="E802" s="40"/>
     </row>
@@ -7913,9 +9472,6 @@
     <row r="808" spans="5:5">
       <c r="E808" s="40"/>
     </row>
-    <row r="809" spans="5:5">
-      <c r="E809" s="40"/>
-    </row>
     <row r="810" spans="5:5">
       <c r="E810" s="40"/>
     </row>
@@ -7958,9 +9514,6 @@
     <row r="823" spans="5:5">
       <c r="E823" s="40"/>
     </row>
-    <row r="824" spans="5:5">
-      <c r="E824" s="40"/>
-    </row>
     <row r="825" spans="5:5">
       <c r="E825" s="40"/>
     </row>
@@ -7976,542 +9529,463 @@
     <row r="829" spans="5:5">
       <c r="E829" s="40"/>
     </row>
+    <row r="830" spans="5:5">
+      <c r="E830" s="40"/>
+    </row>
     <row r="831" spans="5:5">
       <c r="E831" s="40"/>
     </row>
+    <row r="832" spans="5:5">
+      <c r="E832" s="40"/>
+    </row>
+    <row r="833" spans="5:5">
+      <c r="E833" s="40"/>
+    </row>
+    <row r="834" spans="5:5">
+      <c r="E834" s="40"/>
+    </row>
+    <row r="835" spans="5:5">
+      <c r="E835" s="40"/>
+    </row>
+    <row r="836" spans="5:5">
+      <c r="E836" s="40"/>
+    </row>
+    <row r="837" spans="5:5">
+      <c r="E837" s="40"/>
+    </row>
+    <row r="838" spans="5:5">
+      <c r="E838" s="40"/>
+    </row>
+    <row r="840" spans="5:5">
+      <c r="E840" s="40"/>
+    </row>
+    <row r="841" spans="5:5">
+      <c r="E841" s="40"/>
+    </row>
+    <row r="842" spans="5:5">
+      <c r="E842" s="40"/>
+    </row>
+    <row r="843" spans="5:5">
+      <c r="E843" s="40"/>
+    </row>
     <row r="844" spans="5:5">
       <c r="E844" s="40"/>
     </row>
+    <row r="845" spans="5:5">
+      <c r="E845" s="40"/>
+    </row>
+    <row r="846" spans="5:5">
+      <c r="E846" s="40"/>
+    </row>
+    <row r="847" spans="5:5">
+      <c r="E847" s="40"/>
+    </row>
+    <row r="848" spans="5:5">
+      <c r="E848" s="40"/>
+    </row>
+    <row r="849" spans="5:5">
+      <c r="E849" s="40"/>
+    </row>
+    <row r="850" spans="5:5">
+      <c r="E850" s="40"/>
+    </row>
+    <row r="851" spans="5:5">
+      <c r="E851" s="40"/>
+    </row>
+    <row r="852" spans="5:5">
+      <c r="E852" s="40"/>
+    </row>
+    <row r="853" spans="5:5">
+      <c r="E853" s="40"/>
+    </row>
+    <row r="854" spans="5:5">
+      <c r="E854" s="40"/>
+    </row>
+    <row r="855" spans="5:5">
+      <c r="E855" s="40"/>
+    </row>
+    <row r="856" spans="5:5">
+      <c r="E856" s="40"/>
+    </row>
+    <row r="857" spans="5:5">
+      <c r="E857" s="40"/>
+    </row>
     <row r="858" spans="5:5">
       <c r="E858" s="40"/>
     </row>
+    <row r="859" spans="5:5">
+      <c r="E859" s="40"/>
+    </row>
     <row r="860" spans="5:5">
       <c r="E860" s="40"/>
     </row>
-    <row r="873" spans="5:5">
-      <c r="E873" s="40"/>
-    </row>
-    <row r="887" spans="5:5">
-      <c r="E887" s="40"/>
-    </row>
-    <row r="889" spans="5:5">
-      <c r="E889" s="40"/>
-    </row>
-    <row r="902" spans="5:5">
-      <c r="E902" s="40"/>
-    </row>
-    <row r="916" spans="5:5">
-      <c r="E916" s="40"/>
-    </row>
-    <row r="919" spans="5:5">
-      <c r="E919" s="40"/>
-    </row>
-    <row r="920" spans="5:5">
-      <c r="E920" s="40"/>
-    </row>
-    <row r="921" spans="5:5">
-      <c r="E921" s="40"/>
-    </row>
-    <row r="922" spans="5:5">
-      <c r="E922" s="40"/>
-    </row>
-    <row r="923" spans="5:5">
-      <c r="E923" s="40"/>
-    </row>
-    <row r="924" spans="5:5">
-      <c r="E924" s="40"/>
+    <row r="861" spans="5:5">
+      <c r="E861" s="40"/>
+    </row>
+    <row r="862" spans="5:5">
+      <c r="E862" s="40"/>
+    </row>
+    <row r="863" spans="5:5">
+      <c r="E863" s="40"/>
+    </row>
+    <row r="864" spans="5:5">
+      <c r="E864" s="40"/>
+    </row>
+    <row r="865" spans="5:5">
+      <c r="E865" s="40"/>
+    </row>
+    <row r="866" spans="5:5">
+      <c r="E866" s="40"/>
+    </row>
+    <row r="867" spans="5:5">
+      <c r="E867" s="40"/>
+    </row>
+    <row r="869" spans="5:5">
+      <c r="E869" s="40"/>
+    </row>
+    <row r="882" spans="5:5">
+      <c r="E882" s="40"/>
+    </row>
+    <row r="896" spans="5:5">
+      <c r="E896" s="40"/>
+    </row>
+    <row r="898" spans="5:5">
+      <c r="E898" s="40"/>
+    </row>
+    <row r="911" spans="5:5">
+      <c r="E911" s="40"/>
     </row>
     <row r="925" spans="5:5">
       <c r="E925" s="40"/>
     </row>
-    <row r="926" spans="5:5">
-      <c r="E926" s="40"/>
-    </row>
     <row r="927" spans="5:5">
       <c r="E927" s="40"/>
     </row>
-    <row r="928" spans="5:5">
-      <c r="E928" s="40"/>
-    </row>
-    <row r="929" spans="5:5">
-      <c r="E929" s="40"/>
-    </row>
-    <row r="930" spans="5:5">
-      <c r="E930" s="40"/>
-    </row>
-    <row r="931" spans="5:5">
-      <c r="E931" s="40"/>
-    </row>
-    <row r="932" spans="5:5">
-      <c r="E932" s="40"/>
-    </row>
-    <row r="941" spans="5:5">
-      <c r="E941" s="40"/>
-    </row>
-    <row r="952" spans="5:8">
-      <c r="F952" s="40"/>
-      <c r="H952" s="40"/>
-    </row>
-    <row r="953" spans="5:8">
-      <c r="F953" s="40"/>
-    </row>
-    <row r="954" spans="5:8">
-      <c r="F954" s="40"/>
-      <c r="H954" s="40"/>
-    </row>
-    <row r="958" spans="5:8">
+    <row r="940" spans="5:5">
+      <c r="E940" s="40"/>
+    </row>
+    <row r="954" spans="5:5">
+      <c r="E954" s="40"/>
+    </row>
+    <row r="957" spans="5:5">
+      <c r="E957" s="40"/>
+    </row>
+    <row r="958" spans="5:5">
       <c r="E958" s="40"/>
     </row>
-    <row r="975" spans="5:5">
-      <c r="E975" s="40"/>
-    </row>
-    <row r="992" spans="5:5">
-      <c r="E992" s="40"/>
-    </row>
-    <row r="1009" spans="5:8">
-      <c r="E1009" s="40"/>
-    </row>
-    <row r="1023" spans="5:8">
-      <c r="H1023" s="53"/>
-    </row>
-    <row r="1026" spans="5:5">
-      <c r="E1026" s="40"/>
-    </row>
-    <row r="1043" spans="5:5">
-      <c r="E1043" s="40"/>
-    </row>
-    <row r="1060" spans="5:5">
-      <c r="E1060" s="40"/>
-    </row>
-    <row r="1077" spans="5:5">
-      <c r="E1077" s="40"/>
-    </row>
-    <row r="1094" spans="5:5">
-      <c r="E1094" s="40"/>
-    </row>
-    <row r="1111" spans="5:5">
-      <c r="E1111" s="40"/>
-    </row>
-    <row r="1128" spans="5:5">
-      <c r="E1128" s="40"/>
-    </row>
-    <row r="1145" spans="5:5">
-      <c r="E1145" s="40"/>
-    </row>
-    <row r="1162" spans="5:5">
-      <c r="E1162" s="40"/>
-    </row>
-    <row r="1179" spans="5:5">
-      <c r="E1179" s="40"/>
-    </row>
-    <row r="1196" spans="5:5">
-      <c r="E1196" s="40"/>
-    </row>
-    <row r="1206" spans="10:10">
-      <c r="J1206" s="48"/>
-    </row>
-    <row r="1207" spans="10:10">
-      <c r="J1207" s="48"/>
-    </row>
-    <row r="1208" spans="10:10">
-      <c r="J1208" s="48"/>
-    </row>
-    <row r="1209" spans="10:10">
-      <c r="J1209" s="48"/>
-    </row>
-    <row r="1210" spans="10:10">
-      <c r="J1210" s="48"/>
-    </row>
-    <row r="1211" spans="10:10">
-      <c r="J1211" s="48"/>
-    </row>
-    <row r="1212" spans="10:10">
-      <c r="J1212" s="48"/>
-    </row>
-    <row r="1213" spans="10:10">
-      <c r="J1213" s="48"/>
-    </row>
-    <row r="1214" spans="10:10">
-      <c r="J1214" s="48"/>
-    </row>
-    <row r="1215" spans="10:10">
-      <c r="J1215" s="48"/>
-    </row>
-    <row r="1216" spans="10:10">
-      <c r="J1216" s="48"/>
-    </row>
-    <row r="1217" spans="5:10">
-      <c r="J1217" s="48"/>
-    </row>
-    <row r="1218" spans="5:10">
-      <c r="J1218" s="48"/>
-    </row>
-    <row r="1219" spans="5:10">
-      <c r="E1219" s="40"/>
-      <c r="J1219" s="48"/>
-    </row>
-    <row r="1240" spans="5:5">
-      <c r="E1240" s="40"/>
-    </row>
-    <row r="1255" spans="5:5">
-      <c r="E1255" s="40"/>
-    </row>
-    <row r="1270" spans="5:5">
-      <c r="E1270" s="40"/>
-    </row>
-    <row r="1285" spans="5:5">
-      <c r="E1285" s="40"/>
-    </row>
-    <row r="1301" spans="5:5">
-      <c r="E1301" s="40"/>
-    </row>
-    <row r="1309" spans="5:5">
-      <c r="E1309" s="40"/>
-    </row>
-    <row r="1318" spans="10:10">
-      <c r="J1318" s="48"/>
-    </row>
-    <row r="1319" spans="10:10">
-      <c r="J1319" s="48"/>
-    </row>
-    <row r="1320" spans="10:10">
-      <c r="J1320" s="48"/>
-    </row>
-    <row r="1321" spans="10:10">
-      <c r="J1321" s="48"/>
-    </row>
-    <row r="1322" spans="10:10">
-      <c r="J1322" s="48"/>
-    </row>
-    <row r="1323" spans="10:10">
-      <c r="J1323" s="48"/>
-    </row>
-    <row r="1324" spans="10:10">
-      <c r="J1324" s="48"/>
-    </row>
-    <row r="1325" spans="10:10">
-      <c r="J1325" s="48"/>
-    </row>
-    <row r="1326" spans="10:10">
-      <c r="J1326" s="48"/>
-    </row>
-    <row r="1327" spans="10:10">
-      <c r="J1327" s="48"/>
-    </row>
-    <row r="1328" spans="10:10">
-      <c r="J1328" s="48"/>
-    </row>
-    <row r="1329" spans="5:10">
-      <c r="J1329" s="48"/>
-    </row>
-    <row r="1330" spans="5:10">
-      <c r="J1330" s="48"/>
-    </row>
-    <row r="1331" spans="5:10">
-      <c r="J1331" s="48"/>
-    </row>
-    <row r="1332" spans="5:10">
-      <c r="J1332" s="48"/>
-    </row>
-    <row r="1333" spans="5:10">
-      <c r="J1333" s="48"/>
-    </row>
-    <row r="1334" spans="5:10">
-      <c r="J1334" s="48"/>
-    </row>
-    <row r="1335" spans="5:10">
-      <c r="J1335" s="48"/>
-    </row>
-    <row r="1336" spans="5:10">
-      <c r="J1336" s="48"/>
-    </row>
-    <row r="1337" spans="5:10">
-      <c r="E1337" s="40"/>
-      <c r="J1337" s="48"/>
-    </row>
-    <row r="1345" spans="5:5">
-      <c r="E1345" s="40"/>
-    </row>
-    <row r="1352" spans="5:5">
-      <c r="E1352" s="40"/>
-    </row>
-    <row r="1677" spans="6:8">
-      <c r="H1677" s="40"/>
-    </row>
-    <row r="1678" spans="6:8">
-      <c r="F1678" s="40"/>
-      <c r="H1678" s="40"/>
-    </row>
-    <row r="1679" spans="6:8">
-      <c r="F1679" s="40"/>
-      <c r="H1679" s="40"/>
-    </row>
-    <row r="1680" spans="6:8">
-      <c r="F1680" s="40"/>
-      <c r="H1680" s="40"/>
-    </row>
-    <row r="1681" spans="6:8">
-      <c r="F1681" s="40"/>
-      <c r="H1681" s="40"/>
-    </row>
-    <row r="1682" spans="6:8">
-      <c r="F1682" s="40"/>
-      <c r="H1682" s="40"/>
-    </row>
-    <row r="1683" spans="6:8">
-      <c r="F1683" s="40"/>
-      <c r="H1683" s="40"/>
-    </row>
-    <row r="1684" spans="6:8">
-      <c r="F1684" s="40"/>
-      <c r="H1684" s="40"/>
-    </row>
-    <row r="1685" spans="6:8">
-      <c r="H1685" s="40"/>
-    </row>
-    <row r="1687" spans="6:8">
-      <c r="H1687" s="40"/>
-    </row>
-    <row r="1689" spans="6:8">
-      <c r="H1689" s="40"/>
-    </row>
-    <row r="1691" spans="6:8">
-      <c r="H1691" s="40"/>
-    </row>
-    <row r="1693" spans="6:8">
-      <c r="H1693" s="40"/>
-    </row>
-    <row r="1694" spans="6:8">
-      <c r="F1694" s="40"/>
-      <c r="H1694" s="40"/>
-    </row>
-    <row r="1695" spans="6:8">
-      <c r="H1695" s="40"/>
-    </row>
-    <row r="1696" spans="6:8">
-      <c r="F1696" s="40"/>
-      <c r="H1696" s="42"/>
-    </row>
-    <row r="1697" spans="6:8">
-      <c r="H1697" s="40"/>
-    </row>
-    <row r="1698" spans="6:8">
-      <c r="F1698" s="41"/>
-      <c r="H1698" s="42"/>
-    </row>
-    <row r="1699" spans="6:8">
-      <c r="F1699" s="40"/>
-      <c r="H1699" s="40"/>
-    </row>
-    <row r="1700" spans="6:8">
-      <c r="F1700" s="40"/>
-      <c r="H1700" s="42"/>
-    </row>
-    <row r="1701" spans="6:8">
-      <c r="F1701" s="40"/>
-      <c r="H1701" s="40"/>
-    </row>
-    <row r="1702" spans="6:8">
-      <c r="F1702" s="40"/>
-      <c r="H1702" s="42"/>
-    </row>
-    <row r="1703" spans="6:8">
-      <c r="F1703" s="40"/>
-      <c r="H1703" s="40"/>
-    </row>
-    <row r="1704" spans="6:8">
-      <c r="F1704" s="42"/>
-      <c r="H1704" s="42"/>
-    </row>
-    <row r="1705" spans="6:8">
-      <c r="F1705" s="40"/>
-      <c r="G1705" s="40"/>
-      <c r="H1705" s="40"/>
-    </row>
-    <row r="1706" spans="6:8">
-      <c r="F1706" s="40"/>
-      <c r="G1706" s="40"/>
-      <c r="H1706" s="40"/>
-    </row>
-    <row r="1707" spans="6:8">
-      <c r="F1707" s="40"/>
-      <c r="G1707" s="40"/>
-      <c r="H1707" s="40"/>
-    </row>
-    <row r="1708" spans="6:8">
-      <c r="F1708" s="40"/>
-      <c r="G1708" s="40"/>
-      <c r="H1708" s="40"/>
-    </row>
-    <row r="1709" spans="6:8">
-      <c r="F1709" s="40"/>
-      <c r="G1709" s="40"/>
-      <c r="H1709" s="40"/>
-    </row>
-    <row r="1710" spans="6:8">
-      <c r="F1710" s="40"/>
-      <c r="G1710" s="40"/>
-      <c r="H1710" s="40"/>
-    </row>
-    <row r="1711" spans="6:8">
-      <c r="F1711" s="40"/>
-      <c r="G1711" s="40"/>
-      <c r="H1711" s="40"/>
-    </row>
-    <row r="1712" spans="6:8">
-      <c r="F1712" s="40"/>
-      <c r="G1712" s="40"/>
-      <c r="H1712" s="40"/>
-    </row>
-    <row r="1713" spans="6:8">
-      <c r="F1713" s="40"/>
-      <c r="G1713" s="40"/>
-      <c r="H1713" s="40"/>
-    </row>
-    <row r="1714" spans="6:8">
-      <c r="F1714" s="40"/>
-      <c r="G1714" s="40"/>
-      <c r="H1714" s="40"/>
+    <row r="959" spans="5:5">
+      <c r="E959" s="40"/>
+    </row>
+    <row r="960" spans="5:5">
+      <c r="E960" s="40"/>
+    </row>
+    <row r="961" spans="5:5">
+      <c r="E961" s="40"/>
+    </row>
+    <row r="962" spans="5:5">
+      <c r="E962" s="40"/>
+    </row>
+    <row r="963" spans="5:5">
+      <c r="E963" s="40"/>
+    </row>
+    <row r="964" spans="5:5">
+      <c r="E964" s="40"/>
+    </row>
+    <row r="965" spans="5:5">
+      <c r="E965" s="40"/>
+    </row>
+    <row r="966" spans="5:5">
+      <c r="E966" s="40"/>
+    </row>
+    <row r="967" spans="5:5">
+      <c r="E967" s="40"/>
+    </row>
+    <row r="968" spans="5:5">
+      <c r="E968" s="40"/>
+    </row>
+    <row r="969" spans="5:5">
+      <c r="E969" s="40"/>
+    </row>
+    <row r="970" spans="5:5">
+      <c r="E970" s="40"/>
+    </row>
+    <row r="979" spans="5:8">
+      <c r="E979" s="40"/>
+    </row>
+    <row r="990" spans="5:8">
+      <c r="F990" s="40"/>
+      <c r="H990" s="40"/>
+    </row>
+    <row r="991" spans="5:8">
+      <c r="F991" s="40"/>
+    </row>
+    <row r="992" spans="5:8">
+      <c r="F992" s="40"/>
+      <c r="H992" s="40"/>
+    </row>
+    <row r="996" spans="5:5">
+      <c r="E996" s="40"/>
+    </row>
+    <row r="1013" spans="5:5">
+      <c r="E1013" s="40"/>
+    </row>
+    <row r="1030" spans="5:5">
+      <c r="E1030" s="40"/>
+    </row>
+    <row r="1047" spans="5:5">
+      <c r="E1047" s="40"/>
+    </row>
+    <row r="1061" spans="5:8">
+      <c r="H1061" s="53"/>
+    </row>
+    <row r="1064" spans="5:8">
+      <c r="E1064" s="40"/>
+    </row>
+    <row r="1081" spans="5:5">
+      <c r="E1081" s="40"/>
+    </row>
+    <row r="1098" spans="5:5">
+      <c r="E1098" s="40"/>
+    </row>
+    <row r="1115" spans="5:5">
+      <c r="E1115" s="40"/>
+    </row>
+    <row r="1132" spans="5:5">
+      <c r="E1132" s="40"/>
+    </row>
+    <row r="1149" spans="5:5">
+      <c r="E1149" s="40"/>
+    </row>
+    <row r="1166" spans="5:5">
+      <c r="E1166" s="40"/>
+    </row>
+    <row r="1183" spans="5:5">
+      <c r="E1183" s="40"/>
+    </row>
+    <row r="1200" spans="5:5">
+      <c r="E1200" s="40"/>
+    </row>
+    <row r="1217" spans="5:5">
+      <c r="E1217" s="40"/>
+    </row>
+    <row r="1234" spans="5:10">
+      <c r="E1234" s="40"/>
+    </row>
+    <row r="1244" spans="5:10">
+      <c r="J1244" s="48"/>
+    </row>
+    <row r="1245" spans="5:10">
+      <c r="J1245" s="48"/>
+    </row>
+    <row r="1246" spans="5:10">
+      <c r="J1246" s="48"/>
+    </row>
+    <row r="1247" spans="5:10">
+      <c r="J1247" s="48"/>
+    </row>
+    <row r="1248" spans="5:10">
+      <c r="J1248" s="48"/>
+    </row>
+    <row r="1249" spans="5:10">
+      <c r="J1249" s="48"/>
+    </row>
+    <row r="1250" spans="5:10">
+      <c r="J1250" s="48"/>
+    </row>
+    <row r="1251" spans="5:10">
+      <c r="J1251" s="48"/>
+    </row>
+    <row r="1252" spans="5:10">
+      <c r="J1252" s="48"/>
+    </row>
+    <row r="1253" spans="5:10">
+      <c r="J1253" s="48"/>
+    </row>
+    <row r="1254" spans="5:10">
+      <c r="J1254" s="48"/>
+    </row>
+    <row r="1255" spans="5:10">
+      <c r="J1255" s="48"/>
+    </row>
+    <row r="1256" spans="5:10">
+      <c r="J1256" s="48"/>
+    </row>
+    <row r="1257" spans="5:10">
+      <c r="E1257" s="40"/>
+      <c r="J1257" s="48"/>
+    </row>
+    <row r="1278" spans="5:5">
+      <c r="E1278" s="40"/>
+    </row>
+    <row r="1293" spans="5:5">
+      <c r="E1293" s="40"/>
+    </row>
+    <row r="1308" spans="5:5">
+      <c r="E1308" s="40"/>
+    </row>
+    <row r="1323" spans="5:5">
+      <c r="E1323" s="40"/>
+    </row>
+    <row r="1339" spans="5:5">
+      <c r="E1339" s="40"/>
+    </row>
+    <row r="1347" spans="5:10">
+      <c r="E1347" s="40"/>
+    </row>
+    <row r="1356" spans="5:10">
+      <c r="J1356" s="48"/>
+    </row>
+    <row r="1357" spans="5:10">
+      <c r="J1357" s="48"/>
+    </row>
+    <row r="1358" spans="5:10">
+      <c r="J1358" s="48"/>
+    </row>
+    <row r="1359" spans="5:10">
+      <c r="J1359" s="48"/>
+    </row>
+    <row r="1360" spans="5:10">
+      <c r="J1360" s="48"/>
+    </row>
+    <row r="1361" spans="5:10">
+      <c r="J1361" s="48"/>
+    </row>
+    <row r="1362" spans="5:10">
+      <c r="J1362" s="48"/>
+    </row>
+    <row r="1363" spans="5:10">
+      <c r="J1363" s="48"/>
+    </row>
+    <row r="1364" spans="5:10">
+      <c r="J1364" s="48"/>
+    </row>
+    <row r="1365" spans="5:10">
+      <c r="J1365" s="48"/>
+    </row>
+    <row r="1366" spans="5:10">
+      <c r="J1366" s="48"/>
+    </row>
+    <row r="1367" spans="5:10">
+      <c r="J1367" s="48"/>
+    </row>
+    <row r="1368" spans="5:10">
+      <c r="J1368" s="48"/>
+    </row>
+    <row r="1369" spans="5:10">
+      <c r="J1369" s="48"/>
+    </row>
+    <row r="1370" spans="5:10">
+      <c r="J1370" s="48"/>
+    </row>
+    <row r="1371" spans="5:10">
+      <c r="J1371" s="48"/>
+    </row>
+    <row r="1372" spans="5:10">
+      <c r="J1372" s="48"/>
+    </row>
+    <row r="1373" spans="5:10">
+      <c r="J1373" s="48"/>
+    </row>
+    <row r="1374" spans="5:10">
+      <c r="J1374" s="48"/>
+    </row>
+    <row r="1375" spans="5:10">
+      <c r="E1375" s="40"/>
+      <c r="J1375" s="48"/>
+    </row>
+    <row r="1383" spans="5:5">
+      <c r="E1383" s="40"/>
+    </row>
+    <row r="1390" spans="5:5">
+      <c r="E1390" s="40"/>
     </row>
     <row r="1715" spans="6:8">
-      <c r="F1715" s="40"/>
-      <c r="G1715" s="40"/>
       <c r="H1715" s="40"/>
     </row>
     <row r="1716" spans="6:8">
       <c r="F1716" s="40"/>
-      <c r="G1716" s="40"/>
       <c r="H1716" s="40"/>
     </row>
     <row r="1717" spans="6:8">
       <c r="F1717" s="40"/>
-      <c r="G1717" s="40"/>
       <c r="H1717" s="40"/>
     </row>
     <row r="1718" spans="6:8">
       <c r="F1718" s="40"/>
-      <c r="G1718" s="40"/>
       <c r="H1718" s="40"/>
     </row>
     <row r="1719" spans="6:8">
       <c r="F1719" s="40"/>
-      <c r="G1719" s="40"/>
       <c r="H1719" s="40"/>
     </row>
     <row r="1720" spans="6:8">
       <c r="F1720" s="40"/>
-      <c r="G1720" s="40"/>
       <c r="H1720" s="40"/>
     </row>
     <row r="1721" spans="6:8">
       <c r="F1721" s="40"/>
-      <c r="G1721" s="40"/>
       <c r="H1721" s="40"/>
     </row>
     <row r="1722" spans="6:8">
       <c r="F1722" s="40"/>
-      <c r="G1722" s="40"/>
       <c r="H1722" s="40"/>
     </row>
     <row r="1723" spans="6:8">
-      <c r="F1723" s="40"/>
-      <c r="G1723" s="40"/>
       <c r="H1723" s="40"/>
     </row>
-    <row r="1724" spans="6:8">
-      <c r="F1724" s="40"/>
-      <c r="G1724" s="40"/>
-      <c r="H1724" s="40"/>
-    </row>
     <row r="1725" spans="6:8">
-      <c r="F1725" s="40"/>
-      <c r="G1725" s="40"/>
       <c r="H1725" s="40"/>
     </row>
-    <row r="1726" spans="6:8">
-      <c r="F1726" s="40"/>
-      <c r="G1726" s="40"/>
-      <c r="H1726" s="40"/>
-    </row>
     <row r="1727" spans="6:8">
-      <c r="F1727" s="40"/>
-      <c r="G1727" s="40"/>
       <c r="H1727" s="40"/>
     </row>
-    <row r="1728" spans="6:8">
-      <c r="F1728" s="40"/>
-      <c r="G1728" s="40"/>
-      <c r="H1728" s="40"/>
-    </row>
     <row r="1729" spans="6:8">
-      <c r="F1729" s="40"/>
-      <c r="G1729" s="40"/>
       <c r="H1729" s="40"/>
     </row>
-    <row r="1730" spans="6:8">
-      <c r="F1730" s="40"/>
-      <c r="G1730" s="40"/>
-      <c r="H1730" s="40"/>
-    </row>
     <row r="1731" spans="6:8">
-      <c r="F1731" s="40"/>
-      <c r="G1731" s="40"/>
       <c r="H1731" s="40"/>
     </row>
     <row r="1732" spans="6:8">
       <c r="F1732" s="40"/>
-      <c r="G1732" s="40"/>
       <c r="H1732" s="40"/>
     </row>
     <row r="1733" spans="6:8">
-      <c r="F1733" s="40"/>
-      <c r="G1733" s="40"/>
       <c r="H1733" s="40"/>
     </row>
     <row r="1734" spans="6:8">
       <c r="F1734" s="40"/>
-      <c r="G1734" s="40"/>
-      <c r="H1734" s="40"/>
+      <c r="H1734" s="42"/>
     </row>
     <row r="1735" spans="6:8">
-      <c r="F1735" s="40"/>
-      <c r="G1735" s="40"/>
       <c r="H1735" s="40"/>
     </row>
     <row r="1736" spans="6:8">
-      <c r="F1736" s="40"/>
-      <c r="G1736" s="40"/>
-      <c r="H1736" s="40"/>
+      <c r="F1736" s="41"/>
+      <c r="H1736" s="42"/>
     </row>
     <row r="1737" spans="6:8">
       <c r="F1737" s="40"/>
-      <c r="G1737" s="40"/>
       <c r="H1737" s="40"/>
     </row>
     <row r="1738" spans="6:8">
       <c r="F1738" s="40"/>
-      <c r="G1738" s="40"/>
-      <c r="H1738" s="40"/>
+      <c r="H1738" s="42"/>
     </row>
     <row r="1739" spans="6:8">
       <c r="F1739" s="40"/>
-      <c r="G1739" s="40"/>
       <c r="H1739" s="40"/>
     </row>
     <row r="1740" spans="6:8">
       <c r="F1740" s="40"/>
-      <c r="G1740" s="40"/>
-      <c r="H1740" s="40"/>
+      <c r="H1740" s="42"/>
     </row>
     <row r="1741" spans="6:8">
       <c r="F1741" s="40"/>
-      <c r="G1741" s="40"/>
       <c r="H1741" s="40"/>
     </row>
     <row r="1742" spans="6:8">
-      <c r="F1742" s="40"/>
-      <c r="G1742" s="40"/>
-      <c r="H1742" s="40"/>
+      <c r="F1742" s="42"/>
+      <c r="H1742" s="42"/>
     </row>
     <row r="1743" spans="6:8">
       <c r="F1743" s="40"/>
@@ -8519,26 +9993,39 @@
       <c r="H1743" s="40"/>
     </row>
     <row r="1744" spans="6:8">
+      <c r="F1744" s="40"/>
       <c r="G1744" s="40"/>
+      <c r="H1744" s="40"/>
     </row>
     <row r="1745" spans="6:8">
       <c r="F1745" s="40"/>
       <c r="G1745" s="40"/>
+      <c r="H1745" s="40"/>
     </row>
     <row r="1746" spans="6:8">
+      <c r="F1746" s="40"/>
       <c r="G1746" s="40"/>
+      <c r="H1746" s="40"/>
     </row>
     <row r="1747" spans="6:8">
+      <c r="F1747" s="40"/>
       <c r="G1747" s="40"/>
+      <c r="H1747" s="40"/>
     </row>
     <row r="1748" spans="6:8">
+      <c r="F1748" s="40"/>
       <c r="G1748" s="40"/>
+      <c r="H1748" s="40"/>
     </row>
     <row r="1749" spans="6:8">
+      <c r="F1749" s="40"/>
       <c r="G1749" s="40"/>
+      <c r="H1749" s="40"/>
     </row>
     <row r="1750" spans="6:8">
+      <c r="F1750" s="40"/>
       <c r="G1750" s="40"/>
+      <c r="H1750" s="40"/>
     </row>
     <row r="1751" spans="6:8">
       <c r="F1751" s="40"/>
@@ -8546,825 +10033,1003 @@
       <c r="H1751" s="40"/>
     </row>
     <row r="1752" spans="6:8">
+      <c r="F1752" s="40"/>
       <c r="G1752" s="40"/>
+      <c r="H1752" s="40"/>
     </row>
     <row r="1753" spans="6:8">
+      <c r="F1753" s="40"/>
       <c r="G1753" s="40"/>
+      <c r="H1753" s="40"/>
     </row>
     <row r="1754" spans="6:8">
+      <c r="F1754" s="40"/>
       <c r="G1754" s="40"/>
+      <c r="H1754" s="40"/>
     </row>
     <row r="1755" spans="6:8">
+      <c r="F1755" s="40"/>
       <c r="G1755" s="40"/>
+      <c r="H1755" s="40"/>
     </row>
     <row r="1756" spans="6:8">
+      <c r="F1756" s="40"/>
       <c r="G1756" s="40"/>
+      <c r="H1756" s="40"/>
     </row>
     <row r="1757" spans="6:8">
+      <c r="F1757" s="40"/>
       <c r="G1757" s="40"/>
+      <c r="H1757" s="40"/>
     </row>
     <row r="1758" spans="6:8">
+      <c r="F1758" s="40"/>
       <c r="G1758" s="40"/>
+      <c r="H1758" s="40"/>
     </row>
     <row r="1759" spans="6:8">
+      <c r="F1759" s="40"/>
       <c r="G1759" s="40"/>
+      <c r="H1759" s="40"/>
     </row>
     <row r="1760" spans="6:8">
+      <c r="F1760" s="40"/>
       <c r="G1760" s="40"/>
-    </row>
-    <row r="1761" spans="7:7">
+      <c r="H1760" s="40"/>
+    </row>
+    <row r="1761" spans="6:8">
+      <c r="F1761" s="40"/>
       <c r="G1761" s="40"/>
-    </row>
-    <row r="1803" spans="6:6">
-      <c r="F1803" s="40"/>
-    </row>
-    <row r="1820" spans="6:8">
-      <c r="H1820" s="40"/>
-    </row>
-    <row r="1822" spans="6:8">
-      <c r="F1822" s="40"/>
-      <c r="H1822" s="40"/>
-    </row>
-    <row r="1823" spans="6:8">
-      <c r="F1823" s="40"/>
-      <c r="H1823" s="40"/>
-    </row>
-    <row r="1824" spans="6:8">
-      <c r="H1824" s="40"/>
-    </row>
-    <row r="1826" spans="6:8">
-      <c r="F1826" s="40"/>
-      <c r="H1826" s="40"/>
-    </row>
-    <row r="1827" spans="6:8">
-      <c r="F1827" s="40"/>
-      <c r="H1827" s="40"/>
-    </row>
-    <row r="1828" spans="6:8">
-      <c r="F1828" s="40"/>
-      <c r="H1828" s="40"/>
-    </row>
-    <row r="1829" spans="6:8">
-      <c r="F1829" s="40"/>
-      <c r="H1829" s="40"/>
-    </row>
-    <row r="1830" spans="6:8">
-      <c r="F1830" s="40"/>
-      <c r="H1830" s="40"/>
-    </row>
-    <row r="1831" spans="6:8">
-      <c r="F1831" s="40"/>
-      <c r="H1831" s="40"/>
-    </row>
-    <row r="1832" spans="6:8">
-      <c r="H1832" s="40"/>
-    </row>
-    <row r="1833" spans="6:8">
-      <c r="H1833" s="40"/>
-    </row>
-    <row r="1834" spans="6:8">
-      <c r="H1834" s="40"/>
-    </row>
-    <row r="1836" spans="6:8">
-      <c r="H1836" s="40"/>
-    </row>
-    <row r="1837" spans="6:8">
-      <c r="F1837" s="40"/>
-      <c r="H1837" s="40"/>
-    </row>
-    <row r="1838" spans="6:8">
-      <c r="F1838" s="40"/>
-      <c r="H1838" s="40"/>
-    </row>
-    <row r="1839" spans="6:8">
-      <c r="F1839" s="40"/>
-      <c r="H1839" s="40"/>
-    </row>
-    <row r="1840" spans="6:8">
-      <c r="F1840" s="40"/>
-      <c r="H1840" s="40"/>
-    </row>
-    <row r="1841" spans="6:8">
+      <c r="H1761" s="40"/>
+    </row>
+    <row r="1762" spans="6:8">
+      <c r="F1762" s="40"/>
+      <c r="G1762" s="40"/>
+      <c r="H1762" s="40"/>
+    </row>
+    <row r="1763" spans="6:8">
+      <c r="F1763" s="40"/>
+      <c r="G1763" s="40"/>
+      <c r="H1763" s="40"/>
+    </row>
+    <row r="1764" spans="6:8">
+      <c r="F1764" s="40"/>
+      <c r="G1764" s="40"/>
+      <c r="H1764" s="40"/>
+    </row>
+    <row r="1765" spans="6:8">
+      <c r="F1765" s="40"/>
+      <c r="G1765" s="40"/>
+      <c r="H1765" s="40"/>
+    </row>
+    <row r="1766" spans="6:8">
+      <c r="F1766" s="40"/>
+      <c r="G1766" s="40"/>
+      <c r="H1766" s="40"/>
+    </row>
+    <row r="1767" spans="6:8">
+      <c r="F1767" s="40"/>
+      <c r="G1767" s="40"/>
+      <c r="H1767" s="40"/>
+    </row>
+    <row r="1768" spans="6:8">
+      <c r="F1768" s="40"/>
+      <c r="G1768" s="40"/>
+      <c r="H1768" s="40"/>
+    </row>
+    <row r="1769" spans="6:8">
+      <c r="F1769" s="40"/>
+      <c r="G1769" s="40"/>
+      <c r="H1769" s="40"/>
+    </row>
+    <row r="1770" spans="6:8">
+      <c r="F1770" s="40"/>
+      <c r="G1770" s="40"/>
+      <c r="H1770" s="40"/>
+    </row>
+    <row r="1771" spans="6:8">
+      <c r="F1771" s="40"/>
+      <c r="G1771" s="40"/>
+      <c r="H1771" s="40"/>
+    </row>
+    <row r="1772" spans="6:8">
+      <c r="F1772" s="40"/>
+      <c r="G1772" s="40"/>
+      <c r="H1772" s="40"/>
+    </row>
+    <row r="1773" spans="6:8">
+      <c r="F1773" s="40"/>
+      <c r="G1773" s="40"/>
+      <c r="H1773" s="40"/>
+    </row>
+    <row r="1774" spans="6:8">
+      <c r="F1774" s="40"/>
+      <c r="G1774" s="40"/>
+      <c r="H1774" s="40"/>
+    </row>
+    <row r="1775" spans="6:8">
+      <c r="F1775" s="40"/>
+      <c r="G1775" s="40"/>
+      <c r="H1775" s="40"/>
+    </row>
+    <row r="1776" spans="6:8">
+      <c r="F1776" s="40"/>
+      <c r="G1776" s="40"/>
+      <c r="H1776" s="40"/>
+    </row>
+    <row r="1777" spans="6:8">
+      <c r="F1777" s="40"/>
+      <c r="G1777" s="40"/>
+      <c r="H1777" s="40"/>
+    </row>
+    <row r="1778" spans="6:8">
+      <c r="F1778" s="40"/>
+      <c r="G1778" s="40"/>
+      <c r="H1778" s="40"/>
+    </row>
+    <row r="1779" spans="6:8">
+      <c r="F1779" s="40"/>
+      <c r="G1779" s="40"/>
+      <c r="H1779" s="40"/>
+    </row>
+    <row r="1780" spans="6:8">
+      <c r="F1780" s="40"/>
+      <c r="G1780" s="40"/>
+      <c r="H1780" s="40"/>
+    </row>
+    <row r="1781" spans="6:8">
+      <c r="F1781" s="40"/>
+      <c r="G1781" s="40"/>
+      <c r="H1781" s="40"/>
+    </row>
+    <row r="1782" spans="6:8">
+      <c r="G1782" s="40"/>
+    </row>
+    <row r="1783" spans="6:8">
+      <c r="F1783" s="40"/>
+      <c r="G1783" s="40"/>
+    </row>
+    <row r="1784" spans="6:8">
+      <c r="G1784" s="40"/>
+    </row>
+    <row r="1785" spans="6:8">
+      <c r="G1785" s="40"/>
+    </row>
+    <row r="1786" spans="6:8">
+      <c r="G1786" s="40"/>
+    </row>
+    <row r="1787" spans="6:8">
+      <c r="G1787" s="40"/>
+    </row>
+    <row r="1788" spans="6:8">
+      <c r="G1788" s="40"/>
+    </row>
+    <row r="1789" spans="6:8">
+      <c r="F1789" s="40"/>
+      <c r="G1789" s="40"/>
+      <c r="H1789" s="40"/>
+    </row>
+    <row r="1790" spans="6:8">
+      <c r="G1790" s="40"/>
+    </row>
+    <row r="1791" spans="6:8">
+      <c r="G1791" s="40"/>
+    </row>
+    <row r="1792" spans="6:8">
+      <c r="G1792" s="40"/>
+    </row>
+    <row r="1793" spans="7:7">
+      <c r="G1793" s="40"/>
+    </row>
+    <row r="1794" spans="7:7">
+      <c r="G1794" s="40"/>
+    </row>
+    <row r="1795" spans="7:7">
+      <c r="G1795" s="40"/>
+    </row>
+    <row r="1796" spans="7:7">
+      <c r="G1796" s="40"/>
+    </row>
+    <row r="1797" spans="7:7">
+      <c r="G1797" s="40"/>
+    </row>
+    <row r="1798" spans="7:7">
+      <c r="G1798" s="40"/>
+    </row>
+    <row r="1799" spans="7:7">
+      <c r="G1799" s="40"/>
+    </row>
+    <row r="1841" spans="6:6">
       <c r="F1841" s="40"/>
-      <c r="H1841" s="40"/>
-    </row>
-    <row r="1842" spans="6:8">
-      <c r="F1842" s="40"/>
-      <c r="H1842" s="40"/>
-    </row>
-    <row r="1843" spans="6:8">
-      <c r="F1843" s="40"/>
-      <c r="H1843" s="40"/>
-    </row>
-    <row r="1844" spans="6:8">
-      <c r="H1844" s="40"/>
-    </row>
-    <row r="1845" spans="6:8">
-      <c r="F1845" s="40"/>
-      <c r="H1845" s="40"/>
-    </row>
-    <row r="1846" spans="6:8">
-      <c r="F1846" s="40"/>
-      <c r="H1846" s="40"/>
-    </row>
-    <row r="1847" spans="6:8">
-      <c r="F1847" s="40"/>
-      <c r="H1847" s="40"/>
-    </row>
-    <row r="1848" spans="6:8">
-      <c r="F1848" s="40"/>
-      <c r="H1848" s="40"/>
-    </row>
-    <row r="1850" spans="6:8">
-      <c r="H1850" s="40"/>
-    </row>
-    <row r="1852" spans="6:8">
-      <c r="F1852" s="40"/>
-      <c r="H1852" s="40"/>
-    </row>
-    <row r="1854" spans="6:8">
-      <c r="H1854" s="40"/>
-    </row>
-    <row r="1856" spans="6:8">
-      <c r="H1856" s="40"/>
     </row>
     <row r="1858" spans="6:8">
       <c r="H1858" s="40"/>
     </row>
-    <row r="1859" spans="6:8">
-      <c r="F1859" s="40"/>
-      <c r="H1859" s="40"/>
-    </row>
     <row r="1860" spans="6:8">
+      <c r="F1860" s="40"/>
       <c r="H1860" s="40"/>
+    </row>
+    <row r="1861" spans="6:8">
+      <c r="F1861" s="40"/>
+      <c r="H1861" s="40"/>
     </row>
     <row r="1862" spans="6:8">
       <c r="H1862" s="40"/>
     </row>
-    <row r="1863" spans="6:8">
-      <c r="F1863" s="40"/>
-      <c r="H1863" s="40"/>
-    </row>
     <row r="1864" spans="6:8">
+      <c r="F1864" s="40"/>
       <c r="H1864" s="40"/>
     </row>
+    <row r="1865" spans="6:8">
+      <c r="F1865" s="40"/>
+      <c r="H1865" s="40"/>
+    </row>
     <row r="1866" spans="6:8">
+      <c r="F1866" s="40"/>
       <c r="H1866" s="40"/>
     </row>
+    <row r="1867" spans="6:8">
+      <c r="F1867" s="40"/>
+      <c r="H1867" s="40"/>
+    </row>
     <row r="1868" spans="6:8">
+      <c r="F1868" s="40"/>
       <c r="H1868" s="40"/>
+    </row>
+    <row r="1869" spans="6:8">
+      <c r="F1869" s="40"/>
+      <c r="H1869" s="40"/>
     </row>
     <row r="1870" spans="6:8">
       <c r="H1870" s="40"/>
     </row>
+    <row r="1871" spans="6:8">
+      <c r="H1871" s="40"/>
+    </row>
     <row r="1872" spans="6:8">
       <c r="H1872" s="40"/>
     </row>
     <row r="1874" spans="6:8">
-      <c r="F1874" s="40"/>
       <c r="H1874" s="40"/>
+    </row>
+    <row r="1875" spans="6:8">
+      <c r="F1875" s="40"/>
+      <c r="H1875" s="40"/>
+    </row>
+    <row r="1876" spans="6:8">
+      <c r="F1876" s="40"/>
+      <c r="H1876" s="40"/>
+    </row>
+    <row r="1877" spans="6:8">
+      <c r="F1877" s="40"/>
+      <c r="H1877" s="40"/>
+    </row>
+    <row r="1878" spans="6:8">
+      <c r="F1878" s="40"/>
+      <c r="H1878" s="40"/>
+    </row>
+    <row r="1879" spans="6:8">
+      <c r="F1879" s="40"/>
+      <c r="H1879" s="40"/>
+    </row>
+    <row r="1880" spans="6:8">
+      <c r="F1880" s="40"/>
+      <c r="H1880" s="40"/>
+    </row>
+    <row r="1881" spans="6:8">
+      <c r="F1881" s="40"/>
+      <c r="H1881" s="40"/>
+    </row>
+    <row r="1882" spans="6:8">
+      <c r="H1882" s="40"/>
+    </row>
+    <row r="1883" spans="6:8">
+      <c r="F1883" s="40"/>
+      <c r="H1883" s="40"/>
     </row>
     <row r="1884" spans="6:8">
       <c r="F1884" s="40"/>
-    </row>
-    <row r="1901" spans="8:8">
+      <c r="H1884" s="40"/>
+    </row>
+    <row r="1885" spans="6:8">
+      <c r="F1885" s="40"/>
+      <c r="H1885" s="40"/>
+    </row>
+    <row r="1886" spans="6:8">
+      <c r="F1886" s="40"/>
+      <c r="H1886" s="40"/>
+    </row>
+    <row r="1888" spans="6:8">
+      <c r="H1888" s="40"/>
+    </row>
+    <row r="1890" spans="6:8">
+      <c r="F1890" s="40"/>
+      <c r="H1890" s="40"/>
+    </row>
+    <row r="1892" spans="6:8">
+      <c r="H1892" s="40"/>
+    </row>
+    <row r="1894" spans="6:8">
+      <c r="H1894" s="40"/>
+    </row>
+    <row r="1896" spans="6:8">
+      <c r="H1896" s="40"/>
+    </row>
+    <row r="1897" spans="6:8">
+      <c r="F1897" s="40"/>
+      <c r="H1897" s="40"/>
+    </row>
+    <row r="1898" spans="6:8">
+      <c r="H1898" s="40"/>
+    </row>
+    <row r="1900" spans="6:8">
+      <c r="H1900" s="40"/>
+    </row>
+    <row r="1901" spans="6:8">
+      <c r="F1901" s="40"/>
       <c r="H1901" s="40"/>
     </row>
-    <row r="1903" spans="8:8">
-      <c r="H1903" s="40"/>
-    </row>
-    <row r="1905" spans="6:8">
-      <c r="F1905" s="40"/>
-      <c r="H1905" s="40"/>
-    </row>
-    <row r="1907" spans="6:8">
-      <c r="H1907" s="40"/>
-    </row>
-    <row r="1909" spans="6:8">
-      <c r="H1909" s="40"/>
-    </row>
-    <row r="1911" spans="6:8">
-      <c r="H1911" s="40"/>
-    </row>
-    <row r="1913" spans="6:8">
-      <c r="H1913" s="40"/>
-    </row>
-    <row r="1914" spans="6:8">
-      <c r="F1914" s="40"/>
-      <c r="H1914" s="40"/>
-    </row>
-    <row r="1915" spans="6:8">
-      <c r="H1915" s="40"/>
-    </row>
-    <row r="1917" spans="6:8">
-      <c r="H1917" s="40"/>
-    </row>
-    <row r="1919" spans="6:8">
-      <c r="H1919" s="40"/>
-    </row>
-    <row r="1921" spans="6:8">
-      <c r="H1921" s="40"/>
-    </row>
-    <row r="1922" spans="6:8">
+    <row r="1902" spans="6:8">
+      <c r="H1902" s="40"/>
+    </row>
+    <row r="1904" spans="6:8">
+      <c r="H1904" s="40"/>
+    </row>
+    <row r="1906" spans="6:8">
+      <c r="H1906" s="40"/>
+    </row>
+    <row r="1908" spans="6:8">
+      <c r="H1908" s="40"/>
+    </row>
+    <row r="1910" spans="6:8">
+      <c r="H1910" s="40"/>
+    </row>
+    <row r="1912" spans="6:8">
+      <c r="F1912" s="40"/>
+      <c r="H1912" s="40"/>
+    </row>
+    <row r="1922" spans="6:6">
       <c r="F1922" s="40"/>
-      <c r="H1922" s="40"/>
-    </row>
-    <row r="1923" spans="6:8">
-      <c r="H1923" s="40"/>
-    </row>
-    <row r="1925" spans="6:8">
-      <c r="H1925" s="40"/>
-    </row>
-    <row r="1927" spans="6:8">
-      <c r="H1927" s="40"/>
-    </row>
-    <row r="1929" spans="6:8">
-      <c r="H1929" s="40"/>
-    </row>
-    <row r="1931" spans="6:8">
-      <c r="F1931" s="40"/>
-      <c r="H1931" s="40"/>
-    </row>
-    <row r="1939" spans="6:6">
-      <c r="F1939" s="40"/>
-    </row>
-    <row r="1947" spans="6:6">
-      <c r="F1947" s="40"/>
-    </row>
-    <row r="1954" spans="6:8">
-      <c r="F1954" s="40"/>
-      <c r="H1954" s="40"/>
-    </row>
-    <row r="1970" spans="6:8">
-      <c r="F1970" s="41"/>
-      <c r="H1970" s="41"/>
-    </row>
-    <row r="1971" spans="6:8">
-      <c r="F1971" s="41"/>
-    </row>
-    <row r="1974" spans="6:8">
-      <c r="F1974" s="41"/>
-      <c r="H1974" s="41"/>
-    </row>
-    <row r="1975" spans="6:8">
-      <c r="F1975" s="40"/>
-    </row>
-    <row r="1988" spans="6:8">
-      <c r="F1988" s="40"/>
-      <c r="H1988" s="40"/>
-    </row>
-    <row r="2003" spans="6:8">
-      <c r="F2003" s="41"/>
-      <c r="H2003" s="41"/>
-    </row>
-    <row r="2004" spans="6:8">
-      <c r="F2004" s="41"/>
-    </row>
-    <row r="2007" spans="6:8">
-      <c r="F2007" s="41"/>
-      <c r="H2007" s="41"/>
+    </row>
+    <row r="1939" spans="6:8">
+      <c r="H1939" s="40"/>
+    </row>
+    <row r="1941" spans="6:8">
+      <c r="H1941" s="40"/>
+    </row>
+    <row r="1943" spans="6:8">
+      <c r="F1943" s="40"/>
+      <c r="H1943" s="40"/>
+    </row>
+    <row r="1945" spans="6:8">
+      <c r="H1945" s="40"/>
+    </row>
+    <row r="1947" spans="6:8">
+      <c r="H1947" s="40"/>
+    </row>
+    <row r="1949" spans="6:8">
+      <c r="H1949" s="40"/>
+    </row>
+    <row r="1951" spans="6:8">
+      <c r="H1951" s="40"/>
+    </row>
+    <row r="1952" spans="6:8">
+      <c r="F1952" s="40"/>
+      <c r="H1952" s="40"/>
+    </row>
+    <row r="1953" spans="6:8">
+      <c r="H1953" s="40"/>
+    </row>
+    <row r="1955" spans="6:8">
+      <c r="H1955" s="40"/>
+    </row>
+    <row r="1957" spans="6:8">
+      <c r="H1957" s="40"/>
+    </row>
+    <row r="1959" spans="6:8">
+      <c r="H1959" s="40"/>
+    </row>
+    <row r="1960" spans="6:8">
+      <c r="F1960" s="40"/>
+      <c r="H1960" s="40"/>
+    </row>
+    <row r="1961" spans="6:8">
+      <c r="H1961" s="40"/>
+    </row>
+    <row r="1963" spans="6:8">
+      <c r="H1963" s="40"/>
+    </row>
+    <row r="1965" spans="6:8">
+      <c r="H1965" s="40"/>
+    </row>
+    <row r="1967" spans="6:8">
+      <c r="H1967" s="40"/>
+    </row>
+    <row r="1969" spans="6:8">
+      <c r="F1969" s="40"/>
+      <c r="H1969" s="40"/>
+    </row>
+    <row r="1977" spans="6:8">
+      <c r="F1977" s="40"/>
+    </row>
+    <row r="1985" spans="6:8">
+      <c r="F1985" s="40"/>
+    </row>
+    <row r="1992" spans="6:8">
+      <c r="F1992" s="40"/>
+      <c r="H1992" s="40"/>
     </row>
     <row r="2008" spans="6:8">
-      <c r="F2008" s="40"/>
-    </row>
-    <row r="2021" spans="6:8">
-      <c r="F2021" s="40"/>
-      <c r="H2021" s="40"/>
-    </row>
-    <row r="2036" spans="6:8">
-      <c r="F2036" s="41"/>
-      <c r="H2036" s="41"/>
-    </row>
-    <row r="2037" spans="6:8">
-      <c r="F2037" s="41"/>
-    </row>
-    <row r="2040" spans="6:8">
-      <c r="F2040" s="41"/>
-      <c r="H2040" s="41"/>
+      <c r="F2008" s="41"/>
+      <c r="H2008" s="41"/>
+    </row>
+    <row r="2009" spans="6:8">
+      <c r="F2009" s="41"/>
+    </row>
+    <row r="2012" spans="6:8">
+      <c r="F2012" s="41"/>
+      <c r="H2012" s="41"/>
+    </row>
+    <row r="2013" spans="6:8">
+      <c r="F2013" s="40"/>
+    </row>
+    <row r="2026" spans="6:8">
+      <c r="F2026" s="40"/>
+      <c r="H2026" s="40"/>
     </row>
     <row r="2041" spans="6:8">
-      <c r="F2041" s="40"/>
-    </row>
-    <row r="2054" spans="6:8">
-      <c r="F2054" s="40"/>
-      <c r="H2054" s="40"/>
-    </row>
-    <row r="2062" spans="6:8">
-      <c r="F2062" s="40"/>
-      <c r="G2062" s="40"/>
-      <c r="H2062" s="40"/>
-    </row>
-    <row r="2069" spans="6:8">
-      <c r="F2069" s="41"/>
-      <c r="H2069" s="41"/>
-    </row>
-    <row r="2070" spans="6:8">
-      <c r="F2070" s="41"/>
-    </row>
-    <row r="2073" spans="6:8">
-      <c r="F2073" s="41"/>
-      <c r="H2073" s="41"/>
+      <c r="F2041" s="41"/>
+      <c r="H2041" s="41"/>
+    </row>
+    <row r="2042" spans="6:8">
+      <c r="F2042" s="41"/>
+    </row>
+    <row r="2045" spans="6:8">
+      <c r="F2045" s="41"/>
+      <c r="H2045" s="41"/>
+    </row>
+    <row r="2046" spans="6:8">
+      <c r="F2046" s="40"/>
+    </row>
+    <row r="2059" spans="6:8">
+      <c r="F2059" s="40"/>
+      <c r="H2059" s="40"/>
     </row>
     <row r="2074" spans="6:8">
-      <c r="F2074" s="40"/>
-    </row>
-    <row r="2087" spans="6:8">
-      <c r="F2087" s="40"/>
-      <c r="H2087" s="40"/>
-    </row>
-    <row r="2095" spans="6:8">
-      <c r="F2095" s="40"/>
-      <c r="G2095" s="40"/>
-      <c r="H2095" s="40"/>
-    </row>
-    <row r="2102" spans="6:8">
-      <c r="F2102" s="41"/>
-      <c r="H2102" s="41"/>
-    </row>
-    <row r="2103" spans="6:8">
-      <c r="F2103" s="41"/>
-    </row>
-    <row r="2106" spans="6:8">
-      <c r="F2106" s="41"/>
-      <c r="H2106" s="41"/>
+      <c r="F2074" s="41"/>
+      <c r="H2074" s="41"/>
+    </row>
+    <row r="2075" spans="6:8">
+      <c r="F2075" s="41"/>
+    </row>
+    <row r="2078" spans="6:8">
+      <c r="F2078" s="41"/>
+      <c r="H2078" s="41"/>
+    </row>
+    <row r="2079" spans="6:8">
+      <c r="F2079" s="40"/>
+    </row>
+    <row r="2092" spans="6:8">
+      <c r="F2092" s="40"/>
+      <c r="H2092" s="40"/>
+    </row>
+    <row r="2100" spans="6:8">
+      <c r="F2100" s="40"/>
+      <c r="G2100" s="40"/>
+      <c r="H2100" s="40"/>
     </row>
     <row r="2107" spans="6:8">
-      <c r="F2107" s="40"/>
-    </row>
-    <row r="2120" spans="6:8">
-      <c r="F2120" s="40"/>
-      <c r="H2120" s="40"/>
-    </row>
-    <row r="2128" spans="6:8">
-      <c r="F2128" s="40"/>
-      <c r="G2128" s="40"/>
-      <c r="H2128" s="40"/>
-    </row>
-    <row r="2135" spans="6:8">
-      <c r="F2135" s="41"/>
-      <c r="H2135" s="41"/>
-    </row>
-    <row r="2136" spans="6:8">
-      <c r="F2136" s="41"/>
-    </row>
-    <row r="2139" spans="6:8">
-      <c r="F2139" s="41"/>
-      <c r="H2139" s="41"/>
+      <c r="F2107" s="41"/>
+      <c r="H2107" s="41"/>
+    </row>
+    <row r="2108" spans="6:8">
+      <c r="F2108" s="41"/>
+    </row>
+    <row r="2111" spans="6:8">
+      <c r="F2111" s="41"/>
+      <c r="H2111" s="41"/>
+    </row>
+    <row r="2112" spans="6:8">
+      <c r="F2112" s="40"/>
+    </row>
+    <row r="2125" spans="6:8">
+      <c r="F2125" s="40"/>
+      <c r="H2125" s="40"/>
+    </row>
+    <row r="2133" spans="6:8">
+      <c r="F2133" s="40"/>
+      <c r="G2133" s="40"/>
+      <c r="H2133" s="40"/>
     </row>
     <row r="2140" spans="6:8">
-      <c r="F2140" s="40"/>
-    </row>
-    <row r="2153" spans="6:8">
-      <c r="F2153" s="40"/>
-      <c r="H2153" s="40"/>
-    </row>
-    <row r="2168" spans="6:8">
-      <c r="F2168" s="41"/>
-      <c r="H2168" s="41"/>
-    </row>
-    <row r="2169" spans="6:8">
-      <c r="F2169" s="41"/>
-    </row>
-    <row r="2172" spans="6:8">
-      <c r="F2172" s="41"/>
-      <c r="H2172" s="41"/>
+      <c r="F2140" s="41"/>
+      <c r="H2140" s="41"/>
+    </row>
+    <row r="2141" spans="6:8">
+      <c r="F2141" s="41"/>
+    </row>
+    <row r="2144" spans="6:8">
+      <c r="F2144" s="41"/>
+      <c r="H2144" s="41"/>
+    </row>
+    <row r="2145" spans="6:8">
+      <c r="F2145" s="40"/>
+    </row>
+    <row r="2158" spans="6:8">
+      <c r="F2158" s="40"/>
+      <c r="H2158" s="40"/>
+    </row>
+    <row r="2166" spans="6:8">
+      <c r="F2166" s="40"/>
+      <c r="G2166" s="40"/>
+      <c r="H2166" s="40"/>
     </row>
     <row r="2173" spans="6:8">
-      <c r="F2173" s="40"/>
-    </row>
-    <row r="2186" spans="6:8">
-      <c r="F2186" s="40"/>
-      <c r="H2186" s="40"/>
-    </row>
-    <row r="2201" spans="6:8">
-      <c r="F2201" s="41"/>
-      <c r="H2201" s="41"/>
-    </row>
-    <row r="2202" spans="6:8">
-      <c r="F2202" s="41"/>
-    </row>
-    <row r="2205" spans="6:8">
-      <c r="F2205" s="41"/>
-      <c r="H2205" s="41"/>
+      <c r="F2173" s="41"/>
+      <c r="H2173" s="41"/>
+    </row>
+    <row r="2174" spans="6:8">
+      <c r="F2174" s="41"/>
+    </row>
+    <row r="2177" spans="6:8">
+      <c r="F2177" s="41"/>
+      <c r="H2177" s="41"/>
+    </row>
+    <row r="2178" spans="6:8">
+      <c r="F2178" s="40"/>
+    </row>
+    <row r="2191" spans="6:8">
+      <c r="F2191" s="40"/>
+      <c r="H2191" s="40"/>
     </row>
     <row r="2206" spans="6:8">
-      <c r="F2206" s="40"/>
-    </row>
-    <row r="2219" spans="6:8">
-      <c r="F2219" s="40"/>
-      <c r="H2219" s="40"/>
-    </row>
-    <row r="2227" spans="6:8">
-      <c r="F2227" s="40"/>
-      <c r="G2227" s="40"/>
-      <c r="H2227" s="40"/>
-    </row>
-    <row r="2234" spans="6:8">
-      <c r="F2234" s="41"/>
-      <c r="H2234" s="41"/>
-    </row>
-    <row r="2235" spans="6:8">
-      <c r="F2235" s="41"/>
-    </row>
-    <row r="2238" spans="6:8">
-      <c r="F2238" s="41"/>
-      <c r="H2238" s="41"/>
+      <c r="F2206" s="41"/>
+      <c r="H2206" s="41"/>
+    </row>
+    <row r="2207" spans="6:8">
+      <c r="F2207" s="41"/>
+    </row>
+    <row r="2210" spans="6:8">
+      <c r="F2210" s="41"/>
+      <c r="H2210" s="41"/>
+    </row>
+    <row r="2211" spans="6:8">
+      <c r="F2211" s="40"/>
+    </row>
+    <row r="2224" spans="6:8">
+      <c r="F2224" s="40"/>
+      <c r="H2224" s="40"/>
     </row>
     <row r="2239" spans="6:8">
-      <c r="F2239" s="40"/>
-    </row>
-    <row r="2252" spans="6:8">
-      <c r="F2252" s="40"/>
-      <c r="H2252" s="40"/>
-    </row>
-    <row r="2260" spans="6:8">
-      <c r="F2260" s="40"/>
-      <c r="G2260" s="40"/>
-      <c r="H2260" s="40"/>
-    </row>
-    <row r="2267" spans="6:8">
-      <c r="F2267" s="41"/>
-      <c r="H2267" s="41"/>
-    </row>
-    <row r="2268" spans="6:8">
-      <c r="F2268" s="41"/>
-    </row>
-    <row r="2271" spans="6:8">
-      <c r="F2271" s="41"/>
-      <c r="H2271" s="41"/>
+      <c r="F2239" s="41"/>
+      <c r="H2239" s="41"/>
+    </row>
+    <row r="2240" spans="6:8">
+      <c r="F2240" s="41"/>
+    </row>
+    <row r="2243" spans="6:8">
+      <c r="F2243" s="41"/>
+      <c r="H2243" s="41"/>
+    </row>
+    <row r="2244" spans="6:8">
+      <c r="F2244" s="40"/>
+    </row>
+    <row r="2257" spans="6:8">
+      <c r="F2257" s="40"/>
+      <c r="H2257" s="40"/>
+    </row>
+    <row r="2265" spans="6:8">
+      <c r="F2265" s="40"/>
+      <c r="G2265" s="40"/>
+      <c r="H2265" s="40"/>
     </row>
     <row r="2272" spans="6:8">
-      <c r="F2272" s="40"/>
-    </row>
-    <row r="2285" spans="6:8">
-      <c r="F2285" s="40"/>
-      <c r="H2285" s="40"/>
-    </row>
-    <row r="2293" spans="6:8">
-      <c r="F2293" s="40"/>
-      <c r="G2293" s="40"/>
-      <c r="H2293" s="40"/>
-    </row>
-    <row r="2295" spans="6:8">
-      <c r="F2295" s="40"/>
-      <c r="G2295" s="40"/>
-      <c r="H2295" s="40"/>
-    </row>
-    <row r="2296" spans="6:8">
-      <c r="F2296" s="40"/>
-      <c r="G2296" s="40"/>
-      <c r="H2296" s="40"/>
-    </row>
-    <row r="2297" spans="6:8">
-      <c r="F2297" s="40"/>
-      <c r="G2297" s="40"/>
-      <c r="H2297" s="40"/>
+      <c r="F2272" s="41"/>
+      <c r="H2272" s="41"/>
+    </row>
+    <row r="2273" spans="6:8">
+      <c r="F2273" s="41"/>
+    </row>
+    <row r="2276" spans="6:8">
+      <c r="F2276" s="41"/>
+      <c r="H2276" s="41"/>
+    </row>
+    <row r="2277" spans="6:8">
+      <c r="F2277" s="40"/>
+    </row>
+    <row r="2290" spans="6:8">
+      <c r="F2290" s="40"/>
+      <c r="H2290" s="40"/>
     </row>
     <row r="2298" spans="6:8">
       <c r="F2298" s="40"/>
       <c r="G2298" s="40"/>
       <c r="H2298" s="40"/>
     </row>
-    <row r="2299" spans="6:8">
-      <c r="F2299" s="40"/>
-      <c r="G2299" s="40"/>
-      <c r="H2299" s="40"/>
-    </row>
-    <row r="2300" spans="6:8">
-      <c r="F2300" s="40"/>
-      <c r="G2300" s="40"/>
-      <c r="H2300" s="40"/>
-    </row>
-    <row r="2301" spans="6:8">
-      <c r="F2301" s="40"/>
-      <c r="G2301" s="40"/>
-      <c r="H2301" s="40"/>
-    </row>
-    <row r="2302" spans="6:8">
-      <c r="F2302" s="40"/>
-      <c r="G2302" s="40"/>
-      <c r="H2302" s="40"/>
-    </row>
-    <row r="2303" spans="6:8">
-      <c r="F2303" s="40"/>
-      <c r="G2303" s="40"/>
-      <c r="H2303" s="40"/>
-    </row>
-    <row r="2304" spans="6:8">
-      <c r="F2304" s="40"/>
-      <c r="G2304" s="40"/>
-      <c r="H2304" s="40"/>
-    </row>
     <row r="2305" spans="6:8">
-      <c r="F2305" s="40"/>
-      <c r="G2305" s="40"/>
-      <c r="H2305" s="40"/>
+      <c r="F2305" s="41"/>
+      <c r="H2305" s="41"/>
     </row>
     <row r="2306" spans="6:8">
-      <c r="F2306" s="40"/>
-      <c r="G2306" s="40"/>
-      <c r="H2306" s="40"/>
-    </row>
-    <row r="2307" spans="6:8">
-      <c r="F2307" s="40"/>
-      <c r="G2307" s="40"/>
-      <c r="H2307" s="40"/>
-    </row>
-    <row r="2308" spans="6:8">
-      <c r="F2308" s="40"/>
-      <c r="G2308" s="40"/>
-      <c r="H2308" s="40"/>
+      <c r="F2306" s="41"/>
     </row>
     <row r="2309" spans="6:8">
-      <c r="F2309" s="40"/>
-      <c r="G2309" s="40"/>
-      <c r="H2309" s="40"/>
+      <c r="F2309" s="41"/>
+      <c r="H2309" s="41"/>
     </row>
     <row r="2310" spans="6:8">
       <c r="F2310" s="40"/>
-      <c r="G2310" s="40"/>
-      <c r="H2310" s="40"/>
-    </row>
-    <row r="2311" spans="6:8">
-      <c r="F2311" s="40"/>
-      <c r="G2311" s="40"/>
-      <c r="H2311" s="40"/>
-    </row>
-    <row r="2312" spans="6:8">
-      <c r="F2312" s="40"/>
-      <c r="G2312" s="40"/>
-      <c r="H2312" s="40"/>
-    </row>
-    <row r="2313" spans="6:8">
-      <c r="F2313" s="40"/>
-      <c r="G2313" s="40"/>
-      <c r="H2313" s="40"/>
-    </row>
-    <row r="2314" spans="6:8">
-      <c r="F2314" s="40"/>
-      <c r="G2314" s="40"/>
-      <c r="H2314" s="40"/>
-    </row>
-    <row r="2315" spans="6:8">
-      <c r="F2315" s="40"/>
-      <c r="G2315" s="40"/>
-      <c r="H2315" s="40"/>
-    </row>
-    <row r="2316" spans="6:8">
-      <c r="F2316" s="40"/>
-      <c r="G2316" s="40"/>
-      <c r="H2316" s="40"/>
-    </row>
-    <row r="2317" spans="6:8">
-      <c r="F2317" s="40"/>
-      <c r="G2317" s="40"/>
-      <c r="H2317" s="40"/>
-    </row>
-    <row r="2318" spans="6:8">
-      <c r="F2318" s="40"/>
-      <c r="G2318" s="40"/>
-      <c r="H2318" s="40"/>
-    </row>
-    <row r="2319" spans="6:8">
-      <c r="F2319" s="40"/>
-      <c r="G2319" s="40"/>
-      <c r="H2319" s="40"/>
-    </row>
-    <row r="2320" spans="6:8">
-      <c r="F2320" s="40"/>
-      <c r="G2320" s="40"/>
-      <c r="H2320" s="40"/>
-    </row>
-    <row r="2321" spans="6:8">
-      <c r="F2321" s="40"/>
-      <c r="G2321" s="40"/>
-      <c r="H2321" s="40"/>
-    </row>
-    <row r="2322" spans="6:8">
-      <c r="F2322" s="40"/>
-      <c r="G2322" s="40"/>
-      <c r="H2322" s="40"/>
-    </row>
-    <row r="2324" spans="6:8">
-      <c r="F2324" s="40"/>
-      <c r="G2324" s="40"/>
-      <c r="H2324" s="40"/>
+    </row>
+    <row r="2323" spans="6:8">
+      <c r="F2323" s="40"/>
+      <c r="H2323" s="40"/>
+    </row>
+    <row r="2331" spans="6:8">
+      <c r="F2331" s="40"/>
+      <c r="G2331" s="40"/>
+      <c r="H2331" s="40"/>
+    </row>
+    <row r="2333" spans="6:8">
+      <c r="F2333" s="40"/>
+      <c r="G2333" s="40"/>
+      <c r="H2333" s="40"/>
+    </row>
+    <row r="2334" spans="6:8">
+      <c r="F2334" s="40"/>
+      <c r="G2334" s="40"/>
+      <c r="H2334" s="40"/>
+    </row>
+    <row r="2335" spans="6:8">
+      <c r="F2335" s="40"/>
+      <c r="G2335" s="40"/>
+      <c r="H2335" s="40"/>
+    </row>
+    <row r="2336" spans="6:8">
+      <c r="F2336" s="40"/>
+      <c r="G2336" s="40"/>
+      <c r="H2336" s="40"/>
     </row>
     <row r="2337" spans="6:8">
       <c r="F2337" s="40"/>
       <c r="G2337" s="40"/>
       <c r="H2337" s="40"/>
     </row>
+    <row r="2338" spans="6:8">
+      <c r="F2338" s="40"/>
+      <c r="G2338" s="40"/>
+      <c r="H2338" s="40"/>
+    </row>
+    <row r="2339" spans="6:8">
+      <c r="F2339" s="40"/>
+      <c r="G2339" s="40"/>
+      <c r="H2339" s="40"/>
+    </row>
+    <row r="2340" spans="6:8">
+      <c r="F2340" s="40"/>
+      <c r="G2340" s="40"/>
+      <c r="H2340" s="40"/>
+    </row>
+    <row r="2341" spans="6:8">
+      <c r="F2341" s="40"/>
+      <c r="G2341" s="40"/>
+      <c r="H2341" s="40"/>
+    </row>
+    <row r="2342" spans="6:8">
+      <c r="F2342" s="40"/>
+      <c r="G2342" s="40"/>
+      <c r="H2342" s="40"/>
+    </row>
+    <row r="2343" spans="6:8">
+      <c r="F2343" s="40"/>
+      <c r="G2343" s="40"/>
+      <c r="H2343" s="40"/>
+    </row>
+    <row r="2344" spans="6:8">
+      <c r="F2344" s="40"/>
+      <c r="G2344" s="40"/>
+      <c r="H2344" s="40"/>
+    </row>
+    <row r="2345" spans="6:8">
+      <c r="F2345" s="40"/>
+      <c r="G2345" s="40"/>
+      <c r="H2345" s="40"/>
+    </row>
+    <row r="2346" spans="6:8">
+      <c r="F2346" s="40"/>
+      <c r="G2346" s="40"/>
+      <c r="H2346" s="40"/>
+    </row>
+    <row r="2347" spans="6:8">
+      <c r="F2347" s="40"/>
+      <c r="G2347" s="40"/>
+      <c r="H2347" s="40"/>
+    </row>
+    <row r="2348" spans="6:8">
+      <c r="F2348" s="40"/>
+      <c r="G2348" s="40"/>
+      <c r="H2348" s="40"/>
+    </row>
+    <row r="2349" spans="6:8">
+      <c r="F2349" s="40"/>
+      <c r="G2349" s="40"/>
+      <c r="H2349" s="40"/>
+    </row>
+    <row r="2350" spans="6:8">
+      <c r="F2350" s="40"/>
+      <c r="G2350" s="40"/>
+      <c r="H2350" s="40"/>
+    </row>
     <row r="2351" spans="6:8">
       <c r="F2351" s="40"/>
       <c r="G2351" s="40"/>
       <c r="H2351" s="40"/>
     </row>
+    <row r="2352" spans="6:8">
+      <c r="F2352" s="40"/>
+      <c r="G2352" s="40"/>
+      <c r="H2352" s="40"/>
+    </row>
     <row r="2353" spans="6:8">
       <c r="F2353" s="40"/>
       <c r="G2353" s="40"/>
       <c r="H2353" s="40"/>
     </row>
-    <row r="2366" spans="6:8">
-      <c r="F2366" s="40"/>
-      <c r="G2366" s="40"/>
-      <c r="H2366" s="40"/>
-    </row>
-    <row r="2380" spans="6:8">
-      <c r="F2380" s="40"/>
-      <c r="G2380" s="40"/>
-      <c r="H2380" s="40"/>
-    </row>
-    <row r="2382" spans="6:8">
-      <c r="F2382" s="40"/>
-      <c r="G2382" s="40"/>
-      <c r="H2382" s="40"/>
-    </row>
-    <row r="2395" spans="6:8">
-      <c r="F2395" s="40"/>
-      <c r="G2395" s="40"/>
-      <c r="H2395" s="40"/>
-    </row>
-    <row r="2409" spans="6:8">
-      <c r="F2409" s="40"/>
-      <c r="G2409" s="40"/>
-      <c r="H2409" s="40"/>
-    </row>
-    <row r="2412" spans="6:8">
-      <c r="F2412" s="40"/>
-      <c r="G2412" s="40"/>
-      <c r="H2412" s="40"/>
-    </row>
-    <row r="2413" spans="6:8">
-      <c r="F2413" s="40"/>
-      <c r="G2413" s="40"/>
-      <c r="H2413" s="40"/>
-    </row>
-    <row r="2414" spans="6:8">
-      <c r="F2414" s="40"/>
-      <c r="G2414" s="40"/>
-      <c r="H2414" s="40"/>
-    </row>
-    <row r="2415" spans="6:8">
-      <c r="F2415" s="40"/>
-      <c r="G2415" s="40"/>
-      <c r="H2415" s="40"/>
-    </row>
-    <row r="2416" spans="6:8">
-      <c r="F2416" s="40"/>
-      <c r="G2416" s="40"/>
-      <c r="H2416" s="40"/>
-    </row>
-    <row r="2417" spans="6:8">
-      <c r="F2417" s="40"/>
-      <c r="G2417" s="40"/>
-      <c r="H2417" s="40"/>
+    <row r="2354" spans="6:8">
+      <c r="F2354" s="40"/>
+      <c r="G2354" s="40"/>
+      <c r="H2354" s="40"/>
+    </row>
+    <row r="2355" spans="6:8">
+      <c r="F2355" s="40"/>
+      <c r="G2355" s="40"/>
+      <c r="H2355" s="40"/>
+    </row>
+    <row r="2356" spans="6:8">
+      <c r="F2356" s="40"/>
+      <c r="G2356" s="40"/>
+      <c r="H2356" s="40"/>
+    </row>
+    <row r="2357" spans="6:8">
+      <c r="F2357" s="40"/>
+      <c r="G2357" s="40"/>
+      <c r="H2357" s="40"/>
+    </row>
+    <row r="2358" spans="6:8">
+      <c r="F2358" s="40"/>
+      <c r="G2358" s="40"/>
+      <c r="H2358" s="40"/>
+    </row>
+    <row r="2359" spans="6:8">
+      <c r="F2359" s="40"/>
+      <c r="G2359" s="40"/>
+      <c r="H2359" s="40"/>
+    </row>
+    <row r="2360" spans="6:8">
+      <c r="F2360" s="40"/>
+      <c r="G2360" s="40"/>
+      <c r="H2360" s="40"/>
+    </row>
+    <row r="2362" spans="6:8">
+      <c r="F2362" s="40"/>
+      <c r="G2362" s="40"/>
+      <c r="H2362" s="40"/>
+    </row>
+    <row r="2375" spans="6:8">
+      <c r="F2375" s="40"/>
+      <c r="G2375" s="40"/>
+      <c r="H2375" s="40"/>
+    </row>
+    <row r="2389" spans="6:8">
+      <c r="F2389" s="40"/>
+      <c r="G2389" s="40"/>
+      <c r="H2389" s="40"/>
+    </row>
+    <row r="2391" spans="6:8">
+      <c r="F2391" s="40"/>
+      <c r="G2391" s="40"/>
+      <c r="H2391" s="40"/>
+    </row>
+    <row r="2404" spans="6:8">
+      <c r="F2404" s="40"/>
+      <c r="G2404" s="40"/>
+      <c r="H2404" s="40"/>
     </row>
     <row r="2418" spans="6:8">
       <c r="F2418" s="40"/>
       <c r="G2418" s="40"/>
       <c r="H2418" s="40"/>
     </row>
-    <row r="2419" spans="6:8">
-      <c r="F2419" s="40"/>
-      <c r="G2419" s="40"/>
-      <c r="H2419" s="40"/>
-    </row>
     <row r="2420" spans="6:8">
       <c r="F2420" s="40"/>
       <c r="G2420" s="40"/>
       <c r="H2420" s="40"/>
     </row>
-    <row r="2421" spans="6:8">
-      <c r="F2421" s="40"/>
-      <c r="G2421" s="40"/>
-      <c r="H2421" s="40"/>
-    </row>
-    <row r="2422" spans="6:8">
-      <c r="F2422" s="40"/>
-      <c r="G2422" s="40"/>
-      <c r="H2422" s="40"/>
-    </row>
-    <row r="2423" spans="6:8">
-      <c r="F2423" s="40"/>
-      <c r="G2423" s="40"/>
-      <c r="H2423" s="40"/>
-    </row>
-    <row r="2424" spans="6:8">
-      <c r="F2424" s="40"/>
-      <c r="G2424" s="40"/>
-      <c r="H2424" s="40"/>
-    </row>
-    <row r="2425" spans="6:8">
-      <c r="F2425" s="40"/>
-      <c r="G2425" s="40"/>
-      <c r="H2425" s="40"/>
-    </row>
-    <row r="2434" spans="6:8">
-      <c r="F2434" s="40"/>
-      <c r="G2434" s="40"/>
-      <c r="H2434" s="40"/>
+    <row r="2433" spans="6:8">
+      <c r="F2433" s="40"/>
+      <c r="G2433" s="40"/>
+      <c r="H2433" s="40"/>
+    </row>
+    <row r="2447" spans="6:8">
+      <c r="F2447" s="40"/>
+      <c r="G2447" s="40"/>
+      <c r="H2447" s="40"/>
+    </row>
+    <row r="2450" spans="6:8">
+      <c r="F2450" s="40"/>
+      <c r="G2450" s="40"/>
+      <c r="H2450" s="40"/>
     </row>
     <row r="2451" spans="6:8">
       <c r="F2451" s="40"/>
       <c r="G2451" s="40"/>
       <c r="H2451" s="40"/>
     </row>
-    <row r="2468" spans="6:8">
-      <c r="F2468" s="40"/>
-      <c r="G2468" s="40"/>
-      <c r="H2468" s="40"/>
-    </row>
-    <row r="2485" spans="6:8">
-      <c r="F2485" s="40"/>
-      <c r="G2485" s="40"/>
-      <c r="H2485" s="40"/>
-    </row>
-    <row r="2502" spans="6:6">
-      <c r="F2502" s="40"/>
-    </row>
-    <row r="2519" spans="6:6">
-      <c r="F2519" s="40"/>
-    </row>
-    <row r="2536" spans="6:6">
-      <c r="F2536" s="40"/>
-    </row>
-    <row r="2553" spans="6:6">
-      <c r="F2553" s="40"/>
-    </row>
-    <row r="2570" spans="6:6">
-      <c r="F2570" s="40"/>
-    </row>
-    <row r="2587" spans="6:6">
-      <c r="F2587" s="40"/>
-    </row>
-    <row r="2604" spans="6:6">
-      <c r="F2604" s="40"/>
-    </row>
-    <row r="2621" spans="6:8">
-      <c r="F2621" s="40"/>
-      <c r="H2621" s="40"/>
-    </row>
-    <row r="2638" spans="6:6">
-      <c r="F2638" s="40"/>
-    </row>
-    <row r="2672" spans="6:6">
-      <c r="F2672" s="40"/>
-    </row>
-    <row r="2689" spans="6:6">
-      <c r="F2689" s="40"/>
-    </row>
-    <row r="2712" spans="6:8">
-      <c r="F2712" s="40"/>
-      <c r="H2712" s="40"/>
-    </row>
-    <row r="2733" spans="6:6">
-      <c r="F2733" s="40"/>
-    </row>
-    <row r="2748" spans="6:8">
-      <c r="F2748" s="40"/>
-      <c r="G2748" s="40"/>
-      <c r="H2748" s="40"/>
-    </row>
-    <row r="2763" spans="6:8">
-      <c r="F2763" s="40"/>
-      <c r="H2763" s="40"/>
-    </row>
-    <row r="2778" spans="6:8">
-      <c r="F2778" s="40"/>
-      <c r="G2778" s="40"/>
-      <c r="H2778" s="40"/>
-    </row>
-    <row r="2794" spans="6:8">
-      <c r="F2794" s="40"/>
-      <c r="G2794" s="40"/>
-      <c r="H2794" s="40"/>
-    </row>
-    <row r="2802" spans="6:8">
-      <c r="F2802" s="40"/>
-      <c r="G2802" s="40"/>
-      <c r="H2802" s="40"/>
-    </row>
-    <row r="2830" spans="6:8">
-      <c r="F2830" s="40"/>
-      <c r="G2830" s="40"/>
-      <c r="H2830" s="40"/>
-    </row>
-    <row r="2838" spans="6:8">
-      <c r="F2838" s="40"/>
-      <c r="G2838" s="40"/>
-      <c r="H2838" s="40"/>
-    </row>
-    <row r="2845" spans="6:8">
-      <c r="F2845" s="40"/>
-      <c r="G2845" s="40"/>
-      <c r="H2845" s="40"/>
+    <row r="2452" spans="6:8">
+      <c r="F2452" s="40"/>
+      <c r="G2452" s="40"/>
+      <c r="H2452" s="40"/>
+    </row>
+    <row r="2453" spans="6:8">
+      <c r="F2453" s="40"/>
+      <c r="G2453" s="40"/>
+      <c r="H2453" s="40"/>
+    </row>
+    <row r="2454" spans="6:8">
+      <c r="F2454" s="40"/>
+      <c r="G2454" s="40"/>
+      <c r="H2454" s="40"/>
+    </row>
+    <row r="2455" spans="6:8">
+      <c r="F2455" s="40"/>
+      <c r="G2455" s="40"/>
+      <c r="H2455" s="40"/>
+    </row>
+    <row r="2456" spans="6:8">
+      <c r="F2456" s="40"/>
+      <c r="G2456" s="40"/>
+      <c r="H2456" s="40"/>
+    </row>
+    <row r="2457" spans="6:8">
+      <c r="F2457" s="40"/>
+      <c r="G2457" s="40"/>
+      <c r="H2457" s="40"/>
+    </row>
+    <row r="2458" spans="6:8">
+      <c r="F2458" s="40"/>
+      <c r="G2458" s="40"/>
+      <c r="H2458" s="40"/>
+    </row>
+    <row r="2459" spans="6:8">
+      <c r="F2459" s="40"/>
+      <c r="G2459" s="40"/>
+      <c r="H2459" s="40"/>
+    </row>
+    <row r="2460" spans="6:8">
+      <c r="F2460" s="40"/>
+      <c r="G2460" s="40"/>
+      <c r="H2460" s="40"/>
+    </row>
+    <row r="2461" spans="6:8">
+      <c r="F2461" s="40"/>
+      <c r="G2461" s="40"/>
+      <c r="H2461" s="40"/>
+    </row>
+    <row r="2462" spans="6:8">
+      <c r="F2462" s="40"/>
+      <c r="G2462" s="40"/>
+      <c r="H2462" s="40"/>
+    </row>
+    <row r="2463" spans="6:8">
+      <c r="F2463" s="40"/>
+      <c r="G2463" s="40"/>
+      <c r="H2463" s="40"/>
+    </row>
+    <row r="2472" spans="6:8">
+      <c r="F2472" s="40"/>
+      <c r="G2472" s="40"/>
+      <c r="H2472" s="40"/>
+    </row>
+    <row r="2489" spans="6:8">
+      <c r="F2489" s="40"/>
+      <c r="G2489" s="40"/>
+      <c r="H2489" s="40"/>
+    </row>
+    <row r="2506" spans="6:8">
+      <c r="F2506" s="40"/>
+      <c r="G2506" s="40"/>
+      <c r="H2506" s="40"/>
+    </row>
+    <row r="2523" spans="6:8">
+      <c r="F2523" s="40"/>
+      <c r="G2523" s="40"/>
+      <c r="H2523" s="40"/>
+    </row>
+    <row r="2540" spans="6:6">
+      <c r="F2540" s="40"/>
+    </row>
+    <row r="2557" spans="6:6">
+      <c r="F2557" s="40"/>
+    </row>
+    <row r="2574" spans="6:6">
+      <c r="F2574" s="40"/>
+    </row>
+    <row r="2591" spans="6:6">
+      <c r="F2591" s="40"/>
+    </row>
+    <row r="2608" spans="6:6">
+      <c r="F2608" s="40"/>
+    </row>
+    <row r="2625" spans="6:6">
+      <c r="F2625" s="40"/>
+    </row>
+    <row r="2642" spans="6:6">
+      <c r="F2642" s="40"/>
+    </row>
+    <row r="2659" spans="6:8">
+      <c r="F2659" s="40"/>
+      <c r="H2659" s="40"/>
+    </row>
+    <row r="2676" spans="6:6">
+      <c r="F2676" s="40"/>
+    </row>
+    <row r="2710" spans="6:6">
+      <c r="F2710" s="40"/>
+    </row>
+    <row r="2727" spans="6:6">
+      <c r="F2727" s="40"/>
+    </row>
+    <row r="2750" spans="6:8">
+      <c r="F2750" s="40"/>
+      <c r="H2750" s="40"/>
+    </row>
+    <row r="2771" spans="6:6">
+      <c r="F2771" s="40"/>
+    </row>
+    <row r="2786" spans="6:8">
+      <c r="F2786" s="40"/>
+      <c r="G2786" s="40"/>
+      <c r="H2786" s="40"/>
+    </row>
+    <row r="2801" spans="6:8">
+      <c r="F2801" s="40"/>
+      <c r="H2801" s="40"/>
+    </row>
+    <row r="2816" spans="6:8">
+      <c r="F2816" s="40"/>
+      <c r="G2816" s="40"/>
+      <c r="H2816" s="40"/>
+    </row>
+    <row r="2832" spans="6:8">
+      <c r="F2832" s="40"/>
+      <c r="G2832" s="40"/>
+      <c r="H2832" s="40"/>
+    </row>
+    <row r="2840" spans="6:8">
+      <c r="F2840" s="40"/>
+      <c r="G2840" s="40"/>
+      <c r="H2840" s="40"/>
+    </row>
+    <row r="2868" spans="6:8">
+      <c r="F2868" s="40"/>
+      <c r="G2868" s="40"/>
+      <c r="H2868" s="40"/>
+    </row>
+    <row r="2876" spans="6:8">
+      <c r="F2876" s="40"/>
+      <c r="G2876" s="40"/>
+      <c r="H2876" s="40"/>
+    </row>
+    <row r="2883" spans="6:8">
+      <c r="F2883" s="40"/>
+      <c r="G2883" s="40"/>
+      <c r="H2883" s="40"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A9:J93">
-    <sortCondition ref="A9:A93"/>
-    <sortCondition ref="C9:C93"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A9:J131">
+    <sortCondition ref="A9:A131"/>
+    <sortCondition ref="C9:C131"/>
   </sortState>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -11779,7 +13444,7 @@
       <c r="C8" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="59" t="s">
+      <c r="D8" s="57" t="s">
         <v>339</v>
       </c>
     </row>
@@ -11793,7 +13458,7 @@
       <c r="C9" t="s">
         <v>60</v>
       </c>
-      <c r="D9" s="63" t="s">
+      <c r="D9" s="61" t="s">
         <v>370</v>
       </c>
     </row>
@@ -12003,7 +13668,7 @@
       <c r="C24" t="s">
         <v>261</v>
       </c>
-      <c r="D24" s="63" t="s">
+      <c r="D24" s="61" t="s">
         <v>385</v>
       </c>
     </row>
@@ -12225,7 +13890,7 @@
       <c r="C8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="59" t="s">
+      <c r="D8" s="57" t="s">
         <v>339</v>
       </c>
     </row>
@@ -12239,7 +13904,7 @@
       <c r="C9" s="39" t="s">
         <v>67</v>
       </c>
-      <c r="D9" s="63" t="s">
+      <c r="D9" s="61" t="s">
         <v>397</v>
       </c>
     </row>
@@ -12449,7 +14114,7 @@
       <c r="C24" s="39" t="s">
         <v>119</v>
       </c>
-      <c r="D24" s="63" t="s">
+      <c r="D24" s="61" t="s">
         <v>412</v>
       </c>
     </row>
@@ -12793,7 +14458,7 @@
       <c r="C8" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="59" t="s">
+      <c r="D8" s="57" t="s">
         <v>339</v>
       </c>
     </row>
@@ -12807,7 +14472,7 @@
       <c r="C9" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D9" s="63" t="s">
+      <c r="D9" s="61" t="s">
         <v>430</v>
       </c>
     </row>
@@ -12827,7 +14492,7 @@
       <c r="A23" s="18"/>
     </row>
     <row r="24" spans="1:4">
-      <c r="D24" s="63"/>
+      <c r="D24" s="61"/>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="19"/>
@@ -12903,7 +14568,7 @@
       <c r="C8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="59" t="s">
+      <c r="D8" s="57" t="s">
         <v>339</v>
       </c>
     </row>
@@ -12917,7 +14582,7 @@
       <c r="C9" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="D9" s="63" t="s">
+      <c r="D9" s="61" t="s">
         <v>431</v>
       </c>
     </row>
@@ -12966,7 +14631,7 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="9"/>
-      <c r="D24" s="63"/>
+      <c r="D24" s="61"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -13043,7 +14708,7 @@
       <c r="D8" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E8" s="59" t="s">
+      <c r="E8" s="57" t="s">
         <v>339</v>
       </c>
     </row>
@@ -13071,7 +14736,7 @@
       <c r="D10" t="s">
         <v>245</v>
       </c>
-      <c r="E10" s="63" t="s">
+      <c r="E10" s="61" t="s">
         <v>435</v>
       </c>
     </row>
@@ -13085,7 +14750,7 @@
       <c r="D11" t="s">
         <v>245</v>
       </c>
-      <c r="E11" s="63" t="s">
+      <c r="E11" s="61" t="s">
         <v>436</v>
       </c>
     </row>
@@ -13107,7 +14772,7 @@
       <c r="E14" s="41"/>
     </row>
     <row r="25" spans="5:5">
-      <c r="E25" s="63"/>
+      <c r="E25" s="61"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/Assets/Data/Amstrad CPC 664/MC0005A/Data CPC 664 MC0005A.xlsx
+++ b/Assets/Data/Amstrad CPC 664/MC0005A/Data CPC 664 MC0005A.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbewe\RetroComputing\CRT\Data\Amstrad CPC 664\MC0005A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dennis\AppData\Local\Classic-Repair-Toolbox\Data\Amstrad CPC 664\MC0005A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD929A52-D2DB-41D8-9BAD-3762C6701C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8479478-1767-48A0-8E7B-ADF03BA529C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Board schematics" sheetId="5" r:id="rId1"/>
@@ -570,12 +570,6 @@
     <t>Amstrad shared files/Component local files/ACCC1-8-EN.pdf</t>
   </si>
   <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC116_19_NPHI.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC116_24_CK16.jpg</t>
-  </si>
-  <si>
     <t>Custom Gate Array provides a 4MHz clock to the Z80 CPU and 1 MHz clock to the AY-3-8912 Sound Generator and RAM Multiplexers. It also provides a phase shifted 1MHz clock to the CRTC and RAM Multiplexers.
 Also determines whether the CRTC or the Z80 CPU can access the RAM and whether the Z80 CPU will access ROM or RAM. 
 The Gate Array also produces the RGB, LUM and SYNC signals.
@@ -603,9 +597,6 @@
     <t>4MHz</t>
   </si>
   <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/X101_1_CLK.jpg</t>
-  </si>
-  <si>
     <t>Output 16MHz clock to Gate Array CK16 (Pin 24) via IC125 NOT Gate</t>
   </si>
   <si>
@@ -615,9 +606,6 @@
     <t>1MHz</t>
   </si>
   <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC116_4_CCLK.jpg</t>
-  </si>
-  <si>
     <t>Amstrad shared files/Component images/74HCU04.jpg</t>
   </si>
   <si>
@@ -654,9 +642,6 @@
     <t>Truth Table</t>
   </si>
   <si>
-    <t>Amstrad CPC 664/MC0005A/Truth Tables/IC109_TRUTH_TABLE.jpg</t>
-  </si>
-  <si>
     <t>CPU or CRTC Address Lines are presented to the RAM ICs as a Column Address (CAS) or Row Address (RAS)</t>
   </si>
   <si>
@@ -699,24 +684,15 @@
     <t>Input Column Address Strobe (CAS) from Gate Array (GA) CAS (Pin 16)</t>
   </si>
   <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC120_15_CAS.jpg</t>
-  </si>
-  <si>
     <t>RAS</t>
   </si>
   <si>
     <t>Input Row Address Strobe (RAS) from Gate Array (GA) RAS (Pin 34)</t>
   </si>
   <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC120_4_RAS.jpg</t>
-  </si>
-  <si>
     <t>W</t>
   </si>
   <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC120_3_W.jpg</t>
-  </si>
-  <si>
     <t>Input Write Enable (WE) from Gate Array (GA) MWE (Pin 33)</t>
   </si>
   <si>
@@ -730,15 +706,6 @@
   </si>
   <si>
     <t>40008/40010</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Truth Tables/IC105_TRUTH_TABLE.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Truth Tables/IC104_TRUTH_TABLE.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Truth Tables/IC113_TRUTH_TABLE.jpg</t>
   </si>
   <si>
     <t>Amstrad shared files/Component images/AY-3-8912.jpg</t>
@@ -789,9 +756,6 @@
     <t>PC0</t>
   </si>
   <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC107_14_PC0.jpg</t>
-  </si>
-  <si>
     <t>Amstrad shared files/Component images/74LS145_TRUTH_TABLE.jpg</t>
   </si>
   <si>
@@ -944,9 +908,6 @@
     <t>20us</t>
   </si>
   <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC116_8_B.jpg</t>
-  </si>
-  <si>
     <t>Output to Monitor
 Trace taken with CTM644 contected. Border and Ink 0 set blue (i.e. colour 1) and no text on screen (i.e. 10 cls 20 goto 10 running).
 See Grimware link for more RGB signal colours.</t>
@@ -955,12 +916,6 @@
     <t>G</t>
   </si>
   <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC116_12_R.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC116_10_G.jpg</t>
-  </si>
-  <si>
     <t>R</t>
   </si>
   <si>
@@ -978,16 +933,10 @@
 See Grimware link for more RGB signal colours.</t>
   </si>
   <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC116_5_NSYNC.jpg</t>
-  </si>
-  <si>
     <t>/NSYNC</t>
   </si>
   <si>
     <t>/NCPU</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC116_14_NCPU.jpg</t>
   </si>
   <si>
     <t>Output 1MHz, phase shifted (i.e. high when from CCLK (Pin 4) is low), to all RAM Multiplexer (Pin 2) and AY-3-8912 Sound Generator CLOCK (pin 15).
@@ -997,9 +946,6 @@
     <t>/NCAS</t>
   </si>
   <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC116_16_NCAS.jpg</t>
-  </si>
-  <si>
     <t>Output 4MHz Clock to the Z80 CPU (Pin 6).
 Trace taken at Ready Prompt.</t>
   </si>
@@ -1020,9 +966,6 @@
     <t>/NCASAD</t>
   </si>
   <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC116_31_NCASAD.jpg</t>
-  </si>
-  <si>
     <t>/NMWE</t>
   </si>
   <si>
@@ -1044,12 +987,6 @@
     <t>20ms</t>
   </si>
   <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC116_34_NRAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC116_33_NMWE.jpg</t>
-  </si>
-  <si>
     <t>Output to Multiplexers (Pin 4) to select Row Address .
 Trace taken at Ready Prompt.</t>
   </si>
@@ -1058,9 +995,6 @@
 Trace taken at Ready Prompt.</t>
   </si>
   <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC116_23_N244EN.jpg</t>
-  </si>
-  <si>
     <t>2us</t>
   </si>
   <si>
@@ -1070,9 +1004,6 @@
     <t>MA0</t>
   </si>
   <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC108_4_MA0.jpg</t>
-  </si>
-  <si>
     <t>DISPEN</t>
   </si>
   <si>
@@ -1083,18 +1014,6 @@
   </si>
   <si>
     <t>VSYNC</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC108_18_DISPEN.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC108_38_RA0.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC108_39_HSYNC.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC108_40_VSYNC.jpg</t>
   </si>
   <si>
     <t>50Hz</t>
@@ -1717,102 +1636,24 @@
     <t>8c91c782-9999-4105-8683-a9cf405f0a5c</t>
   </si>
   <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC117_3_W.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC117_4_RAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC117_15_CAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC118_3_W.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC118_4_RAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC118_15_CAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC119_3_W.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC119_4_RAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC119_15_CAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC121_3_W.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC121_4_RAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC121_15_CAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC122_3_W.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC122_4_RAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC122_15_CAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC123_3_W.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC123_4_RAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC123_15_CAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC124_3_W.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC124_4_RAS.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC124_15_CAS.jpg</t>
-  </si>
-  <si>
     <t>/MREQ</t>
   </si>
   <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_19_MREQ.jpg</t>
-  </si>
-  <si>
     <t>/IORQ</t>
   </si>
   <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_20_IORQ.jpg</t>
-  </si>
-  <si>
     <t>/HALT</t>
   </si>
   <si>
     <t>HIGH</t>
   </si>
   <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_18_HALT.jpg</t>
-  </si>
-  <si>
     <t>/M1</t>
   </si>
   <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_27_M1.jpg</t>
-  </si>
-  <si>
     <t>/RFSH</t>
   </si>
   <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_28_RFSH.jpg</t>
-  </si>
-  <si>
     <t>2a2c585e-d929-4df9-aa4e-462a7547d4b8</t>
   </si>
   <si>
@@ -1831,9 +1672,6 @@
     <t>A10</t>
   </si>
   <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_40_A10.jpg</t>
-  </si>
-  <si>
     <t>D0</t>
   </si>
   <si>
@@ -1858,30 +1696,6 @@
     <t>D7</t>
   </si>
   <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_14_D0.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_15_D1.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_12_D2.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_8_D3.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_7_D4.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_9_D5.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_10_D6.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_13_D7.jpg</t>
-  </si>
-  <si>
     <t>18f244f9-4c21-4803-b428-33ac3d34f27d</t>
   </si>
   <si>
@@ -1907,9 +1721,6 @@
   </si>
   <si>
     <t>CLK</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_6_CLK.jpg</t>
   </si>
   <si>
     <t>Input from Gate Array /NPHI (Pin 19) via IC125 Not Gate.
@@ -1987,51 +1798,6 @@
     <t>A15</t>
   </si>
   <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_30_A0.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_31_A1.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_32_A2.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_33_A3.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_34_A4.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_35_A5.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_36_A6.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_37_A7.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_38_A8.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_39_A9.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_1_A11.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_2_A12.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_3_A13.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_4_A14.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_5_A15.jpg</t>
-  </si>
-  <si>
     <t>385bd464-2634-4e9c-8fab-f89483763090</t>
   </si>
   <si>
@@ -2080,15 +1846,9 @@
     <t>a84622f4-5a51-4872-91e8-bfca3b4897aa</t>
   </si>
   <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_17_NMI.jpg</t>
-  </si>
-  <si>
     <t>Input from Expansion Port (Pin 36).</t>
   </si>
   <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_16_INT.jpg</t>
-  </si>
-  <si>
     <t>Input from Gate Array /NINTERRUPT (Pin 32).</t>
   </si>
   <si>
@@ -2101,9 +1861,6 @@
     <t>/INT</t>
   </si>
   <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_24_WAIT.jpg</t>
-  </si>
-  <si>
     <t>Input from Gate Array /READY (Pin 22).</t>
   </si>
   <si>
@@ -2113,24 +1870,15 @@
     <t>/BUSRQ</t>
   </si>
   <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_25_BUSRQ.jpg</t>
-  </si>
-  <si>
     <t>Input from Expansion Port (Pin 37).</t>
   </si>
   <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_26_RESET.jpg</t>
-  </si>
-  <si>
     <t>Input from IC110.</t>
   </si>
   <si>
     <t>/RD</t>
   </si>
   <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_21_RD.jpg</t>
-  </si>
-  <si>
     <t>Ouput to Gate Array /NRD (Pin 21).</t>
   </si>
   <si>
@@ -2141,12 +1889,6 @@
   </si>
   <si>
     <t>/BUSAK</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_22_WR.jpg</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Scope Baseline/IC111_23_BUSAK.jpg</t>
   </si>
   <si>
     <t>Output to Expansion Port (Pin 38).</t>
@@ -2188,8 +1930,266 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>2026-April-21</t>
+      <t>2026-May-1</t>
     </r>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC107_14_PC0.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC108_4_MA0.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC108_18_DISPEN.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC108_38_RA0.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC108_39_HSYNC.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC108_40_VSYNC.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_1_A11.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_2_A12.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_3_A13.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_4_A14.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_5_A15.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_6_CLK.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_7_D4.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_8_D3.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_9_D5.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_10_D6.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_12_D2.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_13_D7.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_14_D0.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_15_D1.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_16_INT.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_17_NMI.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_18_HALT.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_19_MREQ.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_20_IORQ.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_21_RD.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_22_WR.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_23_BUSAK.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_24_WAIT.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_25_BUSRQ.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_26_RESET.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_27_M1.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_28_RFSH.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_30_A0.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_31_A1.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_32_A2.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_33_A3.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_34_A4.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_35_A5.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_36_A6.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_37_A7.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_38_A8.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_39_A9.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC111_40_A10.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC116_4_CCLK.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC116_5_NSYNC.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC116_8_B.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC116_10_G.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC116_12_R.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC116_14_NCPU.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC116_16_NCAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC116_19_NPHI.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC116_23_N244EN.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC116_24_CK16.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC116_31_NCASAD.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC116_33_NMWE.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC116_34_NRAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC117_3_W.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC117_4_RAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC117_15_CAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC118_3_W.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC118_4_RAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC118_15_CAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC119_3_W.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC119_4_RAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC119_15_CAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC120_3_W.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC120_4_RAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC120_15_CAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC121_3_W.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC121_4_RAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC121_15_CAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC122_3_W.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC122_4_RAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC122_15_CAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC123_3_W.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC123_4_RAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC123_15_CAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC124_3_W.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC124_4_RAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/IC124_15_CAS.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Scope baseline/X101_1_CLK.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Truth tables/IC104_TRUTH_TABLE.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Truth tables/IC105_TRUTH_TABLE.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Truth tables/IC109_TRUTH_TABLE.jpg</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/Truth tables/IC113_TRUTH_TABLE.jpg</t>
   </si>
 </sst>
 </file>
@@ -2554,9 +2554,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2594,7 +2594,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2700,7 +2700,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2842,7 +2842,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2852,16 +2852,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBB56770-8233-4B8D-A81F-EDDC9713B054}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:P33"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="38.7109375" style="27" customWidth="1"/>
-    <col min="2" max="2" width="89" style="33" customWidth="1"/>
+    <col min="1" max="1" width="38.6640625" style="27" customWidth="1"/>
+    <col min="2" max="2" width="62.77734375" style="33" customWidth="1"/>
     <col min="3" max="4" width="14" style="33" customWidth="1"/>
-    <col min="5" max="5" width="16.42578125" style="33" customWidth="1"/>
-    <col min="6" max="6" width="16.28515625" style="33" customWidth="1"/>
-    <col min="7" max="15" width="8.85546875" style="33"/>
-    <col min="16" max="16" width="38.5703125" style="33" customWidth="1"/>
-    <col min="17" max="16384" width="8.85546875" style="33"/>
+    <col min="5" max="5" width="16.44140625" style="33" customWidth="1"/>
+    <col min="6" max="6" width="16.33203125" style="33" customWidth="1"/>
+    <col min="7" max="15" width="8.88671875" style="33"/>
+    <col min="16" max="16" width="38.5546875" style="33" customWidth="1"/>
+    <col min="17" max="16384" width="8.88671875" style="33"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" s="9" customFormat="1" ht="21">
@@ -2876,7 +2876,7 @@
     </row>
     <row r="3" spans="1:16" s="8" customFormat="1" ht="21">
       <c r="A3" s="8" t="s">
-        <v>675</v>
+        <v>589</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -2888,7 +2888,7 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="17" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -2926,7 +2926,7 @@
       <c r="F8" s="63"/>
       <c r="G8" s="54"/>
       <c r="H8" s="64" t="s">
-        <v>329</v>
+        <v>302</v>
       </c>
       <c r="I8" s="64"/>
       <c r="J8" s="64"/>
@@ -2937,7 +2937,7 @@
       <c r="O8" s="64"/>
       <c r="P8" s="5"/>
     </row>
-    <row r="9" spans="1:16" s="4" customFormat="1" ht="45">
+    <row r="9" spans="1:16" s="4" customFormat="1" ht="28.8">
       <c r="A9" s="13" t="s">
         <v>22</v>
       </c>
@@ -2957,34 +2957,34 @@
         <v>38</v>
       </c>
       <c r="G9" s="55" t="s">
-        <v>330</v>
+        <v>303</v>
       </c>
       <c r="H9" s="56" t="s">
-        <v>331</v>
+        <v>304</v>
       </c>
       <c r="I9" s="56" t="s">
-        <v>332</v>
+        <v>305</v>
       </c>
       <c r="J9" s="56" t="s">
-        <v>333</v>
+        <v>306</v>
       </c>
       <c r="K9" s="56" t="s">
-        <v>334</v>
+        <v>307</v>
       </c>
       <c r="L9" s="56" t="s">
-        <v>335</v>
+        <v>308</v>
       </c>
       <c r="M9" s="56" t="s">
-        <v>336</v>
+        <v>309</v>
       </c>
       <c r="N9" s="56" t="s">
-        <v>337</v>
+        <v>310</v>
       </c>
       <c r="O9" s="56" t="s">
-        <v>338</v>
+        <v>311</v>
       </c>
       <c r="P9" s="57" t="s">
-        <v>339</v>
+        <v>312</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2992,7 +2992,7 @@
         <v>138</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>9</v>
@@ -3016,7 +3016,7 @@
       <c r="N10" s="59"/>
       <c r="O10" s="59"/>
       <c r="P10" t="s">
-        <v>340</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -3024,7 +3024,7 @@
         <v>137</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="C11" s="33" t="s">
         <v>9</v>
@@ -3048,7 +3048,7 @@
       <c r="N11" s="59"/>
       <c r="O11" s="59"/>
       <c r="P11" t="s">
-        <v>341</v>
+        <v>314</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -3056,7 +3056,7 @@
         <v>71</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>9</v>
@@ -3080,7 +3080,7 @@
       <c r="N12" s="60"/>
       <c r="O12" s="60"/>
       <c r="P12" t="s">
-        <v>342</v>
+        <v>315</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -3088,7 +3088,7 @@
         <v>72</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>9</v>
@@ -3112,7 +3112,7 @@
       <c r="N13" s="60"/>
       <c r="O13" s="60"/>
       <c r="P13" t="s">
-        <v>343</v>
+        <v>316</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -3189,16 +3189,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1251FF9-425C-410E-B269-C7726F9C2504}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:H200"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="15" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="25.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="21.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="25.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="21.109375" style="1" customWidth="1"/>
     <col min="5" max="6" width="10" style="1" customWidth="1"/>
-    <col min="7" max="7" width="42.28515625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="38.28515625" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.85546875" style="1"/>
+    <col min="7" max="7" width="42.33203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="38.33203125" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21">
@@ -3217,7 +3217,7 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="17" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -3240,7 +3240,7 @@
       <c r="G7" s="10"/>
       <c r="H7" s="10"/>
     </row>
-    <row r="8" spans="1:8" s="6" customFormat="1" ht="30">
+    <row r="8" spans="1:8" s="6" customFormat="1" ht="28.8">
       <c r="A8" s="13" t="s">
         <v>3</v>
       </c>
@@ -3263,7 +3263,7 @@
         <v>21</v>
       </c>
       <c r="H8" s="57" t="s">
-        <v>339</v>
+        <v>312</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -3271,22 +3271,22 @@
         <v>133</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>134</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>24</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>344</v>
+        <v>317</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -3309,7 +3309,7 @@
         <v>81</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>345</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -3317,7 +3317,7 @@
         <v>108</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="C11" s="1">
         <v>40022</v>
@@ -3329,10 +3329,10 @@
         <v>24</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>346</v>
+        <v>319</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -3346,7 +3346,7 @@
         <v>117</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>24</v>
@@ -3355,7 +3355,7 @@
         <v>118</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>347</v>
+        <v>320</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -3369,7 +3369,7 @@
         <v>117</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>24</v>
@@ -3378,7 +3378,7 @@
         <v>118</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>348</v>
+        <v>321</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -3386,13 +3386,13 @@
         <v>143</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>144</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>24</v>
@@ -3401,7 +3401,7 @@
         <v>145</v>
       </c>
       <c r="H14" s="61" t="s">
-        <v>349</v>
+        <v>322</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -3424,7 +3424,7 @@
         <v>76</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>350</v>
+        <v>323</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -3447,7 +3447,7 @@
         <v>85</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>351</v>
+        <v>324</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -3461,7 +3461,7 @@
         <v>117</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>24</v>
@@ -3470,7 +3470,7 @@
         <v>118</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>352</v>
+        <v>325</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -3478,13 +3478,13 @@
         <v>128</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>130</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>24</v>
@@ -3493,7 +3493,7 @@
         <v>129</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>353</v>
+        <v>326</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -3516,7 +3516,7 @@
         <v>65</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>354</v>
+        <v>327</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -3524,19 +3524,19 @@
         <v>91</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>92</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>355</v>
+        <v>328</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -3550,7 +3550,7 @@
         <v>117</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>24</v>
@@ -3559,7 +3559,7 @@
         <v>118</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>356</v>
+        <v>329</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -3567,7 +3567,7 @@
         <v>106</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>107</v>
@@ -3579,7 +3579,7 @@
         <v>24</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>357</v>
+        <v>330</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -3587,7 +3587,7 @@
         <v>104</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>105</v>
@@ -3599,7 +3599,7 @@
         <v>24</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>358</v>
+        <v>331</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -3613,7 +3613,7 @@
         <v>89</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>24</v>
@@ -3622,7 +3622,7 @@
         <v>89</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>359</v>
+        <v>332</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -3630,7 +3630,7 @@
         <v>94</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="C25" s="1">
         <v>4164</v>
@@ -3642,10 +3642,10 @@
         <v>24</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>360</v>
+        <v>333</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -3653,7 +3653,7 @@
         <v>96</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="C26" s="1">
         <v>4164</v>
@@ -3665,10 +3665,10 @@
         <v>24</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>361</v>
+        <v>334</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -3676,7 +3676,7 @@
         <v>97</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="C27" s="1">
         <v>4164</v>
@@ -3688,10 +3688,10 @@
         <v>24</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>362</v>
+        <v>335</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -3699,7 +3699,7 @@
         <v>98</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="C28" s="1">
         <v>4164</v>
@@ -3711,10 +3711,10 @@
         <v>24</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>363</v>
+        <v>336</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -3722,7 +3722,7 @@
         <v>99</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="C29" s="1">
         <v>4164</v>
@@ -3734,10 +3734,10 @@
         <v>24</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>364</v>
+        <v>337</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -3745,7 +3745,7 @@
         <v>100</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="C30" s="1">
         <v>4164</v>
@@ -3757,10 +3757,10 @@
         <v>24</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>365</v>
+        <v>338</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -3768,7 +3768,7 @@
         <v>101</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="C31" s="1">
         <v>4164</v>
@@ -3780,10 +3780,10 @@
         <v>24</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>366</v>
+        <v>339</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -3791,7 +3791,7 @@
         <v>102</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="C32" s="1">
         <v>4164</v>
@@ -3803,10 +3803,10 @@
         <v>24</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>367</v>
+        <v>340</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -3814,39 +3814,39 @@
         <v>139</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>140</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>368</v>
+        <v>341</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B34" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>157</v>
-      </c>
       <c r="E34" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>369</v>
+        <v>342</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -4683,19 +4683,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35D2A4B1-8E0B-46C6-8B83-02048610537D}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:L2883"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="15" style="1" customWidth="1"/>
-    <col min="2" max="2" width="7.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="3.7109375" style="28" customWidth="1"/>
-    <col min="4" max="4" width="24.140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="22.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="6.85546875" style="1" customWidth="1"/>
-    <col min="7" max="8" width="7.28515625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="95.85546875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="73.7109375" style="44" customWidth="1"/>
-    <col min="11" max="11" width="49.85546875" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.85546875" style="1"/>
+    <col min="2" max="2" width="7.88671875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="3.6640625" style="28" customWidth="1"/>
+    <col min="4" max="4" width="24.109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="6.88671875" style="1" customWidth="1"/>
+    <col min="7" max="8" width="7.33203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="95.88671875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="73.6640625" style="44" customWidth="1"/>
+    <col min="11" max="11" width="49.88671875" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="21">
@@ -4722,7 +4722,7 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="17" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="24"/>
@@ -4762,7 +4762,7 @@
       <c r="J7" s="46"/>
       <c r="K7" s="46"/>
     </row>
-    <row r="8" spans="1:12" s="6" customFormat="1" ht="30">
+    <row r="8" spans="1:12" s="6" customFormat="1" ht="28.8">
       <c r="A8" s="13" t="s">
         <v>3</v>
       </c>
@@ -4779,13 +4779,13 @@
         <v>47</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="I8" s="13" t="s">
         <v>1</v>
@@ -4794,7 +4794,7 @@
         <v>48</v>
       </c>
       <c r="K8" s="57" t="s">
-        <v>339</v>
+        <v>312</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -4808,31 +4808,31 @@
         <v>135</v>
       </c>
       <c r="J9" s="44" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="K9" s="61" t="s">
-        <v>440</v>
+        <v>413</v>
       </c>
       <c r="L9" s="9"/>
     </row>
-    <row r="10" spans="1:12" ht="30">
+    <row r="10" spans="1:12" ht="28.8">
       <c r="A10" s="1" t="s">
         <v>133</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="J10" s="44" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="135">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="115.2">
       <c r="A11" s="9" t="s">
         <v>78</v>
       </c>
@@ -4842,35 +4842,35 @@
         <v>26</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="J11" s="44" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="30">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="28.8">
       <c r="A12" s="50" t="s">
         <v>78</v>
       </c>
       <c r="B12" s="50"/>
       <c r="C12" s="51"/>
       <c r="D12" s="41" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="E12" s="41" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="I12" s="41" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="J12" s="52" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>443</v>
+        <v>416</v>
       </c>
     </row>
     <row r="13" spans="1:12" s="41" customFormat="1">
@@ -4891,10 +4891,10 @@
       </c>
       <c r="J13" s="44"/>
       <c r="K13" s="41" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="30">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="28.8">
       <c r="A14" s="1" t="s">
         <v>112</v>
       </c>
@@ -4905,30 +4905,30 @@
         <v>126</v>
       </c>
       <c r="J14" s="44" t="s">
-        <v>328</v>
+        <v>301</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="30">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="28.8">
       <c r="A15" s="1" t="s">
         <v>112</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>206</v>
+        <v>672</v>
       </c>
       <c r="J15" s="44" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="30">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="28.8">
       <c r="A16" s="1" t="s">
         <v>113</v>
       </c>
@@ -4939,27 +4939,27 @@
         <v>126</v>
       </c>
       <c r="J16" s="44" t="s">
-        <v>328</v>
+        <v>301</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="30">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="28.8">
       <c r="A17" s="1" t="s">
         <v>113</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>205</v>
+        <v>673</v>
       </c>
       <c r="J17" s="44" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>448</v>
+        <v>421</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -4973,10 +4973,10 @@
         <v>146</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="75">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="57.6">
       <c r="A19" s="9" t="s">
         <v>73</v>
       </c>
@@ -4986,16 +4986,16 @@
         <v>26</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="J19" s="44" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="30">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="28.8">
       <c r="A20" s="9" t="s">
         <v>73</v>
       </c>
@@ -5004,28 +5004,28 @@
         <v>14</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>320</v>
+        <v>293</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>223</v>
+        <v>590</v>
       </c>
       <c r="J20" s="44" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>451</v>
+        <v>424</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -5038,13 +5038,13 @@
         <v>26</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>308</v>
+        <v>286</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="45">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="43.2">
       <c r="A22" s="9" t="s">
         <v>82</v>
       </c>
@@ -5053,31 +5053,31 @@
         <v>4</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>309</v>
+        <v>287</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>322</v>
+        <v>295</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>310</v>
+        <v>591</v>
       </c>
       <c r="J22" s="44" t="s">
-        <v>326</v>
+        <v>299</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="45">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="43.2">
       <c r="A23" s="9" t="s">
         <v>82</v>
       </c>
@@ -5086,31 +5086,31 @@
         <v>18</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>311</v>
+        <v>288</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>315</v>
+        <v>592</v>
       </c>
       <c r="J23" s="44" t="s">
-        <v>324</v>
+        <v>297</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="45">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="43.2">
       <c r="A24" s="9" t="s">
         <v>82</v>
       </c>
@@ -5119,31 +5119,31 @@
         <v>38</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>312</v>
+        <v>289</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>323</v>
+        <v>296</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>320</v>
+        <v>293</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>316</v>
+        <v>593</v>
       </c>
       <c r="J24" s="44" t="s">
-        <v>327</v>
+        <v>300</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="45">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="43.2">
       <c r="A25" s="9" t="s">
         <v>82</v>
       </c>
@@ -5152,31 +5152,31 @@
         <v>39</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>317</v>
+        <v>594</v>
       </c>
       <c r="J25" s="44" t="s">
-        <v>325</v>
+        <v>298</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="45">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="43.2">
       <c r="A26" s="9" t="s">
         <v>82</v>
       </c>
@@ -5185,31 +5185,31 @@
         <v>40</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>319</v>
+        <v>292</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>301</v>
+        <v>282</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>318</v>
+        <v>595</v>
       </c>
       <c r="J26" s="44" t="s">
-        <v>321</v>
+        <v>294</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="60">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="57.6">
       <c r="A27" s="1" t="s">
         <v>114</v>
       </c>
@@ -5220,27 +5220,27 @@
         <v>126</v>
       </c>
       <c r="J27" s="44" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="30">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="28.8">
       <c r="A28" s="1" t="s">
         <v>114</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>179</v>
+        <v>674</v>
       </c>
       <c r="J28" s="44" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>459</v>
+        <v>432</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -5254,7 +5254,7 @@
         <v>131</v>
       </c>
       <c r="K29" s="61" t="s">
-        <v>460</v>
+        <v>433</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -5271,7 +5271,7 @@
       </c>
       <c r="J30" s="1"/>
       <c r="K30" s="1" t="s">
-        <v>461</v>
+        <v>434</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -5283,28 +5283,28 @@
         <v>1</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>607</v>
+        <v>544</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>622</v>
+        <v>596</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>590</v>
+        <v>527</v>
       </c>
       <c r="K31" s="61" t="s">
-        <v>638</v>
+        <v>560</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -5316,28 +5316,28 @@
         <v>2</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>608</v>
+        <v>545</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>623</v>
+        <v>597</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>590</v>
+        <v>527</v>
       </c>
       <c r="K32" s="61" t="s">
-        <v>639</v>
+        <v>561</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -5349,28 +5349,28 @@
         <v>3</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>609</v>
+        <v>546</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>624</v>
+        <v>598</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>590</v>
+        <v>527</v>
       </c>
       <c r="K33" s="61" t="s">
-        <v>640</v>
+        <v>562</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -5382,28 +5382,28 @@
         <v>4</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>610</v>
+        <v>547</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>625</v>
+        <v>599</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>590</v>
+        <v>527</v>
       </c>
       <c r="K34" s="61" t="s">
-        <v>641</v>
+        <v>563</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="53.25" customHeight="1">
@@ -5415,31 +5415,31 @@
         <v>5</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>611</v>
+        <v>548</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>626</v>
+        <v>600</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>590</v>
+        <v>527</v>
       </c>
       <c r="K35" s="61" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" ht="45">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="43.2">
       <c r="A36" s="62" t="s">
         <v>52</v>
       </c>
@@ -5448,28 +5448,28 @@
         <v>6</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>587</v>
+        <v>525</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>588</v>
+        <v>601</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>589</v>
+        <v>526</v>
       </c>
       <c r="K36" s="61" t="s">
-        <v>596</v>
+        <v>533</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -5481,28 +5481,28 @@
         <v>7</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>567</v>
+        <v>513</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>575</v>
+        <v>602</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>590</v>
+        <v>527</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>583</v>
+        <v>521</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -5514,28 +5514,28 @@
         <v>8</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>566</v>
+        <v>512</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>574</v>
+        <v>603</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>590</v>
+        <v>527</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>582</v>
+        <v>520</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -5547,28 +5547,28 @@
         <v>9</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>568</v>
+        <v>514</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>576</v>
+        <v>604</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>590</v>
+        <v>527</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>584</v>
+        <v>522</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -5580,28 +5580,28 @@
         <v>10</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>569</v>
+        <v>515</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>577</v>
+        <v>605</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>590</v>
+        <v>527</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>585</v>
+        <v>523</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -5613,28 +5613,28 @@
         <v>12</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>565</v>
+        <v>511</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>573</v>
+        <v>606</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>590</v>
+        <v>527</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>581</v>
+        <v>519</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -5646,28 +5646,28 @@
         <v>13</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>570</v>
+        <v>516</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>578</v>
+        <v>607</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>590</v>
+        <v>527</v>
       </c>
       <c r="K42" s="61" t="s">
-        <v>586</v>
+        <v>524</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -5679,28 +5679,28 @@
         <v>14</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>563</v>
+        <v>509</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I43" s="9" t="s">
-        <v>571</v>
+        <v>608</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>590</v>
+        <v>527</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>579</v>
+        <v>517</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -5712,28 +5712,28 @@
         <v>15</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>564</v>
+        <v>510</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I44" s="9" t="s">
-        <v>572</v>
+        <v>609</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>590</v>
+        <v>527</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>580</v>
+        <v>518</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -5745,28 +5745,28 @@
         <v>16</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>649</v>
+        <v>569</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I45" s="9" t="s">
-        <v>645</v>
+        <v>610</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>646</v>
+        <v>566</v>
       </c>
       <c r="K45" s="61" t="s">
-        <v>673</v>
+        <v>587</v>
       </c>
     </row>
     <row r="46" spans="1:11">
@@ -5778,31 +5778,31 @@
         <v>17</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>648</v>
+        <v>568</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I46" s="9" t="s">
-        <v>643</v>
+        <v>611</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>644</v>
+        <v>565</v>
       </c>
       <c r="K46" s="61" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" ht="45">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="43.2">
       <c r="A47" s="62" t="s">
         <v>52</v>
       </c>
@@ -5811,31 +5811,31 @@
         <v>18</v>
       </c>
       <c r="D47" s="33" t="s">
-        <v>549</v>
+        <v>499</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>320</v>
+        <v>293</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I47" s="9" t="s">
-        <v>551</v>
+        <v>612</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>595</v>
+        <v>532</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" ht="45">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="43.2">
       <c r="A48" s="62" t="s">
         <v>52</v>
       </c>
@@ -5844,31 +5844,31 @@
         <v>19</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>545</v>
+        <v>497</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I48" s="9" t="s">
-        <v>546</v>
+        <v>613</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>594</v>
+        <v>531</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" ht="60">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="57.6">
       <c r="A49" s="62" t="s">
         <v>52</v>
       </c>
@@ -5877,28 +5877,28 @@
         <v>20</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>547</v>
+        <v>498</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>320</v>
+        <v>293</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I49" s="9" t="s">
-        <v>548</v>
+        <v>614</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>593</v>
+        <v>530</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>558</v>
+        <v>505</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -5910,28 +5910,28 @@
         <v>21</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>658</v>
+        <v>575</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>659</v>
+        <v>615</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>660</v>
+        <v>576</v>
       </c>
       <c r="K50" s="61" t="s">
-        <v>667</v>
+        <v>581</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -5943,28 +5943,28 @@
         <v>22</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>662</v>
+        <v>578</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I51" s="9" t="s">
-        <v>664</v>
+        <v>616</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>661</v>
+        <v>577</v>
       </c>
       <c r="K51" s="61" t="s">
-        <v>668</v>
+        <v>582</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -5976,28 +5976,28 @@
         <v>23</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>663</v>
+        <v>579</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I52" s="9" t="s">
-        <v>665</v>
+        <v>617</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>666</v>
+        <v>580</v>
       </c>
       <c r="K52" s="61" t="s">
-        <v>669</v>
+        <v>583</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -6009,28 +6009,28 @@
         <v>24</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>647</v>
+        <v>567</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I53" s="9" t="s">
-        <v>650</v>
+        <v>618</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>651</v>
+        <v>570</v>
       </c>
       <c r="K53" s="61" t="s">
-        <v>670</v>
+        <v>584</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -6042,28 +6042,28 @@
         <v>25</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>653</v>
+        <v>572</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I54" s="9" t="s">
-        <v>654</v>
+        <v>619</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>655</v>
+        <v>573</v>
       </c>
       <c r="K54" s="61" t="s">
-        <v>671</v>
+        <v>585</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -6075,31 +6075,31 @@
         <v>26</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>652</v>
+        <v>571</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I55" s="9" t="s">
-        <v>656</v>
+        <v>620</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>657</v>
+        <v>574</v>
       </c>
       <c r="K55" s="61" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" ht="45">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="43.2">
       <c r="A56" s="62" t="s">
         <v>52</v>
       </c>
@@ -6108,31 +6108,31 @@
         <v>27</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>552</v>
+        <v>501</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I56" s="9" t="s">
-        <v>553</v>
+        <v>621</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>592</v>
+        <v>529</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" ht="45">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="43.2">
       <c r="A57" s="62" t="s">
         <v>52</v>
       </c>
@@ -6141,28 +6141,28 @@
         <v>28</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>554</v>
+        <v>502</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I57" s="9" t="s">
-        <v>555</v>
+        <v>622</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>591</v>
+        <v>528</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>560</v>
+        <v>507</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -6174,28 +6174,28 @@
         <v>30</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>597</v>
+        <v>534</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I58" s="9" t="s">
-        <v>612</v>
+        <v>623</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>590</v>
+        <v>527</v>
       </c>
       <c r="K58" s="61" t="s">
-        <v>627</v>
+        <v>549</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -6207,28 +6207,28 @@
         <v>31</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>598</v>
+        <v>535</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I59" s="9" t="s">
-        <v>613</v>
+        <v>624</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>590</v>
+        <v>527</v>
       </c>
       <c r="K59" s="61" t="s">
-        <v>628</v>
+        <v>550</v>
       </c>
     </row>
     <row r="60" spans="1:11">
@@ -6240,28 +6240,28 @@
         <v>32</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>599</v>
+        <v>536</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I60" s="9" t="s">
-        <v>614</v>
+        <v>625</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>590</v>
+        <v>527</v>
       </c>
       <c r="K60" s="61" t="s">
-        <v>629</v>
+        <v>551</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -6273,28 +6273,28 @@
         <v>33</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>600</v>
+        <v>537</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I61" s="9" t="s">
-        <v>615</v>
+        <v>626</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>590</v>
+        <v>527</v>
       </c>
       <c r="K61" s="61" t="s">
-        <v>630</v>
+        <v>552</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -6306,28 +6306,28 @@
         <v>34</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>601</v>
+        <v>538</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I62" s="9" t="s">
-        <v>616</v>
+        <v>627</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>590</v>
+        <v>527</v>
       </c>
       <c r="K62" s="61" t="s">
-        <v>631</v>
+        <v>553</v>
       </c>
     </row>
     <row r="63" spans="1:11">
@@ -6339,28 +6339,28 @@
         <v>35</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>602</v>
+        <v>539</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I63" s="9" t="s">
-        <v>617</v>
+        <v>628</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>590</v>
+        <v>527</v>
       </c>
       <c r="K63" s="61" t="s">
-        <v>632</v>
+        <v>554</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -6372,28 +6372,28 @@
         <v>36</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>603</v>
+        <v>540</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I64" s="9" t="s">
-        <v>618</v>
+        <v>629</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>590</v>
+        <v>527</v>
       </c>
       <c r="K64" s="61" t="s">
-        <v>633</v>
+        <v>555</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -6405,28 +6405,28 @@
         <v>37</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>604</v>
+        <v>541</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I65" s="9" t="s">
-        <v>619</v>
+        <v>630</v>
       </c>
       <c r="J65" s="1" t="s">
-        <v>590</v>
+        <v>527</v>
       </c>
       <c r="K65" s="61" t="s">
-        <v>634</v>
+        <v>556</v>
       </c>
     </row>
     <row r="66" spans="1:11">
@@ -6438,28 +6438,28 @@
         <v>38</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>605</v>
+        <v>542</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I66" s="9" t="s">
-        <v>620</v>
+        <v>631</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>590</v>
+        <v>527</v>
       </c>
       <c r="K66" s="61" t="s">
-        <v>635</v>
+        <v>557</v>
       </c>
     </row>
     <row r="67" spans="1:11">
@@ -6471,28 +6471,28 @@
         <v>39</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>606</v>
+        <v>543</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I67" s="9" t="s">
-        <v>621</v>
+        <v>632</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>590</v>
+        <v>527</v>
       </c>
       <c r="K67" s="61" t="s">
-        <v>636</v>
+        <v>558</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -6504,28 +6504,28 @@
         <v>40</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>561</v>
+        <v>508</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I68" s="9" t="s">
-        <v>562</v>
+        <v>633</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>590</v>
+        <v>527</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>637</v>
+        <v>559</v>
       </c>
     </row>
     <row r="69" spans="1:11">
@@ -6538,10 +6538,10 @@
         <v>26</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>462</v>
+        <v>435</v>
       </c>
     </row>
     <row r="70" spans="1:11" ht="67.5" customHeight="1">
@@ -6555,27 +6555,27 @@
         <v>126</v>
       </c>
       <c r="J70" s="44" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" ht="30">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" ht="28.8">
       <c r="A71" s="1" t="s">
         <v>115</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>207</v>
+        <v>675</v>
       </c>
       <c r="J71" s="44" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>464</v>
+        <v>437</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -6586,10 +6586,10 @@
         <v>26</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>465</v>
+        <v>438</v>
       </c>
     </row>
     <row r="73" spans="1:11">
@@ -6600,13 +6600,13 @@
         <v>26</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" ht="150">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" ht="144">
       <c r="A74" s="9" t="s">
         <v>87</v>
       </c>
@@ -6616,16 +6616,16 @@
         <v>26</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="J74" s="44" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" ht="60">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" ht="57.6">
       <c r="A75" s="9" t="s">
         <v>87</v>
       </c>
@@ -6634,31 +6634,31 @@
         <v>4</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>166</v>
+        <v>634</v>
       </c>
       <c r="J75" s="44" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" ht="45">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" ht="43.2">
       <c r="A76" s="9" t="s">
         <v>87</v>
       </c>
@@ -6667,31 +6667,31 @@
         <v>5</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>282</v>
+        <v>635</v>
       </c>
       <c r="J76" s="44" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" ht="90">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" ht="86.4">
       <c r="A77" s="9" t="s">
         <v>87</v>
       </c>
@@ -6700,31 +6700,31 @@
         <v>8</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>273</v>
+        <v>636</v>
       </c>
       <c r="J77" s="44" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" ht="90">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" ht="86.4">
       <c r="A78" s="9" t="s">
         <v>87</v>
       </c>
@@ -6733,31 +6733,31 @@
         <v>10</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>277</v>
+        <v>637</v>
       </c>
       <c r="J78" s="44" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" ht="90">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" ht="86.4">
       <c r="A79" s="9" t="s">
         <v>87</v>
       </c>
@@ -6766,31 +6766,31 @@
         <v>12</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>276</v>
+        <v>638</v>
       </c>
       <c r="J79" s="44" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11" ht="60">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" ht="57.6">
       <c r="A80" s="9" t="s">
         <v>87</v>
       </c>
@@ -6799,31 +6799,31 @@
         <v>14</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>284</v>
+        <v>268</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>285</v>
+        <v>639</v>
       </c>
       <c r="J80" s="44" t="s">
-        <v>286</v>
+        <v>269</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11" ht="45">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" ht="43.2">
       <c r="A81" s="9" t="s">
         <v>87</v>
       </c>
@@ -6832,31 +6832,31 @@
         <v>16</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>287</v>
+        <v>270</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>288</v>
+        <v>640</v>
       </c>
       <c r="J81" s="44" t="s">
-        <v>299</v>
+        <v>280</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" ht="45">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" ht="43.2">
       <c r="A82" s="9" t="s">
         <v>87</v>
       </c>
@@ -6865,31 +6865,31 @@
         <v>19</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>290</v>
+        <v>272</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>152</v>
+        <v>641</v>
       </c>
       <c r="J82" s="44" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11" ht="45">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" ht="43.2">
       <c r="A83" s="9" t="s">
         <v>87</v>
       </c>
@@ -6898,31 +6898,31 @@
         <v>23</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>292</v>
+        <v>274</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>306</v>
+        <v>642</v>
       </c>
       <c r="J83" s="44" t="s">
-        <v>293</v>
+        <v>275</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11" ht="45">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" ht="43.2">
       <c r="A84" s="9" t="s">
         <v>87</v>
       </c>
@@ -6937,25 +6937,25 @@
         <v>124</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>291</v>
+        <v>273</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>153</v>
+        <v>643</v>
       </c>
       <c r="J84" s="44" t="s">
-        <v>298</v>
+        <v>279</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11" ht="45">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" ht="43.2">
       <c r="A85" s="9" t="s">
         <v>87</v>
       </c>
@@ -6964,31 +6964,31 @@
         <v>31</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>294</v>
+        <v>276</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>295</v>
+        <v>644</v>
       </c>
       <c r="J85" s="44" t="s">
-        <v>305</v>
+        <v>284</v>
       </c>
       <c r="K85" s="61" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" ht="45">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" ht="43.2">
       <c r="A86" s="9" t="s">
         <v>87</v>
       </c>
@@ -6997,31 +6997,31 @@
         <v>33</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>296</v>
+        <v>277</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>303</v>
+        <v>645</v>
       </c>
       <c r="J86" s="44" t="s">
-        <v>297</v>
+        <v>278</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11" ht="45">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" ht="43.2">
       <c r="A87" s="9" t="s">
         <v>87</v>
       </c>
@@ -7030,31 +7030,31 @@
         <v>34</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>300</v>
+        <v>281</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>301</v>
+        <v>282</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>302</v>
+        <v>646</v>
       </c>
       <c r="J87" s="44" t="s">
-        <v>304</v>
+        <v>283</v>
       </c>
       <c r="K87" s="1" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11" ht="60">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" ht="57.6">
       <c r="A88" s="50" t="s">
         <v>94</v>
       </c>
@@ -7065,13 +7065,13 @@
       </c>
       <c r="E88" s="41"/>
       <c r="I88" s="41" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="J88" s="52" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="K88" s="1" t="s">
-        <v>480</v>
+        <v>453</v>
       </c>
     </row>
     <row r="89" spans="1:11">
@@ -7083,28 +7083,28 @@
         <v>3</v>
       </c>
       <c r="D89" s="41" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="E89" s="41" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I89" s="41" t="s">
-        <v>524</v>
+        <v>647</v>
       </c>
       <c r="J89" s="52" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>481</v>
+        <v>454</v>
       </c>
     </row>
     <row r="90" spans="1:11">
@@ -7116,28 +7116,28 @@
         <v>4</v>
       </c>
       <c r="D90" s="41" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="E90" s="41" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I90" s="41" t="s">
-        <v>525</v>
+        <v>648</v>
       </c>
       <c r="J90" s="52" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="K90" s="1" t="s">
-        <v>482</v>
+        <v>455</v>
       </c>
     </row>
     <row r="91" spans="1:11">
@@ -7149,53 +7149,53 @@
         <v>15</v>
       </c>
       <c r="D91" s="41" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="E91" s="41" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I91" s="41" t="s">
-        <v>526</v>
+        <v>649</v>
       </c>
       <c r="J91" s="52" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="K91" s="1" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11" ht="75">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" ht="72">
       <c r="A92" s="50" t="s">
         <v>94</v>
       </c>
       <c r="B92" s="50"/>
       <c r="C92" s="51"/>
       <c r="D92" s="41" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="E92" s="41" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I92" s="41" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="J92" s="52" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="K92" s="1" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11" ht="60">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" ht="57.6">
       <c r="A93" s="50" t="s">
         <v>96</v>
       </c>
@@ -7206,13 +7206,13 @@
       </c>
       <c r="E93" s="41"/>
       <c r="I93" s="41" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="J93" s="52" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="K93" s="1" t="s">
-        <v>485</v>
+        <v>458</v>
       </c>
     </row>
     <row r="94" spans="1:11">
@@ -7224,28 +7224,28 @@
         <v>3</v>
       </c>
       <c r="D94" s="41" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="E94" s="41" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I94" s="41" t="s">
-        <v>527</v>
+        <v>650</v>
       </c>
       <c r="J94" s="52" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>486</v>
+        <v>459</v>
       </c>
     </row>
     <row r="95" spans="1:11">
@@ -7257,28 +7257,28 @@
         <v>4</v>
       </c>
       <c r="D95" s="41" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="E95" s="41" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I95" s="41" t="s">
-        <v>528</v>
+        <v>651</v>
       </c>
       <c r="J95" s="52" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>487</v>
+        <v>460</v>
       </c>
     </row>
     <row r="96" spans="1:11">
@@ -7290,53 +7290,53 @@
         <v>15</v>
       </c>
       <c r="D96" s="41" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="E96" s="41" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I96" s="41" t="s">
-        <v>529</v>
+        <v>652</v>
       </c>
       <c r="J96" s="52" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="K96" s="1" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="97" spans="1:11" ht="75">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" ht="72">
       <c r="A97" s="50" t="s">
         <v>96</v>
       </c>
       <c r="B97" s="50"/>
       <c r="C97" s="51"/>
       <c r="D97" s="41" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="E97" s="41" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I97" s="41" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="J97" s="52" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="98" spans="1:11" ht="60">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" ht="57.6">
       <c r="A98" s="50" t="s">
         <v>97</v>
       </c>
@@ -7347,13 +7347,13 @@
       </c>
       <c r="E98" s="41"/>
       <c r="I98" s="41" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="J98" s="52" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="K98" s="1" t="s">
-        <v>490</v>
+        <v>463</v>
       </c>
     </row>
     <row r="99" spans="1:11">
@@ -7365,28 +7365,28 @@
         <v>3</v>
       </c>
       <c r="D99" s="41" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="E99" s="41" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I99" s="41" t="s">
-        <v>530</v>
+        <v>653</v>
       </c>
       <c r="J99" s="52" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="K99" s="1" t="s">
-        <v>491</v>
+        <v>464</v>
       </c>
     </row>
     <row r="100" spans="1:11">
@@ -7398,28 +7398,28 @@
         <v>4</v>
       </c>
       <c r="D100" s="41" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="E100" s="41" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I100" s="41" t="s">
-        <v>531</v>
+        <v>654</v>
       </c>
       <c r="J100" s="52" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="K100" s="1" t="s">
-        <v>492</v>
+        <v>465</v>
       </c>
     </row>
     <row r="101" spans="1:11">
@@ -7431,53 +7431,53 @@
         <v>15</v>
       </c>
       <c r="D101" s="41" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="E101" s="41" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I101" s="41" t="s">
-        <v>532</v>
+        <v>655</v>
       </c>
       <c r="J101" s="52" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="K101" s="1" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="102" spans="1:11" ht="75">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" ht="72">
       <c r="A102" s="50" t="s">
         <v>97</v>
       </c>
       <c r="B102" s="50"/>
       <c r="C102" s="51"/>
       <c r="D102" s="41" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="E102" s="41" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I102" s="41" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="J102" s="52" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="K102" s="1" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="103" spans="1:11" ht="60">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" ht="57.6">
       <c r="A103" s="50" t="s">
         <v>98</v>
       </c>
@@ -7488,13 +7488,13 @@
       </c>
       <c r="E103" s="41"/>
       <c r="I103" s="41" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="J103" s="52" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="K103" s="1" t="s">
-        <v>495</v>
+        <v>468</v>
       </c>
     </row>
     <row r="104" spans="1:11">
@@ -7506,28 +7506,28 @@
         <v>3</v>
       </c>
       <c r="D104" s="41" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="E104" s="41" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I104" s="41" t="s">
-        <v>199</v>
+        <v>656</v>
       </c>
       <c r="J104" s="52" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="K104" s="1" t="s">
-        <v>496</v>
+        <v>469</v>
       </c>
     </row>
     <row r="105" spans="1:11">
@@ -7539,28 +7539,28 @@
         <v>4</v>
       </c>
       <c r="D105" s="41" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="E105" s="41" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I105" s="41" t="s">
-        <v>197</v>
+        <v>657</v>
       </c>
       <c r="J105" s="52" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>497</v>
+        <v>470</v>
       </c>
     </row>
     <row r="106" spans="1:11">
@@ -7572,53 +7572,53 @@
         <v>15</v>
       </c>
       <c r="D106" s="41" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="E106" s="41" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I106" s="41" t="s">
-        <v>194</v>
+        <v>658</v>
       </c>
       <c r="J106" s="52" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="K106" s="1" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="107" spans="1:11" ht="75">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" ht="72">
       <c r="A107" s="50" t="s">
         <v>98</v>
       </c>
       <c r="B107" s="50"/>
       <c r="C107" s="51"/>
       <c r="D107" s="41" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="E107" s="41" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I107" s="41" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="J107" s="52" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="K107" s="1" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="108" spans="1:11" ht="60">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" ht="57.6">
       <c r="A108" s="50" t="s">
         <v>99</v>
       </c>
@@ -7629,13 +7629,13 @@
       </c>
       <c r="E108" s="41"/>
       <c r="I108" s="41" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="J108" s="52" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="K108" s="1" t="s">
-        <v>500</v>
+        <v>473</v>
       </c>
     </row>
     <row r="109" spans="1:11">
@@ -7647,28 +7647,28 @@
         <v>3</v>
       </c>
       <c r="D109" s="41" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="E109" s="41" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I109" s="41" t="s">
-        <v>533</v>
+        <v>659</v>
       </c>
       <c r="J109" s="52" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="K109" s="1" t="s">
-        <v>501</v>
+        <v>474</v>
       </c>
     </row>
     <row r="110" spans="1:11">
@@ -7680,28 +7680,28 @@
         <v>4</v>
       </c>
       <c r="D110" s="41" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="E110" s="41" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I110" s="41" t="s">
-        <v>534</v>
+        <v>660</v>
       </c>
       <c r="J110" s="52" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>502</v>
+        <v>475</v>
       </c>
     </row>
     <row r="111" spans="1:11">
@@ -7713,53 +7713,53 @@
         <v>15</v>
       </c>
       <c r="D111" s="41" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="E111" s="41" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I111" s="41" t="s">
-        <v>535</v>
+        <v>661</v>
       </c>
       <c r="J111" s="52" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="K111" s="1" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="112" spans="1:11" ht="75">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" ht="72">
       <c r="A112" s="50" t="s">
         <v>99</v>
       </c>
       <c r="B112" s="50"/>
       <c r="C112" s="51"/>
       <c r="D112" s="41" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="E112" s="41" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I112" s="41" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="J112" s="52" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="K112" s="1" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="113" spans="1:11" ht="60">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" ht="57.6">
       <c r="A113" s="50" t="s">
         <v>100</v>
       </c>
@@ -7770,13 +7770,13 @@
       </c>
       <c r="E113" s="41"/>
       <c r="I113" s="41" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="J113" s="52" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="K113" s="1" t="s">
-        <v>505</v>
+        <v>478</v>
       </c>
     </row>
     <row r="114" spans="1:11">
@@ -7788,28 +7788,28 @@
         <v>3</v>
       </c>
       <c r="D114" s="41" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="E114" s="41" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I114" s="41" t="s">
-        <v>536</v>
+        <v>662</v>
       </c>
       <c r="J114" s="52" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="K114" s="1" t="s">
-        <v>506</v>
+        <v>479</v>
       </c>
     </row>
     <row r="115" spans="1:11">
@@ -7821,28 +7821,28 @@
         <v>4</v>
       </c>
       <c r="D115" s="41" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="E115" s="41" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I115" s="41" t="s">
-        <v>537</v>
+        <v>663</v>
       </c>
       <c r="J115" s="52" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="K115" s="1" t="s">
-        <v>507</v>
+        <v>480</v>
       </c>
     </row>
     <row r="116" spans="1:11">
@@ -7854,53 +7854,53 @@
         <v>15</v>
       </c>
       <c r="D116" s="41" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="E116" s="41" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I116" s="41" t="s">
-        <v>538</v>
+        <v>664</v>
       </c>
       <c r="J116" s="52" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="K116" s="1" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="117" spans="1:11" ht="75">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" ht="72">
       <c r="A117" s="50" t="s">
         <v>100</v>
       </c>
       <c r="B117" s="50"/>
       <c r="C117" s="51"/>
       <c r="D117" s="41" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="E117" s="41" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I117" s="41" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="J117" s="52" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="K117" s="1" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="118" spans="1:11" ht="60">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" ht="57.6">
       <c r="A118" s="50" t="s">
         <v>101</v>
       </c>
@@ -7911,13 +7911,13 @@
       </c>
       <c r="E118" s="41"/>
       <c r="I118" s="41" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="J118" s="52" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="K118" s="1" t="s">
-        <v>510</v>
+        <v>483</v>
       </c>
     </row>
     <row r="119" spans="1:11">
@@ -7929,28 +7929,28 @@
         <v>3</v>
       </c>
       <c r="D119" s="41" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="E119" s="41" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I119" s="41" t="s">
-        <v>539</v>
+        <v>665</v>
       </c>
       <c r="J119" s="52" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="K119" s="1" t="s">
-        <v>511</v>
+        <v>484</v>
       </c>
     </row>
     <row r="120" spans="1:11">
@@ -7962,28 +7962,28 @@
         <v>4</v>
       </c>
       <c r="D120" s="41" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="E120" s="41" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I120" s="41" t="s">
-        <v>540</v>
+        <v>666</v>
       </c>
       <c r="J120" s="52" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="K120" s="1" t="s">
-        <v>512</v>
+        <v>485</v>
       </c>
     </row>
     <row r="121" spans="1:11">
@@ -7995,53 +7995,53 @@
         <v>15</v>
       </c>
       <c r="D121" s="41" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="E121" s="41" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I121" s="41" t="s">
-        <v>541</v>
+        <v>667</v>
       </c>
       <c r="J121" s="52" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="K121" s="1" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="122" spans="1:11" ht="75">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" ht="72">
       <c r="A122" s="50" t="s">
         <v>101</v>
       </c>
       <c r="B122" s="50"/>
       <c r="C122" s="51"/>
       <c r="D122" s="41" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="E122" s="41" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I122" s="41" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="J122" s="52" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="K122" s="1" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="123" spans="1:11" ht="60">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" ht="57.6">
       <c r="A123" s="50" t="s">
         <v>102</v>
       </c>
@@ -8052,13 +8052,13 @@
       </c>
       <c r="E123" s="41"/>
       <c r="I123" s="41" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="J123" s="52" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="K123" s="1" t="s">
-        <v>515</v>
+        <v>488</v>
       </c>
     </row>
     <row r="124" spans="1:11">
@@ -8070,28 +8070,28 @@
         <v>3</v>
       </c>
       <c r="D124" s="41" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="E124" s="41" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I124" s="41" t="s">
-        <v>542</v>
+        <v>668</v>
       </c>
       <c r="J124" s="52" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="K124" s="1" t="s">
-        <v>516</v>
+        <v>489</v>
       </c>
     </row>
     <row r="125" spans="1:11">
@@ -8103,28 +8103,28 @@
         <v>4</v>
       </c>
       <c r="D125" s="41" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="E125" s="41" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I125" s="41" t="s">
-        <v>543</v>
+        <v>669</v>
       </c>
       <c r="J125" s="52" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="K125" s="1" t="s">
-        <v>517</v>
+        <v>490</v>
       </c>
     </row>
     <row r="126" spans="1:11">
@@ -8136,53 +8136,53 @@
         <v>15</v>
       </c>
       <c r="D126" s="41" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="E126" s="41" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I126" s="41" t="s">
-        <v>544</v>
+        <v>670</v>
       </c>
       <c r="J126" s="52" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="K126" s="1" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="127" spans="1:11" ht="75">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" ht="72">
       <c r="A127" s="50" t="s">
         <v>102</v>
       </c>
       <c r="B127" s="50"/>
       <c r="C127" s="51"/>
       <c r="D127" s="41" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="E127" s="41" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I127" s="41" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="J127" s="52" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="K127" s="1" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="128" spans="1:11" ht="60">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" ht="57.6">
       <c r="A128" s="1" t="s">
         <v>139</v>
       </c>
@@ -8190,59 +8190,59 @@
         <v>26</v>
       </c>
       <c r="I128" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="J128" s="44" t="s">
         <v>142</v>
       </c>
       <c r="K128" s="1" t="s">
-        <v>520</v>
+        <v>493</v>
       </c>
     </row>
     <row r="129" spans="1:11">
       <c r="A129" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D129" s="1" t="s">
         <v>26</v>
       </c>
       <c r="I129" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K129" s="1" t="s">
-        <v>521</v>
+        <v>494</v>
       </c>
     </row>
     <row r="130" spans="1:11">
       <c r="A130" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C130" s="28">
         <v>1</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E130" s="1" t="s">
         <v>124</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>291</v>
+        <v>273</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H130" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I130" s="1" t="s">
-        <v>162</v>
+        <v>671</v>
       </c>
       <c r="J130" s="44" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="K130" s="1" t="s">
-        <v>522</v>
+        <v>495</v>
       </c>
     </row>
     <row r="223" spans="5:5">
@@ -11039,15 +11039,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECD30A18-04B8-42E0-9E13-F4ED24029528}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:H587"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="42.5703125" style="33" customWidth="1"/>
-    <col min="2" max="2" width="10.28515625" style="9" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" style="27" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" style="27" customWidth="1"/>
-    <col min="5" max="5" width="8.85546875" style="27" customWidth="1"/>
-    <col min="6" max="6" width="8.85546875" style="27" bestFit="1"/>
-    <col min="7" max="16384" width="8.85546875" style="33"/>
+    <col min="1" max="1" width="42.5546875" style="33" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" style="9" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" style="27" customWidth="1"/>
+    <col min="4" max="4" width="8.6640625" style="27" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="27" customWidth="1"/>
+    <col min="6" max="6" width="8.88671875" style="27" bestFit="1"/>
+    <col min="7" max="16384" width="8.88671875" style="33"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="9" customFormat="1" ht="21">
@@ -11072,7 +11072,7 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="17" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="B4" s="35"/>
       <c r="C4" s="35"/>
@@ -11839,7 +11839,7 @@
         <v>138</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C44" s="12">
         <v>1416</v>
@@ -12359,7 +12359,7 @@
         <v>71</v>
       </c>
       <c r="B70" s="12" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C70" s="12">
         <v>1305</v>
@@ -13382,11 +13382,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F00A795-F924-4957-BF24-7CBCF1582012}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:D35"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.28515625" customWidth="1"/>
-    <col min="2" max="2" width="36.7109375" customWidth="1"/>
-    <col min="3" max="3" width="82.42578125" customWidth="1"/>
+    <col min="1" max="1" width="12.33203125" customWidth="1"/>
+    <col min="2" max="2" width="36.6640625" customWidth="1"/>
+    <col min="3" max="3" width="82.44140625" customWidth="1"/>
     <col min="4" max="4" width="39" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -13409,7 +13409,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="17" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -13445,7 +13445,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="57" t="s">
-        <v>339</v>
+        <v>312</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -13459,7 +13459,7 @@
         <v>60</v>
       </c>
       <c r="D9" s="61" t="s">
-        <v>370</v>
+        <v>343</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -13473,7 +13473,7 @@
         <v>62</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>371</v>
+        <v>344</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -13487,7 +13487,7 @@
         <v>148</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>372</v>
+        <v>345</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -13501,7 +13501,7 @@
         <v>149</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>373</v>
+        <v>346</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -13515,7 +13515,7 @@
         <v>150</v>
       </c>
       <c r="D13" s="41" t="s">
-        <v>374</v>
+        <v>347</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -13529,7 +13529,7 @@
         <v>151</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>375</v>
+        <v>348</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -13543,7 +13543,7 @@
         <v>93</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>376</v>
+        <v>349</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -13557,7 +13557,7 @@
         <v>103</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>377</v>
+        <v>350</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -13571,7 +13571,7 @@
         <v>103</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>378</v>
+        <v>351</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -13585,7 +13585,7 @@
         <v>103</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>379</v>
+        <v>352</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -13599,7 +13599,7 @@
         <v>103</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>380</v>
+        <v>353</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -13613,7 +13613,7 @@
         <v>103</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>381</v>
+        <v>354</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -13627,7 +13627,7 @@
         <v>103</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>382</v>
+        <v>355</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -13641,7 +13641,7 @@
         <v>103</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>383</v>
+        <v>356</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -13655,7 +13655,7 @@
         <v>103</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>384</v>
+        <v>357</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -13666,10 +13666,10 @@
         <v>59</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="D24" s="61" t="s">
-        <v>385</v>
+        <v>358</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -13680,10 +13680,10 @@
         <v>59</v>
       </c>
       <c r="C25" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>386</v>
+        <v>359</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -13697,7 +13697,7 @@
         <v>111</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>387</v>
+        <v>360</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -13711,7 +13711,7 @@
         <v>127</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>388</v>
+        <v>361</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -13725,7 +13725,7 @@
         <v>127</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>389</v>
+        <v>362</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -13739,7 +13739,7 @@
         <v>127</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>390</v>
+        <v>363</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -13753,7 +13753,7 @@
         <v>127</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>391</v>
+        <v>364</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -13767,7 +13767,7 @@
         <v>132</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>392</v>
+        <v>365</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -13781,7 +13781,7 @@
         <v>136</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>393</v>
+        <v>366</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -13795,7 +13795,7 @@
         <v>141</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>394</v>
+        <v>367</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -13809,21 +13809,21 @@
         <v>147</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>395</v>
+        <v>368</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="9" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>59</v>
       </c>
       <c r="C35" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>396</v>
+        <v>369</v>
       </c>
     </row>
   </sheetData>
@@ -13836,11 +13836,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9014B11-7294-4050-ABF4-8B4EFBD7F103}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D42"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.28515625" customWidth="1"/>
-    <col min="2" max="2" width="50.28515625" customWidth="1"/>
-    <col min="3" max="3" width="102.140625" customWidth="1"/>
+    <col min="1" max="1" width="12.33203125" customWidth="1"/>
+    <col min="2" max="2" width="50.33203125" customWidth="1"/>
+    <col min="3" max="3" width="102.109375" customWidth="1"/>
     <col min="4" max="4" width="39" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -13861,7 +13861,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="17" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -13891,7 +13891,7 @@
         <v>15</v>
       </c>
       <c r="D8" s="57" t="s">
-        <v>339</v>
+        <v>312</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -13905,7 +13905,7 @@
         <v>67</v>
       </c>
       <c r="D9" s="61" t="s">
-        <v>397</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -13919,7 +13919,7 @@
         <v>77</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>398</v>
+        <v>371</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -13930,10 +13930,10 @@
         <v>66</v>
       </c>
       <c r="C11" s="39" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>399</v>
+        <v>372</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -13941,13 +13941,13 @@
         <v>78</v>
       </c>
       <c r="B12" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>400</v>
+        <v>373</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -13955,13 +13955,13 @@
         <v>78</v>
       </c>
       <c r="B13" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="C13" s="39" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="D13" s="41" t="s">
-        <v>401</v>
+        <v>374</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -13975,7 +13975,7 @@
         <v>86</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>402</v>
+        <v>375</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -13989,7 +13989,7 @@
         <v>119</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>403</v>
+        <v>376</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -13997,13 +13997,13 @@
         <v>82</v>
       </c>
       <c r="B16" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C16" s="39" t="s">
         <v>122</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>404</v>
+        <v>377</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -14017,7 +14017,7 @@
         <v>90</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>405</v>
+        <v>378</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -14031,7 +14031,7 @@
         <v>119</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>406</v>
+        <v>379</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -14039,13 +14039,13 @@
         <v>87</v>
       </c>
       <c r="B19" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C19" s="39" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>407</v>
+        <v>380</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -14053,13 +14053,13 @@
         <v>87</v>
       </c>
       <c r="B20" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C20" s="39" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>408</v>
+        <v>381</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -14067,13 +14067,13 @@
         <v>87</v>
       </c>
       <c r="B21" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C21" s="39" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>409</v>
+        <v>382</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15.75" customHeight="1">
@@ -14087,7 +14087,7 @@
         <v>110</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>410</v>
+        <v>383</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -14101,7 +14101,7 @@
         <v>119</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>411</v>
+        <v>384</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -14115,7 +14115,7 @@
         <v>119</v>
       </c>
       <c r="D24" s="61" t="s">
-        <v>412</v>
+        <v>385</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -14129,7 +14129,7 @@
         <v>119</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>413</v>
+        <v>386</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -14137,13 +14137,13 @@
         <v>94</v>
       </c>
       <c r="B26" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C26" s="39" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>414</v>
+        <v>387</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -14151,13 +14151,13 @@
         <v>96</v>
       </c>
       <c r="B27" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C27" s="39" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>415</v>
+        <v>388</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -14165,13 +14165,13 @@
         <v>97</v>
       </c>
       <c r="B28" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C28" s="39" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>416</v>
+        <v>389</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -14179,13 +14179,13 @@
         <v>98</v>
       </c>
       <c r="B29" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C29" s="39" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>417</v>
+        <v>390</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -14193,13 +14193,13 @@
         <v>99</v>
       </c>
       <c r="B30" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C30" s="39" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>418</v>
+        <v>391</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -14207,13 +14207,13 @@
         <v>100</v>
       </c>
       <c r="B31" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C31" s="39" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>419</v>
+        <v>392</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -14221,13 +14221,13 @@
         <v>101</v>
       </c>
       <c r="B32" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C32" s="39" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>420</v>
+        <v>393</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -14235,13 +14235,13 @@
         <v>102</v>
       </c>
       <c r="B33" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C33" s="39" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>421</v>
+        <v>394</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -14249,13 +14249,13 @@
         <v>94</v>
       </c>
       <c r="B34" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="C34" s="39" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>422</v>
+        <v>395</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -14263,13 +14263,13 @@
         <v>96</v>
       </c>
       <c r="B35" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="C35" s="39" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>423</v>
+        <v>396</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -14277,13 +14277,13 @@
         <v>97</v>
       </c>
       <c r="B36" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="C36" s="39" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>424</v>
+        <v>397</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -14291,13 +14291,13 @@
         <v>98</v>
       </c>
       <c r="B37" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="C37" s="39" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>425</v>
+        <v>398</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -14305,13 +14305,13 @@
         <v>99</v>
       </c>
       <c r="B38" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="C38" s="39" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>426</v>
+        <v>399</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -14319,13 +14319,13 @@
         <v>100</v>
       </c>
       <c r="B39" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="C39" s="39" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>427</v>
+        <v>400</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -14333,13 +14333,13 @@
         <v>101</v>
       </c>
       <c r="B40" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="C40" s="39" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>428</v>
+        <v>401</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -14347,13 +14347,13 @@
         <v>102</v>
       </c>
       <c r="B41" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="C41" s="39" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>429</v>
+        <v>402</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -14398,11 +14398,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B01DEE13-8567-47C0-98EF-B4590CF5D2FE}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:D29"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
-    <col min="2" max="2" width="43.42578125" customWidth="1"/>
-    <col min="3" max="3" width="107.28515625" customWidth="1"/>
+    <col min="1" max="1" width="24.44140625" customWidth="1"/>
+    <col min="2" max="2" width="43.44140625" customWidth="1"/>
+    <col min="3" max="3" width="107.33203125" customWidth="1"/>
     <col min="4" max="4" width="39" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -14424,7 +14424,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="17" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="57" t="s">
-        <v>339</v>
+        <v>312</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -14473,7 +14473,7 @@
         <v>56</v>
       </c>
       <c r="D9" s="61" t="s">
-        <v>430</v>
+        <v>403</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -14516,11 +14516,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{787D0651-AC56-4C79-A3A0-381B16C48D1E}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:D24"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="25.7109375" customWidth="1"/>
-    <col min="2" max="2" width="44.42578125" customWidth="1"/>
-    <col min="3" max="3" width="86.5703125" customWidth="1"/>
+    <col min="1" max="1" width="25.6640625" customWidth="1"/>
+    <col min="2" max="2" width="44.44140625" customWidth="1"/>
+    <col min="3" max="3" width="86.5546875" customWidth="1"/>
     <col min="4" max="4" width="39" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -14538,7 +14538,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="17" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -14569,7 +14569,7 @@
         <v>15</v>
       </c>
       <c r="D8" s="57" t="s">
-        <v>339</v>
+        <v>312</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -14583,7 +14583,7 @@
         <v>58</v>
       </c>
       <c r="D9" s="61" t="s">
-        <v>431</v>
+        <v>404</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -14597,21 +14597,21 @@
         <v>68</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>432</v>
+        <v>405</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="17" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B11" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="C11" s="39" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>433</v>
+        <v>406</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -14647,12 +14647,12 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBCEBA5B-6A50-48EF-B74E-B76FA9984AEF}">
   <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="33.28515625" customWidth="1"/>
-    <col min="2" max="2" width="16.85546875" customWidth="1"/>
-    <col min="3" max="3" width="38.85546875" customWidth="1"/>
-    <col min="4" max="4" width="47.7109375" customWidth="1"/>
+    <col min="1" max="1" width="33.33203125" customWidth="1"/>
+    <col min="2" max="2" width="16.88671875" customWidth="1"/>
+    <col min="3" max="3" width="38.88671875" customWidth="1"/>
+    <col min="4" max="4" width="47.6640625" customWidth="1"/>
     <col min="5" max="5" width="39" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -14672,7 +14672,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="17" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="4"/>
@@ -14709,63 +14709,63 @@
         <v>44</v>
       </c>
       <c r="E8" s="57" t="s">
-        <v>339</v>
+        <v>312</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="C9" t="s">
         <v>66</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>434</v>
+        <v>407</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>438</v>
+        <v>411</v>
       </c>
       <c r="C10" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="D10" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="E10" s="61" t="s">
-        <v>435</v>
+        <v>408</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>439</v>
+        <v>412</v>
       </c>
       <c r="C11" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="D11" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="E11" s="61" t="s">
-        <v>436</v>
+        <v>409</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="C12" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="D12" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>437</v>
+        <v>410</v>
       </c>
     </row>
     <row r="14" spans="1:5">
